--- a/vestventures/financial-model.xlsx
+++ b/vestventures/financial-model.xlsx
@@ -19,10 +19,10 @@
     <sheet name="Sources" sheetId="9" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="in_A11yAmt" vbProcedure="false">Assumptions!$B$77</definedName>
-    <definedName function="false" hidden="false" name="in_A11yEnd" vbProcedure="false">Assumptions!$B$79</definedName>
-    <definedName function="false" hidden="false" name="in_A11yStart" vbProcedure="false">Assumptions!$B$78</definedName>
-    <definedName function="false" hidden="false" name="in_Admin" vbProcedure="false">Assumptions!$B$67</definedName>
+    <definedName function="false" hidden="false" name="in_A11yAmt" vbProcedure="false">Assumptions!$B$78</definedName>
+    <definedName function="false" hidden="false" name="in_A11yEnd" vbProcedure="false">Assumptions!$B$80</definedName>
+    <definedName function="false" hidden="false" name="in_A11yStart" vbProcedure="false">Assumptions!$B$79</definedName>
+    <definedName function="false" hidden="false" name="in_Admin" vbProcedure="false">Assumptions!$B$68</definedName>
     <definedName function="false" hidden="false" name="in_ARPA" vbProcedure="false">'Unit economics'!$B$7</definedName>
     <definedName function="false" hidden="false" name="in_ARPA1" vbProcedure="false">Assumptions!$B$33</definedName>
     <definedName function="false" hidden="false" name="in_BlendedPriceRON" vbProcedure="false">Assumptions!$B$32</definedName>
@@ -33,26 +33,27 @@
     <definedName function="false" hidden="false" name="in_Cash36" vbProcedure="false">'P&amp;L &amp; Cash'!$C$36</definedName>
     <definedName function="false" hidden="false" name="in_CashLow" vbProcedure="false">'P&amp;L &amp; Cash'!$C$34</definedName>
     <definedName function="false" hidden="false" name="in_CashLowMonth" vbProcedure="false">'P&amp;L &amp; Cash'!$C$35</definedName>
-    <definedName function="false" hidden="false" name="in_Churn" vbProcedure="false">Assumptions!$B$107</definedName>
+    <definedName function="false" hidden="false" name="in_Churn" vbProcedure="false">Assumptions!$B$108</definedName>
     <definedName function="false" hidden="false" name="in_ChurnUE" vbProcedure="false">'Unit economics'!$B$15</definedName>
     <definedName function="false" hidden="false" name="in_CM" vbProcedure="false">'Unit economics'!$B$9</definedName>
     <definedName function="false" hidden="false" name="in_CommMonths" vbProcedure="false">Assumptions!$B$40</definedName>
     <definedName function="false" hidden="false" name="in_CommRate" vbProcedure="false">Assumptions!$B$39</definedName>
-    <definedName function="false" hidden="false" name="in_Contingency" vbProcedure="false">Assumptions!$B$68</definedName>
+    <definedName function="false" hidden="false" name="in_Contingency" vbProcedure="false">Assumptions!$B$69</definedName>
     <definedName function="false" hidden="false" name="in_Cost12" vbProcedure="false">'P&amp;L &amp; Cash'!$C$40</definedName>
     <definedName function="false" hidden="false" name="in_Cost24" vbProcedure="false">'P&amp;L &amp; Cash'!$C$41</definedName>
     <definedName function="false" hidden="false" name="in_Cost36" vbProcedure="false">'P&amp;L &amp; Cash'!$C$42</definedName>
-    <definedName function="false" hidden="false" name="in_CostPerTrial" vbProcedure="false">Assumptions!$B$106</definedName>
-    <definedName function="false" hidden="false" name="in_DevStart" vbProcedure="false">Assumptions!$B$109</definedName>
+    <definedName function="false" hidden="false" name="in_CostPerTrial" vbProcedure="false">Assumptions!$B$107</definedName>
+    <definedName function="false" hidden="false" name="in_DevStart" vbProcedure="false">Assumptions!$B$110</definedName>
+    <definedName function="false" hidden="false" name="in_FounderPayStart" vbProcedure="false">Assumptions!$B$46</definedName>
     <definedName function="false" hidden="false" name="in_FundingMonth" vbProcedure="false">Assumptions!$B$9</definedName>
     <definedName function="false" hidden="false" name="in_FX" vbProcedure="false">Assumptions!$B$7</definedName>
     <definedName function="false" hidden="false" name="in_GMPL" vbProcedure="false">'Unit economics'!$B$10</definedName>
-    <definedName function="false" hidden="false" name="in_InfraFixed" vbProcedure="false">Assumptions!$B$57</definedName>
-    <definedName function="false" hidden="false" name="in_InfraVar" vbProcedure="false">Assumptions!$B$58</definedName>
-    <definedName function="false" hidden="false" name="in_Insurance" vbProcedure="false">Assumptions!$B$66</definedName>
-    <definedName function="false" hidden="false" name="in_LegalAmt" vbProcedure="false">Assumptions!$B$71</definedName>
-    <definedName function="false" hidden="false" name="in_LegalEnd" vbProcedure="false">Assumptions!$B$73</definedName>
-    <definedName function="false" hidden="false" name="in_LegalStart" vbProcedure="false">Assumptions!$B$72</definedName>
+    <definedName function="false" hidden="false" name="in_InfraFixed" vbProcedure="false">Assumptions!$B$58</definedName>
+    <definedName function="false" hidden="false" name="in_InfraVar" vbProcedure="false">Assumptions!$B$59</definedName>
+    <definedName function="false" hidden="false" name="in_Insurance" vbProcedure="false">Assumptions!$B$67</definedName>
+    <definedName function="false" hidden="false" name="in_LegalAmt" vbProcedure="false">Assumptions!$B$72</definedName>
+    <definedName function="false" hidden="false" name="in_LegalEnd" vbProcedure="false">Assumptions!$B$74</definedName>
+    <definedName function="false" hidden="false" name="in_LegalStart" vbProcedure="false">Assumptions!$B$73</definedName>
     <definedName function="false" hidden="false" name="in_Lifetime" vbProcedure="false">'Unit economics'!$B$16</definedName>
     <definedName function="false" hidden="false" name="in_LTV" vbProcedure="false">'Unit economics'!$B$17</definedName>
     <definedName function="false" hidden="false" name="in_LTVCAC" vbProcedure="false">'Unit economics'!$B$18</definedName>
@@ -60,72 +61,72 @@
     <definedName function="false" hidden="false" name="in_M30" vbProcedure="false">Revenue!$C$31</definedName>
     <definedName function="false" hidden="false" name="in_M300" vbProcedure="false">Revenue!$C$33</definedName>
     <definedName function="false" hidden="false" name="in_MaxCheck" vbProcedure="false">'P&amp;L &amp; Cash'!$C$43</definedName>
-    <definedName function="false" hidden="false" name="in_MicroRate" vbProcedure="false">Assumptions!$B$86</definedName>
+    <definedName function="false" hidden="false" name="in_MicroRate" vbProcedure="false">Assumptions!$B$87</definedName>
     <definedName function="false" hidden="false" name="in_MixAll" vbProcedure="false">Assumptions!$B$30</definedName>
     <definedName function="false" hidden="false" name="in_MixCheck" vbProcedure="false">Assumptions!$B$31</definedName>
     <definedName function="false" hidden="false" name="in_MixCore" vbProcedure="false">Assumptions!$B$26</definedName>
     <definedName function="false" hidden="false" name="in_MixExtHR" vbProcedure="false">Assumptions!$B$27</definedName>
     <definedName function="false" hidden="false" name="in_MixFin" vbProcedure="false">Assumptions!$B$29</definedName>
     <definedName function="false" hidden="false" name="in_MixOps" vbProcedure="false">Assumptions!$B$28</definedName>
-    <definedName function="false" hidden="false" name="in_MktY1" vbProcedure="false">Assumptions!$B$61</definedName>
-    <definedName function="false" hidden="false" name="in_MktY2" vbProcedure="false">Assumptions!$B$62</definedName>
-    <definedName function="false" hidden="false" name="in_MktY3" vbProcedure="false">Assumptions!$B$63</definedName>
-    <definedName function="false" hidden="false" name="in_NewPartnersY1" vbProcedure="false">Assumptions!$B$97</definedName>
-    <definedName function="false" hidden="false" name="in_NewPartnersY2" vbProcedure="false">Assumptions!$B$98</definedName>
-    <definedName function="false" hidden="false" name="in_NewPartnersY3" vbProcedure="false">Assumptions!$B$99</definedName>
-    <definedName function="false" hidden="false" name="in_Office" vbProcedure="false">Assumptions!$B$65</definedName>
+    <definedName function="false" hidden="false" name="in_MktY1" vbProcedure="false">Assumptions!$B$62</definedName>
+    <definedName function="false" hidden="false" name="in_MktY2" vbProcedure="false">Assumptions!$B$63</definedName>
+    <definedName function="false" hidden="false" name="in_MktY3" vbProcedure="false">Assumptions!$B$64</definedName>
+    <definedName function="false" hidden="false" name="in_NewPartnersY1" vbProcedure="false">Assumptions!$B$98</definedName>
+    <definedName function="false" hidden="false" name="in_NewPartnersY2" vbProcedure="false">Assumptions!$B$99</definedName>
+    <definedName function="false" hidden="false" name="in_NewPartnersY3" vbProcedure="false">Assumptions!$B$100</definedName>
+    <definedName function="false" hidden="false" name="in_Office" vbProcedure="false">Assumptions!$B$66</definedName>
     <definedName function="false" hidden="false" name="in_OpeningCash" vbProcedure="false">Assumptions!$B$10</definedName>
-    <definedName function="false" hidden="false" name="in_OrganicY1" vbProcedure="false">Assumptions!$B$102</definedName>
-    <definedName function="false" hidden="false" name="in_OrganicY2" vbProcedure="false">Assumptions!$B$103</definedName>
-    <definedName function="false" hidden="false" name="in_OrganicY3" vbProcedure="false">Assumptions!$B$104</definedName>
+    <definedName function="false" hidden="false" name="in_OrganicY1" vbProcedure="false">Assumptions!$B$103</definedName>
+    <definedName function="false" hidden="false" name="in_OrganicY2" vbProcedure="false">Assumptions!$B$104</definedName>
+    <definedName function="false" hidden="false" name="in_OrganicY3" vbProcedure="false">Assumptions!$B$105</definedName>
     <definedName function="false" hidden="false" name="in_PaidShare" vbProcedure="false">Assumptions!$B$38</definedName>
     <definedName function="false" hidden="false" name="in_PartnerStart" vbProcedure="false">Assumptions!$B$37</definedName>
     <definedName function="false" hidden="false" name="in_Payback" vbProcedure="false">'Unit economics'!$B$19</definedName>
-    <definedName function="false" hidden="false" name="in_PayFee" vbProcedure="false">Assumptions!$B$60</definedName>
-    <definedName function="false" hidden="false" name="in_PayrollValAmt" vbProcedure="false">Assumptions!$B$74</definedName>
-    <definedName function="false" hidden="false" name="in_PayrollValEnd" vbProcedure="false">Assumptions!$B$76</definedName>
-    <definedName function="false" hidden="false" name="in_PayrollValStart" vbProcedure="false">Assumptions!$B$75</definedName>
-    <definedName function="false" hidden="false" name="in_PentestAmt" vbProcedure="false">Assumptions!$B$80</definedName>
-    <definedName function="false" hidden="false" name="in_PentestEnd" vbProcedure="false">Assumptions!$B$82</definedName>
-    <definedName function="false" hidden="false" name="in_PentestStart" vbProcedure="false">Assumptions!$B$81</definedName>
-    <definedName function="false" hidden="false" name="in_PilotConv" vbProcedure="false">Assumptions!$B$96</definedName>
+    <definedName function="false" hidden="false" name="in_PayFee" vbProcedure="false">Assumptions!$B$61</definedName>
+    <definedName function="false" hidden="false" name="in_PayrollValAmt" vbProcedure="false">Assumptions!$B$75</definedName>
+    <definedName function="false" hidden="false" name="in_PayrollValEnd" vbProcedure="false">Assumptions!$B$77</definedName>
+    <definedName function="false" hidden="false" name="in_PayrollValStart" vbProcedure="false">Assumptions!$B$76</definedName>
+    <definedName function="false" hidden="false" name="in_PentestAmt" vbProcedure="false">Assumptions!$B$81</definedName>
+    <definedName function="false" hidden="false" name="in_PentestEnd" vbProcedure="false">Assumptions!$B$83</definedName>
+    <definedName function="false" hidden="false" name="in_PentestStart" vbProcedure="false">Assumptions!$B$82</definedName>
+    <definedName function="false" hidden="false" name="in_PilotConv" vbProcedure="false">Assumptions!$B$97</definedName>
     <definedName function="false" hidden="false" name="in_PilotConvMonth" vbProcedure="false">Assumptions!$B$36</definedName>
-    <definedName function="false" hidden="false" name="in_PilotFirmsPerPractice" vbProcedure="false">Assumptions!$B$95</definedName>
-    <definedName function="false" hidden="false" name="in_PilotPractices" vbProcedure="false">Assumptions!$B$94</definedName>
+    <definedName function="false" hidden="false" name="in_PilotFirmsPerPractice" vbProcedure="false">Assumptions!$B$96</definedName>
+    <definedName function="false" hidden="false" name="in_PilotPractices" vbProcedure="false">Assumptions!$B$95</definedName>
     <definedName function="false" hidden="false" name="in_PostMoney" vbProcedure="false">Assumptions!$B$16</definedName>
     <definedName function="false" hidden="false" name="in_PreMoney" vbProcedure="false">Assumptions!$B$15</definedName>
     <definedName function="false" hidden="false" name="in_PriceAll" vbProcedure="false">Assumptions!$B$23</definedName>
     <definedName function="false" hidden="false" name="in_PriceCore" vbProcedure="false">Assumptions!$B$19</definedName>
     <definedName function="false" hidden="false" name="in_PriceExtHR" vbProcedure="false">Assumptions!$B$20</definedName>
     <definedName function="false" hidden="false" name="in_PriceFin" vbProcedure="false">Assumptions!$B$22</definedName>
-    <definedName function="false" hidden="false" name="in_PriceInc" vbProcedure="false">Assumptions!$B$108</definedName>
+    <definedName function="false" hidden="false" name="in_PriceInc" vbProcedure="false">Assumptions!$B$109</definedName>
     <definedName function="false" hidden="false" name="in_PriceOps" vbProcedure="false">Assumptions!$B$21</definedName>
-    <definedName function="false" hidden="false" name="in_ProfitTax" vbProcedure="false">Assumptions!$B$87</definedName>
+    <definedName function="false" hidden="false" name="in_ProfitTax" vbProcedure="false">Assumptions!$B$88</definedName>
     <definedName function="false" hidden="false" name="in_Raise" vbProcedure="false">Assumptions!$B$44</definedName>
-    <definedName function="false" hidden="false" name="in_RefConv" vbProcedure="false">Assumptions!$B$101</definedName>
-    <definedName function="false" hidden="false" name="in_RefRate" vbProcedure="false">Assumptions!$B$100</definedName>
+    <definedName function="false" hidden="false" name="in_RefConv" vbProcedure="false">Assumptions!$B$102</definedName>
+    <definedName function="false" hidden="false" name="in_RefRate" vbProcedure="false">Assumptions!$B$101</definedName>
     <definedName function="false" hidden="false" name="in_Rev12" vbProcedure="false">'P&amp;L &amp; Cash'!$C$37</definedName>
     <definedName function="false" hidden="false" name="in_Rev24" vbProcedure="false">'P&amp;L &amp; Cash'!$C$38</definedName>
     <definedName function="false" hidden="false" name="in_Rev36" vbProcedure="false">'P&amp;L &amp; Cash'!$C$39</definedName>
     <definedName function="false" hidden="false" name="in_Round" vbProcedure="false">Assumptions!$B$14</definedName>
     <definedName function="false" hidden="false" name="in_RunwayPlan" vbProcedure="false">'P&amp;L &amp; Cash'!$C$32</definedName>
     <definedName function="false" hidden="false" name="in_RunwayZeroRev" vbProcedure="false">'P&amp;L &amp; Cash'!$C$31</definedName>
-    <definedName function="false" hidden="false" name="in_SalDev" vbProcedure="false">Assumptions!$B$54</definedName>
-    <definedName function="false" hidden="false" name="in_SalesFTE" vbProcedure="false">Assumptions!$B$48</definedName>
-    <definedName function="false" hidden="false" name="in_SalesFullStart" vbProcedure="false">Assumptions!$B$49</definedName>
-    <definedName function="false" hidden="false" name="in_SalesStart" vbProcedure="false">Assumptions!$B$47</definedName>
+    <definedName function="false" hidden="false" name="in_SalDev" vbProcedure="false">Assumptions!$B$55</definedName>
+    <definedName function="false" hidden="false" name="in_SalesFTE" vbProcedure="false">Assumptions!$B$49</definedName>
+    <definedName function="false" hidden="false" name="in_SalesFullStart" vbProcedure="false">Assumptions!$B$50</definedName>
+    <definedName function="false" hidden="false" name="in_SalesStart" vbProcedure="false">Assumptions!$B$48</definedName>
     <definedName function="false" hidden="false" name="in_SalFounder" vbProcedure="false">Assumptions!$B$45</definedName>
-    <definedName function="false" hidden="false" name="in_SalSales" vbProcedure="false">Assumptions!$B$46</definedName>
-    <definedName function="false" hidden="false" name="in_SalSupport" vbProcedure="false">Assumptions!$B$50</definedName>
+    <definedName function="false" hidden="false" name="in_SalSales" vbProcedure="false">Assumptions!$B$47</definedName>
+    <definedName function="false" hidden="false" name="in_SalSupport" vbProcedure="false">Assumptions!$B$51</definedName>
     <definedName function="false" hidden="false" name="in_StartDate" vbProcedure="false">Assumptions!$B$8</definedName>
-    <definedName function="false" hidden="false" name="in_SupportFTE" vbProcedure="false">Assumptions!$B$52</definedName>
-    <definedName function="false" hidden="false" name="in_SupportFullStart" vbProcedure="false">Assumptions!$B$53</definedName>
-    <definedName function="false" hidden="false" name="in_SupportStart" vbProcedure="false">Assumptions!$B$51</definedName>
-    <definedName function="false" hidden="false" name="in_TaxRegime" vbProcedure="false">Assumptions!$B$85</definedName>
-    <definedName function="false" hidden="false" name="in_Tools" vbProcedure="false">Assumptions!$B$59</definedName>
-    <definedName function="false" hidden="false" name="in_Travel" vbProcedure="false">Assumptions!$B$64</definedName>
-    <definedName function="false" hidden="false" name="in_TrialConv" vbProcedure="false">Assumptions!$B$105</definedName>
-    <definedName function="false" hidden="false" name="in_UEYear" vbProcedure="false">Assumptions!$B$90</definedName>
+    <definedName function="false" hidden="false" name="in_SupportFTE" vbProcedure="false">Assumptions!$B$53</definedName>
+    <definedName function="false" hidden="false" name="in_SupportFullStart" vbProcedure="false">Assumptions!$B$54</definedName>
+    <definedName function="false" hidden="false" name="in_SupportStart" vbProcedure="false">Assumptions!$B$52</definedName>
+    <definedName function="false" hidden="false" name="in_TaxRegime" vbProcedure="false">Assumptions!$B$86</definedName>
+    <definedName function="false" hidden="false" name="in_Tools" vbProcedure="false">Assumptions!$B$60</definedName>
+    <definedName function="false" hidden="false" name="in_Travel" vbProcedure="false">Assumptions!$B$65</definedName>
+    <definedName function="false" hidden="false" name="in_TrialConv" vbProcedure="false">Assumptions!$B$106</definedName>
+    <definedName function="false" hidden="false" name="in_UEYear" vbProcedure="false">Assumptions!$B$91</definedName>
     <definedName function="false" hidden="false" name="in_UE_CustMonths" vbProcedure="false">'Unit economics'!$B$6</definedName>
     <definedName function="false" hidden="false" name="in_UE_New" vbProcedure="false">'Unit economics'!$B$12</definedName>
     <definedName function="false" hidden="false" name="in_UE_Rev" vbProcedure="false">'Unit economics'!$B$5</definedName>
@@ -144,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="414">
   <si>
     <t xml:space="preserve">ADMINISTRATIVO - financial model (pre-seed)</t>
   </si>
@@ -269,7 +270,7 @@
     <t xml:space="preserve">Salaries, conversion rates and partner productivity are founders' assumptions (no external source).</t>
   </si>
   <si>
-    <t xml:space="preserve">Lean pre-seed cost plan: co-founders on lean salaries, partner manager and support specialist part-time first (partner signings scaled to the manager's hours), developer hired only after the seed.</t>
+    <t xml:space="preserve">Lean pre-seed cost plan: co-founders unpaid in year 1 and on lean salaries after, partner manager and support specialist part-time first (partner signings scaled to the manager's hours), developer hired only after the seed.</t>
   </si>
   <si>
     <t xml:space="preserve">[TO CONFIRM]: legal entity and registered office (VV requires Arad, Caraș-Severin, Hunedoara or Timiș), tax regime, social parts.</t>
@@ -341,7 +342,7 @@
     <t xml:space="preserve">Vest Ventures accelerator ticket</t>
   </si>
   <si>
-    <t xml:space="preserve">VV Accelerator ticket EUR 10k-200k, de minimis (vestventures.vc/en/programs-terms). EUR 150k requested, inside the range; Vest Ventures is the only investor in this round.</t>
+    <t xml:space="preserve">VV Accelerator ticket EUR 10k-200k, de minimis (vestventures.vc/en/programs-terms). EUR 100k requested, inside the range; Vest Ventures is the only investor in this round.</t>
   </si>
   <si>
     <t xml:space="preserve">Round size (single investor: Vest Ventures)</t>
@@ -482,7 +483,13 @@
     <t xml:space="preserve">Co-founder gross salary (each, 2 people)</t>
   </si>
   <si>
-    <t xml:space="preserve">Both co-founders full time from close, on a deliberately lean pre-seed salary (~RON 5,000 gross) to stretch the runway; kept at this level in the model (only the annual raise applies). ASSUMPTION - no sourced salary benchmark.</t>
+    <t xml:space="preserve">Both co-founders full time from close; paid from in_FounderPayStart on a deliberately lean pre-seed salary (~RON 5,000 gross); kept at this level in the model (only the annual raise applies). ASSUMPTION - no sourced salary benchmark.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-founders paid from</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan 2028. In year 1 both co-founders work full time without a salary (unpaid directors), so the EUR 100k round reaches the seed trigger. Lower pay is not an option: EUR 1,000 gross is just above the Romanian minimum wage for a full-time contract.</t>
   </si>
   <si>
     <t xml:space="preserve">Partner &amp; sales manager (accountant channel) gross, full-time equivalent</t>
@@ -500,7 +507,7 @@
     <t xml:space="preserve">FTE</t>
   </si>
   <si>
-    <t xml:space="preserve">Half time in year 1 to fit the EUR 150k round. Partner signings scale with it (new partners/month x FTE): fewer sales hours = fewer partners. ASSUMPTION.</t>
+    <t xml:space="preserve">Half time in year 1 to fit the EUR 100k round. Partner signings scale with it (new partners/month x FTE): fewer sales hours = fewer partners. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Partner &amp; sales manager full time from</t>
@@ -518,7 +525,7 @@
     <t xml:space="preserve">Onboarding &amp; support specialist start month</t>
   </si>
   <si>
-    <t xml:space="preserve">Founders onboard the pilot companies (Apr 2027); the specialist starts part-time around 30 paying customers. ASSUMPTION.</t>
+    <t xml:space="preserve">Founders onboard the pilot companies (Apr 2027) and the first paying firms; the specialist starts part-time just after 30 paying customers. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Onboarding &amp; support specialist share of full time until full-time start</t>
@@ -578,13 +585,13 @@
     <t xml:space="preserve">Travel to accounting practices, accountant events</t>
   </si>
   <si>
-    <t xml:space="preserve">Founders' internal cost estimate (accountant sales), trimmed to fit the EUR 150k round: local Timiș/West Region practices first, few paid events.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coworking desk(s) in Timiș county</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VV requires an operating site in the West Region (vestventures.vc/en/programs-terms). ASSUMPTION.</t>
+    <t xml:space="preserve">Founders' internal cost estimate (accountant sales), trimmed to fit the EUR 100k round: local Timiș/West Region practices first, no paid events.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coworking desk in Timiș county</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VV requires an operating site in the West Region (vestventures.vc/en/programs-terms). One flexible coworking desk. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Professional liability insurance</t>
@@ -632,7 +639,7 @@
     <t xml:space="preserve">Founders' internal cost estimate ('~EUR 6,000').</t>
   </si>
   <si>
-    <t xml:space="preserve">Dec 2027: before the year-2 scale-up and before seed due diligence.</t>
+    <t xml:space="preserve">Feb 2029: funded by the seed, not by the pre-seed. Until then: automated security tests, RLS isolation checks and nightly code review.</t>
   </si>
   <si>
     <t xml:space="preserve">Tax</t>
@@ -878,10 +885,10 @@
     <t xml:space="preserve">Headcount (employer cost)</t>
   </si>
   <si>
-    <t xml:space="preserve">Co-founder - Miroslav Maletici (role [TO CONFIRM])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Co-founder - Răzvan Pervulescu (role [TO CONFIRM])</t>
+    <t xml:space="preserve">Co-founder &amp; CEO - Miroslav Maletici (unpaid in year 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Co-founder &amp; CTO - Răzvan Pervulescu (unpaid in year 1)</t>
   </si>
   <si>
     <t xml:space="preserve">Partner &amp; sales manager (accountant channel; part-time first)</t>
@@ -1241,7 +1248,7 @@
     <t xml:space="preserve">Product &amp; engineering (2 co-founders full time)</t>
   </si>
   <si>
-    <t xml:space="preserve">Both co-founders full time on lean salaries; the developer is hired after the seed (in_DevStart), outside this horizon in the base case. REGES-Online, payroll validation fixes, billing, mobile store release.</t>
+    <t xml:space="preserve">Both co-founders full time, unpaid until in_FounderPayStart, then on lean salaries; the developer is hired after the seed (in_DevStart), outside this horizon in the base case. REGES-Online, payroll validation fixes, billing, mobile store release.</t>
   </si>
   <si>
     <t xml:space="preserve">Accountant channel &amp; sales (partner manager, travel, commissions)</t>
@@ -1298,7 +1305,7 @@
     <t xml:space="preserve">Proposed round</t>
   </si>
   <si>
-    <t xml:space="preserve">Vest Ventures maximum accelerator ticket</t>
+    <t xml:space="preserve">Larger ticket, same lean plan</t>
   </si>
   <si>
     <t xml:space="preserve">All rows use the same (lean) cost plan and the selected scenario. Runway on plan assumes the money arrives in model month 1 (running minimum of cumulative operating cash flow).</t>
@@ -1971,7 +1978,7 @@
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">in_Round</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D11" s="1"/>
     </row>
@@ -1982,7 +1989,7 @@
       </c>
       <c r="C12" s="5" t="str">
         <f aca="false">"€"&amp;TEXT(in_PreMoney,"#,##0")&amp;" / €"&amp;TEXT(in_PostMoney,"#,##0")</f>
-        <v>€1,250,000 / €1,400,000</v>
+        <v>€1,250,000 / €1,350,000</v>
       </c>
       <c r="D12" s="1"/>
     </row>
@@ -2004,7 +2011,7 @@
       </c>
       <c r="C14" s="8" t="n">
         <f aca="false">in_RunwayZeroRev</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D14" s="1"/>
     </row>
@@ -2015,7 +2022,7 @@
       </c>
       <c r="C15" s="8" t="n">
         <f aca="false">in_RunwayPlan</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2092,7 +2099,7 @@
       </c>
       <c r="C22" s="6" t="n">
         <f aca="false">in_CashLow</f>
-        <v>-50706.4011609057</v>
+        <v>-63986.3261609057</v>
       </c>
       <c r="D22" s="1"/>
     </row>
@@ -2114,7 +2121,7 @@
       </c>
       <c r="C24" s="5" t="str">
         <f aca="false">"€"&amp;TEXT(in_ARPA,"0")&amp;" / €"&amp;TEXT(in_LTV,"#,##0")&amp;" / €"&amp;TEXT(in_CAC,"#,##0")</f>
-        <v>€50 / €1,583 / €497</v>
+        <v>€50 / €1,583 / €487</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -2125,7 +2132,7 @@
       </c>
       <c r="C25" s="5" t="str">
         <f aca="false">TEXT(in_LTVCAC,"0.0")&amp;"x, "&amp;TEXT(in_Payback,"0.0")&amp;" months"</f>
-        <v>3.2x, 10.5 months</v>
+        <v>3.2x, 10.3 months</v>
       </c>
       <c r="D25" s="1"/>
     </row>
@@ -2288,7 +2295,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="70"/>
@@ -2421,7 +2428,7 @@
         <v>64</v>
       </c>
       <c r="B13" s="20" t="n">
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>61</v>
@@ -2436,7 +2443,7 @@
       </c>
       <c r="B14" s="21" t="n">
         <f aca="false">in_VVTicket</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>61</v>
@@ -2465,7 +2472,7 @@
       </c>
       <c r="B16" s="21" t="n">
         <f aca="false">in_PreMoney+in_Round</f>
-        <v>1400000</v>
+        <v>1350000</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>61</v>
@@ -2829,11 +2836,11 @@
       <c r="A46" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="19" t="n">
-        <v>2000</v>
+      <c r="B46" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D46" s="12" t="s">
         <v>114</v>
@@ -2843,39 +2850,39 @@
       <c r="A47" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B47" s="18" t="n">
-        <v>3</v>
+      <c r="B47" s="19" t="n">
+        <v>2000</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B48" s="23" t="n">
-        <v>0.5</v>
+        <v>117</v>
+      </c>
+      <c r="B48" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B49" s="23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="B49" s="18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>120</v>
@@ -2885,11 +2892,11 @@
       <c r="A50" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="B50" s="19" t="n">
-        <v>1400</v>
+      <c r="B50" s="18" t="n">
+        <v>13</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D50" s="12" t="s">
         <v>122</v>
@@ -2899,11 +2906,11 @@
       <c r="A51" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="18" t="n">
-        <v>7</v>
+      <c r="B51" s="19" t="n">
+        <v>1400</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>58</v>
+        <v>94</v>
       </c>
       <c r="D51" s="12" t="s">
         <v>124</v>
@@ -2913,134 +2920,134 @@
       <c r="A52" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B52" s="23" t="n">
-        <v>0.5</v>
+      <c r="B52" s="18" t="n">
+        <v>9</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>83</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B53" s="18" t="n">
-        <v>25</v>
+        <v>127</v>
+      </c>
+      <c r="B53" s="23" t="n">
+        <v>0.5</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B54" s="19" t="n">
-        <v>2500</v>
+      <c r="B54" s="18" t="n">
+        <v>25</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
+      <c r="A55" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B55" s="19" t="n">
+        <v>2500</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B56" s="15"/>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15"/>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" s="19" t="n">
-        <v>350</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D57" s="12" t="s">
+      <c r="A57" s="14" t="s">
         <v>132</v>
       </c>
+      <c r="B57" s="15"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="15"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B58" s="27" t="n">
-        <v>1.5</v>
+      <c r="B58" s="19" t="n">
+        <v>350</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="19" t="n">
-        <v>250</v>
+      <c r="B59" s="27" t="n">
+        <v>1.5</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>136</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B60" s="23" t="n">
-        <v>0.02</v>
+      <c r="B60" s="19" t="n">
+        <v>250</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>138</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B61" s="23" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B61" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>94</v>
-      </c>
       <c r="D61" s="12" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B62" s="19" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>94</v>
@@ -3051,10 +3058,10 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B63" s="19" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>94</v>
@@ -3065,16 +3072,16 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B64" s="19" t="n">
-        <v>300</v>
+        <v>3500</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>144</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3110,75 +3117,77 @@
         <v>149</v>
       </c>
       <c r="B67" s="19" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>94</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="19" t="n">
         <v>150</v>
       </c>
-      <c r="B68" s="23" t="n">
-        <v>0.05</v>
-      </c>
       <c r="C68" s="1" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
+      <c r="A69" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B69" s="23" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B70" s="15"/>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="B71" s="19" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D71" s="12" t="s">
+      <c r="A71" s="14" t="s">
         <v>153</v>
       </c>
+      <c r="B71" s="15"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="15"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B72" s="18" t="n">
-        <v>1</v>
+      <c r="B72" s="19" t="n">
+        <v>5000</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D72" s="12"/>
+        <v>61</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B73" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>58</v>
@@ -3187,36 +3196,36 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="B74" s="19" t="n">
-        <v>8000</v>
+        <v>157</v>
+      </c>
+      <c r="B74" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D74" s="12" t="s">
-        <v>157</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D74" s="12"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B75" s="18" t="n">
-        <v>2</v>
+        <v>158</v>
+      </c>
+      <c r="B75" s="19" t="n">
+        <v>8000</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D75" s="12"/>
+        <v>61</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B76" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>58</v>
@@ -3225,36 +3234,36 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="B77" s="19" t="n">
-        <v>3000</v>
+        <v>157</v>
+      </c>
+      <c r="B77" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D77" s="12" t="s">
-        <v>159</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D77" s="12"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B78" s="18" t="n">
-        <v>5</v>
+        <v>160</v>
+      </c>
+      <c r="B78" s="19" t="n">
+        <v>3000</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D78" s="12"/>
+        <v>61</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B79" s="18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>58</v>
@@ -3263,81 +3272,79 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B80" s="19" t="n">
-        <v>6000</v>
+        <v>157</v>
+      </c>
+      <c r="B80" s="18" t="n">
+        <v>6</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D80" s="12" t="s">
-        <v>161</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="D80" s="12"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B81" s="18" t="n">
-        <v>12</v>
+        <v>162</v>
+      </c>
+      <c r="B81" s="19" t="n">
+        <v>6000</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B82" s="18" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D82" s="12"/>
+      <c r="D82" s="12" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
+      <c r="A83" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" s="18" t="n">
+        <v>26</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D83" s="12"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="B84" s="15"/>
-      <c r="C84" s="15"/>
-      <c r="D84" s="15"/>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B85" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" s="1" t="s">
+      <c r="A85" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="D85" s="12" t="s">
-        <v>166</v>
-      </c>
+      <c r="B85" s="15"/>
+      <c r="C85" s="15"/>
+      <c r="D85" s="15"/>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B86" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="B86" s="23" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C86" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>168</v>
@@ -3348,108 +3355,107 @@
         <v>169</v>
       </c>
       <c r="B87" s="23" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88" s="23" t="n">
         <v>0.16</v>
       </c>
-      <c r="C87" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
+      <c r="C88" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="B89" s="15"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="15"/>
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+      <c r="C89" s="1"/>
+      <c r="D89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B90" s="18" t="n">
+      <c r="A90" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B90" s="15"/>
+      <c r="C90" s="15"/>
+      <c r="D90" s="15"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B91" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="C90" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D90" s="12" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
+      <c r="C91" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="B92" s="15"/>
-      <c r="C92" s="15"/>
-      <c r="D92" s="15"/>
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+      <c r="C92" s="1"/>
+      <c r="D92" s="1"/>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B93" s="5" t="str">
+      <c r="A93" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="B93" s="15"/>
+      <c r="C93" s="15"/>
+      <c r="D93" s="15"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94" s="5" t="str">
         <f aca="false">INDEX(Scenarios!$C$4:$E$4,1,ScenarioIdx)</f>
         <v>Base</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B94" s="9" t="n">
+      <c r="C94" s="1"/>
+      <c r="D94" s="1"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B95" s="9" t="n">
         <f aca="false">INDEX(Scenarios!$C$5:$E$5,1,ScenarioIdx)</f>
         <v>6</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D94" s="12" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="C95" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B95" s="28" t="n">
+      <c r="D95" s="12" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$6:$E$6,1,ScenarioIdx)</f>
         <v>2</v>
       </c>
-      <c r="C95" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="C96" s="1" t="s">
         <v>184</v>
-      </c>
-      <c r="B96" s="29" t="n">
-        <f aca="false">INDEX(Scenarios!$C$7:$E$7,1,ScenarioIdx)</f>
-        <v>0.5</v>
-      </c>
-      <c r="C96" s="1" t="s">
-        <v>82</v>
       </c>
       <c r="D96" s="12" t="s">
         <v>185</v>
@@ -3459,72 +3465,72 @@
       <c r="A97" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B97" s="28" t="n">
+      <c r="B97" s="29" t="n">
+        <f aca="false">INDEX(Scenarios!$C$7:$E$7,1,ScenarioIdx)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B98" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$8:$E$8,1,ScenarioIdx)</f>
         <v>2</v>
       </c>
-      <c r="C97" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D97" s="12" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+      <c r="C98" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="B98" s="28" t="n">
+      <c r="D98" s="12" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B99" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$9:$E$9,1,ScenarioIdx)</f>
         <v>3</v>
       </c>
-      <c r="C98" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D98" s="12" t="s">
+      <c r="C99" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D99" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B99" s="28" t="n">
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$10:$E$10,1,ScenarioIdx)</f>
         <v>4</v>
       </c>
-      <c r="C99" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D99" s="12" t="s">
+      <c r="C100" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D100" s="12" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B100" s="30" t="n">
-        <f aca="false">INDEX(Scenarios!$C$11:$E$11,1,ScenarioIdx)</f>
-        <v>0.2</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B101" s="29" t="n">
-        <f aca="false">INDEX(Scenarios!$C$12:$E$12,1,ScenarioIdx)</f>
-        <v>0.5</v>
+      <c r="B101" s="30" t="n">
+        <f aca="false">INDEX(Scenarios!$C$11:$E$11,1,ScenarioIdx)</f>
+        <v>0.2</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="D101" s="12" t="s">
         <v>194</v>
@@ -3534,72 +3540,72 @@
       <c r="A102" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B102" s="28" t="n">
+      <c r="B102" s="29" t="n">
+        <f aca="false">INDEX(Scenarios!$C$12:$E$12,1,ScenarioIdx)</f>
+        <v>0.5</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D102" s="12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B103" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$13:$E$13,1,ScenarioIdx)</f>
         <v>4</v>
       </c>
-      <c r="C102" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="C103" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B103" s="28" t="n">
+      <c r="D103" s="12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B104" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$14:$E$14,1,ScenarioIdx)</f>
         <v>12</v>
       </c>
-      <c r="C103" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D103" s="12" t="s">
+      <c r="C104" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D104" s="12" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B104" s="28" t="n">
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B105" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$15:$E$15,1,ScenarioIdx)</f>
         <v>20</v>
       </c>
-      <c r="C104" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="D104" s="12" t="s">
+      <c r="C105" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D105" s="12" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B105" s="29" t="n">
-        <f aca="false">INDEX(Scenarios!$C$16:$E$16,1,ScenarioIdx)</f>
-        <v>0.25</v>
-      </c>
-      <c r="C105" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B106" s="6" t="n">
-        <f aca="false">INDEX(Scenarios!$C$17:$E$17,1,ScenarioIdx)</f>
-        <v>80</v>
+      <c r="B106" s="29" t="n">
+        <f aca="false">INDEX(Scenarios!$C$16:$E$16,1,ScenarioIdx)</f>
+        <v>0.25</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="D106" s="12" t="s">
         <v>203</v>
@@ -3609,45 +3615,60 @@
       <c r="A107" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B107" s="29" t="n">
+      <c r="B107" s="6" t="n">
+        <f aca="false">INDEX(Scenarios!$C$17:$E$17,1,ScenarioIdx)</f>
+        <v>80</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B108" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$18:$E$18,1,ScenarioIdx)</f>
         <v>0.03</v>
       </c>
-      <c r="C107" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="C108" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B108" s="29" t="n">
-        <f aca="false">INDEX(Scenarios!$C$19:$E$19,1,ScenarioIdx)</f>
-        <v>0.05</v>
-      </c>
-      <c r="C108" s="1" t="s">
+      <c r="D108" s="12" t="s">
         <v>208</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B109" s="9" t="n">
+      <c r="B109" s="29" t="n">
+        <f aca="false">INDEX(Scenarios!$C$19:$E$19,1,ScenarioIdx)</f>
+        <v>0.05</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B110" s="9" t="n">
         <f aca="false">INDEX(Scenarios!$C$20:$E$20,1,ScenarioIdx)</f>
         <v>25</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C110" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D109" s="12" t="s">
-        <v>210</v>
+      <c r="D110" s="12" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3676,7 +3697,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3718,7 +3739,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -3760,7 +3781,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="31" t="n">
@@ -3909,7 +3930,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="32" t="n">
@@ -4059,7 +4080,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="31" t="n">
@@ -4249,7 +4270,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -4291,10 +4312,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C8" s="33" t="n">
         <f aca="false">IF(C$3=in_PilotConvMonth,in_PilotPractices*in_PilotFirmsPerPractice*in_PilotConv,0)</f>
@@ -4443,10 +4464,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C9" s="33" t="n">
         <f aca="false">IF(C$3&gt;=in_PartnerStart,CHOOSE(C$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(C$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
@@ -4595,10 +4616,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C10" s="33" t="n">
         <f aca="false">0+C9+IF(C$3=in_PilotConvMonth,in_PilotPractices,0)</f>
@@ -4747,10 +4768,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C11" s="33" t="n">
         <f aca="false">0*in_RefRate</f>
@@ -4899,10 +4920,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C12" s="33" t="n">
         <f aca="false">0*in_RefConv</f>
@@ -5051,10 +5072,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C13" s="33" t="n">
         <f aca="false">CHOOSE(C$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
@@ -5203,10 +5224,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C14" s="28" t="n">
         <f aca="false">Costs!C21*in_PaidShare/in_CostPerTrial</f>
@@ -5355,10 +5376,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C15" s="33" t="n">
         <f aca="false">(0+0)*in_TrialConv</f>
@@ -5547,7 +5568,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
@@ -5589,10 +5610,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C18" s="34" t="n">
         <f aca="false">C8+C12+C15</f>
@@ -5741,10 +5762,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C19" s="33" t="n">
         <f aca="false">C8+C12</f>
@@ -5893,10 +5914,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C20" s="33" t="n">
         <f aca="false">0*in_Churn</f>
@@ -6045,10 +6066,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C21" s="35" t="n">
         <f aca="false">0+C18-C20</f>
@@ -6237,7 +6258,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -6279,7 +6300,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>74</v>
@@ -6431,7 +6452,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>94</v>
@@ -6583,7 +6604,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>61</v>
@@ -6735,7 +6756,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>61</v>
@@ -6887,7 +6908,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>61</v>
@@ -7079,7 +7100,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -7121,7 +7142,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B31" s="10" t="n">
         <v>30</v>
@@ -7135,7 +7156,7 @@
         <v>46600</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -7173,7 +7194,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B32" s="10" t="n">
         <v>100</v>
@@ -7187,7 +7208,7 @@
         <v>46966</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -7225,7 +7246,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B33" s="10" t="n">
         <v>300</v>
@@ -7239,7 +7260,7 @@
         <v>-</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -7301,7 +7322,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7343,7 +7364,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -7385,7 +7406,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42" t="n">
@@ -7535,7 +7556,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="43" t="n">
@@ -7685,7 +7706,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="42" t="n">
@@ -7875,7 +7896,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -7917,311 +7938,311 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C8" s="39" t="n">
-        <f aca="false">IF(C$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(C$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(C$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(C$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="D8" s="39" t="n">
-        <f aca="false">IF(D$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(D$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(D$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(D$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="E8" s="39" t="n">
-        <f aca="false">IF(E$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(E$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(E$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(E$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="F8" s="39" t="n">
-        <f aca="false">IF(F$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(F$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(F$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(F$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="G8" s="39" t="n">
-        <f aca="false">IF(G$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(G$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(G$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(G$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="H8" s="39" t="n">
-        <f aca="false">IF(H$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(H$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(H$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(H$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="I8" s="39" t="n">
-        <f aca="false">IF(I$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(I$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(I$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(I$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="J8" s="39" t="n">
-        <f aca="false">IF(J$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(J$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(J$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(J$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="K8" s="39" t="n">
-        <f aca="false">IF(K$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(K$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(K$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(K$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="L8" s="39" t="n">
-        <f aca="false">IF(L$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(L$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(L$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(L$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="M8" s="39" t="n">
-        <f aca="false">IF(M$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(M$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(M$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(M$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="N8" s="39" t="n">
-        <f aca="false">IF(N$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(N$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(N$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(N$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="O8" s="39" t="n">
-        <f aca="false">IF(O$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(O$5-1),0)</f>
+        <f aca="false">IF(O$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(O$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="P8" s="39" t="n">
-        <f aca="false">IF(P$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(P$5-1),0)</f>
+        <f aca="false">IF(P$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(P$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Q8" s="39" t="n">
-        <f aca="false">IF(Q$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Q$5-1),0)</f>
+        <f aca="false">IF(Q$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Q$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="R8" s="39" t="n">
-        <f aca="false">IF(R$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(R$5-1),0)</f>
+        <f aca="false">IF(R$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(R$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="S8" s="39" t="n">
-        <f aca="false">IF(S$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(S$5-1),0)</f>
+        <f aca="false">IF(S$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(S$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="T8" s="39" t="n">
-        <f aca="false">IF(T$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(T$5-1),0)</f>
+        <f aca="false">IF(T$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(T$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="U8" s="39" t="n">
-        <f aca="false">IF(U$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(U$5-1),0)</f>
+        <f aca="false">IF(U$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(U$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="V8" s="39" t="n">
-        <f aca="false">IF(V$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(V$5-1),0)</f>
+        <f aca="false">IF(V$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(V$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="W8" s="39" t="n">
-        <f aca="false">IF(W$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(W$5-1),0)</f>
+        <f aca="false">IF(W$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(W$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="X8" s="39" t="n">
-        <f aca="false">IF(X$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(X$5-1),0)</f>
+        <f aca="false">IF(X$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(X$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Y8" s="39" t="n">
-        <f aca="false">IF(Y$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Y$5-1),0)</f>
+        <f aca="false">IF(Y$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Y$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Z8" s="39" t="n">
-        <f aca="false">IF(Z$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Z$5-1),0)</f>
+        <f aca="false">IF(Z$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Z$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="AA8" s="39" t="n">
-        <f aca="false">IF(AA$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AA$5-1),0)</f>
+        <f aca="false">IF(AA$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AA$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AB8" s="39" t="n">
-        <f aca="false">IF(AB$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AB$5-1),0)</f>
+        <f aca="false">IF(AB$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AB$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AC8" s="39" t="n">
-        <f aca="false">IF(AC$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AC$5-1),0)</f>
+        <f aca="false">IF(AC$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AC$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AD8" s="39" t="n">
-        <f aca="false">IF(AD$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AD$5-1),0)</f>
+        <f aca="false">IF(AD$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AD$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AE8" s="39" t="n">
-        <f aca="false">IF(AE$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AE$5-1),0)</f>
+        <f aca="false">IF(AE$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AE$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AF8" s="39" t="n">
-        <f aca="false">IF(AF$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AF$5-1),0)</f>
+        <f aca="false">IF(AF$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AF$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AG8" s="39" t="n">
-        <f aca="false">IF(AG$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AG$5-1),0)</f>
+        <f aca="false">IF(AG$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AG$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AH8" s="39" t="n">
-        <f aca="false">IF(AH$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AH$5-1),0)</f>
+        <f aca="false">IF(AH$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AH$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AI8" s="39" t="n">
-        <f aca="false">IF(AI$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AI$5-1),0)</f>
+        <f aca="false">IF(AI$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AI$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AJ8" s="39" t="n">
-        <f aca="false">IF(AJ$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AJ$5-1),0)</f>
+        <f aca="false">IF(AJ$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AJ$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AK8" s="39" t="n">
-        <f aca="false">IF(AK$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AK$5-1),0)</f>
+        <f aca="false">IF(AK$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AK$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AL8" s="39" t="n">
-        <f aca="false">IF(AL$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AL$5-1),0)</f>
+        <f aca="false">IF(AL$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AL$5-1),0)</f>
         <v>1127.30625</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C9" s="39" t="n">
-        <f aca="false">IF(C$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(C$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(C$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(C$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="D9" s="39" t="n">
-        <f aca="false">IF(D$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(D$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(D$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(D$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="E9" s="39" t="n">
-        <f aca="false">IF(E$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(E$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(E$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(E$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="F9" s="39" t="n">
-        <f aca="false">IF(F$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(F$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(F$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(F$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="G9" s="39" t="n">
-        <f aca="false">IF(G$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(G$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(G$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(G$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="H9" s="39" t="n">
-        <f aca="false">IF(H$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(H$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(H$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(H$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="I9" s="39" t="n">
-        <f aca="false">IF(I$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(I$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(I$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(I$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="J9" s="39" t="n">
-        <f aca="false">IF(J$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(J$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(J$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(J$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="K9" s="39" t="n">
-        <f aca="false">IF(K$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(K$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(K$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(K$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="L9" s="39" t="n">
-        <f aca="false">IF(L$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(L$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(L$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(L$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="M9" s="39" t="n">
-        <f aca="false">IF(M$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(M$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(M$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(M$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="N9" s="39" t="n">
-        <f aca="false">IF(N$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(N$5-1),0)</f>
-        <v>1022.5</v>
+        <f aca="false">IF(N$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(N$5-1),0)</f>
+        <v>0</v>
       </c>
       <c r="O9" s="39" t="n">
-        <f aca="false">IF(O$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(O$5-1),0)</f>
+        <f aca="false">IF(O$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(O$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="P9" s="39" t="n">
-        <f aca="false">IF(P$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(P$5-1),0)</f>
+        <f aca="false">IF(P$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(P$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Q9" s="39" t="n">
-        <f aca="false">IF(Q$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Q$5-1),0)</f>
+        <f aca="false">IF(Q$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Q$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="R9" s="39" t="n">
-        <f aca="false">IF(R$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(R$5-1),0)</f>
+        <f aca="false">IF(R$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(R$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="S9" s="39" t="n">
-        <f aca="false">IF(S$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(S$5-1),0)</f>
+        <f aca="false">IF(S$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(S$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="T9" s="39" t="n">
-        <f aca="false">IF(T$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(T$5-1),0)</f>
+        <f aca="false">IF(T$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(T$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="U9" s="39" t="n">
-        <f aca="false">IF(U$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(U$5-1),0)</f>
+        <f aca="false">IF(U$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(U$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="V9" s="39" t="n">
-        <f aca="false">IF(V$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(V$5-1),0)</f>
+        <f aca="false">IF(V$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(V$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="W9" s="39" t="n">
-        <f aca="false">IF(W$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(W$5-1),0)</f>
+        <f aca="false">IF(W$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(W$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="X9" s="39" t="n">
-        <f aca="false">IF(X$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(X$5-1),0)</f>
+        <f aca="false">IF(X$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(X$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Y9" s="39" t="n">
-        <f aca="false">IF(Y$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Y$5-1),0)</f>
+        <f aca="false">IF(Y$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Y$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="Z9" s="39" t="n">
-        <f aca="false">IF(Z$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Z$5-1),0)</f>
+        <f aca="false">IF(Z$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(Z$5-1),0)</f>
         <v>1073.625</v>
       </c>
       <c r="AA9" s="39" t="n">
-        <f aca="false">IF(AA$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AA$5-1),0)</f>
+        <f aca="false">IF(AA$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AA$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AB9" s="39" t="n">
-        <f aca="false">IF(AB$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AB$5-1),0)</f>
+        <f aca="false">IF(AB$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AB$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AC9" s="39" t="n">
-        <f aca="false">IF(AC$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AC$5-1),0)</f>
+        <f aca="false">IF(AC$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AC$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AD9" s="39" t="n">
-        <f aca="false">IF(AD$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AD$5-1),0)</f>
+        <f aca="false">IF(AD$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AD$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AE9" s="39" t="n">
-        <f aca="false">IF(AE$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AE$5-1),0)</f>
+        <f aca="false">IF(AE$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AE$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AF9" s="39" t="n">
-        <f aca="false">IF(AF$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AF$5-1),0)</f>
+        <f aca="false">IF(AF$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AF$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AG9" s="39" t="n">
-        <f aca="false">IF(AG$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AG$5-1),0)</f>
+        <f aca="false">IF(AG$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AG$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AH9" s="39" t="n">
-        <f aca="false">IF(AH$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AH$5-1),0)</f>
+        <f aca="false">IF(AH$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AH$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AI9" s="39" t="n">
-        <f aca="false">IF(AI$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AI$5-1),0)</f>
+        <f aca="false">IF(AI$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AI$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AJ9" s="39" t="n">
-        <f aca="false">IF(AJ$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AJ$5-1),0)</f>
+        <f aca="false">IF(AJ$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AJ$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AK9" s="39" t="n">
-        <f aca="false">IF(AK$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AK$5-1),0)</f>
+        <f aca="false">IF(AK$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AK$5-1),0)</f>
         <v>1127.30625</v>
       </c>
       <c r="AL9" s="39" t="n">
-        <f aca="false">IF(AL$3&gt;=1,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AL$5-1),0)</f>
+        <f aca="false">IF(AL$3&gt;=in_FounderPayStart,in_SalFounder*(1+in_CAM)*(1+in_Raise)^(AL$5-1),0)</f>
         <v>1127.30625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>61</v>
@@ -8373,7 +8394,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>61</v>
@@ -8404,11 +8425,11 @@
       </c>
       <c r="I11" s="39" t="n">
         <f aca="false">IF(I$3&gt;=in_SupportStart,in_SalSupport*IF(I$3&gt;=in_SupportFullStart,1,in_SupportFTE)*(1+in_CAM)*(1+in_Raise)^(I$5-1),0)</f>
-        <v>715.75</v>
+        <v>0</v>
       </c>
       <c r="J11" s="39" t="n">
         <f aca="false">IF(J$3&gt;=in_SupportStart,in_SalSupport*IF(J$3&gt;=in_SupportFullStart,1,in_SupportFTE)*(1+in_CAM)*(1+in_Raise)^(J$5-1),0)</f>
-        <v>715.75</v>
+        <v>0</v>
       </c>
       <c r="K11" s="39" t="n">
         <f aca="false">IF(K$3&gt;=in_SupportStart,in_SalSupport*IF(K$3&gt;=in_SupportFullStart,1,in_SupportFTE)*(1+in_CAM)*(1+in_Raise)^(K$5-1),0)</f>
@@ -8525,7 +8546,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>61</v>
@@ -8677,58 +8698,58 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="40" t="n">
         <f aca="false">SUM(C8:C12)</f>
-        <v>2045</v>
+        <v>0</v>
       </c>
       <c r="D13" s="40" t="n">
         <f aca="false">SUM(D8:D12)</f>
-        <v>2045</v>
+        <v>0</v>
       </c>
       <c r="E13" s="40" t="n">
         <f aca="false">SUM(E8:E12)</f>
-        <v>3067.5</v>
+        <v>1022.5</v>
       </c>
       <c r="F13" s="40" t="n">
         <f aca="false">SUM(F8:F12)</f>
-        <v>3067.5</v>
+        <v>1022.5</v>
       </c>
       <c r="G13" s="40" t="n">
         <f aca="false">SUM(G8:G12)</f>
-        <v>3067.5</v>
+        <v>1022.5</v>
       </c>
       <c r="H13" s="40" t="n">
         <f aca="false">SUM(H8:H12)</f>
-        <v>3067.5</v>
+        <v>1022.5</v>
       </c>
       <c r="I13" s="40" t="n">
         <f aca="false">SUM(I8:I12)</f>
-        <v>3783.25</v>
+        <v>1022.5</v>
       </c>
       <c r="J13" s="40" t="n">
         <f aca="false">SUM(J8:J12)</f>
-        <v>3783.25</v>
+        <v>1022.5</v>
       </c>
       <c r="K13" s="40" t="n">
         <f aca="false">SUM(K8:K12)</f>
-        <v>3783.25</v>
+        <v>1738.25</v>
       </c>
       <c r="L13" s="40" t="n">
         <f aca="false">SUM(L8:L12)</f>
-        <v>3783.25</v>
+        <v>1738.25</v>
       </c>
       <c r="M13" s="40" t="n">
         <f aca="false">SUM(M8:M12)</f>
-        <v>3783.25</v>
+        <v>1738.25</v>
       </c>
       <c r="N13" s="40" t="n">
         <f aca="false">SUM(N8:N12)</f>
-        <v>3783.25</v>
+        <v>1738.25</v>
       </c>
       <c r="O13" s="40" t="n">
         <f aca="false">SUM(O8:O12)</f>
@@ -8829,10 +8850,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C14" s="33" t="n">
         <f aca="false">2+IF(C$3&gt;=in_SalesStart,IF(C$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)+IF(C$3&gt;=in_SupportStart,IF(C$3&gt;=in_SupportFullStart,1,in_SupportFTE),0)+IF(C$3&gt;=in_DevStart,1,0)</f>
@@ -8860,11 +8881,11 @@
       </c>
       <c r="I14" s="33" t="n">
         <f aca="false">2+IF(I$3&gt;=in_SalesStart,IF(I$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)+IF(I$3&gt;=in_SupportStart,IF(I$3&gt;=in_SupportFullStart,1,in_SupportFTE),0)+IF(I$3&gt;=in_DevStart,1,0)</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J14" s="33" t="n">
         <f aca="false">2+IF(J$3&gt;=in_SalesStart,IF(J$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)+IF(J$3&gt;=in_SupportStart,IF(J$3&gt;=in_SupportFullStart,1,in_SupportFTE),0)+IF(J$3&gt;=in_DevStart,1,0)</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="K14" s="33" t="n">
         <f aca="false">2+IF(K$3&gt;=in_SalesStart,IF(K$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)+IF(K$3&gt;=in_SupportStart,IF(K$3&gt;=in_SupportFullStart,1,in_SupportFTE),0)+IF(K$3&gt;=in_DevStart,1,0)</f>
@@ -9021,7 +9042,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B16" s="15"/>
       <c r="C16" s="15"/>
@@ -9063,7 +9084,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>61</v>
@@ -9215,7 +9236,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>61</v>
@@ -9367,7 +9388,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>61</v>
@@ -9519,7 +9540,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>61</v>
@@ -9671,7 +9692,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>61</v>
@@ -9823,159 +9844,159 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="D22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="E22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="G22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="H22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="J22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="L22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="M22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="O22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="P22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Y22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Z22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AB22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AC22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AD22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AE22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AF22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AG22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AH22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AI22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AJ22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AK22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="AL22" s="39" t="n">
         <f aca="false">in_Travel</f>
-        <v>300</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>61</v>
@@ -10127,159 +10148,159 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="O24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="P24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="R24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="S24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="T24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="U24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="V24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="W24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="X24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AA24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AB24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AE24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AG24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AH24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AI24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AJ24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AK24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AL24" s="39" t="n">
         <f aca="false">in_Office</f>
-        <v>200</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>61</v>
@@ -10431,159 +10452,159 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="D26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="F26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="G26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="J26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="K26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="L26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="N26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="O26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="P26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="Q26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="R26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="S26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="T26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="U26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="V26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="W26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="X26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="Y26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="Z26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AA26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AB26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AC26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AD26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AE26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AF26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AG26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AH26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AI26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AJ26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AK26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AL26" s="39" t="n">
         <f aca="false">in_Admin</f>
-        <v>200</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>61</v>
@@ -10735,7 +10756,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>61</v>
@@ -10887,7 +10908,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>61</v>
@@ -11039,7 +11060,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>61</v>
@@ -11090,7 +11111,7 @@
       </c>
       <c r="N30" s="39" t="n">
         <f aca="false">IF(AND(N$3&gt;=in_PentestStart,N$3&lt;=in_PentestEnd),in_PentestAmt/(in_PentestEnd-in_PentestStart+1),0)</f>
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="O30" s="39" t="n">
         <f aca="false">IF(AND(O$3&gt;=in_PentestStart,O$3&lt;=in_PentestEnd),in_PentestAmt/(in_PentestEnd-in_PentestStart+1),0)</f>
@@ -11146,7 +11167,7 @@
       </c>
       <c r="AB30" s="39" t="n">
         <f aca="false">IF(AND(AB$3&gt;=in_PentestStart,AB$3&lt;=in_PentestEnd),in_PentestAmt/(in_PentestEnd-in_PentestStart+1),0)</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="AC30" s="39" t="n">
         <f aca="false">IF(AND(AC$3&gt;=in_PentestStart,AC$3&lt;=in_PentestEnd),in_PentestAmt/(in_PentestEnd-in_PentestStart+1),0)</f>
@@ -11191,306 +11212,306 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B31" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="40" t="n">
         <f aca="false">SUM(C17:C30)</f>
-        <v>5400</v>
+        <v>5150</v>
       </c>
       <c r="D31" s="40" t="n">
         <f aca="false">SUM(D17:D30)</f>
-        <v>7409.34825</v>
+        <v>7159.34825</v>
       </c>
       <c r="E31" s="40" t="n">
         <f aca="false">SUM(E17:E30)</f>
-        <v>4918.4160525</v>
+        <v>4668.4160525</v>
       </c>
       <c r="F31" s="40" t="n">
         <f aca="false">SUM(F17:F30)</f>
-        <v>4999.043820925</v>
+        <v>4749.043820925</v>
       </c>
       <c r="G31" s="40" t="n">
         <f aca="false">SUM(G17:G30)</f>
-        <v>6507.13435629725</v>
+        <v>6257.13435629725</v>
       </c>
       <c r="H31" s="40" t="n">
         <f aca="false">SUM(H17:H30)</f>
-        <v>4523.36257560833</v>
+        <v>4273.36257560833</v>
       </c>
       <c r="I31" s="40" t="n">
         <f aca="false">SUM(I17:I30)</f>
-        <v>3040.50106834008</v>
+        <v>2790.50106834008</v>
       </c>
       <c r="J31" s="40" t="n">
         <f aca="false">SUM(J17:J30)</f>
-        <v>3058.55108628988</v>
+        <v>2808.55108628988</v>
       </c>
       <c r="K31" s="40" t="n">
         <f aca="false">SUM(K17:K30)</f>
-        <v>3077.51384370118</v>
+        <v>2827.51384370118</v>
       </c>
       <c r="L31" s="40" t="n">
         <f aca="false">SUM(L17:L30)</f>
-        <v>3040.27051839015</v>
+        <v>2790.27051839015</v>
       </c>
       <c r="M31" s="40" t="n">
         <f aca="false">SUM(M17:M30)</f>
-        <v>3061.06225283844</v>
+        <v>2811.06225283844</v>
       </c>
       <c r="N31" s="40" t="n">
         <f aca="false">SUM(N17:N30)</f>
-        <v>9076.10615525329</v>
+        <v>2826.10615525329</v>
       </c>
       <c r="O31" s="40" t="n">
         <f aca="false">SUM(O17:O30)</f>
-        <v>4096.83458620269</v>
+        <v>3846.83458620269</v>
       </c>
       <c r="P31" s="40" t="n">
         <f aca="false">SUM(P17:P30)</f>
-        <v>4121.96139561661</v>
+        <v>3871.96139561661</v>
       </c>
       <c r="Q31" s="40" t="n">
         <f aca="false">SUM(Q17:Q30)</f>
-        <v>4149.26340874811</v>
+        <v>3899.26340874811</v>
       </c>
       <c r="R31" s="40" t="n">
         <f aca="false">SUM(R17:R30)</f>
-        <v>4178.73534548567</v>
+        <v>3928.73534548567</v>
       </c>
       <c r="S31" s="40" t="n">
         <f aca="false">SUM(S17:S30)</f>
-        <v>4210.3720841211</v>
+        <v>3960.3720841211</v>
       </c>
       <c r="T31" s="40" t="n">
         <f aca="false">SUM(T17:T30)</f>
-        <v>4244.16865659746</v>
+        <v>3994.16865659746</v>
       </c>
       <c r="U31" s="40" t="n">
         <f aca="false">SUM(U17:U30)</f>
-        <v>4280.12024389954</v>
+        <v>4030.12024389954</v>
       </c>
       <c r="V31" s="40" t="n">
         <f aca="false">SUM(V17:V30)</f>
-        <v>4318.22217158255</v>
+        <v>4068.22217158255</v>
       </c>
       <c r="W31" s="40" t="n">
         <f aca="false">SUM(W17:W30)</f>
-        <v>4356.47070543508</v>
+        <v>4106.47070543508</v>
       </c>
       <c r="X31" s="40" t="n">
         <f aca="false">SUM(X17:X30)</f>
-        <v>4394.86144727202</v>
+        <v>4144.86144727202</v>
       </c>
       <c r="Y31" s="40" t="n">
         <f aca="false">SUM(Y17:Y30)</f>
-        <v>4433.39013085386</v>
+        <v>4183.39013085386</v>
       </c>
       <c r="Z31" s="40" t="n">
         <f aca="false">SUM(Z17:Z30)</f>
-        <v>4472.05261792825</v>
+        <v>4222.05261792825</v>
       </c>
       <c r="AA31" s="40" t="n">
         <f aca="false">SUM(AA17:AA30)</f>
-        <v>5530.34710987353</v>
+        <v>5280.34710987353</v>
       </c>
       <c r="AB31" s="40" t="n">
         <f aca="false">SUM(AB17:AB30)</f>
-        <v>5580.46295152733</v>
+        <v>11330.4629515273</v>
       </c>
       <c r="AC31" s="40" t="n">
         <f aca="false">SUM(AC17:AC30)</f>
-        <v>5631.7115031315</v>
+        <v>5381.7115031315</v>
       </c>
       <c r="AD31" s="40" t="n">
         <f aca="false">SUM(AD17:AD30)</f>
-        <v>5684.09027078756</v>
+        <v>5434.09027078756</v>
       </c>
       <c r="AE31" s="40" t="n">
         <f aca="false">SUM(AE17:AE30)</f>
-        <v>5737.59683541393</v>
+        <v>5487.59683541393</v>
       </c>
       <c r="AF31" s="40" t="n">
         <f aca="false">SUM(AF17:AF30)</f>
-        <v>5792.22885050152</v>
+        <v>5542.22885050152</v>
       </c>
       <c r="AG31" s="40" t="n">
         <f aca="false">SUM(AG17:AG30)</f>
-        <v>5847.98403993647</v>
+        <v>5597.98403993647</v>
       </c>
       <c r="AH31" s="40" t="n">
         <f aca="false">SUM(AH17:AH30)</f>
-        <v>5904.86019588838</v>
+        <v>5654.86019588838</v>
       </c>
       <c r="AI31" s="40" t="n">
         <f aca="false">SUM(AI17:AI30)</f>
-        <v>5961.80559676172</v>
+        <v>5711.80559676172</v>
       </c>
       <c r="AJ31" s="40" t="n">
         <f aca="false">SUM(AJ17:AJ30)</f>
-        <v>6018.81816520887</v>
+        <v>5768.81816520887</v>
       </c>
       <c r="AK31" s="40" t="n">
         <f aca="false">SUM(AK17:AK30)</f>
-        <v>6075.89588620261</v>
+        <v>5825.89588620261</v>
       </c>
       <c r="AL31" s="40" t="n">
         <f aca="false">SUM(AL17:AL30)</f>
-        <v>6133.03680516653</v>
+        <v>5883.03680516653</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="39" t="n">
         <f aca="false">(C13+C31)*in_Contingency</f>
-        <v>372.25</v>
+        <v>257.5</v>
       </c>
       <c r="D32" s="39" t="n">
         <f aca="false">(D13+D31)*in_Contingency</f>
-        <v>472.7174125</v>
+        <v>357.9674125</v>
       </c>
       <c r="E32" s="39" t="n">
         <f aca="false">(E13+E31)*in_Contingency</f>
-        <v>399.295802625</v>
+        <v>284.545802625</v>
       </c>
       <c r="F32" s="39" t="n">
         <f aca="false">(F13+F31)*in_Contingency</f>
-        <v>403.32719104625</v>
+        <v>288.57719104625</v>
       </c>
       <c r="G32" s="39" t="n">
         <f aca="false">(G13+G31)*in_Contingency</f>
-        <v>478.731717814863</v>
+        <v>363.981717814863</v>
       </c>
       <c r="H32" s="39" t="n">
         <f aca="false">(H13+H31)*in_Contingency</f>
-        <v>379.543128780417</v>
+        <v>264.793128780417</v>
       </c>
       <c r="I32" s="39" t="n">
         <f aca="false">(I13+I31)*in_Contingency</f>
-        <v>341.187553417004</v>
+        <v>190.650053417004</v>
       </c>
       <c r="J32" s="39" t="n">
         <f aca="false">(J13+J31)*in_Contingency</f>
-        <v>342.090054314494</v>
+        <v>191.552554314494</v>
       </c>
       <c r="K32" s="39" t="n">
         <f aca="false">(K13+K31)*in_Contingency</f>
-        <v>343.038192185059</v>
+        <v>228.288192185059</v>
       </c>
       <c r="L32" s="39" t="n">
         <f aca="false">(L13+L31)*in_Contingency</f>
-        <v>341.176025919507</v>
+        <v>226.426025919507</v>
       </c>
       <c r="M32" s="39" t="n">
         <f aca="false">(M13+M31)*in_Contingency</f>
-        <v>342.215612641922</v>
+        <v>227.465612641922</v>
       </c>
       <c r="N32" s="39" t="n">
         <f aca="false">(N13+N31)*in_Contingency</f>
-        <v>642.967807762665</v>
+        <v>228.217807762665</v>
       </c>
       <c r="O32" s="39" t="n">
         <f aca="false">(O13+O31)*in_Contingency</f>
-        <v>457.143604310135</v>
+        <v>444.643604310135</v>
       </c>
       <c r="P32" s="39" t="n">
         <f aca="false">(P13+P31)*in_Contingency</f>
-        <v>458.399944780831</v>
+        <v>445.89994478083</v>
       </c>
       <c r="Q32" s="39" t="n">
         <f aca="false">(Q13+Q31)*in_Contingency</f>
-        <v>459.765045437406</v>
+        <v>447.265045437406</v>
       </c>
       <c r="R32" s="39" t="n">
         <f aca="false">(R13+R31)*in_Contingency</f>
-        <v>461.238642274283</v>
+        <v>448.738642274283</v>
       </c>
       <c r="S32" s="39" t="n">
         <f aca="false">(S13+S31)*in_Contingency</f>
-        <v>462.820479206055</v>
+        <v>450.320479206055</v>
       </c>
       <c r="T32" s="39" t="n">
         <f aca="false">(T13+T31)*in_Contingency</f>
-        <v>464.510307829873</v>
+        <v>452.010307829873</v>
       </c>
       <c r="U32" s="39" t="n">
         <f aca="false">(U13+U31)*in_Contingency</f>
-        <v>466.307887194977</v>
+        <v>453.807887194977</v>
       </c>
       <c r="V32" s="39" t="n">
         <f aca="false">(V13+V31)*in_Contingency</f>
-        <v>468.212983579128</v>
+        <v>455.712983579128</v>
       </c>
       <c r="W32" s="39" t="n">
         <f aca="false">(W13+W31)*in_Contingency</f>
-        <v>470.125410271754</v>
+        <v>457.625410271754</v>
       </c>
       <c r="X32" s="39" t="n">
         <f aca="false">(X13+X31)*in_Contingency</f>
-        <v>472.044947363601</v>
+        <v>459.544947363601</v>
       </c>
       <c r="Y32" s="39" t="n">
         <f aca="false">(Y13+Y31)*in_Contingency</f>
-        <v>473.971381542693</v>
+        <v>461.471381542693</v>
       </c>
       <c r="Z32" s="39" t="n">
         <f aca="false">(Z13+Z31)*in_Contingency</f>
-        <v>475.904505896412</v>
+        <v>463.404505896412</v>
       </c>
       <c r="AA32" s="39" t="n">
         <f aca="false">(AA13+AA31)*in_Contingency</f>
-        <v>721.803324243677</v>
+        <v>709.303324243677</v>
       </c>
       <c r="AB32" s="39" t="n">
         <f aca="false">(AB13+AB31)*in_Contingency</f>
-        <v>724.309116326366</v>
+        <v>1011.80911632637</v>
       </c>
       <c r="AC32" s="39" t="n">
         <f aca="false">(AC13+AC31)*in_Contingency</f>
-        <v>726.871543906575</v>
+        <v>714.371543906575</v>
       </c>
       <c r="AD32" s="39" t="n">
         <f aca="false">(AD13+AD31)*in_Contingency</f>
-        <v>729.490482289378</v>
+        <v>716.990482289378</v>
       </c>
       <c r="AE32" s="39" t="n">
         <f aca="false">(AE13+AE31)*in_Contingency</f>
-        <v>732.165810520697</v>
+        <v>719.665810520697</v>
       </c>
       <c r="AF32" s="39" t="n">
         <f aca="false">(AF13+AF31)*in_Contingency</f>
-        <v>734.897411275076</v>
+        <v>722.397411275076</v>
       </c>
       <c r="AG32" s="39" t="n">
         <f aca="false">(AG13+AG31)*in_Contingency</f>
-        <v>737.685170746824</v>
+        <v>725.185170746824</v>
       </c>
       <c r="AH32" s="39" t="n">
         <f aca="false">(AH13+AH31)*in_Contingency</f>
-        <v>740.528978544419</v>
+        <v>728.028978544419</v>
       </c>
       <c r="AI32" s="39" t="n">
         <f aca="false">(AI13+AI31)*in_Contingency</f>
-        <v>743.376248588086</v>
+        <v>730.876248588086</v>
       </c>
       <c r="AJ32" s="39" t="n">
         <f aca="false">(AJ13+AJ31)*in_Contingency</f>
-        <v>746.226877010444</v>
+        <v>733.726877010444</v>
       </c>
       <c r="AK32" s="39" t="n">
         <f aca="false">(AK13+AK31)*in_Contingency</f>
-        <v>749.08076306013</v>
+        <v>736.58076306013</v>
       </c>
       <c r="AL32" s="39" t="n">
         <f aca="false">(AL13+AL31)*in_Contingency</f>
-        <v>751.937809008326</v>
+        <v>739.437809008326</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11535,154 +11556,154 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="40" t="n">
         <f aca="false">C13+C31+C32</f>
-        <v>7817.25</v>
+        <v>5407.5</v>
       </c>
       <c r="D34" s="40" t="n">
         <f aca="false">D13+D31+D32</f>
-        <v>9927.0656625</v>
+        <v>7517.3156625</v>
       </c>
       <c r="E34" s="40" t="n">
         <f aca="false">E13+E31+E32</f>
-        <v>8385.211855125</v>
+        <v>5975.461855125</v>
       </c>
       <c r="F34" s="40" t="n">
         <f aca="false">F13+F31+F32</f>
-        <v>8469.87101197125</v>
+        <v>6060.12101197125</v>
       </c>
       <c r="G34" s="40" t="n">
         <f aca="false">G13+G31+G32</f>
-        <v>10053.3660741121</v>
+        <v>7643.61607411211</v>
       </c>
       <c r="H34" s="40" t="n">
         <f aca="false">H13+H31+H32</f>
-        <v>7970.40570438875</v>
+        <v>5560.65570438875</v>
       </c>
       <c r="I34" s="40" t="n">
         <f aca="false">I13+I31+I32</f>
-        <v>7164.93862175709</v>
+        <v>4003.65112175709</v>
       </c>
       <c r="J34" s="40" t="n">
         <f aca="false">J13+J31+J32</f>
-        <v>7183.89114060437</v>
+        <v>4022.60364060437</v>
       </c>
       <c r="K34" s="40" t="n">
         <f aca="false">K13+K31+K32</f>
-        <v>7203.80203588624</v>
+        <v>4794.05203588624</v>
       </c>
       <c r="L34" s="40" t="n">
         <f aca="false">L13+L31+L32</f>
-        <v>7164.69654430966</v>
+        <v>4754.94654430966</v>
       </c>
       <c r="M34" s="40" t="n">
         <f aca="false">M13+M31+M32</f>
-        <v>7186.52786548037</v>
+        <v>4776.77786548037</v>
       </c>
       <c r="N34" s="40" t="n">
         <f aca="false">N13+N31+N32</f>
-        <v>13502.323963016</v>
+        <v>4792.57396301596</v>
       </c>
       <c r="O34" s="40" t="n">
         <f aca="false">O13+O31+O32</f>
-        <v>9600.01569051282</v>
+        <v>9337.51569051282</v>
       </c>
       <c r="P34" s="40" t="n">
         <f aca="false">P13+P31+P32</f>
-        <v>9626.39884039744</v>
+        <v>9363.89884039744</v>
       </c>
       <c r="Q34" s="40" t="n">
         <f aca="false">Q13+Q31+Q32</f>
-        <v>9655.06595418552</v>
+        <v>9392.56595418552</v>
       </c>
       <c r="R34" s="40" t="n">
         <f aca="false">R13+R31+R32</f>
-        <v>9686.01148775995</v>
+        <v>9423.51148775995</v>
       </c>
       <c r="S34" s="40" t="n">
         <f aca="false">S13+S31+S32</f>
-        <v>9719.23006332715</v>
+        <v>9456.73006332715</v>
       </c>
       <c r="T34" s="40" t="n">
         <f aca="false">T13+T31+T32</f>
-        <v>9754.71646442734</v>
+        <v>9492.21646442734</v>
       </c>
       <c r="U34" s="40" t="n">
         <f aca="false">U13+U31+U32</f>
-        <v>9792.46563109452</v>
+        <v>9529.96563109452</v>
       </c>
       <c r="V34" s="40" t="n">
         <f aca="false">V13+V31+V32</f>
-        <v>9832.47265516168</v>
+        <v>9569.97265516168</v>
       </c>
       <c r="W34" s="40" t="n">
         <f aca="false">W13+W31+W32</f>
-        <v>9872.63361570683</v>
+        <v>9610.13361570683</v>
       </c>
       <c r="X34" s="40" t="n">
         <f aca="false">X13+X31+X32</f>
-        <v>9912.94389463563</v>
+        <v>9650.44389463563</v>
       </c>
       <c r="Y34" s="40" t="n">
         <f aca="false">Y13+Y31+Y32</f>
-        <v>9953.39901239656</v>
+        <v>9690.89901239656</v>
       </c>
       <c r="Z34" s="40" t="n">
         <f aca="false">Z13+Z31+Z32</f>
-        <v>9993.99462382466</v>
+        <v>9731.49462382466</v>
       </c>
       <c r="AA34" s="40" t="n">
         <f aca="false">AA13+AA31+AA32</f>
-        <v>15157.8698091172</v>
+        <v>14895.3698091172</v>
       </c>
       <c r="AB34" s="40" t="n">
         <f aca="false">AB13+AB31+AB32</f>
-        <v>15210.4914428537</v>
+        <v>21247.9914428537</v>
       </c>
       <c r="AC34" s="40" t="n">
         <f aca="false">AC13+AC31+AC32</f>
-        <v>15264.3024220381</v>
+        <v>15001.8024220381</v>
       </c>
       <c r="AD34" s="40" t="n">
         <f aca="false">AD13+AD31+AD32</f>
-        <v>15319.3001280769</v>
+        <v>15056.8001280769</v>
       </c>
       <c r="AE34" s="40" t="n">
         <f aca="false">AE13+AE31+AE32</f>
-        <v>15375.4820209346</v>
+        <v>15112.9820209346</v>
       </c>
       <c r="AF34" s="40" t="n">
         <f aca="false">AF13+AF31+AF32</f>
-        <v>15432.8456367766</v>
+        <v>15170.3456367766</v>
       </c>
       <c r="AG34" s="40" t="n">
         <f aca="false">AG13+AG31+AG32</f>
-        <v>15491.3885856833</v>
+        <v>15228.8885856833</v>
       </c>
       <c r="AH34" s="40" t="n">
         <f aca="false">AH13+AH31+AH32</f>
-        <v>15551.1085494328</v>
+        <v>15288.6085494328</v>
       </c>
       <c r="AI34" s="40" t="n">
         <f aca="false">AI13+AI31+AI32</f>
-        <v>15610.9012203498</v>
+        <v>15348.4012203498</v>
       </c>
       <c r="AJ34" s="40" t="n">
         <f aca="false">AJ13+AJ31+AJ32</f>
-        <v>15670.7644172193</v>
+        <v>15408.2644172193</v>
       </c>
       <c r="AK34" s="40" t="n">
         <f aca="false">AK13+AK31+AK32</f>
-        <v>15730.6960242627</v>
+        <v>15468.1960242627</v>
       </c>
       <c r="AL34" s="40" t="n">
         <f aca="false">AL13+AL31+AL32</f>
-        <v>15790.6939891749</v>
+        <v>15528.1939891749</v>
       </c>
     </row>
   </sheetData>
@@ -11711,7 +11732,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11753,7 +11774,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -11795,7 +11816,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B3" s="15"/>
       <c r="C3" s="42" t="n">
@@ -11945,7 +11966,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="43" t="n">
@@ -12095,7 +12116,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="42" t="n">
@@ -12285,7 +12306,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -12327,7 +12348,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>61</v>
@@ -12479,7 +12500,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B9" s="12" t="s">
         <v>61</v>
@@ -12510,11 +12531,11 @@
       </c>
       <c r="I9" s="6" t="n">
         <f aca="false">Costs!I17+Costs!I18+Costs!I20+Costs!I11</f>
-        <v>1134.85106834008</v>
+        <v>419.101068340083</v>
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">Costs!J17+Costs!J18+Costs!J20+Costs!J11</f>
-        <v>1144.33308628988</v>
+        <v>428.58308628988</v>
       </c>
       <c r="K9" s="6" t="n">
         <f aca="false">Costs!K17+Costs!K18+Costs!K20+Costs!K11</f>
@@ -12631,7 +12652,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>61</v>
@@ -12662,11 +12683,11 @@
       </c>
       <c r="I10" s="40" t="n">
         <f aca="false">I8-I9</f>
-        <v>206.588920643575</v>
+        <v>922.338920643575</v>
       </c>
       <c r="J10" s="40" t="n">
         <f aca="false">J8-J9</f>
-        <v>381.178703024268</v>
+        <v>1096.92870302427</v>
       </c>
       <c r="K10" s="40" t="n">
         <f aca="false">K8-K9</f>
@@ -12783,7 +12804,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>82</v>
@@ -12814,11 +12835,11 @@
       </c>
       <c r="I11" s="24" t="n">
         <f aca="false">IF(I8&gt;0,I10/I8,0)</f>
-        <v>0.154005339292216</v>
+        <v>0.687573747777107</v>
       </c>
       <c r="J11" s="24" t="n">
         <f aca="false">IF(J8&gt;0,J10/J8,0)</f>
-        <v>0.249869391829244</v>
+        <v>0.719056195244112</v>
       </c>
       <c r="K11" s="24" t="n">
         <f aca="false">IF(K8&gt;0,K10/K8,0)</f>
@@ -12935,58 +12956,58 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C12" s="6" t="n">
         <f aca="false">Costs!C8+Costs!C9+Costs!C12+Costs!C19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="D12" s="6" t="n">
         <f aca="false">Costs!D8+Costs!D9+Costs!D12+Costs!D19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="E12" s="6" t="n">
         <f aca="false">Costs!E8+Costs!E9+Costs!E12+Costs!E19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="F12" s="6" t="n">
         <f aca="false">Costs!F8+Costs!F9+Costs!F12+Costs!F19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="G12" s="6" t="n">
         <f aca="false">Costs!G8+Costs!G9+Costs!G12+Costs!G19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="H12" s="6" t="n">
         <f aca="false">Costs!H8+Costs!H9+Costs!H12+Costs!H19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="I12" s="6" t="n">
         <f aca="false">Costs!I8+Costs!I9+Costs!I12+Costs!I19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="J12" s="6" t="n">
         <f aca="false">Costs!J8+Costs!J9+Costs!J12+Costs!J19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="K12" s="6" t="n">
         <f aca="false">Costs!K8+Costs!K9+Costs!K12+Costs!K19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="L12" s="6" t="n">
         <f aca="false">Costs!L8+Costs!L9+Costs!L12+Costs!L19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="M12" s="6" t="n">
         <f aca="false">Costs!M8+Costs!M9+Costs!M12+Costs!M19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="N12" s="6" t="n">
         <f aca="false">Costs!N8+Costs!N9+Costs!N12+Costs!N19</f>
-        <v>2295</v>
+        <v>250</v>
       </c>
       <c r="O12" s="6" t="n">
         <f aca="false">Costs!O8+Costs!O9+Costs!O12+Costs!O19</f>
@@ -13087,463 +13108,463 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Costs!C10+Costs!C21+Costs!C22+Costs!C23</f>
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">Costs!D10+Costs!D21+Costs!D22+Costs!D23</f>
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">Costs!E10+Costs!E21+Costs!E22+Costs!E23</f>
-        <v>2822.5</v>
+        <v>2722.5</v>
       </c>
       <c r="F13" s="6" t="n">
         <f aca="false">Costs!F10+Costs!F21+Costs!F22+Costs!F23</f>
-        <v>2879.62</v>
+        <v>2779.62</v>
       </c>
       <c r="G13" s="6" t="n">
         <f aca="false">Costs!G10+Costs!G21+Costs!G22+Costs!G23</f>
-        <v>2879.62</v>
+        <v>2779.62</v>
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">Costs!H10+Costs!H21+Costs!H22+Costs!H23</f>
-        <v>2886.284</v>
+        <v>2786.284</v>
       </c>
       <c r="I13" s="6" t="n">
         <f aca="false">Costs!I10+Costs!I21+Costs!I22+Costs!I23</f>
-        <v>2893.9</v>
+        <v>2793.9</v>
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">Costs!J10+Costs!J21+Costs!J22+Costs!J23</f>
-        <v>2902.468</v>
+        <v>2802.468</v>
       </c>
       <c r="K13" s="6" t="n">
         <f aca="false">Costs!K10+Costs!K21+Costs!K22+Costs!K23</f>
-        <v>2911.988</v>
+        <v>2811.988</v>
       </c>
       <c r="L13" s="6" t="n">
         <f aca="false">Costs!L10+Costs!L21+Costs!L22+Costs!L23</f>
-        <v>2865.34</v>
+        <v>2765.34</v>
       </c>
       <c r="M13" s="6" t="n">
         <f aca="false">Costs!M10+Costs!M21+Costs!M22+Costs!M23</f>
-        <v>2876.764</v>
+        <v>2776.764</v>
       </c>
       <c r="N13" s="6" t="n">
         <f aca="false">Costs!N10+Costs!N21+Costs!N22+Costs!N23</f>
-        <v>2882.476</v>
+        <v>2782.476</v>
       </c>
       <c r="O13" s="6" t="n">
         <f aca="false">Costs!O10+Costs!O21+Costs!O22+Costs!O23</f>
-        <v>5016.2224</v>
+        <v>4916.2224</v>
       </c>
       <c r="P13" s="6" t="n">
         <f aca="false">Costs!P10+Costs!P21+Costs!P22+Costs!P23</f>
-        <v>5022.22</v>
+        <v>4922.22</v>
       </c>
       <c r="Q13" s="6" t="n">
         <f aca="false">Costs!Q10+Costs!Q21+Costs!Q22+Costs!Q23</f>
-        <v>5030.2168</v>
+        <v>4930.2168</v>
       </c>
       <c r="R13" s="6" t="n">
         <f aca="false">Costs!R10+Costs!R21+Costs!R22+Costs!R23</f>
-        <v>5040.2128</v>
+        <v>4940.2128</v>
       </c>
       <c r="S13" s="6" t="n">
         <f aca="false">Costs!S10+Costs!S21+Costs!S22+Costs!S23</f>
-        <v>5052.208</v>
+        <v>4952.208</v>
       </c>
       <c r="T13" s="6" t="n">
         <f aca="false">Costs!T10+Costs!T21+Costs!T22+Costs!T23</f>
-        <v>5066.2024</v>
+        <v>4966.2024</v>
       </c>
       <c r="U13" s="6" t="n">
         <f aca="false">Costs!U10+Costs!U21+Costs!U22+Costs!U23</f>
-        <v>5082.196</v>
+        <v>4982.196</v>
       </c>
       <c r="V13" s="6" t="n">
         <f aca="false">Costs!V10+Costs!V21+Costs!V22+Costs!V23</f>
-        <v>5100.1888</v>
+        <v>5000.1888</v>
       </c>
       <c r="W13" s="6" t="n">
         <f aca="false">Costs!W10+Costs!W21+Costs!W22+Costs!W23</f>
-        <v>5118.1816</v>
+        <v>5018.1816</v>
       </c>
       <c r="X13" s="6" t="n">
         <f aca="false">Costs!X10+Costs!X21+Costs!X22+Costs!X23</f>
-        <v>5136.1744</v>
+        <v>5036.1744</v>
       </c>
       <c r="Y13" s="6" t="n">
         <f aca="false">Costs!Y10+Costs!Y21+Costs!Y22+Costs!Y23</f>
-        <v>5154.1672</v>
+        <v>5054.1672</v>
       </c>
       <c r="Z13" s="6" t="n">
         <f aca="false">Costs!Z10+Costs!Z21+Costs!Z22+Costs!Z23</f>
-        <v>5172.16</v>
+        <v>5072.16</v>
       </c>
       <c r="AA13" s="6" t="n">
         <f aca="false">Costs!AA10+Costs!AA21+Costs!AA22+Costs!AA23</f>
-        <v>6309.66044</v>
+        <v>6209.66044</v>
       </c>
       <c r="AB13" s="6" t="n">
         <f aca="false">Costs!AB10+Costs!AB21+Costs!AB22+Costs!AB23</f>
-        <v>6328.55288</v>
+        <v>6228.55288</v>
       </c>
       <c r="AC13" s="6" t="n">
         <f aca="false">Costs!AC10+Costs!AC21+Costs!AC22+Costs!AC23</f>
-        <v>6348.4949</v>
+        <v>6248.4949</v>
       </c>
       <c r="AD13" s="6" t="n">
         <f aca="false">Costs!AD10+Costs!AD21+Costs!AD22+Costs!AD23</f>
-        <v>6369.4865</v>
+        <v>6269.4865</v>
       </c>
       <c r="AE13" s="6" t="n">
         <f aca="false">Costs!AE10+Costs!AE21+Costs!AE22+Costs!AE23</f>
-        <v>6391.52768</v>
+        <v>6291.52768</v>
       </c>
       <c r="AF13" s="6" t="n">
         <f aca="false">Costs!AF10+Costs!AF21+Costs!AF22+Costs!AF23</f>
-        <v>6414.61844</v>
+        <v>6314.61844</v>
       </c>
       <c r="AG13" s="6" t="n">
         <f aca="false">Costs!AG10+Costs!AG21+Costs!AG22+Costs!AG23</f>
-        <v>6438.75878</v>
+        <v>6338.75878</v>
       </c>
       <c r="AH13" s="6" t="n">
         <f aca="false">Costs!AH10+Costs!AH21+Costs!AH22+Costs!AH23</f>
-        <v>6463.9487</v>
+        <v>6363.9487</v>
       </c>
       <c r="AI13" s="6" t="n">
         <f aca="false">Costs!AI10+Costs!AI21+Costs!AI22+Costs!AI23</f>
-        <v>6489.13862</v>
+        <v>6389.13862</v>
       </c>
       <c r="AJ13" s="6" t="n">
         <f aca="false">Costs!AJ10+Costs!AJ21+Costs!AJ22+Costs!AJ23</f>
-        <v>6514.32854</v>
+        <v>6414.32854</v>
       </c>
       <c r="AK13" s="6" t="n">
         <f aca="false">Costs!AK10+Costs!AK21+Costs!AK22+Costs!AK23</f>
-        <v>6539.51846</v>
+        <v>6439.51846</v>
       </c>
       <c r="AL13" s="6" t="n">
         <f aca="false">Costs!AL10+Costs!AL21+Costs!AL22+Costs!AL23</f>
-        <v>6564.70838</v>
+        <v>6464.70838</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="6" t="n">
         <f aca="false">Costs!C24+Costs!C25+Costs!C26+Costs!C27+Costs!C28+Costs!C29+Costs!C30+Costs!C32</f>
-        <v>3372.25</v>
+        <v>3107.5</v>
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">Costs!D24+Costs!D25+Costs!D26+Costs!D27+Costs!D28+Costs!D29+Costs!D30+Costs!D32</f>
-        <v>5472.7174125</v>
+        <v>5207.9674125</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">Costs!E24+Costs!E25+Costs!E26+Costs!E27+Costs!E28+Costs!E29+Costs!E30+Costs!E32</f>
-        <v>2899.295802625</v>
+        <v>2634.545802625</v>
       </c>
       <c r="F14" s="6" t="n">
         <f aca="false">Costs!F24+Costs!F25+Costs!F26+Costs!F27+Costs!F28+Costs!F29+Costs!F30+Costs!F32</f>
-        <v>2903.32719104625</v>
+        <v>2638.57719104625</v>
       </c>
       <c r="G14" s="6" t="n">
         <f aca="false">Costs!G24+Costs!G25+Costs!G26+Costs!G27+Costs!G28+Costs!G29+Costs!G30+Costs!G32</f>
-        <v>4478.73171781486</v>
+        <v>4213.98171781486</v>
       </c>
       <c r="H14" s="6" t="n">
         <f aca="false">Costs!H24+Costs!H25+Costs!H26+Costs!H27+Costs!H28+Costs!H29+Costs!H30+Costs!H32</f>
-        <v>2379.54312878042</v>
+        <v>2114.79312878042</v>
       </c>
       <c r="I14" s="6" t="n">
         <f aca="false">Costs!I24+Costs!I25+Costs!I26+Costs!I27+Costs!I28+Costs!I29+Costs!I30+Costs!I32</f>
-        <v>841.187553417004</v>
+        <v>540.650053417004</v>
       </c>
       <c r="J14" s="6" t="n">
         <f aca="false">Costs!J24+Costs!J25+Costs!J26+Costs!J27+Costs!J28+Costs!J29+Costs!J30+Costs!J32</f>
-        <v>842.090054314494</v>
+        <v>541.552554314494</v>
       </c>
       <c r="K14" s="6" t="n">
         <f aca="false">Costs!K24+Costs!K25+Costs!K26+Costs!K27+Costs!K28+Costs!K29+Costs!K30+Costs!K32</f>
-        <v>843.038192185059</v>
+        <v>578.288192185059</v>
       </c>
       <c r="L14" s="6" t="n">
         <f aca="false">Costs!L24+Costs!L25+Costs!L26+Costs!L27+Costs!L28+Costs!L29+Costs!L30+Costs!L32</f>
-        <v>841.176025919507</v>
+        <v>576.426025919507</v>
       </c>
       <c r="M14" s="6" t="n">
         <f aca="false">Costs!M24+Costs!M25+Costs!M26+Costs!M27+Costs!M28+Costs!M29+Costs!M30+Costs!M32</f>
-        <v>842.215612641922</v>
+        <v>577.465612641922</v>
       </c>
       <c r="N14" s="6" t="n">
         <f aca="false">Costs!N24+Costs!N25+Costs!N26+Costs!N27+Costs!N28+Costs!N29+Costs!N30+Costs!N32</f>
-        <v>7142.96780776267</v>
+        <v>578.217807762665</v>
       </c>
       <c r="O14" s="6" t="n">
         <f aca="false">Costs!O24+Costs!O25+Costs!O26+Costs!O27+Costs!O28+Costs!O29+Costs!O30+Costs!O32</f>
-        <v>957.143604310135</v>
+        <v>794.643604310135</v>
       </c>
       <c r="P14" s="6" t="n">
         <f aca="false">Costs!P24+Costs!P25+Costs!P26+Costs!P27+Costs!P28+Costs!P29+Costs!P30+Costs!P32</f>
-        <v>958.399944780831</v>
+        <v>795.89994478083</v>
       </c>
       <c r="Q14" s="6" t="n">
         <f aca="false">Costs!Q24+Costs!Q25+Costs!Q26+Costs!Q27+Costs!Q28+Costs!Q29+Costs!Q30+Costs!Q32</f>
-        <v>959.765045437405</v>
+        <v>797.265045437405</v>
       </c>
       <c r="R14" s="6" t="n">
         <f aca="false">Costs!R24+Costs!R25+Costs!R26+Costs!R27+Costs!R28+Costs!R29+Costs!R30+Costs!R32</f>
-        <v>961.238642274283</v>
+        <v>798.738642274283</v>
       </c>
       <c r="S14" s="6" t="n">
         <f aca="false">Costs!S24+Costs!S25+Costs!S26+Costs!S27+Costs!S28+Costs!S29+Costs!S30+Costs!S32</f>
-        <v>962.820479206055</v>
+        <v>800.320479206055</v>
       </c>
       <c r="T14" s="6" t="n">
         <f aca="false">Costs!T24+Costs!T25+Costs!T26+Costs!T27+Costs!T28+Costs!T29+Costs!T30+Costs!T32</f>
-        <v>964.510307829873</v>
+        <v>802.010307829873</v>
       </c>
       <c r="U14" s="6" t="n">
         <f aca="false">Costs!U24+Costs!U25+Costs!U26+Costs!U27+Costs!U28+Costs!U29+Costs!U30+Costs!U32</f>
-        <v>966.307887194977</v>
+        <v>803.807887194977</v>
       </c>
       <c r="V14" s="6" t="n">
         <f aca="false">Costs!V24+Costs!V25+Costs!V26+Costs!V27+Costs!V28+Costs!V29+Costs!V30+Costs!V32</f>
-        <v>968.212983579128</v>
+        <v>805.712983579128</v>
       </c>
       <c r="W14" s="6" t="n">
         <f aca="false">Costs!W24+Costs!W25+Costs!W26+Costs!W27+Costs!W28+Costs!W29+Costs!W30+Costs!W32</f>
-        <v>970.125410271754</v>
+        <v>807.625410271754</v>
       </c>
       <c r="X14" s="6" t="n">
         <f aca="false">Costs!X24+Costs!X25+Costs!X26+Costs!X27+Costs!X28+Costs!X29+Costs!X30+Costs!X32</f>
-        <v>972.044947363601</v>
+        <v>809.544947363601</v>
       </c>
       <c r="Y14" s="6" t="n">
         <f aca="false">Costs!Y24+Costs!Y25+Costs!Y26+Costs!Y27+Costs!Y28+Costs!Y29+Costs!Y30+Costs!Y32</f>
-        <v>973.971381542693</v>
+        <v>811.471381542693</v>
       </c>
       <c r="Z14" s="6" t="n">
         <f aca="false">Costs!Z24+Costs!Z25+Costs!Z26+Costs!Z27+Costs!Z28+Costs!Z29+Costs!Z30+Costs!Z32</f>
-        <v>975.904505896413</v>
+        <v>813.404505896413</v>
       </c>
       <c r="AA14" s="6" t="n">
         <f aca="false">Costs!AA24+Costs!AA25+Costs!AA26+Costs!AA27+Costs!AA28+Costs!AA29+Costs!AA30+Costs!AA32</f>
-        <v>1221.80332424368</v>
+        <v>1059.30332424368</v>
       </c>
       <c r="AB14" s="6" t="n">
         <f aca="false">Costs!AB24+Costs!AB25+Costs!AB26+Costs!AB27+Costs!AB28+Costs!AB29+Costs!AB30+Costs!AB32</f>
-        <v>1224.30911632637</v>
+        <v>7361.80911632637</v>
       </c>
       <c r="AC14" s="6" t="n">
         <f aca="false">Costs!AC24+Costs!AC25+Costs!AC26+Costs!AC27+Costs!AC28+Costs!AC29+Costs!AC30+Costs!AC32</f>
-        <v>1226.87154390658</v>
+        <v>1064.37154390658</v>
       </c>
       <c r="AD14" s="6" t="n">
         <f aca="false">Costs!AD24+Costs!AD25+Costs!AD26+Costs!AD27+Costs!AD28+Costs!AD29+Costs!AD30+Costs!AD32</f>
-        <v>1229.49048228938</v>
+        <v>1066.99048228938</v>
       </c>
       <c r="AE14" s="6" t="n">
         <f aca="false">Costs!AE24+Costs!AE25+Costs!AE26+Costs!AE27+Costs!AE28+Costs!AE29+Costs!AE30+Costs!AE32</f>
-        <v>1232.1658105207</v>
+        <v>1069.6658105207</v>
       </c>
       <c r="AF14" s="6" t="n">
         <f aca="false">Costs!AF24+Costs!AF25+Costs!AF26+Costs!AF27+Costs!AF28+Costs!AF29+Costs!AF30+Costs!AF32</f>
-        <v>1234.89741127508</v>
+        <v>1072.39741127508</v>
       </c>
       <c r="AG14" s="6" t="n">
         <f aca="false">Costs!AG24+Costs!AG25+Costs!AG26+Costs!AG27+Costs!AG28+Costs!AG29+Costs!AG30+Costs!AG32</f>
-        <v>1237.68517074682</v>
+        <v>1075.18517074682</v>
       </c>
       <c r="AH14" s="6" t="n">
         <f aca="false">Costs!AH24+Costs!AH25+Costs!AH26+Costs!AH27+Costs!AH28+Costs!AH29+Costs!AH30+Costs!AH32</f>
-        <v>1240.52897854442</v>
+        <v>1078.02897854442</v>
       </c>
       <c r="AI14" s="6" t="n">
         <f aca="false">Costs!AI24+Costs!AI25+Costs!AI26+Costs!AI27+Costs!AI28+Costs!AI29+Costs!AI30+Costs!AI32</f>
-        <v>1243.37624858809</v>
+        <v>1080.87624858809</v>
       </c>
       <c r="AJ14" s="6" t="n">
         <f aca="false">Costs!AJ24+Costs!AJ25+Costs!AJ26+Costs!AJ27+Costs!AJ28+Costs!AJ29+Costs!AJ30+Costs!AJ32</f>
-        <v>1246.22687701044</v>
+        <v>1083.72687701044</v>
       </c>
       <c r="AK14" s="6" t="n">
         <f aca="false">Costs!AK24+Costs!AK25+Costs!AK26+Costs!AK27+Costs!AK28+Costs!AK29+Costs!AK30+Costs!AK32</f>
-        <v>1249.08076306013</v>
+        <v>1086.58076306013</v>
       </c>
       <c r="AL14" s="6" t="n">
         <f aca="false">Costs!AL24+Costs!AL25+Costs!AL26+Costs!AL27+Costs!AL28+Costs!AL29+Costs!AL30+Costs!AL32</f>
-        <v>1251.93780900833</v>
+        <v>1089.43780900833</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="40" t="n">
         <f aca="false">C10-C12-C13-C14</f>
-        <v>-7817.25</v>
+        <v>-5407.5</v>
       </c>
       <c r="D15" s="40" t="n">
         <f aca="false">D10-D12-D13-D14</f>
-        <v>-9745.5906625</v>
+        <v>-7335.8406625</v>
       </c>
       <c r="E15" s="40" t="n">
         <f aca="false">E10-E12-E13-E14</f>
-        <v>-8027.706105125</v>
+        <v>-5617.956105125</v>
       </c>
       <c r="F15" s="40" t="n">
         <f aca="false">F10-F12-F13-F14</f>
-        <v>-7656.01543447125</v>
+        <v>-5246.26543447125</v>
       </c>
       <c r="G15" s="40" t="n">
         <f aca="false">G10-G12-G13-G14</f>
-        <v>-9082.45116393711</v>
+        <v>-6672.70116393711</v>
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">H10-H12-H13-H14</f>
-        <v>-6813.823241519</v>
+        <v>-4404.073241519</v>
       </c>
       <c r="I15" s="40" t="n">
         <f aca="false">I10-I12-I13-I14</f>
-        <v>-5823.49863277343</v>
+        <v>-2662.21113277343</v>
       </c>
       <c r="J15" s="40" t="n">
         <f aca="false">J10-J12-J13-J14</f>
-        <v>-5658.37935129023</v>
+        <v>-2497.09185129023</v>
       </c>
       <c r="K15" s="40" t="n">
         <f aca="false">K10-K12-K13-K14</f>
-        <v>-5494.98060025152</v>
+        <v>-3085.23060025152</v>
       </c>
       <c r="L15" s="40" t="n">
         <f aca="false">L10-L12-L13-L14</f>
-        <v>-5273.30475174397</v>
+        <v>-2863.55475174397</v>
       </c>
       <c r="M15" s="40" t="n">
         <f aca="false">M10-M12-M13-M14</f>
-        <v>-5113.28282669165</v>
+        <v>-2703.53282669165</v>
       </c>
       <c r="N15" s="40" t="n">
         <f aca="false">N10-N12-N13-N14</f>
-        <v>-11247.9212753909</v>
+        <v>-2538.17127539091</v>
       </c>
       <c r="O15" s="40" t="n">
         <f aca="false">O10-O12-O13-O14</f>
-        <v>-7043.38580316671</v>
+        <v>-6780.88580316671</v>
       </c>
       <c r="P15" s="40" t="n">
         <f aca="false">P10-P12-P13-P14</f>
-        <v>-6687.27659967171</v>
+        <v>-6424.77659967171</v>
       </c>
       <c r="Q15" s="40" t="n">
         <f aca="false">Q10-Q12-Q13-Q14</f>
-        <v>-6329.93213068156</v>
+        <v>-6067.43213068156</v>
       </c>
       <c r="R15" s="40" t="n">
         <f aca="false">R10-R12-R13-R14</f>
-        <v>-5971.45242896111</v>
+        <v>-5708.95242896111</v>
       </c>
       <c r="S15" s="40" t="n">
         <f aca="false">S10-S12-S13-S14</f>
-        <v>-5611.93452629228</v>
+        <v>-5349.43452629228</v>
       </c>
       <c r="T15" s="40" t="n">
         <f aca="false">T10-T12-T13-T14</f>
-        <v>-5251.47254350351</v>
+        <v>-4988.97254350351</v>
       </c>
       <c r="U15" s="40" t="n">
         <f aca="false">U10-U12-U13-U14</f>
-        <v>-4890.1577777984</v>
+        <v>-4627.6577777984</v>
       </c>
       <c r="V15" s="40" t="n">
         <f aca="false">V10-V12-V13-V14</f>
-        <v>-4528.07878746445</v>
+        <v>-4265.57878746445</v>
       </c>
       <c r="W15" s="40" t="n">
         <f aca="false">W10-W12-W13-W14</f>
-        <v>-4163.22231404052</v>
+        <v>-3900.72231404052</v>
       </c>
       <c r="X15" s="40" t="n">
         <f aca="false">X10-X12-X13-X14</f>
-        <v>-3795.6716820193</v>
+        <v>-3533.1716820193</v>
       </c>
       <c r="Y15" s="40" t="n">
         <f aca="false">Y10-Y12-Y13-Y14</f>
-        <v>-3425.50771615872</v>
+        <v>-3163.00771615872</v>
       </c>
       <c r="Z15" s="40" t="n">
         <f aca="false">Z10-Z12-Z13-Z14</f>
-        <v>-3052.80881647396</v>
+        <v>-2790.30881647396</v>
       </c>
       <c r="AA15" s="40" t="n">
         <f aca="false">AA10-AA12-AA13-AA14</f>
-        <v>-7432.94055183052</v>
+        <v>-7170.44055183052</v>
       </c>
       <c r="AB15" s="40" t="n">
         <f aca="false">AB10-AB12-AB13-AB14</f>
-        <v>-6842.8787257856</v>
+        <v>-12880.3787257856</v>
       </c>
       <c r="AC15" s="40" t="n">
         <f aca="false">AC10-AC12-AC13-AC14</f>
-        <v>-6252.29514898203</v>
+        <v>-5989.79514898203</v>
       </c>
       <c r="AD15" s="40" t="n">
         <f aca="false">AD10-AD12-AD13-AD14</f>
-        <v>-5661.23853571258</v>
+        <v>-5398.73853571258</v>
       </c>
       <c r="AE15" s="40" t="n">
         <f aca="false">AE10-AE12-AE13-AE14</f>
-        <v>-5069.7561388412</v>
+        <v>-4807.2561388412</v>
       </c>
       <c r="AF15" s="40" t="n">
         <f aca="false">AF10-AF12-AF13-AF14</f>
-        <v>-4477.89379364596</v>
+        <v>-4215.39379364596</v>
       </c>
       <c r="AG15" s="40" t="n">
         <f aca="false">AG10-AG12-AG13-AG14</f>
-        <v>-3885.69596034658</v>
+        <v>-3623.19596034658</v>
       </c>
       <c r="AH15" s="40" t="n">
         <f aca="false">AH10-AH12-AH13-AH14</f>
-        <v>-3293.20576535619</v>
+        <v>-3030.70576535619</v>
       </c>
       <c r="AI15" s="40" t="n">
         <f aca="false">AI10-AI12-AI13-AI14</f>
-        <v>-2699.3629822955</v>
+        <v>-2436.8629822955</v>
       </c>
       <c r="AJ15" s="40" t="n">
         <f aca="false">AJ10-AJ12-AJ13-AJ14</f>
-        <v>-2104.20818880664</v>
+        <v>-1841.70818880664</v>
       </c>
       <c r="AK15" s="40" t="n">
         <f aca="false">AK10-AK12-AK13-AK14</f>
-        <v>-1507.78074520243</v>
+        <v>-1245.28074520243</v>
       </c>
       <c r="AL15" s="40" t="n">
         <f aca="false">AL10-AL12-AL13-AL14</f>
-        <v>-910.11883098636</v>
+        <v>-647.61883098636</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>61</v>
@@ -13695,7 +13716,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>61</v>
@@ -13847,154 +13868,154 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C18" s="40" t="n">
         <f aca="false">C15-C17</f>
-        <v>-7817.25</v>
+        <v>-5407.5</v>
       </c>
       <c r="D18" s="40" t="n">
         <f aca="false">D15-D17</f>
-        <v>-9747.4054125</v>
+        <v>-7337.6554125</v>
       </c>
       <c r="E18" s="40" t="n">
         <f aca="false">E15-E17</f>
-        <v>-8031.281162625</v>
+        <v>-5621.531162625</v>
       </c>
       <c r="F18" s="40" t="n">
         <f aca="false">F15-F17</f>
-        <v>-7664.15399024625</v>
+        <v>-5254.40399024625</v>
       </c>
       <c r="G18" s="40" t="n">
         <f aca="false">G15-G17</f>
-        <v>-9092.16031303886</v>
+        <v>-6682.41031303886</v>
       </c>
       <c r="H18" s="40" t="n">
         <f aca="false">H15-H17</f>
-        <v>-6825.3890661477</v>
+        <v>-4415.6390661477</v>
       </c>
       <c r="I18" s="40" t="n">
         <f aca="false">I15-I17</f>
-        <v>-5836.91303266327</v>
+        <v>-2675.62553266327</v>
       </c>
       <c r="J18" s="40" t="n">
         <f aca="false">J15-J17</f>
-        <v>-5673.63446918337</v>
+        <v>-2512.34696918337</v>
       </c>
       <c r="K18" s="40" t="n">
         <f aca="false">K15-K17</f>
-        <v>-5512.06881460787</v>
+        <v>-3102.31881460787</v>
       </c>
       <c r="L18" s="40" t="n">
         <f aca="false">L15-L17</f>
-        <v>-5292.21866966963</v>
+        <v>-2882.46866966963</v>
       </c>
       <c r="M18" s="40" t="n">
         <f aca="false">M15-M17</f>
-        <v>-5134.01527707954</v>
+        <v>-2724.26527707954</v>
       </c>
       <c r="N18" s="40" t="n">
         <f aca="false">N15-N17</f>
-        <v>-11270.4653022672</v>
+        <v>-2560.71530226716</v>
       </c>
       <c r="O18" s="40" t="n">
         <f aca="false">O15-O17</f>
-        <v>-7068.95210204017</v>
+        <v>-6806.45210204017</v>
       </c>
       <c r="P18" s="40" t="n">
         <f aca="false">P15-P17</f>
-        <v>-6716.66782207897</v>
+        <v>-6454.16782207896</v>
       </c>
       <c r="Q18" s="40" t="n">
         <f aca="false">Q15-Q17</f>
-        <v>-6363.1834689166</v>
+        <v>-6100.6834689166</v>
       </c>
       <c r="R18" s="40" t="n">
         <f aca="false">R15-R17</f>
-        <v>-6008.5980195491</v>
+        <v>-5746.0980195491</v>
       </c>
       <c r="S18" s="40" t="n">
         <f aca="false">S15-S17</f>
-        <v>-5653.00748166262</v>
+        <v>-5390.50748166262</v>
       </c>
       <c r="T18" s="40" t="n">
         <f aca="false">T15-T17</f>
-        <v>-5296.50498271275</v>
+        <v>-5034.00498271275</v>
       </c>
       <c r="U18" s="40" t="n">
         <f aca="false">U15-U17</f>
-        <v>-4939.18085633136</v>
+        <v>-4676.68085633136</v>
       </c>
       <c r="V18" s="40" t="n">
         <f aca="false">V15-V17</f>
-        <v>-4581.12272614142</v>
+        <v>-4318.62272614142</v>
       </c>
       <c r="W18" s="40" t="n">
         <f aca="false">W15-W17</f>
-        <v>-4220.31642705718</v>
+        <v>-3957.81642705718</v>
       </c>
       <c r="X18" s="40" t="n">
         <f aca="false">X15-X17</f>
-        <v>-3856.84440414546</v>
+        <v>-3594.34440414546</v>
       </c>
       <c r="Y18" s="40" t="n">
         <f aca="false">Y15-Y17</f>
-        <v>-3490.7866291211</v>
+        <v>-3228.2866291211</v>
       </c>
       <c r="Z18" s="40" t="n">
         <f aca="false">Z15-Z17</f>
-        <v>-3122.22067454747</v>
+        <v>-2859.72067454747</v>
       </c>
       <c r="AA18" s="40" t="n">
         <f aca="false">AA15-AA17</f>
-        <v>-7510.18984440339</v>
+        <v>-7247.68984440339</v>
       </c>
       <c r="AB18" s="40" t="n">
         <f aca="false">AB15-AB17</f>
-        <v>-6926.55485295628</v>
+        <v>-12964.0548529563</v>
       </c>
       <c r="AC18" s="40" t="n">
         <f aca="false">AC15-AC17</f>
-        <v>-6342.4152217126</v>
+        <v>-6079.9152217126</v>
       </c>
       <c r="AD18" s="40" t="n">
         <f aca="false">AD15-AD17</f>
-        <v>-5757.81915163622</v>
+        <v>-5495.31915163622</v>
       </c>
       <c r="AE18" s="40" t="n">
         <f aca="false">AE15-AE17</f>
-        <v>-5172.81339766213</v>
+        <v>-4910.31339766213</v>
       </c>
       <c r="AF18" s="40" t="n">
         <f aca="false">AF15-AF17</f>
-        <v>-4587.44331207727</v>
+        <v>-4324.94331207727</v>
       </c>
       <c r="AG18" s="40" t="n">
         <f aca="false">AG15-AG17</f>
-        <v>-4001.75288659995</v>
+        <v>-3739.25288659995</v>
       </c>
       <c r="AH18" s="40" t="n">
         <f aca="false">AH15-AH17</f>
-        <v>-3415.78479319695</v>
+        <v>-3153.28479319695</v>
       </c>
       <c r="AI18" s="40" t="n">
         <f aca="false">AI15-AI17</f>
-        <v>-2828.47836467604</v>
+        <v>-2565.97836467604</v>
       </c>
       <c r="AJ18" s="40" t="n">
         <f aca="false">AJ15-AJ17</f>
-        <v>-2239.87375109076</v>
+        <v>-1977.37375109076</v>
       </c>
       <c r="AK18" s="40" t="n">
         <f aca="false">AK15-AK17</f>
-        <v>-1650.00989799304</v>
+        <v>-1387.50989799304</v>
       </c>
       <c r="AL18" s="40" t="n">
         <f aca="false">AL15-AL17</f>
-        <v>-1058.92458256825</v>
+        <v>-796.424582568245</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14039,7 +14060,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B20" s="15"/>
       <c r="C20" s="15"/>
@@ -14081,7 +14102,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>61</v>
@@ -14092,155 +14113,155 @@
       </c>
       <c r="D21" s="39" t="n">
         <f aca="false">C23</f>
-        <v>142182.75</v>
+        <v>94592.5</v>
       </c>
       <c r="E21" s="39" t="n">
         <f aca="false">D23</f>
-        <v>132435.3445875</v>
+        <v>87254.8445875</v>
       </c>
       <c r="F21" s="39" t="n">
         <f aca="false">E23</f>
-        <v>124404.063424875</v>
+        <v>81633.313424875</v>
       </c>
       <c r="G21" s="39" t="n">
         <f aca="false">F23</f>
-        <v>116739.909434629</v>
+        <v>76378.9094346288</v>
       </c>
       <c r="H21" s="39" t="n">
         <f aca="false">G23</f>
-        <v>107647.74912159</v>
+        <v>69696.4991215899</v>
       </c>
       <c r="I21" s="39" t="n">
         <f aca="false">H23</f>
-        <v>100822.360055442</v>
+        <v>65280.8600554422</v>
       </c>
       <c r="J21" s="39" t="n">
         <f aca="false">I23</f>
-        <v>94985.4470227789</v>
+        <v>62605.2345227789</v>
       </c>
       <c r="K21" s="39" t="n">
         <f aca="false">J23</f>
-        <v>89311.8125535956</v>
+        <v>60092.8875535955</v>
       </c>
       <c r="L21" s="39" t="n">
         <f aca="false">K23</f>
-        <v>83799.7437389877</v>
+        <v>56990.5687389877</v>
       </c>
       <c r="M21" s="39" t="n">
         <f aca="false">L23</f>
-        <v>78507.5250693181</v>
+        <v>54108.1000693181</v>
       </c>
       <c r="N21" s="39" t="n">
         <f aca="false">M23</f>
-        <v>73373.5097922385</v>
+        <v>51383.8347922385</v>
       </c>
       <c r="O21" s="39" t="n">
         <f aca="false">N23</f>
-        <v>62103.0444899714</v>
+        <v>48823.1194899714</v>
       </c>
       <c r="P21" s="39" t="n">
         <f aca="false">O23</f>
-        <v>55034.0923879312</v>
+        <v>42016.6673879312</v>
       </c>
       <c r="Q21" s="39" t="n">
         <f aca="false">P23</f>
-        <v>48317.4245658522</v>
+        <v>35562.4995658522</v>
       </c>
       <c r="R21" s="39" t="n">
         <f aca="false">Q23</f>
-        <v>41954.2410969356</v>
+        <v>29461.8160969356</v>
       </c>
       <c r="S21" s="39" t="n">
         <f aca="false">R23</f>
-        <v>35945.6430773865</v>
+        <v>23715.7180773865</v>
       </c>
       <c r="T21" s="39" t="n">
         <f aca="false">S23</f>
-        <v>30292.6355957239</v>
+        <v>18325.2105957239</v>
       </c>
       <c r="U21" s="39" t="n">
         <f aca="false">T23</f>
-        <v>24996.1306130112</v>
+        <v>13291.2056130112</v>
       </c>
       <c r="V21" s="39" t="n">
         <f aca="false">U23</f>
-        <v>20056.9497566798</v>
+        <v>8614.5247566798</v>
       </c>
       <c r="W21" s="39" t="n">
         <f aca="false">V23</f>
-        <v>15475.8270305384</v>
+        <v>4295.90203053838</v>
       </c>
       <c r="X21" s="39" t="n">
         <f aca="false">W23</f>
-        <v>11255.5106034812</v>
+        <v>338.085603481202</v>
       </c>
       <c r="Y21" s="39" t="n">
         <f aca="false">X23</f>
-        <v>7398.66619933575</v>
+        <v>-3256.25880066426</v>
       </c>
       <c r="Z21" s="39" t="n">
         <f aca="false">Y23</f>
-        <v>3907.87957021465</v>
+        <v>-6484.54542978536</v>
       </c>
       <c r="AA21" s="39" t="n">
         <f aca="false">Z23</f>
-        <v>785.658895667184</v>
+        <v>-9344.26610433283</v>
       </c>
       <c r="AB21" s="39" t="n">
         <f aca="false">AA23</f>
-        <v>-6724.5309487362</v>
+        <v>-16591.9559487362</v>
       </c>
       <c r="AC21" s="39" t="n">
         <f aca="false">AB23</f>
-        <v>-13651.0858016925</v>
+        <v>-29556.0108016925</v>
       </c>
       <c r="AD21" s="39" t="n">
         <f aca="false">AC23</f>
-        <v>-19993.5010234051</v>
+        <v>-35635.9260234051</v>
       </c>
       <c r="AE21" s="39" t="n">
         <f aca="false">AD23</f>
-        <v>-25751.3201750413</v>
+        <v>-41131.2451750413</v>
       </c>
       <c r="AF21" s="39" t="n">
         <f aca="false">AE23</f>
-        <v>-30924.1335727034</v>
+        <v>-46041.5585727034</v>
       </c>
       <c r="AG21" s="39" t="n">
         <f aca="false">AF23</f>
-        <v>-35511.5768847807</v>
+        <v>-50366.5018847807</v>
       </c>
       <c r="AH21" s="39" t="n">
         <f aca="false">AG23</f>
-        <v>-39513.3297713806</v>
+        <v>-54105.7547713807</v>
       </c>
       <c r="AI21" s="39" t="n">
         <f aca="false">AH23</f>
-        <v>-42929.1145645776</v>
+        <v>-57259.0395645776</v>
       </c>
       <c r="AJ21" s="39" t="n">
         <f aca="false">AI23</f>
-        <v>-45757.5929292536</v>
+        <v>-59825.0179292537</v>
       </c>
       <c r="AK21" s="39" t="n">
         <f aca="false">AJ23</f>
-        <v>-47997.4666803444</v>
+        <v>-61802.3916803444</v>
       </c>
       <c r="AL21" s="39" t="n">
         <f aca="false">AK23</f>
-        <v>-49647.4765783374</v>
+        <v>-63189.9015783374</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="39" t="n">
         <f aca="false">IF(C$3=in_FundingMonth,in_Round,0)</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D22" s="39" t="n">
         <f aca="false">IF(D$3=in_FundingMonth,in_Round,0)</f>
@@ -14385,466 +14406,466 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B23" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="40" t="n">
         <f aca="false">C21+C22+C18</f>
-        <v>142182.75</v>
+        <v>94592.5</v>
       </c>
       <c r="D23" s="40" t="n">
         <f aca="false">D21+D22+D18</f>
-        <v>132435.3445875</v>
+        <v>87254.8445875</v>
       </c>
       <c r="E23" s="40" t="n">
         <f aca="false">E21+E22+E18</f>
-        <v>124404.063424875</v>
+        <v>81633.313424875</v>
       </c>
       <c r="F23" s="40" t="n">
         <f aca="false">F21+F22+F18</f>
-        <v>116739.909434629</v>
+        <v>76378.9094346288</v>
       </c>
       <c r="G23" s="40" t="n">
         <f aca="false">G21+G22+G18</f>
-        <v>107647.74912159</v>
+        <v>69696.4991215899</v>
       </c>
       <c r="H23" s="40" t="n">
         <f aca="false">H21+H22+H18</f>
-        <v>100822.360055442</v>
+        <v>65280.8600554422</v>
       </c>
       <c r="I23" s="40" t="n">
         <f aca="false">I21+I22+I18</f>
-        <v>94985.4470227789</v>
+        <v>62605.2345227789</v>
       </c>
       <c r="J23" s="40" t="n">
         <f aca="false">J21+J22+J18</f>
-        <v>89311.8125535956</v>
+        <v>60092.8875535955</v>
       </c>
       <c r="K23" s="40" t="n">
         <f aca="false">K21+K22+K18</f>
-        <v>83799.7437389877</v>
+        <v>56990.5687389877</v>
       </c>
       <c r="L23" s="40" t="n">
         <f aca="false">L21+L22+L18</f>
-        <v>78507.5250693181</v>
+        <v>54108.1000693181</v>
       </c>
       <c r="M23" s="40" t="n">
         <f aca="false">M21+M22+M18</f>
-        <v>73373.5097922385</v>
+        <v>51383.8347922385</v>
       </c>
       <c r="N23" s="40" t="n">
         <f aca="false">N21+N22+N18</f>
-        <v>62103.0444899714</v>
+        <v>48823.1194899714</v>
       </c>
       <c r="O23" s="40" t="n">
         <f aca="false">O21+O22+O18</f>
-        <v>55034.0923879312</v>
+        <v>42016.6673879312</v>
       </c>
       <c r="P23" s="40" t="n">
         <f aca="false">P21+P22+P18</f>
-        <v>48317.4245658522</v>
+        <v>35562.4995658522</v>
       </c>
       <c r="Q23" s="40" t="n">
         <f aca="false">Q21+Q22+Q18</f>
-        <v>41954.2410969356</v>
+        <v>29461.8160969356</v>
       </c>
       <c r="R23" s="40" t="n">
         <f aca="false">R21+R22+R18</f>
-        <v>35945.6430773865</v>
+        <v>23715.7180773865</v>
       </c>
       <c r="S23" s="40" t="n">
         <f aca="false">S21+S22+S18</f>
-        <v>30292.6355957239</v>
+        <v>18325.2105957239</v>
       </c>
       <c r="T23" s="40" t="n">
         <f aca="false">T21+T22+T18</f>
-        <v>24996.1306130112</v>
+        <v>13291.2056130112</v>
       </c>
       <c r="U23" s="40" t="n">
         <f aca="false">U21+U22+U18</f>
-        <v>20056.9497566798</v>
+        <v>8614.5247566798</v>
       </c>
       <c r="V23" s="40" t="n">
         <f aca="false">V21+V22+V18</f>
-        <v>15475.8270305384</v>
+        <v>4295.90203053838</v>
       </c>
       <c r="W23" s="40" t="n">
         <f aca="false">W21+W22+W18</f>
-        <v>11255.5106034812</v>
+        <v>338.085603481202</v>
       </c>
       <c r="X23" s="40" t="n">
         <f aca="false">X21+X22+X18</f>
-        <v>7398.66619933575</v>
+        <v>-3256.25880066426</v>
       </c>
       <c r="Y23" s="40" t="n">
         <f aca="false">Y21+Y22+Y18</f>
-        <v>3907.87957021465</v>
+        <v>-6484.54542978536</v>
       </c>
       <c r="Z23" s="40" t="n">
         <f aca="false">Z21+Z22+Z18</f>
-        <v>785.658895667184</v>
+        <v>-9344.26610433283</v>
       </c>
       <c r="AA23" s="40" t="n">
         <f aca="false">AA21+AA22+AA18</f>
-        <v>-6724.5309487362</v>
+        <v>-16591.9559487362</v>
       </c>
       <c r="AB23" s="40" t="n">
         <f aca="false">AB21+AB22+AB18</f>
-        <v>-13651.0858016925</v>
+        <v>-29556.0108016925</v>
       </c>
       <c r="AC23" s="40" t="n">
         <f aca="false">AC21+AC22+AC18</f>
-        <v>-19993.5010234051</v>
+        <v>-35635.9260234051</v>
       </c>
       <c r="AD23" s="40" t="n">
         <f aca="false">AD21+AD22+AD18</f>
-        <v>-25751.3201750413</v>
+        <v>-41131.2451750413</v>
       </c>
       <c r="AE23" s="40" t="n">
         <f aca="false">AE21+AE22+AE18</f>
-        <v>-30924.1335727034</v>
+        <v>-46041.5585727034</v>
       </c>
       <c r="AF23" s="40" t="n">
         <f aca="false">AF21+AF22+AF18</f>
-        <v>-35511.5768847807</v>
+        <v>-50366.5018847807</v>
       </c>
       <c r="AG23" s="40" t="n">
         <f aca="false">AG21+AG22+AG18</f>
-        <v>-39513.3297713806</v>
+        <v>-54105.7547713807</v>
       </c>
       <c r="AH23" s="40" t="n">
         <f aca="false">AH21+AH22+AH18</f>
-        <v>-42929.1145645776</v>
+        <v>-57259.0395645776</v>
       </c>
       <c r="AI23" s="40" t="n">
         <f aca="false">AI21+AI22+AI18</f>
-        <v>-45757.5929292536</v>
+        <v>-59825.0179292537</v>
       </c>
       <c r="AJ23" s="40" t="n">
         <f aca="false">AJ21+AJ22+AJ18</f>
-        <v>-47997.4666803444</v>
+        <v>-61802.3916803444</v>
       </c>
       <c r="AK23" s="40" t="n">
         <f aca="false">AK21+AK22+AK18</f>
-        <v>-49647.4765783374</v>
+        <v>-63189.9015783374</v>
       </c>
       <c r="AL23" s="40" t="n">
         <f aca="false">AL21+AL22+AL18</f>
-        <v>-50706.4011609057</v>
+        <v>-63986.3261609057</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="39" t="n">
         <f aca="false">Costs!C34</f>
-        <v>7817.25</v>
+        <v>5407.5</v>
       </c>
       <c r="D24" s="39" t="n">
         <f aca="false">C24+Costs!D34</f>
-        <v>17744.3156625</v>
+        <v>12924.8156625</v>
       </c>
       <c r="E24" s="39" t="n">
         <f aca="false">D24+Costs!E34</f>
-        <v>26129.527517625</v>
+        <v>18900.277517625</v>
       </c>
       <c r="F24" s="39" t="n">
         <f aca="false">E24+Costs!F34</f>
-        <v>34599.3985295963</v>
+        <v>24960.3985295963</v>
       </c>
       <c r="G24" s="39" t="n">
         <f aca="false">F24+Costs!G34</f>
-        <v>44652.7646037084</v>
+        <v>32604.0146037084</v>
       </c>
       <c r="H24" s="39" t="n">
         <f aca="false">G24+Costs!H34</f>
-        <v>52623.1703080971</v>
+        <v>38164.6703080971</v>
       </c>
       <c r="I24" s="39" t="n">
         <f aca="false">H24+Costs!I34</f>
-        <v>59788.1089298542</v>
+        <v>42168.3214298542</v>
       </c>
       <c r="J24" s="39" t="n">
         <f aca="false">I24+Costs!J34</f>
-        <v>66972.0000704586</v>
+        <v>46190.9250704586</v>
       </c>
       <c r="K24" s="39" t="n">
         <f aca="false">J24+Costs!K34</f>
-        <v>74175.8021063448</v>
+        <v>50984.9771063448</v>
       </c>
       <c r="L24" s="39" t="n">
         <f aca="false">K24+Costs!L34</f>
-        <v>81340.4986506545</v>
+        <v>55739.9236506545</v>
       </c>
       <c r="M24" s="39" t="n">
         <f aca="false">L24+Costs!M34</f>
-        <v>88527.0265161348</v>
+        <v>60516.7015161348</v>
       </c>
       <c r="N24" s="39" t="n">
         <f aca="false">M24+Costs!N34</f>
-        <v>102029.350479151</v>
+        <v>65309.2754791508</v>
       </c>
       <c r="O24" s="39" t="n">
         <f aca="false">N24+Costs!O34</f>
-        <v>111629.366169664</v>
+        <v>74646.7911696636</v>
       </c>
       <c r="P24" s="39" t="n">
         <f aca="false">O24+Costs!P34</f>
-        <v>121255.765010061</v>
+        <v>84010.6900100611</v>
       </c>
       <c r="Q24" s="39" t="n">
         <f aca="false">P24+Costs!Q34</f>
-        <v>130910.830964247</v>
+        <v>93403.2559642466</v>
       </c>
       <c r="R24" s="39" t="n">
         <f aca="false">Q24+Costs!R34</f>
-        <v>140596.842452007</v>
+        <v>102826.767452007</v>
       </c>
       <c r="S24" s="39" t="n">
         <f aca="false">R24+Costs!S34</f>
-        <v>150316.072515334</v>
+        <v>112283.497515334</v>
       </c>
       <c r="T24" s="39" t="n">
         <f aca="false">S24+Costs!T34</f>
-        <v>160070.788979761</v>
+        <v>121775.713979761</v>
       </c>
       <c r="U24" s="39" t="n">
         <f aca="false">T24+Costs!U34</f>
-        <v>169863.254610856</v>
+        <v>131305.679610856</v>
       </c>
       <c r="V24" s="39" t="n">
         <f aca="false">U24+Costs!V34</f>
-        <v>179695.727266017</v>
+        <v>140875.652266017</v>
       </c>
       <c r="W24" s="39" t="n">
         <f aca="false">V24+Costs!W34</f>
-        <v>189568.360881724</v>
+        <v>150485.785881724</v>
       </c>
       <c r="X24" s="39" t="n">
         <f aca="false">W24+Costs!X34</f>
-        <v>199481.30477636</v>
+        <v>160136.22977636</v>
       </c>
       <c r="Y24" s="39" t="n">
         <f aca="false">X24+Costs!Y34</f>
-        <v>209434.703788756</v>
+        <v>169827.128788756</v>
       </c>
       <c r="Z24" s="39" t="n">
         <f aca="false">Y24+Costs!Z34</f>
-        <v>219428.698412581</v>
+        <v>179558.623412581</v>
       </c>
       <c r="AA24" s="39" t="n">
         <f aca="false">Z24+Costs!AA34</f>
-        <v>234586.568221698</v>
+        <v>194453.993221698</v>
       </c>
       <c r="AB24" s="39" t="n">
         <f aca="false">AA24+Costs!AB34</f>
-        <v>249797.059664552</v>
+        <v>215701.984664552</v>
       </c>
       <c r="AC24" s="39" t="n">
         <f aca="false">AB24+Costs!AC34</f>
-        <v>265061.36208659</v>
+        <v>230703.78708659</v>
       </c>
       <c r="AD24" s="39" t="n">
         <f aca="false">AC24+Costs!AD34</f>
-        <v>280380.662214667</v>
+        <v>245760.587214667</v>
       </c>
       <c r="AE24" s="39" t="n">
         <f aca="false">AD24+Costs!AE34</f>
-        <v>295756.144235601</v>
+        <v>260873.569235601</v>
       </c>
       <c r="AF24" s="39" t="n">
         <f aca="false">AE24+Costs!AF34</f>
-        <v>311188.989872378</v>
+        <v>276043.914872378</v>
       </c>
       <c r="AG24" s="39" t="n">
         <f aca="false">AF24+Costs!AG34</f>
-        <v>326680.378458061</v>
+        <v>291272.803458061</v>
       </c>
       <c r="AH24" s="39" t="n">
         <f aca="false">AG24+Costs!AH34</f>
-        <v>342231.487007494</v>
+        <v>306561.412007494</v>
       </c>
       <c r="AI24" s="39" t="n">
         <f aca="false">AH24+Costs!AI34</f>
-        <v>357842.388227844</v>
+        <v>321909.813227844</v>
       </c>
       <c r="AJ24" s="39" t="n">
         <f aca="false">AI24+Costs!AJ34</f>
-        <v>373513.152645063</v>
+        <v>337318.077645063</v>
       </c>
       <c r="AK24" s="39" t="n">
         <f aca="false">AJ24+Costs!AK34</f>
-        <v>389243.848669326</v>
+        <v>352786.273669326</v>
       </c>
       <c r="AL24" s="39" t="n">
         <f aca="false">AK24+Costs!AL34</f>
-        <v>405034.542658501</v>
+        <v>368314.467658501</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="39" t="n">
         <f aca="false">C18</f>
-        <v>-7817.25</v>
+        <v>-5407.5</v>
       </c>
       <c r="D25" s="39" t="n">
         <f aca="false">C25+D18</f>
-        <v>-17564.6554125</v>
+        <v>-12745.1554125</v>
       </c>
       <c r="E25" s="39" t="n">
         <f aca="false">D25+E18</f>
-        <v>-25595.936575125</v>
+        <v>-18366.686575125</v>
       </c>
       <c r="F25" s="39" t="n">
         <f aca="false">E25+F18</f>
-        <v>-33260.0905653713</v>
+        <v>-23621.0905653713</v>
       </c>
       <c r="G25" s="39" t="n">
         <f aca="false">F25+G18</f>
-        <v>-42352.2508784101</v>
+        <v>-30303.5008784101</v>
       </c>
       <c r="H25" s="39" t="n">
         <f aca="false">G25+H18</f>
-        <v>-49177.6399445578</v>
+        <v>-34719.1399445578</v>
       </c>
       <c r="I25" s="39" t="n">
         <f aca="false">H25+I18</f>
-        <v>-55014.5529772211</v>
+        <v>-37394.7654772211</v>
       </c>
       <c r="J25" s="39" t="n">
         <f aca="false">I25+J18</f>
-        <v>-60688.1874464044</v>
+        <v>-39907.1124464044</v>
       </c>
       <c r="K25" s="39" t="n">
         <f aca="false">J25+K18</f>
-        <v>-66200.2562610123</v>
+        <v>-43009.4312610123</v>
       </c>
       <c r="L25" s="39" t="n">
         <f aca="false">K25+L18</f>
-        <v>-71492.4749306819</v>
+        <v>-45891.8999306819</v>
       </c>
       <c r="M25" s="39" t="n">
         <f aca="false">L25+M18</f>
-        <v>-76626.4902077615</v>
+        <v>-48616.1652077615</v>
       </c>
       <c r="N25" s="39" t="n">
         <f aca="false">M25+N18</f>
-        <v>-87896.9555100286</v>
+        <v>-51176.8805100286</v>
       </c>
       <c r="O25" s="39" t="n">
         <f aca="false">N25+O18</f>
-        <v>-94965.9076120688</v>
+        <v>-57983.3326120688</v>
       </c>
       <c r="P25" s="39" t="n">
         <f aca="false">O25+P18</f>
-        <v>-101682.575434148</v>
+        <v>-64437.5004341478</v>
       </c>
       <c r="Q25" s="39" t="n">
         <f aca="false">P25+Q18</f>
-        <v>-108045.758903064</v>
+        <v>-70538.1839030644</v>
       </c>
       <c r="R25" s="39" t="n">
         <f aca="false">Q25+R18</f>
-        <v>-114054.356922613</v>
+        <v>-76284.2819226135</v>
       </c>
       <c r="S25" s="39" t="n">
         <f aca="false">R25+S18</f>
-        <v>-119707.364404276</v>
+        <v>-81674.7894042761</v>
       </c>
       <c r="T25" s="39" t="n">
         <f aca="false">S25+T18</f>
-        <v>-125003.869386989</v>
+        <v>-86708.7943869888</v>
       </c>
       <c r="U25" s="39" t="n">
         <f aca="false">T25+U18</f>
-        <v>-129943.05024332</v>
+        <v>-91385.4752433202</v>
       </c>
       <c r="V25" s="39" t="n">
         <f aca="false">U25+V18</f>
-        <v>-134524.172969462</v>
+        <v>-95704.0979694616</v>
       </c>
       <c r="W25" s="39" t="n">
         <f aca="false">V25+W18</f>
-        <v>-138744.489396519</v>
+        <v>-99661.9143965188</v>
       </c>
       <c r="X25" s="39" t="n">
         <f aca="false">W25+X18</f>
-        <v>-142601.333800664</v>
+        <v>-103256.258800664</v>
       </c>
       <c r="Y25" s="39" t="n">
         <f aca="false">X25+Y18</f>
-        <v>-146092.120429785</v>
+        <v>-106484.545429785</v>
       </c>
       <c r="Z25" s="39" t="n">
         <f aca="false">Y25+Z18</f>
-        <v>-149214.341104333</v>
+        <v>-109344.266104333</v>
       </c>
       <c r="AA25" s="39" t="n">
         <f aca="false">Z25+AA18</f>
-        <v>-156724.530948736</v>
+        <v>-116591.955948736</v>
       </c>
       <c r="AB25" s="39" t="n">
         <f aca="false">AA25+AB18</f>
-        <v>-163651.085801693</v>
+        <v>-129556.010801693</v>
       </c>
       <c r="AC25" s="39" t="n">
         <f aca="false">AB25+AC18</f>
-        <v>-169993.501023405</v>
+        <v>-135635.926023405</v>
       </c>
       <c r="AD25" s="39" t="n">
         <f aca="false">AC25+AD18</f>
-        <v>-175751.320175041</v>
+        <v>-141131.245175041</v>
       </c>
       <c r="AE25" s="39" t="n">
         <f aca="false">AD25+AE18</f>
-        <v>-180924.133572703</v>
+        <v>-146041.558572703</v>
       </c>
       <c r="AF25" s="39" t="n">
         <f aca="false">AE25+AF18</f>
-        <v>-185511.576884781</v>
+        <v>-150366.501884781</v>
       </c>
       <c r="AG25" s="39" t="n">
         <f aca="false">AF25+AG18</f>
-        <v>-189513.329771381</v>
+        <v>-154105.754771381</v>
       </c>
       <c r="AH25" s="39" t="n">
         <f aca="false">AG25+AH18</f>
-        <v>-192929.114564578</v>
+        <v>-157259.039564578</v>
       </c>
       <c r="AI25" s="39" t="n">
         <f aca="false">AH25+AI18</f>
-        <v>-195757.592929254</v>
+        <v>-159825.017929254</v>
       </c>
       <c r="AJ25" s="39" t="n">
         <f aca="false">AI25+AJ18</f>
-        <v>-197997.466680344</v>
+        <v>-161802.391680344</v>
       </c>
       <c r="AK25" s="39" t="n">
         <f aca="false">AJ25+AK18</f>
-        <v>-199647.476578337</v>
+        <v>-163189.901578337</v>
       </c>
       <c r="AL25" s="39" t="n">
         <f aca="false">AK25+AL18</f>
-        <v>-200706.401160906</v>
+        <v>-163986.326160906</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C26" s="45" t="n">
         <f aca="false">IF(C23&lt;0,1,0)</f>
@@ -14932,15 +14953,15 @@
       </c>
       <c r="X26" s="45" t="n">
         <f aca="false">IF(X23&lt;0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" s="45" t="n">
         <f aca="false">IF(Y23&lt;0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z26" s="45" t="n">
         <f aca="false">IF(Z23&lt;0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" s="45" t="n">
         <f aca="false">IF(AA23&lt;0,1,0)</f>
@@ -14993,10 +15014,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B27" s="12" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C27" s="45" t="n">
         <f aca="false">IF(C18&gt;=0,1,0)</f>
@@ -15145,154 +15166,154 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="39" t="n">
         <f aca="false">C25</f>
-        <v>-7817.25</v>
+        <v>-5407.5</v>
       </c>
       <c r="D28" s="39" t="n">
         <f aca="false">MIN(C28,D25)</f>
-        <v>-17564.6554125</v>
+        <v>-12745.1554125</v>
       </c>
       <c r="E28" s="39" t="n">
         <f aca="false">MIN(D28,E25)</f>
-        <v>-25595.936575125</v>
+        <v>-18366.686575125</v>
       </c>
       <c r="F28" s="39" t="n">
         <f aca="false">MIN(E28,F25)</f>
-        <v>-33260.0905653713</v>
+        <v>-23621.0905653713</v>
       </c>
       <c r="G28" s="39" t="n">
         <f aca="false">MIN(F28,G25)</f>
-        <v>-42352.2508784101</v>
+        <v>-30303.5008784101</v>
       </c>
       <c r="H28" s="39" t="n">
         <f aca="false">MIN(G28,H25)</f>
-        <v>-49177.6399445578</v>
+        <v>-34719.1399445578</v>
       </c>
       <c r="I28" s="39" t="n">
         <f aca="false">MIN(H28,I25)</f>
-        <v>-55014.5529772211</v>
+        <v>-37394.7654772211</v>
       </c>
       <c r="J28" s="39" t="n">
         <f aca="false">MIN(I28,J25)</f>
-        <v>-60688.1874464044</v>
+        <v>-39907.1124464044</v>
       </c>
       <c r="K28" s="39" t="n">
         <f aca="false">MIN(J28,K25)</f>
-        <v>-66200.2562610123</v>
+        <v>-43009.4312610123</v>
       </c>
       <c r="L28" s="39" t="n">
         <f aca="false">MIN(K28,L25)</f>
-        <v>-71492.4749306819</v>
+        <v>-45891.8999306819</v>
       </c>
       <c r="M28" s="39" t="n">
         <f aca="false">MIN(L28,M25)</f>
-        <v>-76626.4902077615</v>
+        <v>-48616.1652077615</v>
       </c>
       <c r="N28" s="39" t="n">
         <f aca="false">MIN(M28,N25)</f>
-        <v>-87896.9555100286</v>
+        <v>-51176.8805100286</v>
       </c>
       <c r="O28" s="39" t="n">
         <f aca="false">MIN(N28,O25)</f>
-        <v>-94965.9076120688</v>
+        <v>-57983.3326120688</v>
       </c>
       <c r="P28" s="39" t="n">
         <f aca="false">MIN(O28,P25)</f>
-        <v>-101682.575434148</v>
+        <v>-64437.5004341478</v>
       </c>
       <c r="Q28" s="39" t="n">
         <f aca="false">MIN(P28,Q25)</f>
-        <v>-108045.758903064</v>
+        <v>-70538.1839030644</v>
       </c>
       <c r="R28" s="39" t="n">
         <f aca="false">MIN(Q28,R25)</f>
-        <v>-114054.356922613</v>
+        <v>-76284.2819226135</v>
       </c>
       <c r="S28" s="39" t="n">
         <f aca="false">MIN(R28,S25)</f>
-        <v>-119707.364404276</v>
+        <v>-81674.7894042761</v>
       </c>
       <c r="T28" s="39" t="n">
         <f aca="false">MIN(S28,T25)</f>
-        <v>-125003.869386989</v>
+        <v>-86708.7943869888</v>
       </c>
       <c r="U28" s="39" t="n">
         <f aca="false">MIN(T28,U25)</f>
-        <v>-129943.05024332</v>
+        <v>-91385.4752433202</v>
       </c>
       <c r="V28" s="39" t="n">
         <f aca="false">MIN(U28,V25)</f>
-        <v>-134524.172969462</v>
+        <v>-95704.0979694616</v>
       </c>
       <c r="W28" s="39" t="n">
         <f aca="false">MIN(V28,W25)</f>
-        <v>-138744.489396519</v>
+        <v>-99661.9143965188</v>
       </c>
       <c r="X28" s="39" t="n">
         <f aca="false">MIN(W28,X25)</f>
-        <v>-142601.333800664</v>
+        <v>-103256.258800664</v>
       </c>
       <c r="Y28" s="39" t="n">
         <f aca="false">MIN(X28,Y25)</f>
-        <v>-146092.120429785</v>
+        <v>-106484.545429785</v>
       </c>
       <c r="Z28" s="39" t="n">
         <f aca="false">MIN(Y28,Z25)</f>
-        <v>-149214.341104333</v>
+        <v>-109344.266104333</v>
       </c>
       <c r="AA28" s="39" t="n">
         <f aca="false">MIN(Z28,AA25)</f>
-        <v>-156724.530948736</v>
+        <v>-116591.955948736</v>
       </c>
       <c r="AB28" s="39" t="n">
         <f aca="false">MIN(AA28,AB25)</f>
-        <v>-163651.085801693</v>
+        <v>-129556.010801693</v>
       </c>
       <c r="AC28" s="39" t="n">
         <f aca="false">MIN(AB28,AC25)</f>
-        <v>-169993.501023405</v>
+        <v>-135635.926023405</v>
       </c>
       <c r="AD28" s="39" t="n">
         <f aca="false">MIN(AC28,AD25)</f>
-        <v>-175751.320175041</v>
+        <v>-141131.245175041</v>
       </c>
       <c r="AE28" s="39" t="n">
         <f aca="false">MIN(AD28,AE25)</f>
-        <v>-180924.133572703</v>
+        <v>-146041.558572703</v>
       </c>
       <c r="AF28" s="39" t="n">
         <f aca="false">MIN(AE28,AF25)</f>
-        <v>-185511.576884781</v>
+        <v>-150366.501884781</v>
       </c>
       <c r="AG28" s="39" t="n">
         <f aca="false">MIN(AF28,AG25)</f>
-        <v>-189513.329771381</v>
+        <v>-154105.754771381</v>
       </c>
       <c r="AH28" s="39" t="n">
         <f aca="false">MIN(AG28,AH25)</f>
-        <v>-192929.114564578</v>
+        <v>-157259.039564578</v>
       </c>
       <c r="AI28" s="39" t="n">
         <f aca="false">MIN(AH28,AI25)</f>
-        <v>-195757.592929254</v>
+        <v>-159825.017929254</v>
       </c>
       <c r="AJ28" s="39" t="n">
         <f aca="false">MIN(AI28,AJ25)</f>
-        <v>-197997.466680344</v>
+        <v>-161802.391680344</v>
       </c>
       <c r="AK28" s="39" t="n">
         <f aca="false">MIN(AJ28,AK25)</f>
-        <v>-199647.476578337</v>
+        <v>-163189.901578337</v>
       </c>
       <c r="AL28" s="39" t="n">
         <f aca="false">MIN(AK28,AL25)</f>
-        <v>-200706.401160906</v>
+        <v>-163986.326160906</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15337,7 +15358,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="14" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" s="15"/>
       <c r="C30" s="15"/>
@@ -15379,16 +15400,16 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="46" t="n">
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(in_Round+in_OpeningCash))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
@@ -15426,16 +15447,16 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="46" t="n">
         <f aca="false">IF(MAX('P&amp;L &amp; Cash'!$C$26:$AL$26)=0,"&gt; 36",MATCH(1,'P&amp;L &amp; Cash'!$C$26:$AL$26,0)-1)</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="12" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
@@ -15473,7 +15494,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="47" t="str">
@@ -15485,7 +15506,7 @@
         <v>-</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -15528,7 +15549,7 @@
       <c r="B34" s="1"/>
       <c r="C34" s="21" t="n">
         <f aca="false">MIN('P&amp;L &amp; Cash'!$C$23:$AL$23)</f>
-        <v>-50706.4011609057</v>
+        <v>-63986.3261609057</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="12"/>
@@ -15568,7 +15589,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B35" s="1"/>
       <c r="C35" s="47" t="n">
@@ -15616,12 +15637,12 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="21" t="n">
         <f aca="false">AL23</f>
-        <v>-50706.4011609057</v>
+        <v>-63986.3261609057</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="12"/>
@@ -15661,7 +15682,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="21" t="n">
@@ -15706,7 +15727,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="21" t="n">
@@ -15751,7 +15772,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="21" t="n">
@@ -15796,12 +15817,12 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,1,Costs!$C$34:$AL$34)</f>
-        <v>102029.350479151</v>
+        <v>65309.2754791508</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="12"/>
@@ -15841,12 +15862,12 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,2,Costs!$C$34:$AL$34)</f>
-        <v>117399.34793343</v>
+        <v>114249.34793343</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="12"/>
@@ -15886,12 +15907,12 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,3,Costs!$C$34:$AL$34)</f>
-        <v>185605.84424592</v>
+        <v>188755.84424592</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="12"/>
@@ -15931,7 +15952,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="26" t="n">
@@ -16000,14 +16021,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16019,18 +16040,18 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>47</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B5" s="39" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$28:$AL$28)</f>
@@ -16040,79 +16061,79 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B6" s="45" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$21:$AL$21)</f>
         <v>1133.42230506598</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B7" s="37" t="n">
         <f aca="false">IF(in_UE_CustMonths&gt;0,in_UE_Rev/in_UE_CustMonths,0)</f>
         <v>49.98</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B8" s="37" t="n">
         <f aca="false">in_InfraVar+in_PayFee*in_ARPA</f>
         <v>2.4996</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">IF(in_ARPA&gt;0,(in_ARPA-in_VarCost)/in_ARPA,0)</f>
         <v>0.949987995198079</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">IF(in_UE_Rev&gt;0,SUMIF(Revenue!$C$5:$AL$5,in_UEYear,'P&amp;L &amp; Cash'!$C$10:$AL$10)/in_UE_Rev,0)</f>
         <v>0.716646204822276</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,'P&amp;L &amp; Cash'!$C$13:$AL$13)</f>
-        <v>60990.3504</v>
+        <v>59790.3504</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B12" s="45" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$18:$AL$18)</f>
@@ -16122,86 +16143,86 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B13" s="39" t="n">
         <f aca="false">IF(in_UE_New&gt;0,in_UE_SnM/in_UE_New,0)</f>
-        <v>496.765224190593</v>
+        <v>486.991247403787</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">in_CostPerTrial/in_TrialConv</f>
         <v>320</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">in_Churn</f>
         <v>0.03</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B16" s="48" t="n">
         <f aca="false">IF(in_Churn&gt;0,1/in_Churn,0)</f>
         <v>33.3333333333333</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(in_Churn&gt;0,in_ARPA*in_CM/in_Churn,0)</f>
         <v>1582.68</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B18" s="49" t="n">
         <f aca="false">IF(in_CAC&gt;0,in_LTV/in_CAC,0)</f>
-        <v>3.1859718090749</v>
+        <v>3.24991467184979</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B19" s="50" t="n">
         <f aca="false">IF(in_ARPA*in_CM&gt;0,in_CAC/(in_ARPA*in_CM),0)</f>
-        <v>10.4625324173889</v>
+        <v>10.2566795436388</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
@@ -16231,7 +16252,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16241,7 +16262,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16265,24 +16286,24 @@
         <v>48</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C5" s="18" t="n">
         <v>6</v>
@@ -16294,15 +16315,15 @@
         <v>10</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C6" s="51" t="n">
         <v>2</v>
@@ -16314,12 +16335,12 @@
         <v>2.5</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>82</v>
@@ -16334,15 +16355,15 @@
         <v>0.7</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C8" s="51" t="n">
         <v>2</v>
@@ -16354,15 +16375,15 @@
         <v>3</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>189</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C9" s="51" t="n">
         <v>3</v>
@@ -16379,10 +16400,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C10" s="51" t="n">
         <v>4</v>
@@ -16399,10 +16420,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C11" s="16" t="n">
         <v>0.2</v>
@@ -16414,12 +16435,12 @@
         <v>0.3</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>82</v>
@@ -16434,15 +16455,15 @@
         <v>0.6</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C13" s="51" t="n">
         <v>4</v>
@@ -16454,15 +16475,15 @@
         <v>8</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="C14" s="51" t="n">
         <v>12</v>
@@ -16479,10 +16500,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C15" s="51" t="n">
         <v>20</v>
@@ -16499,7 +16520,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>82</v>
@@ -16514,12 +16535,12 @@
         <v>0.3</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>61</v>
@@ -16534,15 +16555,15 @@
         <v>60</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C18" s="23" t="n">
         <v>0.03</v>
@@ -16554,15 +16575,15 @@
         <v>0.02</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C19" s="23" t="n">
         <v>0.05</v>
@@ -16579,7 +16600,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>58</v>
@@ -16594,7 +16615,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16615,7 +16636,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B23" s="15"/>
       <c r="C23" s="15"/>
@@ -16625,7 +16646,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -16635,28 +16656,28 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B25" s="13" t="s">
         <v>48</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F25" s="1"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C26" s="45" t="n">
         <v>47</v>
@@ -16671,7 +16692,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>61</v>
@@ -16689,10 +16710,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C28" s="45" t="n">
         <v>139</v>
@@ -16707,7 +16728,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>61</v>
@@ -16725,10 +16746,10 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C30" s="45" t="n">
         <v>284</v>
@@ -16743,7 +16764,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>61</v>
@@ -16761,7 +16782,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>61</v>
@@ -16779,16 +16800,16 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C33" s="52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D33" s="52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E33" s="45" t="n">
         <v>22</v>
@@ -16803,37 +16824,37 @@
         <v>61</v>
       </c>
       <c r="C34" s="39" t="n">
-        <v>-50706</v>
+        <v>-63986</v>
       </c>
       <c r="D34" s="39" t="n">
-        <v>-170735</v>
+        <v>-184015</v>
       </c>
       <c r="E34" s="39" t="n">
-        <v>57773</v>
+        <v>46856</v>
       </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>61</v>
       </c>
       <c r="C35" s="39" t="n">
-        <v>-50706</v>
+        <v>-63986</v>
       </c>
       <c r="D35" s="39" t="n">
-        <v>-170735</v>
+        <v>-184015</v>
       </c>
       <c r="E35" s="39" t="n">
-        <v>188830</v>
+        <v>175550</v>
       </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>58</v>
@@ -16851,7 +16872,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>58</v>
@@ -16860,7 +16881,7 @@
         <v>20</v>
       </c>
       <c r="D37" s="52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E37" s="45" t="n">
         <v>12</v>
@@ -16869,16 +16890,16 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>58</v>
       </c>
       <c r="C38" s="52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D38" s="52" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E38" s="45" t="n">
         <v>24</v>
@@ -16912,7 +16933,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -16921,7 +16942,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="12" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -16941,7 +16962,7 @@
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">in_Round</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -16949,11 +16970,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B5" s="8" t="n">
         <f aca="false">in_RunwayZeroRev</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -16961,11 +16982,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B6" s="41" t="n">
         <f aca="false">INDEX(Revenue!$C$4:$AL$4,1,B5)</f>
-        <v>46844</v>
+        <v>46813</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -16980,172 +17001,172 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>82</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B9" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$8:$AL$8)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$9:$AL$9)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$12:$AL$12)</f>
-        <v>33129</v>
+        <v>6441.75</v>
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B9/$B$16*$B$4,0)</f>
-        <v>35344.6771160335</v>
+        <v>6896.70818591785</v>
       </c>
       <c r="D9" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C9/$B$4,0)</f>
-        <v>0.235631180773557</v>
+        <v>0.0689670818591786</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B10" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$10:$AL$10)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$22:$AL$22)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$23:$AL$23)</f>
-        <v>24509.832</v>
+        <v>20469.6192</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B10/$B$16*$B$4,0)</f>
-        <v>26149.0566635946</v>
+        <v>21915.3165365407</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C10/$B$4,0)</f>
-        <v>0.174327044423964</v>
+        <v>0.219153165365407</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$11:$AL$11)</f>
-        <v>7300.65</v>
+        <v>5117.6125</v>
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B11/$B$16*$B$4,0)</f>
-        <v>7788.91958668145</v>
+        <v>5479.05150325696</v>
       </c>
       <c r="D11" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C11/$B$4,0)</f>
-        <v>0.0519261305778764</v>
+        <v>0.0547905150325696</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B12" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$21:$AL$21)</f>
-        <v>28000</v>
+        <v>25500</v>
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B12/$B$16*$B$4,0)</f>
-        <v>29872.6481103848</v>
+        <v>27300.9754710918</v>
       </c>
       <c r="D12" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C12/$B$4,0)</f>
-        <v>0.199150987402565</v>
+        <v>0.273009754710918</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B13" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$27:$AL$27)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$28:$AL$28)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$29:$AL$29)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$30:$AL$30)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$25:$AL$25)</f>
-        <v>23600</v>
+        <v>17500</v>
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B13/$B$16*$B$4,0)</f>
-        <v>25178.3748358958</v>
+        <v>18735.9635585924</v>
       </c>
       <c r="D13" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C13/$B$4,0)</f>
-        <v>0.167855832239305</v>
+        <v>0.187359635585924</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$17:$AL$17)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$18:$AL$18)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$19:$AL$19)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$20:$AL$20)</f>
-        <v>10962.2727161967</v>
+        <v>10176.500170711</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B14/$B$16*$B$4,0)</f>
-        <v>11695.4326907506</v>
+        <v>10895.2306487115</v>
       </c>
       <c r="D14" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C14/$B$4,0)</f>
-        <v>0.0779695512716704</v>
+        <v>0.108952306487115</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$24:$AL$24)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$26:$AL$26)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$32:$AL$32)</f>
-        <v>13095.0877358098</v>
+        <v>8197.77409353555</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B15/$B$16*$B$4,0)</f>
-        <v>13970.8909966594</v>
+        <v>8776.75409588884</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C15/$B$4,0)</f>
-        <v>0.0931392733110625</v>
+        <v>0.0877675409588885</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B16" s="53" t="n">
         <f aca="false">SUM(B9:B15)</f>
-        <v>140596.842452007</v>
+        <v>93403.2559642466</v>
       </c>
       <c r="C16" s="53" t="n">
         <f aca="false">SUM(C9:C15)</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="D16" s="54" t="n">
         <f aca="false">SUM(D9:D15)</f>
@@ -17162,7 +17183,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
@@ -17171,13 +17192,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D19" s="13" t="s">
         <v>14</v>
@@ -17186,59 +17207,59 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B20" s="19" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="C20" s="48" t="n">
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B20+in_OpeningCash))</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D20" s="48" t="n">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B20+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B20+in_OpeningCash)))</f>
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B21" s="6" t="n">
         <f aca="false">in_Round</f>
-        <v>150000</v>
+        <v>100000</v>
       </c>
       <c r="C21" s="48" t="n">
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B21+in_OpeningCash))</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="48" t="n">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B21+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B21+in_OpeningCash)))</f>
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E21" s="1"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B22" s="19" t="n">
-        <v>200000</v>
+        <v>150000</v>
       </c>
       <c r="C22" s="48" t="n">
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B22+in_OpeningCash))</f>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D22" s="48" t="n">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B22+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B22+in_OpeningCash)))</f>
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E22" s="1"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -17254,7 +17275,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="14" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B25" s="15"/>
       <c r="C25" s="15"/>
@@ -17264,7 +17285,7 @@
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="str">
         <f aca="false">"Round: €"&amp;TEXT(in_Round,"#,##0")&amp;" = Vest Ventures accelerator ticket (published range €10,000-200,000); Vest Ventures is the only investor in this round."</f>
-        <v>Round: €150,000 = Vest Ventures accelerator ticket (published range €10,000-200,000); Vest Ventures is the only investor in this round.</v>
+        <v>Round: €100,000 = Vest Ventures accelerator ticket (published range €10,000-200,000); Vest Ventures is the only investor in this round.</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -17274,7 +17295,7 @@
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="str">
         <f aca="false">"Zero-revenue runway: "&amp;in_RunwayZeroRev&amp;" months - the round alone pays every planned cost even if no customer ever pays."</f>
-        <v>Zero-revenue runway: 16 months - the round alone pays every planned cost even if no customer ever pays.</v>
+        <v>Zero-revenue runway: 15 months - the round alone pays every planned cost even if no customer ever pays.</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -17284,7 +17305,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="str">
         <f aca="false">IF(in_CashLow&lt;0,"On the selected scenario cash lasts "&amp;in_RunwayPlan&amp;" months on plan without further funding; the seed round is raised from the 100-paying-customer milestone (model month "&amp;in_M100&amp;").","On the selected scenario cash never falls below €"&amp;TEXT(in_CashLow,"#,##0")&amp;"; break-even in model month "&amp;in_Breakeven&amp;".")</f>
-        <v>On the selected scenario cash lasts 24 months on plan without further funding; the seed round is raised from the 100-paying-customer milestone (model month 20).</v>
+        <v>On the selected scenario cash lasts 21 months on plan without further funding; the seed round is raised from the 100-paying-customer milestone (model month 20).</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -17303,8 +17324,8 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="str">
-        <f aca="false">"Why this size: the round funds the path to the seed trigger (100 paying firms, model month "&amp;in_M100&amp;") with "&amp;in_RunwayPlan&amp;" months of runway on plan, on a lean cost plan: co-founders at €"&amp;TEXT(in_SalFounder,"#,##0")&amp;" gross, partner manager at "&amp;TEXT(in_SalesFTE,"0%")&amp;" until model month "&amp;in_SalesFullStart&amp;" (partner signings scaled to the manager's hours), support specialist at "&amp;TEXT(in_SupportFTE,"0%")&amp;" from model month "&amp;in_SupportStart&amp;", developer after the seed (model month "&amp;in_DevStart&amp;")."</f>
-        <v>Why this size: the round funds the path to the seed trigger (100 paying firms, model month 20) with 24 months of runway on plan, on a lean cost plan: co-founders at €1,000 gross, partner manager at 50% until model month 13 (partner signings scaled to the manager's hours), support specialist at 50% from model month 7, developer after the seed (model month 25).</v>
+        <f aca="false">"Why this size: the round funds the path to the seed trigger (100 paying firms, model month "&amp;in_M100&amp;") with "&amp;in_RunwayPlan&amp;" months of runway on plan, on a lean cost plan: co-founders unpaid until model month "&amp;in_FounderPayStart&amp;", then €"&amp;TEXT(in_SalFounder,"#,##0")&amp;" gross, partner manager at "&amp;TEXT(in_SalesFTE,"0%")&amp;" until model month "&amp;in_SalesFullStart&amp;" (partner signings scaled to the manager's hours), support specialist at "&amp;TEXT(in_SupportFTE,"0%")&amp;" from model month "&amp;in_SupportStart&amp;", developer after the seed (model month "&amp;in_DevStart&amp;")."</f>
+        <v>Why this size: the round funds the path to the seed trigger (100 paying firms, model month 20) with 21 months of runway on plan, on a lean cost plan: co-founders unpaid until model month 13, then €1,000 gross, partner manager at 50% until model month 13 (partner signings scaled to the manager's hours), support specialist at 50% from model month 9, developer after the seed (model month 25).</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -17314,7 +17335,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="str">
         <f aca="false">"A smaller ticket (€"&amp;TEXT(B20,"#,##0")&amp;") gives "&amp;C20&amp;" months with zero revenue and "&amp;D20&amp;" on plan"&amp;IF(AND(ISNUMBER(D20),ISNUMBER(in_M100)),IF(D20&lt;in_M100," - cash runs out before the seed trigger."," - with little margin before the seed trigger."),".")</f>
-        <v>A smaller ticket (€100,000) gives 11 months with zero revenue and 13 on plan - cash runs out before the seed trigger.</v>
+        <v>A smaller ticket (€75,000) gives 13 months with zero revenue and 15 on plan - cash runs out before the seed trigger.</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -17323,8 +17344,8 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="str">
-        <f aca="false">"The Vest Ventures maximum (€"&amp;TEXT(B22,"#,##0")&amp;") buys "&amp;C22&amp;" months with zero revenue and "&amp;D22&amp;" on plan: more runway than the lean plan needs to reach the seed trigger."</f>
-        <v>The Vest Ventures maximum (€200,000) buys 22 months with zero revenue and 35 on plan: more runway than the lean plan needs to reach the seed trigger.</v>
+        <f aca="false">"A larger ticket (€"&amp;TEXT(B22,"#,##0")&amp;") would buy "&amp;C22&amp;" months with zero revenue and "&amp;D22&amp;" on plan on the same lean plan: more than the plan needs, so we ask for the smallest ticket that reaches the seed trigger."</f>
+        <v>A larger ticket (€150,000) would buy 20 months with zero revenue and 29 on plan on the same lean plan: more than the plan needs, so we ask for the smallest ticket that reaches the seed trigger.</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -17356,7 +17377,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B1" s="1"/>
     </row>
@@ -17366,98 +17387,98 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>

--- a/vestventures/financial-model.xlsx
+++ b/vestventures/financial-model.xlsx
@@ -145,7 +145,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="414">
   <si>
     <t xml:space="preserve">ADMINISTRATIVO - financial model (pre-seed)</t>
   </si>
@@ -693,7 +693,7 @@
     <t xml:space="preserve">practices</t>
   </si>
   <si>
-    <t xml:space="preserve">Pilot offers 10 places, sign-up until 15 Nov 2026 (administrativo.ro/pentru-contabili). Zero signed on 6 Oct 2026 -&gt; base assumes 6. ASSUMPTION.</t>
+    <t xml:space="preserve">Pilot offers 10 places, sign-up until 15 Nov 2026 (administrativo.ro/pentru-contabili). Zero signed on 6 Oct 2026 (2 qualified conversations) -&gt; base assumes 8, conservative 6. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Client companies per pilot practice</t>
@@ -729,7 +729,7 @@
     <t xml:space="preserve">Firms referred per active partner per month</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20 = one referral every 5 months per partner. No sourced figure for clients per accountant. ASSUMPTION.</t>
+    <t xml:space="preserve">0.25 = one referral every 4 months per partner. No sourced figure for clients per accountant. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Referred firm -&gt; paying customer</t>
@@ -771,7 +771,7 @@
     <t xml:space="preserve">% / month</t>
   </si>
   <si>
-    <t xml:space="preserve">ChartMogul median 6.1%/mo for ARPA &lt; US$25; our ARPA ~US$50 sits in a better band. 3% base / 5% conservative / 2% upside: ASSUMPTION, to be tested in the pilot.</t>
+    <t xml:space="preserve">ChartMogul median 6.1%/mo for ARPA &lt; US$25; our ARPA ~US$50 sits in a better band. 2.5% base / 3% conservative / 2% upside: ASSUMPTION, to be tested in the pilot.</t>
   </si>
   <si>
     <t xml:space="preserve">Annual list-price / upsell increase (from year 2)</t>
@@ -783,7 +783,7 @@
     <t xml:space="preserve">Month the developer is hired</t>
   </si>
   <si>
-    <t xml:space="preserve">AFTER the seed: seed raise starts at 100 paying customers (in_M100), ~5-6 months to close. Base Jan 2029; Upside Jul 2028 (100 customers sooner); Conservative Jul 2029 (seed trigger not reached - deliberately late). Not funded by the pre-seed. ASSUMPTION.</t>
+    <t xml:space="preserve">AFTER the seed: seed conversations start at 100 paying customers (in_M100) or earlier, ~5-6 months to close. Base and Conservative Jan 2029; Upside Jul 2028 (100 customers sooner). Not funded by the pre-seed. ASSUMPTION.</t>
   </si>
   <si>
     <t xml:space="preserve">Revenue - customers, MRR, ARR (PROJECTION, selected scenario)</t>
@@ -2020,9 +2020,9 @@
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="n">
+      <c r="C15" s="8" t="str">
         <f aca="false">in_RunwayPlan</f>
-        <v>21</v>
+        <v>&gt; 36</v>
       </c>
       <c r="D15" s="1"/>
     </row>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="C16" s="5" t="str">
         <f aca="false">TEXT(Revenue!N21,"0")&amp;" / "&amp;TEXT(Revenue!Z21,"0")&amp;" / "&amp;TEXT(Revenue!AL21,"0")</f>
-        <v>47 / 139 / 284</v>
+        <v>71 / 212 / 448</v>
       </c>
       <c r="D16" s="1"/>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="C17" s="6" t="n">
         <f aca="false">Revenue!N26</f>
-        <v>2254.40268762505</v>
+        <v>3378.0056948639</v>
       </c>
       <c r="D17" s="1"/>
     </row>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">Revenue!Z26</f>
-        <v>6941.1858073507</v>
+        <v>10751.0530555363</v>
       </c>
       <c r="D18" s="1"/>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C19" s="6" t="n">
         <f aca="false">Revenue!AL26</f>
-        <v>14880.5751581885</v>
+        <v>24204.3460469995</v>
       </c>
       <c r="D19" s="1"/>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="C20" s="6" t="n">
         <f aca="false">Revenue!AL27</f>
-        <v>178566.901898262</v>
+        <v>290452.152563994</v>
       </c>
       <c r="D20" s="1"/>
     </row>
@@ -2086,9 +2086,9 @@
       <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="9" t="str">
+      <c r="C21" s="9" t="n">
         <f aca="false">in_Breakeven</f>
-        <v>not within 36 months</v>
+        <v>24</v>
       </c>
       <c r="D21" s="1"/>
     </row>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="C22" s="6" t="n">
         <f aca="false">in_CashLow</f>
-        <v>-63986.3261609057</v>
+        <v>9624.04666332409</v>
       </c>
       <c r="D22" s="1"/>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="C23" s="5" t="str">
         <f aca="false">in_M30&amp;" / "&amp;in_M100&amp;" / "&amp;in_M300</f>
-        <v>8 / 20 / not within 36 months</v>
+        <v>5 / 16 / 29</v>
       </c>
       <c r="D23" s="1"/>
     </row>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C24" s="5" t="str">
         <f aca="false">"€"&amp;TEXT(in_ARPA,"0")&amp;" / €"&amp;TEXT(in_LTV,"#,##0")&amp;" / €"&amp;TEXT(in_CAC,"#,##0")</f>
-        <v>€50 / €1,583 / €487</v>
+        <v>€51 / €1,927 / €339</v>
       </c>
       <c r="D24" s="1"/>
     </row>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C25" s="5" t="str">
         <f aca="false">TEXT(in_LTVCAC,"0.0")&amp;"x, "&amp;TEXT(in_Payback,"0.0")&amp;" months"</f>
-        <v>3.2x, 10.3 months</v>
+        <v>5.7x, 7.0 months</v>
       </c>
       <c r="D25" s="1"/>
     </row>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="B95" s="9" t="n">
         <f aca="false">INDEX(Scenarios!$C$5:$E$5,1,ScenarioIdx)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>181</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B96" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$6:$E$6,1,ScenarioIdx)</f>
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>184</v>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="B97" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$7:$E$7,1,ScenarioIdx)</f>
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>82</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B98" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$8:$E$8,1,ScenarioIdx)</f>
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>189</v>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B99" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$9:$E$9,1,ScenarioIdx)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>189</v>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B100" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$10:$E$10,1,ScenarioIdx)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>189</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="B101" s="30" t="n">
         <f aca="false">INDEX(Scenarios!$C$11:$E$11,1,ScenarioIdx)</f>
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>184</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="B102" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$12:$E$12,1,ScenarioIdx)</f>
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>82</v>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="B103" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$13:$E$13,1,ScenarioIdx)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>198</v>
@@ -3572,7 +3572,7 @@
       </c>
       <c r="B104" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$14:$E$14,1,ScenarioIdx)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>198</v>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B105" s="28" t="n">
         <f aca="false">INDEX(Scenarios!$C$15:$E$15,1,ScenarioIdx)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>198</v>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B106" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$16:$E$16,1,ScenarioIdx)</f>
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>82</v>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="B107" s="6" t="n">
         <f aca="false">INDEX(Scenarios!$C$17:$E$17,1,ScenarioIdx)</f>
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>61</v>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B108" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$18:$E$18,1,ScenarioIdx)</f>
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>207</v>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="B109" s="29" t="n">
         <f aca="false">INDEX(Scenarios!$C$19:$E$19,1,ScenarioIdx)</f>
-        <v>0.05</v>
+        <v>0.065</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>210</v>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="F8" s="33" t="n">
         <f aca="false">IF(F$3=in_PilotConvMonth,in_PilotPractices*in_PilotFirmsPerPractice*in_PilotConv,0)</f>
-        <v>6</v>
+        <v>10.8</v>
       </c>
       <c r="G8" s="33" t="n">
         <f aca="false">IF(G$3=in_PilotConvMonth,in_PilotPractices*in_PilotFirmsPerPractice*in_PilotConv,0)</f>
@@ -4483,135 +4483,135 @@
       </c>
       <c r="F9" s="33" t="n">
         <f aca="false">IF(F$3&gt;=in_PartnerStart,CHOOSE(F$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(F$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G9" s="33" t="n">
         <f aca="false">IF(G$3&gt;=in_PartnerStart,CHOOSE(G$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(G$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="H9" s="33" t="n">
         <f aca="false">IF(H$3&gt;=in_PartnerStart,CHOOSE(H$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(H$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="I9" s="33" t="n">
         <f aca="false">IF(I$3&gt;=in_PartnerStart,CHOOSE(I$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(I$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="J9" s="33" t="n">
         <f aca="false">IF(J$3&gt;=in_PartnerStart,CHOOSE(J$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(J$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="K9" s="33" t="n">
         <f aca="false">IF(K$3&gt;=in_PartnerStart,CHOOSE(K$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(K$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L9" s="33" t="n">
         <f aca="false">IF(L$3&gt;=in_PartnerStart,CHOOSE(L$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(L$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="M9" s="33" t="n">
         <f aca="false">IF(M$3&gt;=in_PartnerStart,CHOOSE(M$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(M$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="N9" s="33" t="n">
         <f aca="false">IF(N$3&gt;=in_PartnerStart,CHOOSE(N$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(N$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="O9" s="33" t="n">
         <f aca="false">IF(O$3&gt;=in_PartnerStart,CHOOSE(O$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(O$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" s="33" t="n">
         <f aca="false">IF(P$3&gt;=in_PartnerStart,CHOOSE(P$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(P$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q9" s="33" t="n">
         <f aca="false">IF(Q$3&gt;=in_PartnerStart,CHOOSE(Q$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(Q$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R9" s="33" t="n">
         <f aca="false">IF(R$3&gt;=in_PartnerStart,CHOOSE(R$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(R$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S9" s="33" t="n">
         <f aca="false">IF(S$3&gt;=in_PartnerStart,CHOOSE(S$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(S$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T9" s="33" t="n">
         <f aca="false">IF(T$3&gt;=in_PartnerStart,CHOOSE(T$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(T$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U9" s="33" t="n">
         <f aca="false">IF(U$3&gt;=in_PartnerStart,CHOOSE(U$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(U$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V9" s="33" t="n">
         <f aca="false">IF(V$3&gt;=in_PartnerStart,CHOOSE(V$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(V$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W9" s="33" t="n">
         <f aca="false">IF(W$3&gt;=in_PartnerStart,CHOOSE(W$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(W$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X9" s="33" t="n">
         <f aca="false">IF(X$3&gt;=in_PartnerStart,CHOOSE(X$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(X$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y9" s="33" t="n">
         <f aca="false">IF(Y$3&gt;=in_PartnerStart,CHOOSE(Y$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(Y$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z9" s="33" t="n">
         <f aca="false">IF(Z$3&gt;=in_PartnerStart,CHOOSE(Z$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(Z$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA9" s="33" t="n">
         <f aca="false">IF(AA$3&gt;=in_PartnerStart,CHOOSE(AA$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AA$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AB9" s="33" t="n">
         <f aca="false">IF(AB$3&gt;=in_PartnerStart,CHOOSE(AB$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AB$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC9" s="33" t="n">
         <f aca="false">IF(AC$3&gt;=in_PartnerStart,CHOOSE(AC$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AC$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD9" s="33" t="n">
         <f aca="false">IF(AD$3&gt;=in_PartnerStart,CHOOSE(AD$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AD$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE9" s="33" t="n">
         <f aca="false">IF(AE$3&gt;=in_PartnerStart,CHOOSE(AE$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AE$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF9" s="33" t="n">
         <f aca="false">IF(AF$3&gt;=in_PartnerStart,CHOOSE(AF$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AF$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG9" s="33" t="n">
         <f aca="false">IF(AG$3&gt;=in_PartnerStart,CHOOSE(AG$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AG$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH9" s="33" t="n">
         <f aca="false">IF(AH$3&gt;=in_PartnerStart,CHOOSE(AH$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AH$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI9" s="33" t="n">
         <f aca="false">IF(AI$3&gt;=in_PartnerStart,CHOOSE(AI$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AI$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ9" s="33" t="n">
         <f aca="false">IF(AJ$3&gt;=in_PartnerStart,CHOOSE(AJ$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AJ$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK9" s="33" t="n">
         <f aca="false">IF(AK$3&gt;=in_PartnerStart,CHOOSE(AK$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AK$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL9" s="33" t="n">
         <f aca="false">IF(AL$3&gt;=in_PartnerStart,CHOOSE(AL$5,in_NewPartnersY1,in_NewPartnersY2,in_NewPartnersY3)*IF(AL$3&gt;=in_SalesFullStart,1,in_SalesFTE),0)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4635,135 +4635,135 @@
       </c>
       <c r="F10" s="33" t="n">
         <f aca="false">E10+F9+IF(F$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>7</v>
+        <v>9.25</v>
       </c>
       <c r="G10" s="33" t="n">
         <f aca="false">F10+G9+IF(G$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="H10" s="33" t="n">
         <f aca="false">G10+H9+IF(H$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>9</v>
+        <v>11.75</v>
       </c>
       <c r="I10" s="33" t="n">
         <f aca="false">H10+I9+IF(I$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J10" s="33" t="n">
         <f aca="false">I10+J9+IF(J$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>11</v>
+        <v>14.25</v>
       </c>
       <c r="K10" s="33" t="n">
         <f aca="false">J10+K9+IF(K$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="L10" s="33" t="n">
         <f aca="false">K10+L9+IF(L$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>13</v>
+        <v>16.75</v>
       </c>
       <c r="M10" s="33" t="n">
         <f aca="false">L10+M9+IF(M$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="N10" s="33" t="n">
         <f aca="false">M10+N9+IF(N$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>15</v>
+        <v>19.25</v>
       </c>
       <c r="O10" s="33" t="n">
         <f aca="false">N10+O9+IF(O$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>18</v>
+        <v>23.25</v>
       </c>
       <c r="P10" s="33" t="n">
         <f aca="false">O10+P9+IF(P$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>21</v>
+        <v>27.25</v>
       </c>
       <c r="Q10" s="33" t="n">
         <f aca="false">P10+Q9+IF(Q$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>24</v>
+        <v>31.25</v>
       </c>
       <c r="R10" s="33" t="n">
         <f aca="false">Q10+R9+IF(R$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>27</v>
+        <v>35.25</v>
       </c>
       <c r="S10" s="33" t="n">
         <f aca="false">R10+S9+IF(S$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>30</v>
+        <v>39.25</v>
       </c>
       <c r="T10" s="33" t="n">
         <f aca="false">S10+T9+IF(T$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>33</v>
+        <v>43.25</v>
       </c>
       <c r="U10" s="33" t="n">
         <f aca="false">T10+U9+IF(U$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>36</v>
+        <v>47.25</v>
       </c>
       <c r="V10" s="33" t="n">
         <f aca="false">U10+V9+IF(V$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>39</v>
+        <v>51.25</v>
       </c>
       <c r="W10" s="33" t="n">
         <f aca="false">V10+W9+IF(W$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>42</v>
+        <v>55.25</v>
       </c>
       <c r="X10" s="33" t="n">
         <f aca="false">W10+X9+IF(X$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>45</v>
+        <v>59.25</v>
       </c>
       <c r="Y10" s="33" t="n">
         <f aca="false">X10+Y9+IF(Y$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>48</v>
+        <v>63.25</v>
       </c>
       <c r="Z10" s="33" t="n">
         <f aca="false">Y10+Z9+IF(Z$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>51</v>
+        <v>67.25</v>
       </c>
       <c r="AA10" s="33" t="n">
         <f aca="false">Z10+AA9+IF(AA$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>55</v>
+        <v>72.25</v>
       </c>
       <c r="AB10" s="33" t="n">
         <f aca="false">AA10+AB9+IF(AB$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>59</v>
+        <v>77.25</v>
       </c>
       <c r="AC10" s="33" t="n">
         <f aca="false">AB10+AC9+IF(AC$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>63</v>
+        <v>82.25</v>
       </c>
       <c r="AD10" s="33" t="n">
         <f aca="false">AC10+AD9+IF(AD$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>67</v>
+        <v>87.25</v>
       </c>
       <c r="AE10" s="33" t="n">
         <f aca="false">AD10+AE9+IF(AE$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>71</v>
+        <v>92.25</v>
       </c>
       <c r="AF10" s="33" t="n">
         <f aca="false">AE10+AF9+IF(AF$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>75</v>
+        <v>97.25</v>
       </c>
       <c r="AG10" s="33" t="n">
         <f aca="false">AF10+AG9+IF(AG$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>79</v>
+        <v>102.25</v>
       </c>
       <c r="AH10" s="33" t="n">
         <f aca="false">AG10+AH9+IF(AH$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>83</v>
+        <v>107.25</v>
       </c>
       <c r="AI10" s="33" t="n">
         <f aca="false">AH10+AI9+IF(AI$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>87</v>
+        <v>112.25</v>
       </c>
       <c r="AJ10" s="33" t="n">
         <f aca="false">AI10+AJ9+IF(AJ$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>91</v>
+        <v>117.25</v>
       </c>
       <c r="AK10" s="33" t="n">
         <f aca="false">AJ10+AK9+IF(AK$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>95</v>
+        <v>122.25</v>
       </c>
       <c r="AL10" s="33" t="n">
         <f aca="false">AK10+AL9+IF(AL$3=in_PilotConvMonth,in_PilotPractices,0)</f>
-        <v>99</v>
+        <v>127.25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4791,131 +4791,131 @@
       </c>
       <c r="G11" s="33" t="n">
         <f aca="false">F10*in_RefRate</f>
-        <v>1.4</v>
+        <v>2.3125</v>
       </c>
       <c r="H11" s="33" t="n">
         <f aca="false">G10*in_RefRate</f>
-        <v>1.6</v>
+        <v>2.625</v>
       </c>
       <c r="I11" s="33" t="n">
         <f aca="false">H10*in_RefRate</f>
-        <v>1.8</v>
+        <v>2.9375</v>
       </c>
       <c r="J11" s="33" t="n">
         <f aca="false">I10*in_RefRate</f>
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="K11" s="33" t="n">
         <f aca="false">J10*in_RefRate</f>
-        <v>2.2</v>
+        <v>3.5625</v>
       </c>
       <c r="L11" s="33" t="n">
         <f aca="false">K10*in_RefRate</f>
-        <v>2.4</v>
+        <v>3.875</v>
       </c>
       <c r="M11" s="33" t="n">
         <f aca="false">L10*in_RefRate</f>
-        <v>2.6</v>
+        <v>4.1875</v>
       </c>
       <c r="N11" s="33" t="n">
         <f aca="false">M10*in_RefRate</f>
-        <v>2.8</v>
+        <v>4.5</v>
       </c>
       <c r="O11" s="33" t="n">
         <f aca="false">N10*in_RefRate</f>
-        <v>3</v>
+        <v>4.8125</v>
       </c>
       <c r="P11" s="33" t="n">
         <f aca="false">O10*in_RefRate</f>
-        <v>3.6</v>
+        <v>5.8125</v>
       </c>
       <c r="Q11" s="33" t="n">
         <f aca="false">P10*in_RefRate</f>
-        <v>4.2</v>
+        <v>6.8125</v>
       </c>
       <c r="R11" s="33" t="n">
         <f aca="false">Q10*in_RefRate</f>
-        <v>4.8</v>
+        <v>7.8125</v>
       </c>
       <c r="S11" s="33" t="n">
         <f aca="false">R10*in_RefRate</f>
-        <v>5.4</v>
+        <v>8.8125</v>
       </c>
       <c r="T11" s="33" t="n">
         <f aca="false">S10*in_RefRate</f>
-        <v>6</v>
+        <v>9.8125</v>
       </c>
       <c r="U11" s="33" t="n">
         <f aca="false">T10*in_RefRate</f>
-        <v>6.6</v>
+        <v>10.8125</v>
       </c>
       <c r="V11" s="33" t="n">
         <f aca="false">U10*in_RefRate</f>
-        <v>7.2</v>
+        <v>11.8125</v>
       </c>
       <c r="W11" s="33" t="n">
         <f aca="false">V10*in_RefRate</f>
-        <v>7.8</v>
+        <v>12.8125</v>
       </c>
       <c r="X11" s="33" t="n">
         <f aca="false">W10*in_RefRate</f>
-        <v>8.4</v>
+        <v>13.8125</v>
       </c>
       <c r="Y11" s="33" t="n">
         <f aca="false">X10*in_RefRate</f>
-        <v>9</v>
+        <v>14.8125</v>
       </c>
       <c r="Z11" s="33" t="n">
         <f aca="false">Y10*in_RefRate</f>
-        <v>9.6</v>
+        <v>15.8125</v>
       </c>
       <c r="AA11" s="33" t="n">
         <f aca="false">Z10*in_RefRate</f>
-        <v>10.2</v>
+        <v>16.8125</v>
       </c>
       <c r="AB11" s="33" t="n">
         <f aca="false">AA10*in_RefRate</f>
-        <v>11</v>
+        <v>18.0625</v>
       </c>
       <c r="AC11" s="33" t="n">
         <f aca="false">AB10*in_RefRate</f>
-        <v>11.8</v>
+        <v>19.3125</v>
       </c>
       <c r="AD11" s="33" t="n">
         <f aca="false">AC10*in_RefRate</f>
-        <v>12.6</v>
+        <v>20.5625</v>
       </c>
       <c r="AE11" s="33" t="n">
         <f aca="false">AD10*in_RefRate</f>
-        <v>13.4</v>
+        <v>21.8125</v>
       </c>
       <c r="AF11" s="33" t="n">
         <f aca="false">AE10*in_RefRate</f>
-        <v>14.2</v>
+        <v>23.0625</v>
       </c>
       <c r="AG11" s="33" t="n">
         <f aca="false">AF10*in_RefRate</f>
-        <v>15</v>
+        <v>24.3125</v>
       </c>
       <c r="AH11" s="33" t="n">
         <f aca="false">AG10*in_RefRate</f>
-        <v>15.8</v>
+        <v>25.5625</v>
       </c>
       <c r="AI11" s="33" t="n">
         <f aca="false">AH10*in_RefRate</f>
-        <v>16.6</v>
+        <v>26.8125</v>
       </c>
       <c r="AJ11" s="33" t="n">
         <f aca="false">AI10*in_RefRate</f>
-        <v>17.4</v>
+        <v>28.0625</v>
       </c>
       <c r="AK11" s="33" t="n">
         <f aca="false">AJ10*in_RefRate</f>
-        <v>18.2</v>
+        <v>29.3125</v>
       </c>
       <c r="AL11" s="33" t="n">
         <f aca="false">AK10*in_RefRate</f>
-        <v>19</v>
+        <v>30.5625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4947,127 +4947,127 @@
       </c>
       <c r="H12" s="33" t="n">
         <f aca="false">G11*in_RefConv</f>
-        <v>0.7</v>
+        <v>1.271875</v>
       </c>
       <c r="I12" s="33" t="n">
         <f aca="false">H11*in_RefConv</f>
-        <v>0.8</v>
+        <v>1.44375</v>
       </c>
       <c r="J12" s="33" t="n">
         <f aca="false">I11*in_RefConv</f>
-        <v>0.9</v>
+        <v>1.615625</v>
       </c>
       <c r="K12" s="33" t="n">
         <f aca="false">J11*in_RefConv</f>
-        <v>1</v>
+        <v>1.7875</v>
       </c>
       <c r="L12" s="33" t="n">
         <f aca="false">K11*in_RefConv</f>
-        <v>1.1</v>
+        <v>1.959375</v>
       </c>
       <c r="M12" s="33" t="n">
         <f aca="false">L11*in_RefConv</f>
-        <v>1.2</v>
+        <v>2.13125</v>
       </c>
       <c r="N12" s="33" t="n">
         <f aca="false">M11*in_RefConv</f>
-        <v>1.3</v>
+        <v>2.303125</v>
       </c>
       <c r="O12" s="33" t="n">
         <f aca="false">N11*in_RefConv</f>
-        <v>1.4</v>
+        <v>2.475</v>
       </c>
       <c r="P12" s="33" t="n">
         <f aca="false">O11*in_RefConv</f>
-        <v>1.5</v>
+        <v>2.646875</v>
       </c>
       <c r="Q12" s="33" t="n">
         <f aca="false">P11*in_RefConv</f>
-        <v>1.8</v>
+        <v>3.196875</v>
       </c>
       <c r="R12" s="33" t="n">
         <f aca="false">Q11*in_RefConv</f>
-        <v>2.1</v>
+        <v>3.746875</v>
       </c>
       <c r="S12" s="33" t="n">
         <f aca="false">R11*in_RefConv</f>
-        <v>2.4</v>
+        <v>4.296875</v>
       </c>
       <c r="T12" s="33" t="n">
         <f aca="false">S11*in_RefConv</f>
-        <v>2.7</v>
+        <v>4.846875</v>
       </c>
       <c r="U12" s="33" t="n">
         <f aca="false">T11*in_RefConv</f>
-        <v>3</v>
+        <v>5.396875</v>
       </c>
       <c r="V12" s="33" t="n">
         <f aca="false">U11*in_RefConv</f>
-        <v>3.3</v>
+        <v>5.946875</v>
       </c>
       <c r="W12" s="33" t="n">
         <f aca="false">V11*in_RefConv</f>
-        <v>3.6</v>
+        <v>6.496875</v>
       </c>
       <c r="X12" s="33" t="n">
         <f aca="false">W11*in_RefConv</f>
-        <v>3.9</v>
+        <v>7.046875</v>
       </c>
       <c r="Y12" s="33" t="n">
         <f aca="false">X11*in_RefConv</f>
-        <v>4.2</v>
+        <v>7.596875</v>
       </c>
       <c r="Z12" s="33" t="n">
         <f aca="false">Y11*in_RefConv</f>
-        <v>4.5</v>
+        <v>8.146875</v>
       </c>
       <c r="AA12" s="33" t="n">
         <f aca="false">Z11*in_RefConv</f>
-        <v>4.8</v>
+        <v>8.696875</v>
       </c>
       <c r="AB12" s="33" t="n">
         <f aca="false">AA11*in_RefConv</f>
-        <v>5.1</v>
+        <v>9.246875</v>
       </c>
       <c r="AC12" s="33" t="n">
         <f aca="false">AB11*in_RefConv</f>
-        <v>5.5</v>
+        <v>9.934375</v>
       </c>
       <c r="AD12" s="33" t="n">
         <f aca="false">AC11*in_RefConv</f>
-        <v>5.9</v>
+        <v>10.621875</v>
       </c>
       <c r="AE12" s="33" t="n">
         <f aca="false">AD11*in_RefConv</f>
-        <v>6.3</v>
+        <v>11.309375</v>
       </c>
       <c r="AF12" s="33" t="n">
         <f aca="false">AE11*in_RefConv</f>
-        <v>6.7</v>
+        <v>11.996875</v>
       </c>
       <c r="AG12" s="33" t="n">
         <f aca="false">AF11*in_RefConv</f>
-        <v>7.1</v>
+        <v>12.684375</v>
       </c>
       <c r="AH12" s="33" t="n">
         <f aca="false">AG11*in_RefConv</f>
-        <v>7.5</v>
+        <v>13.371875</v>
       </c>
       <c r="AI12" s="33" t="n">
         <f aca="false">AH11*in_RefConv</f>
-        <v>7.9</v>
+        <v>14.059375</v>
       </c>
       <c r="AJ12" s="33" t="n">
         <f aca="false">AI11*in_RefConv</f>
-        <v>8.3</v>
+        <v>14.746875</v>
       </c>
       <c r="AK12" s="33" t="n">
         <f aca="false">AJ11*in_RefConv</f>
-        <v>8.7</v>
+        <v>15.434375</v>
       </c>
       <c r="AL12" s="33" t="n">
         <f aca="false">AK11*in_RefConv</f>
-        <v>9.1</v>
+        <v>16.121875</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5079,147 +5079,147 @@
       </c>
       <c r="C13" s="33" t="n">
         <f aca="false">CHOOSE(C$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D13" s="33" t="n">
         <f aca="false">CHOOSE(D$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E13" s="33" t="n">
         <f aca="false">CHOOSE(E$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F13" s="33" t="n">
         <f aca="false">CHOOSE(F$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G13" s="33" t="n">
         <f aca="false">CHOOSE(G$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H13" s="33" t="n">
         <f aca="false">CHOOSE(H$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" s="33" t="n">
         <f aca="false">CHOOSE(I$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J13" s="33" t="n">
         <f aca="false">CHOOSE(J$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K13" s="33" t="n">
         <f aca="false">CHOOSE(K$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L13" s="33" t="n">
         <f aca="false">CHOOSE(L$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M13" s="33" t="n">
         <f aca="false">CHOOSE(M$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13" s="33" t="n">
         <f aca="false">CHOOSE(N$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O13" s="33" t="n">
         <f aca="false">CHOOSE(O$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="P13" s="33" t="n">
         <f aca="false">CHOOSE(P$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Q13" s="33" t="n">
         <f aca="false">CHOOSE(Q$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="R13" s="33" t="n">
         <f aca="false">CHOOSE(R$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="S13" s="33" t="n">
         <f aca="false">CHOOSE(S$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="T13" s="33" t="n">
         <f aca="false">CHOOSE(T$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="U13" s="33" t="n">
         <f aca="false">CHOOSE(U$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="V13" s="33" t="n">
         <f aca="false">CHOOSE(V$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="W13" s="33" t="n">
         <f aca="false">CHOOSE(W$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="X13" s="33" t="n">
         <f aca="false">CHOOSE(X$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Y13" s="33" t="n">
         <f aca="false">CHOOSE(Y$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z13" s="33" t="n">
         <f aca="false">CHOOSE(Z$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA13" s="33" t="n">
         <f aca="false">CHOOSE(AA$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AB13" s="33" t="n">
         <f aca="false">CHOOSE(AB$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AC13" s="33" t="n">
         <f aca="false">CHOOSE(AC$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AD13" s="33" t="n">
         <f aca="false">CHOOSE(AD$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE13" s="33" t="n">
         <f aca="false">CHOOSE(AE$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AF13" s="33" t="n">
         <f aca="false">CHOOSE(AF$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AG13" s="33" t="n">
         <f aca="false">CHOOSE(AG$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AH13" s="33" t="n">
         <f aca="false">CHOOSE(AH$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AI13" s="33" t="n">
         <f aca="false">CHOOSE(AI$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AJ13" s="33" t="n">
         <f aca="false">CHOOSE(AJ$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AK13" s="33" t="n">
         <f aca="false">CHOOSE(AK$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AL13" s="33" t="n">
         <f aca="false">CHOOSE(AL$5,in_OrganicY1,in_OrganicY2,in_OrganicY3)</f>
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5231,147 +5231,147 @@
       </c>
       <c r="C14" s="28" t="n">
         <f aca="false">Costs!C21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="D14" s="28" t="n">
         <f aca="false">Costs!D21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="E14" s="28" t="n">
         <f aca="false">Costs!E21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="F14" s="28" t="n">
         <f aca="false">Costs!F21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="G14" s="28" t="n">
         <f aca="false">Costs!G21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="H14" s="28" t="n">
         <f aca="false">Costs!H21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="I14" s="28" t="n">
         <f aca="false">Costs!I21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="J14" s="28" t="n">
         <f aca="false">Costs!J21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="K14" s="28" t="n">
         <f aca="false">Costs!K21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="L14" s="28" t="n">
         <f aca="false">Costs!L21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="M14" s="28" t="n">
         <f aca="false">Costs!M21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="N14" s="28" t="n">
         <f aca="false">Costs!N21*in_PaidShare/in_CostPerTrial</f>
-        <v>11.25</v>
+        <v>12.8571428571429</v>
       </c>
       <c r="O14" s="28" t="n">
         <f aca="false">Costs!O21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="P14" s="28" t="n">
         <f aca="false">Costs!P21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="Q14" s="28" t="n">
         <f aca="false">Costs!Q21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="R14" s="28" t="n">
         <f aca="false">Costs!R21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="S14" s="28" t="n">
         <f aca="false">Costs!S21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="T14" s="28" t="n">
         <f aca="false">Costs!T21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="U14" s="28" t="n">
         <f aca="false">Costs!U21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="V14" s="28" t="n">
         <f aca="false">Costs!V21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="W14" s="28" t="n">
         <f aca="false">Costs!W21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="X14" s="28" t="n">
         <f aca="false">Costs!X21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="Y14" s="28" t="n">
         <f aca="false">Costs!Y21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="Z14" s="28" t="n">
         <f aca="false">Costs!Z21*in_PaidShare/in_CostPerTrial</f>
-        <v>18.75</v>
+        <v>21.4285714285714</v>
       </c>
       <c r="AA14" s="28" t="n">
         <f aca="false">Costs!AA21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AB14" s="28" t="n">
         <f aca="false">Costs!AB21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AC14" s="28" t="n">
         <f aca="false">Costs!AC21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AD14" s="28" t="n">
         <f aca="false">Costs!AD21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AE14" s="28" t="n">
         <f aca="false">Costs!AE21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AF14" s="28" t="n">
         <f aca="false">Costs!AF21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AG14" s="28" t="n">
         <f aca="false">Costs!AG21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AH14" s="28" t="n">
         <f aca="false">Costs!AH21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AI14" s="28" t="n">
         <f aca="false">Costs!AI21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AJ14" s="28" t="n">
         <f aca="false">Costs!AJ21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AK14" s="28" t="n">
         <f aca="false">Costs!AK21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
       <c r="AL14" s="28" t="n">
         <f aca="false">Costs!AL21*in_PaidShare/in_CostPerTrial</f>
-        <v>26.25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5387,143 +5387,143 @@
       </c>
       <c r="D15" s="33" t="n">
         <f aca="false">(C13+C14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="E15" s="33" t="n">
         <f aca="false">(D13+D14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="F15" s="33" t="n">
         <f aca="false">(E13+E14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="G15" s="33" t="n">
         <f aca="false">(F13+F14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="H15" s="33" t="n">
         <f aca="false">(G13+G14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="I15" s="33" t="n">
         <f aca="false">(H13+H14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="J15" s="33" t="n">
         <f aca="false">(I13+I14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="K15" s="33" t="n">
         <f aca="false">(J13+J14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="L15" s="33" t="n">
         <f aca="false">(K13+K14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="M15" s="33" t="n">
         <f aca="false">(L13+L14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="N15" s="33" t="n">
         <f aca="false">(M13+M14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="O15" s="33" t="n">
         <f aca="false">(N13+N14)*in_TrialConv</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="P15" s="33" t="n">
         <f aca="false">(O13+O14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="Q15" s="33" t="n">
         <f aca="false">(P13+P14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="R15" s="33" t="n">
         <f aca="false">(Q13+Q14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="S15" s="33" t="n">
         <f aca="false">(R13+R14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="T15" s="33" t="n">
         <f aca="false">(S13+S14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="U15" s="33" t="n">
         <f aca="false">(T13+T14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="V15" s="33" t="n">
         <f aca="false">(U13+U14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="W15" s="33" t="n">
         <f aca="false">(V13+V14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="X15" s="33" t="n">
         <f aca="false">(W13+W14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="Y15" s="33" t="n">
         <f aca="false">(X13+X14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="Z15" s="33" t="n">
         <f aca="false">(Y13+Y14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="AA15" s="33" t="n">
         <f aca="false">(Z13+Z14)*in_TrialConv</f>
-        <v>7.6875</v>
+        <v>10.2928571428571</v>
       </c>
       <c r="AB15" s="33" t="n">
         <f aca="false">(AA13+AA14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AC15" s="33" t="n">
         <f aca="false">(AB13+AB14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AD15" s="33" t="n">
         <f aca="false">(AC13+AC14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AE15" s="33" t="n">
         <f aca="false">(AD13+AD14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AF15" s="33" t="n">
         <f aca="false">(AE13+AE14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AG15" s="33" t="n">
         <f aca="false">(AF13+AF14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AH15" s="33" t="n">
         <f aca="false">(AG13+AG14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AI15" s="33" t="n">
         <f aca="false">(AH13+AH14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AJ15" s="33" t="n">
         <f aca="false">(AI13+AI14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AK15" s="33" t="n">
         <f aca="false">(AJ13+AJ14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
       <c r="AL15" s="33" t="n">
         <f aca="false">(AK13+AK14)*in_TrialConv</f>
-        <v>11.5625</v>
+        <v>15.675</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5621,143 +5621,143 @@
       </c>
       <c r="D18" s="34" t="n">
         <f aca="false">D8+D12+D15</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="E18" s="34" t="n">
         <f aca="false">E8+E12+E15</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="F18" s="34" t="n">
         <f aca="false">F8+F12+F15</f>
-        <v>9.8125</v>
+        <v>15.9857142857143</v>
       </c>
       <c r="G18" s="34" t="n">
         <f aca="false">G8+G12+G15</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="H18" s="34" t="n">
         <f aca="false">H8+H12+H15</f>
-        <v>4.5125</v>
+        <v>6.45758928571429</v>
       </c>
       <c r="I18" s="34" t="n">
         <f aca="false">I8+I12+I15</f>
-        <v>4.6125</v>
+        <v>6.62946428571429</v>
       </c>
       <c r="J18" s="34" t="n">
         <f aca="false">J8+J12+J15</f>
-        <v>4.7125</v>
+        <v>6.80133928571429</v>
       </c>
       <c r="K18" s="34" t="n">
         <f aca="false">K8+K12+K15</f>
-        <v>4.8125</v>
+        <v>6.97321428571429</v>
       </c>
       <c r="L18" s="34" t="n">
         <f aca="false">L8+L12+L15</f>
-        <v>4.9125</v>
+        <v>7.14508928571429</v>
       </c>
       <c r="M18" s="34" t="n">
         <f aca="false">M8+M12+M15</f>
-        <v>5.0125</v>
+        <v>7.31696428571429</v>
       </c>
       <c r="N18" s="34" t="n">
         <f aca="false">N8+N12+N15</f>
-        <v>5.1125</v>
+        <v>7.48883928571429</v>
       </c>
       <c r="O18" s="34" t="n">
         <f aca="false">O8+O12+O15</f>
-        <v>5.2125</v>
+        <v>7.66071428571429</v>
       </c>
       <c r="P18" s="34" t="n">
         <f aca="false">P8+P12+P15</f>
-        <v>9.1875</v>
+        <v>12.9397321428571</v>
       </c>
       <c r="Q18" s="34" t="n">
         <f aca="false">Q8+Q12+Q15</f>
-        <v>9.4875</v>
+        <v>13.4897321428571</v>
       </c>
       <c r="R18" s="34" t="n">
         <f aca="false">R8+R12+R15</f>
-        <v>9.7875</v>
+        <v>14.0397321428571</v>
       </c>
       <c r="S18" s="34" t="n">
         <f aca="false">S8+S12+S15</f>
-        <v>10.0875</v>
+        <v>14.5897321428571</v>
       </c>
       <c r="T18" s="34" t="n">
         <f aca="false">T8+T12+T15</f>
-        <v>10.3875</v>
+        <v>15.1397321428571</v>
       </c>
       <c r="U18" s="34" t="n">
         <f aca="false">U8+U12+U15</f>
-        <v>10.6875</v>
+        <v>15.6897321428571</v>
       </c>
       <c r="V18" s="34" t="n">
         <f aca="false">V8+V12+V15</f>
-        <v>10.9875</v>
+        <v>16.2397321428571</v>
       </c>
       <c r="W18" s="34" t="n">
         <f aca="false">W8+W12+W15</f>
-        <v>11.2875</v>
+        <v>16.7897321428571</v>
       </c>
       <c r="X18" s="34" t="n">
         <f aca="false">X8+X12+X15</f>
-        <v>11.5875</v>
+        <v>17.3397321428571</v>
       </c>
       <c r="Y18" s="34" t="n">
         <f aca="false">Y8+Y12+Y15</f>
-        <v>11.8875</v>
+        <v>17.8897321428571</v>
       </c>
       <c r="Z18" s="34" t="n">
         <f aca="false">Z8+Z12+Z15</f>
-        <v>12.1875</v>
+        <v>18.4397321428571</v>
       </c>
       <c r="AA18" s="34" t="n">
         <f aca="false">AA8+AA12+AA15</f>
-        <v>12.4875</v>
+        <v>18.9897321428571</v>
       </c>
       <c r="AB18" s="34" t="n">
         <f aca="false">AB8+AB12+AB15</f>
-        <v>16.6625</v>
+        <v>24.921875</v>
       </c>
       <c r="AC18" s="34" t="n">
         <f aca="false">AC8+AC12+AC15</f>
-        <v>17.0625</v>
+        <v>25.609375</v>
       </c>
       <c r="AD18" s="34" t="n">
         <f aca="false">AD8+AD12+AD15</f>
-        <v>17.4625</v>
+        <v>26.296875</v>
       </c>
       <c r="AE18" s="34" t="n">
         <f aca="false">AE8+AE12+AE15</f>
-        <v>17.8625</v>
+        <v>26.984375</v>
       </c>
       <c r="AF18" s="34" t="n">
         <f aca="false">AF8+AF12+AF15</f>
-        <v>18.2625</v>
+        <v>27.671875</v>
       </c>
       <c r="AG18" s="34" t="n">
         <f aca="false">AG8+AG12+AG15</f>
-        <v>18.6625</v>
+        <v>28.359375</v>
       </c>
       <c r="AH18" s="34" t="n">
         <f aca="false">AH8+AH12+AH15</f>
-        <v>19.0625</v>
+        <v>29.046875</v>
       </c>
       <c r="AI18" s="34" t="n">
         <f aca="false">AI8+AI12+AI15</f>
-        <v>19.4625</v>
+        <v>29.734375</v>
       </c>
       <c r="AJ18" s="34" t="n">
         <f aca="false">AJ8+AJ12+AJ15</f>
-        <v>19.8625</v>
+        <v>30.421875</v>
       </c>
       <c r="AK18" s="34" t="n">
         <f aca="false">AK8+AK12+AK15</f>
-        <v>20.2625</v>
+        <v>31.109375</v>
       </c>
       <c r="AL18" s="34" t="n">
         <f aca="false">AL8+AL12+AL15</f>
-        <v>20.6625</v>
+        <v>31.796875</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="F19" s="33" t="n">
         <f aca="false">F8+F12</f>
-        <v>6</v>
+        <v>10.8</v>
       </c>
       <c r="G19" s="33" t="n">
         <f aca="false">G8+G12</f>
@@ -5789,127 +5789,127 @@
       </c>
       <c r="H19" s="33" t="n">
         <f aca="false">H8+H12</f>
-        <v>0.7</v>
+        <v>1.271875</v>
       </c>
       <c r="I19" s="33" t="n">
         <f aca="false">I8+I12</f>
-        <v>0.8</v>
+        <v>1.44375</v>
       </c>
       <c r="J19" s="33" t="n">
         <f aca="false">J8+J12</f>
-        <v>0.9</v>
+        <v>1.615625</v>
       </c>
       <c r="K19" s="33" t="n">
         <f aca="false">K8+K12</f>
-        <v>1</v>
+        <v>1.7875</v>
       </c>
       <c r="L19" s="33" t="n">
         <f aca="false">L8+L12</f>
-        <v>1.1</v>
+        <v>1.959375</v>
       </c>
       <c r="M19" s="33" t="n">
         <f aca="false">M8+M12</f>
-        <v>1.2</v>
+        <v>2.13125</v>
       </c>
       <c r="N19" s="33" t="n">
         <f aca="false">N8+N12</f>
-        <v>1.3</v>
+        <v>2.303125</v>
       </c>
       <c r="O19" s="33" t="n">
         <f aca="false">O8+O12</f>
-        <v>1.4</v>
+        <v>2.475</v>
       </c>
       <c r="P19" s="33" t="n">
         <f aca="false">P8+P12</f>
-        <v>1.5</v>
+        <v>2.646875</v>
       </c>
       <c r="Q19" s="33" t="n">
         <f aca="false">Q8+Q12</f>
-        <v>1.8</v>
+        <v>3.196875</v>
       </c>
       <c r="R19" s="33" t="n">
         <f aca="false">R8+R12</f>
-        <v>2.1</v>
+        <v>3.746875</v>
       </c>
       <c r="S19" s="33" t="n">
         <f aca="false">S8+S12</f>
-        <v>2.4</v>
+        <v>4.296875</v>
       </c>
       <c r="T19" s="33" t="n">
         <f aca="false">T8+T12</f>
-        <v>2.7</v>
+        <v>4.846875</v>
       </c>
       <c r="U19" s="33" t="n">
         <f aca="false">U8+U12</f>
-        <v>3</v>
+        <v>5.396875</v>
       </c>
       <c r="V19" s="33" t="n">
         <f aca="false">V8+V12</f>
-        <v>3.3</v>
+        <v>5.946875</v>
       </c>
       <c r="W19" s="33" t="n">
         <f aca="false">W8+W12</f>
-        <v>3.6</v>
+        <v>6.496875</v>
       </c>
       <c r="X19" s="33" t="n">
         <f aca="false">X8+X12</f>
-        <v>3.9</v>
+        <v>7.046875</v>
       </c>
       <c r="Y19" s="33" t="n">
         <f aca="false">Y8+Y12</f>
-        <v>4.2</v>
+        <v>7.596875</v>
       </c>
       <c r="Z19" s="33" t="n">
         <f aca="false">Z8+Z12</f>
-        <v>4.5</v>
+        <v>8.146875</v>
       </c>
       <c r="AA19" s="33" t="n">
         <f aca="false">AA8+AA12</f>
-        <v>4.8</v>
+        <v>8.696875</v>
       </c>
       <c r="AB19" s="33" t="n">
         <f aca="false">AB8+AB12</f>
-        <v>5.1</v>
+        <v>9.246875</v>
       </c>
       <c r="AC19" s="33" t="n">
         <f aca="false">AC8+AC12</f>
-        <v>5.5</v>
+        <v>9.934375</v>
       </c>
       <c r="AD19" s="33" t="n">
         <f aca="false">AD8+AD12</f>
-        <v>5.9</v>
+        <v>10.621875</v>
       </c>
       <c r="AE19" s="33" t="n">
         <f aca="false">AE8+AE12</f>
-        <v>6.3</v>
+        <v>11.309375</v>
       </c>
       <c r="AF19" s="33" t="n">
         <f aca="false">AF8+AF12</f>
-        <v>6.7</v>
+        <v>11.996875</v>
       </c>
       <c r="AG19" s="33" t="n">
         <f aca="false">AG8+AG12</f>
-        <v>7.1</v>
+        <v>12.684375</v>
       </c>
       <c r="AH19" s="33" t="n">
         <f aca="false">AH8+AH12</f>
-        <v>7.5</v>
+        <v>13.371875</v>
       </c>
       <c r="AI19" s="33" t="n">
         <f aca="false">AI8+AI12</f>
-        <v>7.9</v>
+        <v>14.059375</v>
       </c>
       <c r="AJ19" s="33" t="n">
         <f aca="false">AJ8+AJ12</f>
-        <v>8.3</v>
+        <v>14.746875</v>
       </c>
       <c r="AK19" s="33" t="n">
         <f aca="false">AK8+AK12</f>
-        <v>8.7</v>
+        <v>15.434375</v>
       </c>
       <c r="AL19" s="33" t="n">
         <f aca="false">AL8+AL12</f>
-        <v>9.1</v>
+        <v>16.121875</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5929,139 +5929,139 @@
       </c>
       <c r="E20" s="33" t="n">
         <f aca="false">D21*in_Churn</f>
-        <v>0.114375</v>
+        <v>0.129642857142857</v>
       </c>
       <c r="F20" s="33" t="n">
         <f aca="false">E21*in_Churn</f>
-        <v>0.22531875</v>
+        <v>0.256044642857143</v>
       </c>
       <c r="G20" s="33" t="n">
         <f aca="false">F21*in_Churn</f>
-        <v>0.5129341875</v>
+        <v>0.649286383928571</v>
       </c>
       <c r="H20" s="33" t="n">
         <f aca="false">G21*in_Churn</f>
-        <v>0.611921161875</v>
+        <v>0.762697081473214</v>
       </c>
       <c r="I20" s="33" t="n">
         <f aca="false">H21*in_Churn</f>
-        <v>0.72893852701875</v>
+        <v>0.905069386579241</v>
       </c>
       <c r="J20" s="33" t="n">
         <f aca="false">I21*in_Churn</f>
-        <v>0.845445371208187</v>
+        <v>1.04817925905762</v>
       </c>
       <c r="K20" s="33" t="n">
         <f aca="false">J21*in_Churn</f>
-        <v>0.961457010071942</v>
+        <v>1.19200825972403</v>
       </c>
       <c r="L20" s="33" t="n">
         <f aca="false">K21*in_Churn</f>
-        <v>1.07698829976978</v>
+        <v>1.33653841037379</v>
       </c>
       <c r="M20" s="33" t="n">
         <f aca="false">L21*in_Churn</f>
-        <v>1.19205365077669</v>
+        <v>1.4817521822573</v>
       </c>
       <c r="N20" s="33" t="n">
         <f aca="false">M21*in_Churn</f>
-        <v>1.30666704125339</v>
+        <v>1.62763248484373</v>
       </c>
       <c r="O20" s="33" t="n">
         <f aca="false">N21*in_Churn</f>
-        <v>1.42084203001579</v>
+        <v>1.77416265486549</v>
       </c>
       <c r="P20" s="33" t="n">
         <f aca="false">O21*in_Churn</f>
-        <v>1.53459176911531</v>
+        <v>1.92132644563671</v>
       </c>
       <c r="Q20" s="33" t="n">
         <f aca="false">P21*in_Churn</f>
-        <v>1.76417901604185</v>
+        <v>2.19678658806722</v>
       </c>
       <c r="R20" s="33" t="n">
         <f aca="false">Q21*in_Churn</f>
-        <v>1.9958786455606</v>
+        <v>2.47911022693697</v>
       </c>
       <c r="S20" s="33" t="n">
         <f aca="false">R21*in_Churn</f>
-        <v>2.22962728619378</v>
+        <v>2.76812577483498</v>
       </c>
       <c r="T20" s="33" t="n">
         <f aca="false">S21*in_Churn</f>
-        <v>2.46536346760797</v>
+        <v>3.06366593403553</v>
       </c>
       <c r="U20" s="33" t="n">
         <f aca="false">T21*in_Churn</f>
-        <v>2.70302756357973</v>
+        <v>3.36556758925607</v>
       </c>
       <c r="V20" s="33" t="n">
         <f aca="false">U21*in_Churn</f>
-        <v>2.94256173667234</v>
+        <v>3.6736717030961</v>
       </c>
       <c r="W20" s="33" t="n">
         <f aca="false">V21*in_Churn</f>
-        <v>3.18390988457217</v>
+        <v>3.98782321409012</v>
       </c>
       <c r="X20" s="33" t="n">
         <f aca="false">W21*in_Churn</f>
-        <v>3.427017588035</v>
+        <v>4.3078709373093</v>
       </c>
       <c r="Y20" s="33" t="n">
         <f aca="false">X21*in_Churn</f>
-        <v>3.67183206039395</v>
+        <v>4.63366746744799</v>
       </c>
       <c r="Z20" s="33" t="n">
         <f aca="false">Y21*in_Churn</f>
-        <v>3.91830209858213</v>
+        <v>4.96506908433322</v>
       </c>
       <c r="AA20" s="33" t="n">
         <f aca="false">Z21*in_Churn</f>
-        <v>4.16637803562467</v>
+        <v>5.30193566079632</v>
       </c>
       <c r="AB20" s="33" t="n">
         <f aca="false">AA21*in_Churn</f>
-        <v>4.41601169455593</v>
+        <v>5.64413057284784</v>
       </c>
       <c r="AC20" s="33" t="n">
         <f aca="false">AB21*in_Churn</f>
-        <v>4.78340634371925</v>
+        <v>6.12607418352665</v>
       </c>
       <c r="AD20" s="33" t="n">
         <f aca="false">AC21*in_Churn</f>
-        <v>5.15177915340767</v>
+        <v>6.61315670393848</v>
       </c>
       <c r="AE20" s="33" t="n">
         <f aca="false">AD21*in_Churn</f>
-        <v>5.52110077880545</v>
+        <v>7.10524966134002</v>
       </c>
       <c r="AF20" s="33" t="n">
         <f aca="false">AE21*in_Churn</f>
-        <v>5.89134275544128</v>
+        <v>7.60222779480652</v>
       </c>
       <c r="AG20" s="33" t="n">
         <f aca="false">AF21*in_Churn</f>
-        <v>6.26247747277804</v>
+        <v>8.10396897493635</v>
       </c>
       <c r="AH20" s="33" t="n">
         <f aca="false">AG21*in_Churn</f>
-        <v>6.6344781485947</v>
+        <v>8.61035412556294</v>
       </c>
       <c r="AI20" s="33" t="n">
         <f aca="false">AH21*in_Churn</f>
-        <v>7.00731880413686</v>
+        <v>9.12126714742387</v>
       </c>
       <c r="AJ20" s="33" t="n">
         <f aca="false">AI21*in_Churn</f>
-        <v>7.38097424001275</v>
+        <v>9.63659484373827</v>
       </c>
       <c r="AK20" s="33" t="n">
         <f aca="false">AJ21*in_Churn</f>
-        <v>7.75542001281237</v>
+        <v>10.1562268476448</v>
       </c>
       <c r="AL20" s="33" t="n">
         <f aca="false">AK21*in_Churn</f>
-        <v>8.130632412428</v>
+        <v>10.6800555514537</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6077,143 +6077,143 @@
       </c>
       <c r="D21" s="35" t="n">
         <f aca="false">C21+D18-D20</f>
-        <v>3.8125</v>
+        <v>5.18571428571429</v>
       </c>
       <c r="E21" s="35" t="n">
         <f aca="false">D21+E18-E20</f>
-        <v>7.510625</v>
+        <v>10.2417857142857</v>
       </c>
       <c r="F21" s="35" t="n">
         <f aca="false">E21+F18-F20</f>
-        <v>17.09780625</v>
+        <v>25.9714553571429</v>
       </c>
       <c r="G21" s="35" t="n">
         <f aca="false">F21+G18-G20</f>
-        <v>20.3973720625</v>
+        <v>30.5078832589286</v>
       </c>
       <c r="H21" s="35" t="n">
         <f aca="false">G21+H18-H20</f>
-        <v>24.297950900625</v>
+        <v>36.2027754631696</v>
       </c>
       <c r="I21" s="35" t="n">
         <f aca="false">H21+I18-I20</f>
-        <v>28.1815123736063</v>
+        <v>41.9271703623047</v>
       </c>
       <c r="J21" s="35" t="n">
         <f aca="false">I21+J18-J20</f>
-        <v>32.0485670023981</v>
+        <v>47.6803303889614</v>
       </c>
       <c r="K21" s="35" t="n">
         <f aca="false">J21+K18-K20</f>
-        <v>35.8996099923261</v>
+        <v>53.4615364149516</v>
       </c>
       <c r="L21" s="35" t="n">
         <f aca="false">K21+L18-L20</f>
-        <v>39.7351216925564</v>
+        <v>59.2700872902921</v>
       </c>
       <c r="M21" s="35" t="n">
         <f aca="false">L21+M18-M20</f>
-        <v>43.5555680417797</v>
+        <v>65.1052993937491</v>
       </c>
       <c r="N21" s="35" t="n">
         <f aca="false">M21+N18-N20</f>
-        <v>47.3614010005263</v>
+        <v>70.9665061946197</v>
       </c>
       <c r="O21" s="35" t="n">
         <f aca="false">N21+O18-O20</f>
-        <v>51.1530589705105</v>
+        <v>76.8530578254685</v>
       </c>
       <c r="P21" s="35" t="n">
         <f aca="false">O21+P18-P20</f>
-        <v>58.8059672013952</v>
+        <v>87.8714635226889</v>
       </c>
       <c r="Q21" s="35" t="n">
         <f aca="false">P21+Q18-Q20</f>
-        <v>66.5292881853533</v>
+        <v>99.1644090774788</v>
       </c>
       <c r="R21" s="35" t="n">
         <f aca="false">Q21+R18-R20</f>
-        <v>74.3209095397927</v>
+        <v>110.725030993399</v>
       </c>
       <c r="S21" s="35" t="n">
         <f aca="false">R21+S18-S20</f>
-        <v>82.1787822535989</v>
+        <v>122.546637361421</v>
       </c>
       <c r="T21" s="35" t="n">
         <f aca="false">S21+T18-T20</f>
-        <v>90.100918785991</v>
+        <v>134.622703570243</v>
       </c>
       <c r="U21" s="35" t="n">
         <f aca="false">T21+U18-U20</f>
-        <v>98.0853912224113</v>
+        <v>146.946868123844</v>
       </c>
       <c r="V21" s="35" t="n">
         <f aca="false">U21+V18-V20</f>
-        <v>106.130329485739</v>
+        <v>159.512928563605</v>
       </c>
       <c r="W21" s="35" t="n">
         <f aca="false">V21+W18-W20</f>
-        <v>114.233919601167</v>
+        <v>172.314837492372</v>
       </c>
       <c r="X21" s="35" t="n">
         <f aca="false">W21+X18-X20</f>
-        <v>122.394402013132</v>
+        <v>185.34669869792</v>
       </c>
       <c r="Y21" s="35" t="n">
         <f aca="false">X21+Y18-Y20</f>
-        <v>130.610069952738</v>
+        <v>198.602763373329</v>
       </c>
       <c r="Z21" s="35" t="n">
         <f aca="false">Y21+Z18-Z20</f>
-        <v>138.879267854156</v>
+        <v>212.077426431853</v>
       </c>
       <c r="AA21" s="35" t="n">
         <f aca="false">Z21+AA18-AA20</f>
-        <v>147.200389818531</v>
+        <v>225.765222913914</v>
       </c>
       <c r="AB21" s="35" t="n">
         <f aca="false">AA21+AB18-AB20</f>
-        <v>159.446878123975</v>
+        <v>245.042967341066</v>
       </c>
       <c r="AC21" s="35" t="n">
         <f aca="false">AB21+AC18-AC20</f>
-        <v>171.725971780256</v>
+        <v>264.526268157539</v>
       </c>
       <c r="AD21" s="35" t="n">
         <f aca="false">AC21+AD18-AD20</f>
-        <v>184.036692626848</v>
+        <v>284.209986453601</v>
       </c>
       <c r="AE21" s="35" t="n">
         <f aca="false">AD21+AE18-AE20</f>
-        <v>196.378091848043</v>
+        <v>304.089111792261</v>
       </c>
       <c r="AF21" s="35" t="n">
         <f aca="false">AE21+AF18-AF20</f>
-        <v>208.749249092601</v>
+        <v>324.158758997454</v>
       </c>
       <c r="AG21" s="35" t="n">
         <f aca="false">AF21+AG18-AG20</f>
-        <v>221.149271619823</v>
+        <v>344.414165022518</v>
       </c>
       <c r="AH21" s="35" t="n">
         <f aca="false">AG21+AH18-AH20</f>
-        <v>233.577293471229</v>
+        <v>364.850685896955</v>
       </c>
       <c r="AI21" s="35" t="n">
         <f aca="false">AH21+AI18-AI20</f>
-        <v>246.032474667092</v>
+        <v>385.463793749531</v>
       </c>
       <c r="AJ21" s="35" t="n">
         <f aca="false">AI21+AJ18-AJ20</f>
-        <v>258.514000427079</v>
+        <v>406.249073905793</v>
       </c>
       <c r="AK21" s="35" t="n">
         <f aca="false">AJ21+AK18-AK20</f>
-        <v>271.021080414267</v>
+        <v>427.202222058148</v>
       </c>
       <c r="AL21" s="35" t="n">
         <f aca="false">AK21+AL18-AL20</f>
-        <v>283.552948001839</v>
+        <v>448.319041506694</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6355,99 +6355,99 @@
       </c>
       <c r="O24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(O$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="P24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(P$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="Q24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(Q$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="R24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(R$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="S24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(S$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="T24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(T$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="U24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(U$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="V24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(V$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="W24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(W$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="X24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(X$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="Y24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(Y$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="Z24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(Z$5-1)</f>
-        <v>249.9</v>
+        <v>253.47</v>
       </c>
       <c r="AA24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AA$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AB24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AB$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AC24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AC$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AD24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AD$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AE24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AE$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AF24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AF$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AG24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AG$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AH24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AH$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AI24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AI$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AJ24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AJ$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AK24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AK$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
       <c r="AL24" s="36" t="n">
         <f aca="false">in_BlendedPriceRON*(1+in_PriceInc)^(AL$5-1)</f>
-        <v>262.395</v>
+        <v>269.94555</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6507,99 +6507,99 @@
       </c>
       <c r="O25" s="37" t="n">
         <f aca="false">O24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="P25" s="37" t="n">
         <f aca="false">P24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="Q25" s="37" t="n">
         <f aca="false">Q24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="R25" s="37" t="n">
         <f aca="false">R24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="S25" s="37" t="n">
         <f aca="false">S24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="T25" s="37" t="n">
         <f aca="false">T24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="U25" s="37" t="n">
         <f aca="false">U24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="V25" s="37" t="n">
         <f aca="false">V24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="W25" s="37" t="n">
         <f aca="false">W24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="X25" s="37" t="n">
         <f aca="false">X24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="Y25" s="37" t="n">
         <f aca="false">Y24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="Z25" s="37" t="n">
         <f aca="false">Z24/in_FX</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="AA25" s="37" t="n">
         <f aca="false">AA24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AB25" s="37" t="n">
         <f aca="false">AB24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AC25" s="37" t="n">
         <f aca="false">AC24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AD25" s="37" t="n">
         <f aca="false">AD24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AE25" s="37" t="n">
         <f aca="false">AE24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AF25" s="37" t="n">
         <f aca="false">AF24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AG25" s="37" t="n">
         <f aca="false">AG24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AH25" s="37" t="n">
         <f aca="false">AH24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AI25" s="37" t="n">
         <f aca="false">AI24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AJ25" s="37" t="n">
         <f aca="false">AJ24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AK25" s="37" t="n">
         <f aca="false">AK24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
       <c r="AL25" s="37" t="n">
         <f aca="false">AL24/in_FX</f>
-        <v>52.479</v>
+        <v>53.98911</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6615,143 +6615,143 @@
       </c>
       <c r="D26" s="38" t="n">
         <f aca="false">D21*D25</f>
-        <v>181.475</v>
+        <v>246.84</v>
       </c>
       <c r="E26" s="38" t="n">
         <f aca="false">E21*E25</f>
-        <v>357.50575</v>
+        <v>487.509</v>
       </c>
       <c r="F26" s="38" t="n">
         <f aca="false">F21*F25</f>
-        <v>813.8555775</v>
+        <v>1236.241275</v>
       </c>
       <c r="G26" s="38" t="n">
         <f aca="false">G21*G25</f>
-        <v>970.914910175</v>
+        <v>1452.175243125</v>
       </c>
       <c r="H26" s="38" t="n">
         <f aca="false">H21*H25</f>
-        <v>1156.58246286975</v>
+        <v>1723.25211204688</v>
       </c>
       <c r="I26" s="38" t="n">
         <f aca="false">I21*I25</f>
-        <v>1341.43998898366</v>
+        <v>1995.7333092457</v>
       </c>
       <c r="J26" s="38" t="n">
         <f aca="false">J21*J25</f>
-        <v>1525.51178931415</v>
+        <v>2269.58372651456</v>
       </c>
       <c r="K26" s="38" t="n">
         <f aca="false">K21*K25</f>
-        <v>1708.82143563472</v>
+        <v>2544.7691333517</v>
       </c>
       <c r="L26" s="38" t="n">
         <f aca="false">L21*L25</f>
-        <v>1891.39179256568</v>
+        <v>2821.2561550179</v>
       </c>
       <c r="M26" s="38" t="n">
         <f aca="false">M21*M25</f>
-        <v>2073.24503878871</v>
+        <v>3099.01225114246</v>
       </c>
       <c r="N26" s="38" t="n">
         <f aca="false">N21*N25</f>
-        <v>2254.40268762505</v>
+        <v>3378.0056948639</v>
       </c>
       <c r="O26" s="38" t="n">
         <f aca="false">O21*O25</f>
-        <v>2556.62988734611</v>
+        <v>3895.9889134043</v>
       </c>
       <c r="P26" s="38" t="n">
         <f aca="false">P21*P25</f>
-        <v>2939.12224072573</v>
+        <v>4454.55597181919</v>
       </c>
       <c r="Q26" s="38" t="n">
         <f aca="false">Q21*Q25</f>
-        <v>3325.13382350396</v>
+        <v>5027.04055377371</v>
       </c>
       <c r="R26" s="38" t="n">
         <f aca="false">R21*R25</f>
-        <v>3714.55905879884</v>
+        <v>5613.09472117937</v>
       </c>
       <c r="S26" s="38" t="n">
         <f aca="false">S21*S25</f>
-        <v>4107.29553703488</v>
+        <v>6212.37923439989</v>
       </c>
       <c r="T26" s="38" t="n">
         <f aca="false">T21*T25</f>
-        <v>4503.24392092383</v>
+        <v>6824.56333478989</v>
       </c>
       <c r="U26" s="38" t="n">
         <f aca="false">U21*U25</f>
-        <v>4902.30785329611</v>
+        <v>7449.32453267014</v>
       </c>
       <c r="V26" s="38" t="n">
         <f aca="false">V21*V25</f>
-        <v>5304.39386769723</v>
+        <v>8086.34840060339</v>
       </c>
       <c r="W26" s="38" t="n">
         <f aca="false">W21*W25</f>
-        <v>5709.41130166631</v>
+        <v>8735.3283718383</v>
       </c>
       <c r="X26" s="38" t="n">
         <f aca="false">X21*X25</f>
-        <v>6117.27221261632</v>
+        <v>9395.96554379235</v>
       </c>
       <c r="Y26" s="38" t="n">
         <f aca="false">Y21*Y25</f>
-        <v>6527.89129623784</v>
+        <v>10067.9684864475</v>
       </c>
       <c r="Z26" s="38" t="n">
         <f aca="false">Z21*Z25</f>
-        <v>6941.1858073507</v>
+        <v>10751.0530555363</v>
       </c>
       <c r="AA26" s="38" t="n">
         <f aca="false">AA21*AA25</f>
-        <v>7724.92925728669</v>
+        <v>12188.8634540738</v>
       </c>
       <c r="AB26" s="38" t="n">
         <f aca="false">AB21*AB25</f>
-        <v>8367.61271706809</v>
+        <v>13229.6517185032</v>
       </c>
       <c r="AC26" s="38" t="n">
         <f aca="false">AC21*AC25</f>
-        <v>9012.00727305605</v>
+        <v>14281.5377894469</v>
       </c>
       <c r="AD26" s="38" t="n">
         <f aca="false">AD21*AD25</f>
-        <v>9658.06159236436</v>
+        <v>15344.244221742</v>
       </c>
       <c r="AE26" s="38" t="n">
         <f aca="false">AE21*AE25</f>
-        <v>10305.7258820934</v>
+        <v>16417.5005063547</v>
       </c>
       <c r="AF26" s="38" t="n">
         <f aca="false">AF21*AF25</f>
-        <v>10954.9518431306</v>
+        <v>17501.042896977</v>
       </c>
       <c r="AG26" s="38" t="n">
         <f aca="false">AG21*AG25</f>
-        <v>11605.6926253367</v>
+        <v>18594.6142409589</v>
       </c>
       <c r="AH26" s="38" t="n">
         <f aca="false">AH21*AH25</f>
-        <v>12257.9027840766</v>
+        <v>19697.9638144661</v>
       </c>
       <c r="AI26" s="38" t="n">
         <f aca="false">AI21*AI25</f>
-        <v>12911.5382380543</v>
+        <v>20810.8471617607</v>
       </c>
       <c r="AJ26" s="38" t="n">
         <f aca="false">AJ21*AJ25</f>
-        <v>13566.5562284127</v>
+        <v>21933.025938498</v>
       </c>
       <c r="AK26" s="38" t="n">
         <f aca="false">AK21*AK25</f>
-        <v>14222.9152790603</v>
+        <v>23064.2677589418</v>
       </c>
       <c r="AL26" s="38" t="n">
         <f aca="false">AL21*AL25</f>
-        <v>14880.5751581885</v>
+        <v>24204.3460469995</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6767,143 +6767,143 @@
       </c>
       <c r="D27" s="39" t="n">
         <f aca="false">D26*12</f>
-        <v>2177.7</v>
+        <v>2962.08</v>
       </c>
       <c r="E27" s="39" t="n">
         <f aca="false">E26*12</f>
-        <v>4290.069</v>
+        <v>5850.108</v>
       </c>
       <c r="F27" s="39" t="n">
         <f aca="false">F26*12</f>
-        <v>9766.26693</v>
+        <v>14834.8953</v>
       </c>
       <c r="G27" s="39" t="n">
         <f aca="false">G26*12</f>
-        <v>11650.9789221</v>
+        <v>17426.1029175</v>
       </c>
       <c r="H27" s="39" t="n">
         <f aca="false">H26*12</f>
-        <v>13878.989554437</v>
+        <v>20679.0253445625</v>
       </c>
       <c r="I27" s="39" t="n">
         <f aca="false">I26*12</f>
-        <v>16097.2798678039</v>
+        <v>23948.7997109484</v>
       </c>
       <c r="J27" s="39" t="n">
         <f aca="false">J26*12</f>
-        <v>18306.1414717698</v>
+        <v>27235.0047181747</v>
       </c>
       <c r="K27" s="39" t="n">
         <f aca="false">K26*12</f>
-        <v>20505.8572276167</v>
+        <v>30537.2296002204</v>
       </c>
       <c r="L27" s="39" t="n">
         <f aca="false">L26*12</f>
-        <v>22696.7015107882</v>
+        <v>33855.0738602149</v>
       </c>
       <c r="M27" s="39" t="n">
         <f aca="false">M26*12</f>
-        <v>24878.9404654645</v>
+        <v>37188.1470137095</v>
       </c>
       <c r="N27" s="39" t="n">
         <f aca="false">N26*12</f>
-        <v>27052.8322515006</v>
+        <v>40536.0683383668</v>
       </c>
       <c r="O27" s="39" t="n">
         <f aca="false">O26*12</f>
-        <v>30679.5586481534</v>
+        <v>46751.8669608516</v>
       </c>
       <c r="P27" s="39" t="n">
         <f aca="false">P26*12</f>
-        <v>35269.4668887088</v>
+        <v>53454.6716618303</v>
       </c>
       <c r="Q27" s="39" t="n">
         <f aca="false">Q26*12</f>
-        <v>39901.6058820475</v>
+        <v>60324.4866452845</v>
       </c>
       <c r="R27" s="39" t="n">
         <f aca="false">R26*12</f>
-        <v>44574.7087055861</v>
+        <v>67357.1366541524</v>
       </c>
       <c r="S27" s="39" t="n">
         <f aca="false">S26*12</f>
-        <v>49287.5464444185</v>
+        <v>74548.5508127986</v>
       </c>
       <c r="T27" s="39" t="n">
         <f aca="false">T26*12</f>
-        <v>54038.927051086</v>
+        <v>81894.7600174787</v>
       </c>
       <c r="U27" s="39" t="n">
         <f aca="false">U26*12</f>
-        <v>58827.6942395534</v>
+        <v>89391.8943920417</v>
       </c>
       <c r="V27" s="39" t="n">
         <f aca="false">V26*12</f>
-        <v>63652.7264123668</v>
+        <v>97036.1808072407</v>
       </c>
       <c r="W27" s="39" t="n">
         <f aca="false">W26*12</f>
-        <v>68512.9356199958</v>
+        <v>104823.94046206</v>
       </c>
       <c r="X27" s="39" t="n">
         <f aca="false">X26*12</f>
-        <v>73407.2665513959</v>
+        <v>112751.586525508</v>
       </c>
       <c r="Y27" s="39" t="n">
         <f aca="false">Y26*12</f>
-        <v>78334.695554854</v>
+        <v>120815.62183737</v>
       </c>
       <c r="Z27" s="39" t="n">
         <f aca="false">Z26*12</f>
-        <v>83294.2296882084</v>
+        <v>129012.636666436</v>
       </c>
       <c r="AA27" s="39" t="n">
         <f aca="false">AA26*12</f>
-        <v>92699.1510874403</v>
+        <v>146266.361448886</v>
       </c>
       <c r="AB27" s="39" t="n">
         <f aca="false">AB26*12</f>
-        <v>100411.352604817</v>
+        <v>158755.820622039</v>
       </c>
       <c r="AC27" s="39" t="n">
         <f aca="false">AC26*12</f>
-        <v>108144.087276673</v>
+        <v>171378.453473363</v>
       </c>
       <c r="AD27" s="39" t="n">
         <f aca="false">AD26*12</f>
-        <v>115896.739108372</v>
+        <v>184130.930660903</v>
       </c>
       <c r="AE27" s="39" t="n">
         <f aca="false">AE26*12</f>
-        <v>123668.710585121</v>
+        <v>197010.006076256</v>
       </c>
       <c r="AF27" s="39" t="n">
         <f aca="false">AF26*12</f>
-        <v>131459.422117568</v>
+        <v>210012.514763724</v>
       </c>
       <c r="AG27" s="39" t="n">
         <f aca="false">AG26*12</f>
-        <v>139268.311504041</v>
+        <v>223135.370891506</v>
       </c>
       <c r="AH27" s="39" t="n">
         <f aca="false">AH26*12</f>
-        <v>147094.833408919</v>
+        <v>236375.565773594</v>
       </c>
       <c r="AI27" s="39" t="n">
         <f aca="false">AI26*12</f>
-        <v>154938.458856652</v>
+        <v>249730.165941129</v>
       </c>
       <c r="AJ27" s="39" t="n">
         <f aca="false">AJ26*12</f>
-        <v>162798.674740952</v>
+        <v>263196.311261976</v>
       </c>
       <c r="AK27" s="39" t="n">
         <f aca="false">AK26*12</f>
-        <v>170674.983348724</v>
+        <v>276771.213107301</v>
       </c>
       <c r="AL27" s="39" t="n">
         <f aca="false">AL26*12</f>
-        <v>178566.901898262</v>
+        <v>290452.152563994</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6919,143 +6919,143 @@
       </c>
       <c r="D28" s="40" t="n">
         <f aca="false">D26</f>
-        <v>181.475</v>
+        <v>246.84</v>
       </c>
       <c r="E28" s="40" t="n">
         <f aca="false">E26</f>
-        <v>357.50575</v>
+        <v>487.509</v>
       </c>
       <c r="F28" s="40" t="n">
         <f aca="false">F26</f>
-        <v>813.8555775</v>
+        <v>1236.241275</v>
       </c>
       <c r="G28" s="40" t="n">
         <f aca="false">G26</f>
-        <v>970.914910175</v>
+        <v>1452.175243125</v>
       </c>
       <c r="H28" s="40" t="n">
         <f aca="false">H26</f>
-        <v>1156.58246286975</v>
+        <v>1723.25211204688</v>
       </c>
       <c r="I28" s="40" t="n">
         <f aca="false">I26</f>
-        <v>1341.43998898366</v>
+        <v>1995.7333092457</v>
       </c>
       <c r="J28" s="40" t="n">
         <f aca="false">J26</f>
-        <v>1525.51178931415</v>
+        <v>2269.58372651456</v>
       </c>
       <c r="K28" s="40" t="n">
         <f aca="false">K26</f>
-        <v>1708.82143563472</v>
+        <v>2544.7691333517</v>
       </c>
       <c r="L28" s="40" t="n">
         <f aca="false">L26</f>
-        <v>1891.39179256568</v>
+        <v>2821.2561550179</v>
       </c>
       <c r="M28" s="40" t="n">
         <f aca="false">M26</f>
-        <v>2073.24503878871</v>
+        <v>3099.01225114246</v>
       </c>
       <c r="N28" s="40" t="n">
         <f aca="false">N26</f>
-        <v>2254.40268762505</v>
+        <v>3378.0056948639</v>
       </c>
       <c r="O28" s="40" t="n">
         <f aca="false">O26</f>
-        <v>2556.62988734611</v>
+        <v>3895.9889134043</v>
       </c>
       <c r="P28" s="40" t="n">
         <f aca="false">P26</f>
-        <v>2939.12224072573</v>
+        <v>4454.55597181919</v>
       </c>
       <c r="Q28" s="40" t="n">
         <f aca="false">Q26</f>
-        <v>3325.13382350396</v>
+        <v>5027.04055377371</v>
       </c>
       <c r="R28" s="40" t="n">
         <f aca="false">R26</f>
-        <v>3714.55905879884</v>
+        <v>5613.09472117937</v>
       </c>
       <c r="S28" s="40" t="n">
         <f aca="false">S26</f>
-        <v>4107.29553703488</v>
+        <v>6212.37923439989</v>
       </c>
       <c r="T28" s="40" t="n">
         <f aca="false">T26</f>
-        <v>4503.24392092383</v>
+        <v>6824.56333478989</v>
       </c>
       <c r="U28" s="40" t="n">
         <f aca="false">U26</f>
-        <v>4902.30785329611</v>
+        <v>7449.32453267014</v>
       </c>
       <c r="V28" s="40" t="n">
         <f aca="false">V26</f>
-        <v>5304.39386769723</v>
+        <v>8086.34840060339</v>
       </c>
       <c r="W28" s="40" t="n">
         <f aca="false">W26</f>
-        <v>5709.41130166631</v>
+        <v>8735.3283718383</v>
       </c>
       <c r="X28" s="40" t="n">
         <f aca="false">X26</f>
-        <v>6117.27221261632</v>
+        <v>9395.96554379235</v>
       </c>
       <c r="Y28" s="40" t="n">
         <f aca="false">Y26</f>
-        <v>6527.89129623784</v>
+        <v>10067.9684864475</v>
       </c>
       <c r="Z28" s="40" t="n">
         <f aca="false">Z26</f>
-        <v>6941.1858073507</v>
+        <v>10751.0530555363</v>
       </c>
       <c r="AA28" s="40" t="n">
         <f aca="false">AA26</f>
-        <v>7724.92925728669</v>
+        <v>12188.8634540738</v>
       </c>
       <c r="AB28" s="40" t="n">
         <f aca="false">AB26</f>
-        <v>8367.61271706809</v>
+        <v>13229.6517185032</v>
       </c>
       <c r="AC28" s="40" t="n">
         <f aca="false">AC26</f>
-        <v>9012.00727305605</v>
+        <v>14281.5377894469</v>
       </c>
       <c r="AD28" s="40" t="n">
         <f aca="false">AD26</f>
-        <v>9658.06159236436</v>
+        <v>15344.244221742</v>
       </c>
       <c r="AE28" s="40" t="n">
         <f aca="false">AE26</f>
-        <v>10305.7258820934</v>
+        <v>16417.5005063547</v>
       </c>
       <c r="AF28" s="40" t="n">
         <f aca="false">AF26</f>
-        <v>10954.9518431306</v>
+        <v>17501.042896977</v>
       </c>
       <c r="AG28" s="40" t="n">
         <f aca="false">AG26</f>
-        <v>11605.6926253367</v>
+        <v>18594.6142409589</v>
       </c>
       <c r="AH28" s="40" t="n">
         <f aca="false">AH26</f>
-        <v>12257.9027840766</v>
+        <v>19697.9638144661</v>
       </c>
       <c r="AI28" s="40" t="n">
         <f aca="false">AI26</f>
-        <v>12911.5382380543</v>
+        <v>20810.8471617607</v>
       </c>
       <c r="AJ28" s="40" t="n">
         <f aca="false">AJ26</f>
-        <v>13566.5562284127</v>
+        <v>21933.025938498</v>
       </c>
       <c r="AK28" s="40" t="n">
         <f aca="false">AK26</f>
-        <v>14222.9152790603</v>
+        <v>23064.2677589418</v>
       </c>
       <c r="AL28" s="40" t="n">
         <f aca="false">AL26</f>
-        <v>14880.5751581885</v>
+        <v>24204.3460469995</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7149,11 +7149,11 @@
       </c>
       <c r="C31" s="1" t="n">
         <f aca="false">IF(MAX(Revenue!$C$21:$AL$21)&lt;B31,"not within 36 months",COUNTIF(Revenue!$C$21:$AL$21,"&lt;"&amp;B31)+1)</f>
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D31" s="41" t="n">
         <f aca="false">IF(ISNUMBER(C31),INDEX(Revenue!$C$4:$AL$4,1,C31),"-")</f>
-        <v>46600</v>
+        <v>46508</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>240</v>
@@ -7201,11 +7201,11 @@
       </c>
       <c r="C32" s="1" t="n">
         <f aca="false">IF(MAX(Revenue!$C$21:$AL$21)&lt;B32,"not within 36 months",COUNTIF(Revenue!$C$21:$AL$21,"&lt;"&amp;B32)+1)</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D32" s="41" t="n">
         <f aca="false">IF(ISNUMBER(C32),INDEX(Revenue!$C$4:$AL$4,1,C32),"-")</f>
-        <v>46966</v>
+        <v>46844</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>240</v>
@@ -7251,13 +7251,13 @@
       <c r="B33" s="10" t="n">
         <v>300</v>
       </c>
-      <c r="C33" s="1" t="str">
+      <c r="C33" s="1" t="n">
         <f aca="false">IF(MAX(Revenue!$C$21:$AL$21)&lt;B33,"not within 36 months",COUNTIF(Revenue!$C$21:$AL$21,"&lt;"&amp;B33)+1)</f>
-        <v>not within 36 months</v>
-      </c>
-      <c r="D33" s="41" t="str">
+        <v>29</v>
+      </c>
+      <c r="D33" s="41" t="n">
         <f aca="false">IF(ISNUMBER(C33),INDEX(Revenue!$C$4:$AL$4,1,C33),"-")</f>
-        <v>-</v>
+        <v>47239</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>240</v>
@@ -9247,143 +9247,143 @@
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">Revenue!D21*in_InfraVar</f>
-        <v>5.71875</v>
+        <v>7.77857142857143</v>
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">Revenue!E21*in_InfraVar</f>
-        <v>11.2659375</v>
+        <v>15.3626785714286</v>
       </c>
       <c r="F18" s="6" t="n">
         <f aca="false">Revenue!F21*in_InfraVar</f>
-        <v>25.646709375</v>
+        <v>38.9571830357143</v>
       </c>
       <c r="G18" s="6" t="n">
         <f aca="false">Revenue!G21*in_InfraVar</f>
-        <v>30.59605809375</v>
+        <v>45.7618248883929</v>
       </c>
       <c r="H18" s="6" t="n">
         <f aca="false">Revenue!H21*in_InfraVar</f>
-        <v>36.4469263509375</v>
+        <v>54.3041631947545</v>
       </c>
       <c r="I18" s="6" t="n">
         <f aca="false">Revenue!I21*in_InfraVar</f>
-        <v>42.2722685604094</v>
+        <v>62.890755543457</v>
       </c>
       <c r="J18" s="6" t="n">
         <f aca="false">Revenue!J21*in_InfraVar</f>
-        <v>48.0728505035971</v>
+        <v>71.520495583442</v>
       </c>
       <c r="K18" s="6" t="n">
         <f aca="false">Revenue!K21*in_InfraVar</f>
-        <v>53.8494149884892</v>
+        <v>80.1923046224274</v>
       </c>
       <c r="L18" s="6" t="n">
         <f aca="false">Revenue!L21*in_InfraVar</f>
-        <v>59.6026825388345</v>
+        <v>88.9051309354381</v>
       </c>
       <c r="M18" s="6" t="n">
         <f aca="false">Revenue!M21*in_InfraVar</f>
-        <v>65.3333520626695</v>
+        <v>97.6579490906237</v>
       </c>
       <c r="N18" s="6" t="n">
         <f aca="false">Revenue!N21*in_InfraVar</f>
-        <v>71.0421015007894</v>
+        <v>106.449759291929</v>
       </c>
       <c r="O18" s="6" t="n">
         <f aca="false">Revenue!O21*in_InfraVar</f>
-        <v>76.7295884557657</v>
+        <v>115.279586738203</v>
       </c>
       <c r="P18" s="6" t="n">
         <f aca="false">Revenue!P21*in_InfraVar</f>
-        <v>88.2089508020927</v>
+        <v>131.807195284033</v>
       </c>
       <c r="Q18" s="6" t="n">
         <f aca="false">Revenue!Q21*in_InfraVar</f>
-        <v>99.79393227803</v>
+        <v>148.746613616218</v>
       </c>
       <c r="R18" s="6" t="n">
         <f aca="false">Revenue!R21*in_InfraVar</f>
-        <v>111.481364309689</v>
+        <v>166.087546490098</v>
       </c>
       <c r="S18" s="6" t="n">
         <f aca="false">Revenue!S21*in_InfraVar</f>
-        <v>123.268173380398</v>
+        <v>183.819956042132</v>
       </c>
       <c r="T18" s="6" t="n">
         <f aca="false">Revenue!T21*in_InfraVar</f>
-        <v>135.151378178986</v>
+        <v>201.934055355364</v>
       </c>
       <c r="U18" s="6" t="n">
         <f aca="false">Revenue!U21*in_InfraVar</f>
-        <v>147.128086833617</v>
+        <v>220.420302185766</v>
       </c>
       <c r="V18" s="6" t="n">
         <f aca="false">Revenue!V21*in_InfraVar</f>
-        <v>159.195494228608</v>
+        <v>239.269392845407</v>
       </c>
       <c r="W18" s="6" t="n">
         <f aca="false">Revenue!W21*in_InfraVar</f>
-        <v>171.35087940175</v>
+        <v>258.472256238558</v>
       </c>
       <c r="X18" s="6" t="n">
         <f aca="false">Revenue!X21*in_InfraVar</f>
-        <v>183.591603019698</v>
+        <v>278.02004804688</v>
       </c>
       <c r="Y18" s="6" t="n">
         <f aca="false">Revenue!Y21*in_InfraVar</f>
-        <v>195.915104929107</v>
+        <v>297.904145059993</v>
       </c>
       <c r="Z18" s="6" t="n">
         <f aca="false">Revenue!Z21*in_InfraVar</f>
-        <v>208.318901781234</v>
+        <v>318.116139647779</v>
       </c>
       <c r="AA18" s="6" t="n">
         <f aca="false">Revenue!AA21*in_InfraVar</f>
-        <v>220.800584727797</v>
+        <v>338.64783437087</v>
       </c>
       <c r="AB18" s="6" t="n">
         <f aca="false">Revenue!AB21*in_InfraVar</f>
-        <v>239.170317185963</v>
+        <v>367.564451011599</v>
       </c>
       <c r="AC18" s="6" t="n">
         <f aca="false">Revenue!AC21*in_InfraVar</f>
-        <v>257.588957670384</v>
+        <v>396.789402236309</v>
       </c>
       <c r="AD18" s="6" t="n">
         <f aca="false">Revenue!AD21*in_InfraVar</f>
-        <v>276.055038940272</v>
+        <v>426.314979680401</v>
       </c>
       <c r="AE18" s="6" t="n">
         <f aca="false">Revenue!AE21*in_InfraVar</f>
-        <v>294.567137772064</v>
+        <v>456.133667688391</v>
       </c>
       <c r="AF18" s="6" t="n">
         <f aca="false">Revenue!AF21*in_InfraVar</f>
-        <v>313.123873638902</v>
+        <v>486.238138496181</v>
       </c>
       <c r="AG18" s="6" t="n">
         <f aca="false">Revenue!AG21*in_InfraVar</f>
-        <v>331.723907429735</v>
+        <v>516.621247533777</v>
       </c>
       <c r="AH18" s="6" t="n">
         <f aca="false">Revenue!AH21*in_InfraVar</f>
-        <v>350.365940206843</v>
+        <v>547.276028845432</v>
       </c>
       <c r="AI18" s="6" t="n">
         <f aca="false">Revenue!AI21*in_InfraVar</f>
-        <v>369.048712000638</v>
+        <v>578.195690624297</v>
       </c>
       <c r="AJ18" s="6" t="n">
         <f aca="false">Revenue!AJ21*in_InfraVar</f>
-        <v>387.771000640619</v>
+        <v>609.373610858689</v>
       </c>
       <c r="AK18" s="6" t="n">
         <f aca="false">Revenue!AK21*in_InfraVar</f>
-        <v>406.5316206214</v>
+        <v>640.803333087222</v>
       </c>
       <c r="AL18" s="6" t="n">
         <f aca="false">Revenue!AL21*in_InfraVar</f>
-        <v>425.329422002758</v>
+        <v>672.478562260041</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9551,143 +9551,143 @@
       </c>
       <c r="D20" s="6" t="n">
         <f aca="false">Revenue!D28*in_PayFee</f>
-        <v>3.6295</v>
+        <v>4.9368</v>
       </c>
       <c r="E20" s="6" t="n">
         <f aca="false">Revenue!E28*in_PayFee</f>
-        <v>7.150115</v>
+        <v>9.75018</v>
       </c>
       <c r="F20" s="6" t="n">
         <f aca="false">Revenue!F28*in_PayFee</f>
-        <v>16.27711155</v>
+        <v>24.7248255</v>
       </c>
       <c r="G20" s="6" t="n">
         <f aca="false">Revenue!G28*in_PayFee</f>
-        <v>19.4182982035</v>
+        <v>29.0435048625</v>
       </c>
       <c r="H20" s="6" t="n">
         <f aca="false">Revenue!H28*in_PayFee</f>
-        <v>23.131649257395</v>
+        <v>34.4650422409375</v>
       </c>
       <c r="I20" s="6" t="n">
         <f aca="false">Revenue!I28*in_PayFee</f>
-        <v>26.8287997796732</v>
+        <v>39.9146661849141</v>
       </c>
       <c r="J20" s="6" t="n">
         <f aca="false">Revenue!J28*in_PayFee</f>
-        <v>30.510235786283</v>
+        <v>45.3916745302912</v>
       </c>
       <c r="K20" s="6" t="n">
         <f aca="false">Revenue!K28*in_PayFee</f>
-        <v>34.1764287126945</v>
+        <v>50.8953826670339</v>
       </c>
       <c r="L20" s="6" t="n">
         <f aca="false">Revenue!L28*in_PayFee</f>
-        <v>37.8278358513136</v>
+        <v>56.4251231003581</v>
       </c>
       <c r="M20" s="6" t="n">
         <f aca="false">Revenue!M28*in_PayFee</f>
-        <v>41.4649007757742</v>
+        <v>61.9802450228491</v>
       </c>
       <c r="N20" s="6" t="n">
         <f aca="false">Revenue!N28*in_PayFee</f>
-        <v>45.088053752501</v>
+        <v>67.5601138972779</v>
       </c>
       <c r="O20" s="6" t="n">
         <f aca="false">Revenue!O28*in_PayFee</f>
-        <v>51.1325977469223</v>
+        <v>77.919778268086</v>
       </c>
       <c r="P20" s="6" t="n">
         <f aca="false">Revenue!P28*in_PayFee</f>
-        <v>58.7824448145146</v>
+        <v>89.0911194363838</v>
       </c>
       <c r="Q20" s="6" t="n">
         <f aca="false">Revenue!Q28*in_PayFee</f>
-        <v>66.5026764700792</v>
+        <v>100.540811075474</v>
       </c>
       <c r="R20" s="6" t="n">
         <f aca="false">Revenue!R28*in_PayFee</f>
-        <v>74.2911811759768</v>
+        <v>112.261894423587</v>
       </c>
       <c r="S20" s="6" t="n">
         <f aca="false">Revenue!S28*in_PayFee</f>
-        <v>82.1459107406975</v>
+        <v>124.247584687998</v>
       </c>
       <c r="T20" s="6" t="n">
         <f aca="false">Revenue!T28*in_PayFee</f>
-        <v>90.0648784184766</v>
+        <v>136.491266695798</v>
       </c>
       <c r="U20" s="6" t="n">
         <f aca="false">Revenue!U28*in_PayFee</f>
-        <v>98.0461570659223</v>
+        <v>148.986490653403</v>
       </c>
       <c r="V20" s="6" t="n">
         <f aca="false">Revenue!V28*in_PayFee</f>
-        <v>106.087877353945</v>
+        <v>161.726968012068</v>
       </c>
       <c r="W20" s="6" t="n">
         <f aca="false">Revenue!W28*in_PayFee</f>
-        <v>114.188226033326</v>
+        <v>174.706567436766</v>
       </c>
       <c r="X20" s="6" t="n">
         <f aca="false">Revenue!X28*in_PayFee</f>
-        <v>122.345444252326</v>
+        <v>187.919310875847</v>
       </c>
       <c r="Y20" s="6" t="n">
         <f aca="false">Revenue!Y28*in_PayFee</f>
-        <v>130.557825924757</v>
+        <v>201.359369728951</v>
       </c>
       <c r="Z20" s="6" t="n">
         <f aca="false">Revenue!Z28*in_PayFee</f>
-        <v>138.823716147014</v>
+        <v>215.021061110727</v>
       </c>
       <c r="AA20" s="6" t="n">
         <f aca="false">Revenue!AA28*in_PayFee</f>
-        <v>154.498585145734</v>
+        <v>243.777269081476</v>
       </c>
       <c r="AB20" s="6" t="n">
         <f aca="false">Revenue!AB28*in_PayFee</f>
-        <v>167.352254341362</v>
+        <v>264.593034370064</v>
       </c>
       <c r="AC20" s="6" t="n">
         <f aca="false">Revenue!AC28*in_PayFee</f>
-        <v>180.240145461121</v>
+        <v>285.630755788938</v>
       </c>
       <c r="AD20" s="6" t="n">
         <f aca="false">Revenue!AD28*in_PayFee</f>
-        <v>193.161231847287</v>
+        <v>306.884884434839</v>
       </c>
       <c r="AE20" s="6" t="n">
         <f aca="false">Revenue!AE28*in_PayFee</f>
-        <v>206.114517641869</v>
+        <v>328.350010127093</v>
       </c>
       <c r="AF20" s="6" t="n">
         <f aca="false">Revenue!AF28*in_PayFee</f>
-        <v>219.099036862613</v>
+        <v>350.020857939541</v>
       </c>
       <c r="AG20" s="6" t="n">
         <f aca="false">Revenue!AG28*in_PayFee</f>
-        <v>232.113852506734</v>
+        <v>371.892284819177</v>
       </c>
       <c r="AH20" s="6" t="n">
         <f aca="false">Revenue!AH28*in_PayFee</f>
-        <v>245.158055681532</v>
+        <v>393.959276289323</v>
       </c>
       <c r="AI20" s="6" t="n">
         <f aca="false">Revenue!AI28*in_PayFee</f>
-        <v>258.230764761086</v>
+        <v>416.216943235215</v>
       </c>
       <c r="AJ20" s="6" t="n">
         <f aca="false">Revenue!AJ28*in_PayFee</f>
-        <v>271.331124568254</v>
+        <v>438.660518769959</v>
       </c>
       <c r="AK20" s="6" t="n">
         <f aca="false">Revenue!AK28*in_PayFee</f>
-        <v>284.458305581206</v>
+        <v>461.285355178835</v>
       </c>
       <c r="AL20" s="6" t="n">
         <f aca="false">Revenue!AL28*in_PayFee</f>
-        <v>297.61150316377</v>
+        <v>484.08692093999</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10015,135 +10015,135 @@
       </c>
       <c r="F23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!F25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;F$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=F$3)*Revenue!$C$19:$AL$19)</f>
-        <v>57.12</v>
+        <v>102.816</v>
       </c>
       <c r="G23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!G25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;G$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=G$3)*Revenue!$C$19:$AL$19)</f>
-        <v>57.12</v>
+        <v>102.816</v>
       </c>
       <c r="H23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!H25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;H$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=H$3)*Revenue!$C$19:$AL$19)</f>
-        <v>63.784</v>
+        <v>114.92425</v>
       </c>
       <c r="I23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!I25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;I$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=I$3)*Revenue!$C$19:$AL$19)</f>
-        <v>71.4</v>
+        <v>128.66875</v>
       </c>
       <c r="J23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!J25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;J$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=J$3)*Revenue!$C$19:$AL$19)</f>
-        <v>79.968</v>
+        <v>144.0495</v>
       </c>
       <c r="K23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!K25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;K$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=K$3)*Revenue!$C$19:$AL$19)</f>
-        <v>89.488</v>
+        <v>161.0665</v>
       </c>
       <c r="L23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!L25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;L$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=L$3)*Revenue!$C$19:$AL$19)</f>
-        <v>42.84</v>
+        <v>76.90375</v>
       </c>
       <c r="M23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!M25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;M$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=M$3)*Revenue!$C$19:$AL$19)</f>
-        <v>54.264</v>
+        <v>97.19325</v>
       </c>
       <c r="N23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!N25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;N$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=N$3)*Revenue!$C$19:$AL$19)</f>
-        <v>59.976</v>
+        <v>107.01075</v>
       </c>
       <c r="O23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!O25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;O$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=O$3)*Revenue!$C$19:$AL$19)</f>
-        <v>68.9724</v>
+        <v>124.42208625</v>
       </c>
       <c r="P23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!P25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;P$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=P$3)*Revenue!$C$19:$AL$19)</f>
-        <v>74.97</v>
+        <v>134.87772375</v>
       </c>
       <c r="Q23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!Q25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;Q$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=Q$3)*Revenue!$C$19:$AL$19)</f>
-        <v>82.9668</v>
+        <v>149.167095</v>
       </c>
       <c r="R23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!R25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;R$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=R$3)*Revenue!$C$19:$AL$19)</f>
-        <v>92.9628</v>
+        <v>167.2902</v>
       </c>
       <c r="S23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!S25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;S$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=S$3)*Revenue!$C$19:$AL$19)</f>
-        <v>104.958</v>
+        <v>189.24703875</v>
       </c>
       <c r="T23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!T25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;T$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=T$3)*Revenue!$C$19:$AL$19)</f>
-        <v>118.9524</v>
+        <v>215.03761125</v>
       </c>
       <c r="U23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!U25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;U$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=U$3)*Revenue!$C$19:$AL$19)</f>
-        <v>134.946</v>
+        <v>244.6619175</v>
       </c>
       <c r="V23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!V25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;V$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=V$3)*Revenue!$C$19:$AL$19)</f>
-        <v>152.9388</v>
+        <v>278.1199575</v>
       </c>
       <c r="W23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!W25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;W$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=W$3)*Revenue!$C$19:$AL$19)</f>
-        <v>170.9316</v>
+        <v>311.5779975</v>
       </c>
       <c r="X23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!X25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;X$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=X$3)*Revenue!$C$19:$AL$19)</f>
-        <v>188.9244</v>
+        <v>345.0360375</v>
       </c>
       <c r="Y23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!Y25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;Y$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=Y$3)*Revenue!$C$19:$AL$19)</f>
-        <v>206.9172</v>
+        <v>378.4940775</v>
       </c>
       <c r="Z23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!Z25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;Z$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=Z$3)*Revenue!$C$19:$AL$19)</f>
-        <v>224.91</v>
+        <v>411.9521175</v>
       </c>
       <c r="AA23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AA25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AA$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AA$3)*Revenue!$C$19:$AL$19)</f>
-        <v>255.04794</v>
+        <v>474.3618177375</v>
       </c>
       <c r="AB23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AB25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AB$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AB$3)*Revenue!$C$19:$AL$19)</f>
-        <v>273.94038</v>
+        <v>509.9946303375</v>
       </c>
       <c r="AC23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AC25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AC$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AC$3)*Revenue!$C$19:$AL$19)</f>
-        <v>293.8824</v>
+        <v>547.1121434625</v>
       </c>
       <c r="AD23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AD25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AD$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AD$3)*Revenue!$C$19:$AL$19)</f>
-        <v>314.874</v>
+        <v>585.7143571125</v>
       </c>
       <c r="AE23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AE25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AE$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AE$3)*Revenue!$C$19:$AL$19)</f>
-        <v>336.91518</v>
+        <v>625.8012712875</v>
       </c>
       <c r="AF23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AF25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AF$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AF$3)*Revenue!$C$19:$AL$19)</f>
-        <v>360.00594</v>
+        <v>667.3728859875</v>
       </c>
       <c r="AG23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AG25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AG$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AG$3)*Revenue!$C$19:$AL$19)</f>
-        <v>384.14628</v>
+        <v>710.4292012125</v>
       </c>
       <c r="AH23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AH25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AH$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AH$3)*Revenue!$C$19:$AL$19)</f>
-        <v>409.3362</v>
+        <v>754.9702169625</v>
       </c>
       <c r="AI23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AI25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AI$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AI$3)*Revenue!$C$19:$AL$19)</f>
-        <v>434.52612</v>
+        <v>799.5112327125</v>
       </c>
       <c r="AJ23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AJ25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AJ$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AJ$3)*Revenue!$C$19:$AL$19)</f>
-        <v>459.71604</v>
+        <v>844.0522484625</v>
       </c>
       <c r="AK23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AK25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AK$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AK$3)*Revenue!$C$19:$AL$19)</f>
-        <v>484.90596</v>
+        <v>888.5932642125</v>
       </c>
       <c r="AL23" s="6" t="n">
         <f aca="false">in_CommRate*Revenue!AL25*SUMPRODUCT((Revenue!$C$3:$AL$3&gt;AL$3-in_CommMonths)*(Revenue!$C$3:$AL$3&lt;=AL$3)*Revenue!$C$19:$AL$19)</f>
-        <v>510.09588</v>
+        <v>933.1342799625</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11223,143 +11223,143 @@
       </c>
       <c r="D31" s="40" t="n">
         <f aca="false">SUM(D17:D30)</f>
-        <v>7159.34825</v>
+        <v>7162.71537142857</v>
       </c>
       <c r="E31" s="40" t="n">
         <f aca="false">SUM(E17:E30)</f>
-        <v>4668.4160525</v>
+        <v>4675.11285857143</v>
       </c>
       <c r="F31" s="40" t="n">
         <f aca="false">SUM(F17:F30)</f>
-        <v>4749.043820925</v>
+        <v>4816.49800853572</v>
       </c>
       <c r="G31" s="40" t="n">
         <f aca="false">SUM(G17:G30)</f>
-        <v>6257.13435629725</v>
+        <v>6327.62132975089</v>
       </c>
       <c r="H31" s="40" t="n">
         <f aca="false">SUM(H17:H30)</f>
-        <v>4273.36257560833</v>
+        <v>4353.69345543569</v>
       </c>
       <c r="I31" s="40" t="n">
         <f aca="false">SUM(I17:I30)</f>
-        <v>2790.50106834008</v>
+        <v>2881.47417172837</v>
       </c>
       <c r="J31" s="40" t="n">
         <f aca="false">SUM(J17:J30)</f>
-        <v>2808.55108628988</v>
+        <v>2910.96167011373</v>
       </c>
       <c r="K31" s="40" t="n">
         <f aca="false">SUM(K17:K30)</f>
-        <v>2827.51384370118</v>
+        <v>2942.15418728946</v>
       </c>
       <c r="L31" s="40" t="n">
         <f aca="false">SUM(L17:L30)</f>
-        <v>2790.27051839015</v>
+        <v>2872.2340040358</v>
       </c>
       <c r="M31" s="40" t="n">
         <f aca="false">SUM(M17:M30)</f>
-        <v>2811.06225283844</v>
+        <v>2906.83144411347</v>
       </c>
       <c r="N31" s="40" t="n">
         <f aca="false">SUM(N17:N30)</f>
-        <v>2826.10615525329</v>
+        <v>2931.02062318921</v>
       </c>
       <c r="O31" s="40" t="n">
         <f aca="false">SUM(O17:O30)</f>
-        <v>3846.83458620269</v>
+        <v>3967.62145125629</v>
       </c>
       <c r="P31" s="40" t="n">
         <f aca="false">SUM(P17:P30)</f>
-        <v>3871.96139561661</v>
+        <v>4005.77603847042</v>
       </c>
       <c r="Q31" s="40" t="n">
         <f aca="false">SUM(Q17:Q30)</f>
-        <v>3899.26340874811</v>
+        <v>4048.45451969169</v>
       </c>
       <c r="R31" s="40" t="n">
         <f aca="false">SUM(R17:R30)</f>
-        <v>3928.73534548567</v>
+        <v>4095.63964091369</v>
       </c>
       <c r="S31" s="40" t="n">
         <f aca="false">SUM(S17:S30)</f>
-        <v>3960.3720841211</v>
+        <v>4147.31457948013</v>
       </c>
       <c r="T31" s="40" t="n">
         <f aca="false">SUM(T17:T30)</f>
-        <v>3994.16865659746</v>
+        <v>4203.46293330116</v>
       </c>
       <c r="U31" s="40" t="n">
         <f aca="false">SUM(U17:U30)</f>
-        <v>4030.12024389954</v>
+        <v>4264.06871033917</v>
       </c>
       <c r="V31" s="40" t="n">
         <f aca="false">SUM(V17:V30)</f>
-        <v>4068.22217158255</v>
+        <v>4329.11631835748</v>
       </c>
       <c r="W31" s="40" t="n">
         <f aca="false">SUM(W17:W30)</f>
-        <v>4106.47070543508</v>
+        <v>4394.75682117532</v>
       </c>
       <c r="X31" s="40" t="n">
         <f aca="false">SUM(X17:X30)</f>
-        <v>4144.86144727202</v>
+        <v>4460.97539642273</v>
       </c>
       <c r="Y31" s="40" t="n">
         <f aca="false">SUM(Y17:Y30)</f>
-        <v>4183.39013085386</v>
+        <v>4527.75759228895</v>
       </c>
       <c r="Z31" s="40" t="n">
         <f aca="false">SUM(Z17:Z30)</f>
-        <v>4222.05261792825</v>
+        <v>4595.08931825851</v>
       </c>
       <c r="AA31" s="40" t="n">
         <f aca="false">SUM(AA17:AA30)</f>
-        <v>5280.34710987353</v>
+        <v>5706.78692118985</v>
       </c>
       <c r="AB31" s="40" t="n">
         <f aca="false">SUM(AB17:AB30)</f>
-        <v>11330.4629515273</v>
+        <v>11792.1521157192</v>
       </c>
       <c r="AC31" s="40" t="n">
         <f aca="false">SUM(AC17:AC30)</f>
-        <v>5381.7115031315</v>
+        <v>5879.53230148775</v>
       </c>
       <c r="AD31" s="40" t="n">
         <f aca="false">SUM(AD17:AD30)</f>
-        <v>5434.09027078756</v>
+        <v>5968.91422122774</v>
       </c>
       <c r="AE31" s="40" t="n">
         <f aca="false">SUM(AE17:AE30)</f>
-        <v>5487.59683541393</v>
+        <v>6060.28494910299</v>
       </c>
       <c r="AF31" s="40" t="n">
         <f aca="false">SUM(AF17:AF30)</f>
-        <v>5542.22885050152</v>
+        <v>6153.63188242322</v>
       </c>
       <c r="AG31" s="40" t="n">
         <f aca="false">SUM(AG17:AG30)</f>
-        <v>5597.98403993647</v>
+        <v>6248.94273356545</v>
       </c>
       <c r="AH31" s="40" t="n">
         <f aca="false">SUM(AH17:AH30)</f>
-        <v>5654.86019588838</v>
+        <v>6346.20552209726</v>
       </c>
       <c r="AI31" s="40" t="n">
         <f aca="false">SUM(AI17:AI30)</f>
-        <v>5711.80559676172</v>
+        <v>6443.92386657201</v>
       </c>
       <c r="AJ31" s="40" t="n">
         <f aca="false">SUM(AJ17:AJ30)</f>
-        <v>5768.81816520887</v>
+        <v>6542.08637809115</v>
       </c>
       <c r="AK31" s="40" t="n">
         <f aca="false">SUM(AK17:AK30)</f>
-        <v>5825.89588620261</v>
+        <v>6640.68195247856</v>
       </c>
       <c r="AL31" s="40" t="n">
         <f aca="false">SUM(AL17:AL30)</f>
-        <v>5883.03680516653</v>
+        <v>6739.69976316253</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11375,143 +11375,143 @@
       </c>
       <c r="D32" s="39" t="n">
         <f aca="false">(D13+D31)*in_Contingency</f>
-        <v>357.9674125</v>
+        <v>358.135768571429</v>
       </c>
       <c r="E32" s="39" t="n">
         <f aca="false">(E13+E31)*in_Contingency</f>
-        <v>284.545802625</v>
+        <v>284.880642928571</v>
       </c>
       <c r="F32" s="39" t="n">
         <f aca="false">(F13+F31)*in_Contingency</f>
-        <v>288.57719104625</v>
+        <v>291.949900426786</v>
       </c>
       <c r="G32" s="39" t="n">
         <f aca="false">(G13+G31)*in_Contingency</f>
-        <v>363.981717814863</v>
+        <v>367.506066487545</v>
       </c>
       <c r="H32" s="39" t="n">
         <f aca="false">(H13+H31)*in_Contingency</f>
-        <v>264.793128780417</v>
+        <v>268.809672771785</v>
       </c>
       <c r="I32" s="39" t="n">
         <f aca="false">(I13+I31)*in_Contingency</f>
-        <v>190.650053417004</v>
+        <v>195.198708586419</v>
       </c>
       <c r="J32" s="39" t="n">
         <f aca="false">(J13+J31)*in_Contingency</f>
-        <v>191.552554314494</v>
+        <v>196.673083505687</v>
       </c>
       <c r="K32" s="39" t="n">
         <f aca="false">(K13+K31)*in_Contingency</f>
-        <v>228.288192185059</v>
+        <v>234.020209364473</v>
       </c>
       <c r="L32" s="39" t="n">
         <f aca="false">(L13+L31)*in_Contingency</f>
-        <v>226.426025919507</v>
+        <v>230.52420020179</v>
       </c>
       <c r="M32" s="39" t="n">
         <f aca="false">(M13+M31)*in_Contingency</f>
-        <v>227.465612641922</v>
+        <v>232.254072205674</v>
       </c>
       <c r="N32" s="39" t="n">
         <f aca="false">(N13+N31)*in_Contingency</f>
-        <v>228.217807762665</v>
+        <v>233.46353115946</v>
       </c>
       <c r="O32" s="39" t="n">
         <f aca="false">(O13+O31)*in_Contingency</f>
-        <v>444.643604310135</v>
+        <v>450.682947562815</v>
       </c>
       <c r="P32" s="39" t="n">
         <f aca="false">(P13+P31)*in_Contingency</f>
-        <v>445.89994478083</v>
+        <v>452.590676923521</v>
       </c>
       <c r="Q32" s="39" t="n">
         <f aca="false">(Q13+Q31)*in_Contingency</f>
-        <v>447.265045437406</v>
+        <v>454.724600984585</v>
       </c>
       <c r="R32" s="39" t="n">
         <f aca="false">(R13+R31)*in_Contingency</f>
-        <v>448.738642274283</v>
+        <v>457.083857045684</v>
       </c>
       <c r="S32" s="39" t="n">
         <f aca="false">(S13+S31)*in_Contingency</f>
-        <v>450.320479206055</v>
+        <v>459.667603974007</v>
       </c>
       <c r="T32" s="39" t="n">
         <f aca="false">(T13+T31)*in_Contingency</f>
-        <v>452.010307829873</v>
+        <v>462.475021665058</v>
       </c>
       <c r="U32" s="39" t="n">
         <f aca="false">(U13+U31)*in_Contingency</f>
-        <v>453.807887194977</v>
+        <v>465.505310516958</v>
       </c>
       <c r="V32" s="39" t="n">
         <f aca="false">(V13+V31)*in_Contingency</f>
-        <v>455.712983579128</v>
+        <v>468.757690917874</v>
       </c>
       <c r="W32" s="39" t="n">
         <f aca="false">(W13+W31)*in_Contingency</f>
-        <v>457.625410271754</v>
+        <v>472.039716058766</v>
       </c>
       <c r="X32" s="39" t="n">
         <f aca="false">(X13+X31)*in_Contingency</f>
-        <v>459.544947363601</v>
+        <v>475.350644821136</v>
       </c>
       <c r="Y32" s="39" t="n">
         <f aca="false">(Y13+Y31)*in_Contingency</f>
-        <v>461.471381542693</v>
+        <v>478.689754614447</v>
       </c>
       <c r="Z32" s="39" t="n">
         <f aca="false">(Z13+Z31)*in_Contingency</f>
-        <v>463.404505896412</v>
+        <v>482.056340912925</v>
       </c>
       <c r="AA32" s="39" t="n">
         <f aca="false">(AA13+AA31)*in_Contingency</f>
-        <v>709.303324243677</v>
+        <v>730.625314809493</v>
       </c>
       <c r="AB32" s="39" t="n">
         <f aca="false">(AB13+AB31)*in_Contingency</f>
-        <v>1011.80911632637</v>
+        <v>1034.89357453596</v>
       </c>
       <c r="AC32" s="39" t="n">
         <f aca="false">(AC13+AC31)*in_Contingency</f>
-        <v>714.371543906575</v>
+        <v>739.262583824387</v>
       </c>
       <c r="AD32" s="39" t="n">
         <f aca="false">(AD13+AD31)*in_Contingency</f>
-        <v>716.990482289378</v>
+        <v>743.731679811387</v>
       </c>
       <c r="AE32" s="39" t="n">
         <f aca="false">(AE13+AE31)*in_Contingency</f>
-        <v>719.665810520697</v>
+        <v>748.300216205149</v>
       </c>
       <c r="AF32" s="39" t="n">
         <f aca="false">(AF13+AF31)*in_Contingency</f>
-        <v>722.397411275076</v>
+        <v>752.967562871161</v>
       </c>
       <c r="AG32" s="39" t="n">
         <f aca="false">(AG13+AG31)*in_Contingency</f>
-        <v>725.185170746824</v>
+        <v>757.733105428273</v>
       </c>
       <c r="AH32" s="39" t="n">
         <f aca="false">(AH13+AH31)*in_Contingency</f>
-        <v>728.028978544419</v>
+        <v>762.596244854863</v>
       </c>
       <c r="AI32" s="39" t="n">
         <f aca="false">(AI13+AI31)*in_Contingency</f>
-        <v>730.876248588086</v>
+        <v>767.482162078601</v>
       </c>
       <c r="AJ32" s="39" t="n">
         <f aca="false">(AJ13+AJ31)*in_Contingency</f>
-        <v>733.726877010444</v>
+        <v>772.390287654558</v>
       </c>
       <c r="AK32" s="39" t="n">
         <f aca="false">(AK13+AK31)*in_Contingency</f>
-        <v>736.58076306013</v>
+        <v>777.320066373928</v>
       </c>
       <c r="AL32" s="39" t="n">
         <f aca="false">(AL13+AL31)*in_Contingency</f>
-        <v>739.437809008326</v>
+        <v>782.270956908127</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11567,143 +11567,143 @@
       </c>
       <c r="D34" s="40" t="n">
         <f aca="false">D13+D31+D32</f>
-        <v>7517.3156625</v>
+        <v>7520.85114</v>
       </c>
       <c r="E34" s="40" t="n">
         <f aca="false">E13+E31+E32</f>
-        <v>5975.461855125</v>
+        <v>5982.4935015</v>
       </c>
       <c r="F34" s="40" t="n">
         <f aca="false">F13+F31+F32</f>
-        <v>6060.12101197125</v>
+        <v>6130.9479089625</v>
       </c>
       <c r="G34" s="40" t="n">
         <f aca="false">G13+G31+G32</f>
-        <v>7643.61607411211</v>
+        <v>7717.62739623844</v>
       </c>
       <c r="H34" s="40" t="n">
         <f aca="false">H13+H31+H32</f>
-        <v>5560.65570438875</v>
+        <v>5645.00312820748</v>
       </c>
       <c r="I34" s="40" t="n">
         <f aca="false">I13+I31+I32</f>
-        <v>4003.65112175709</v>
+        <v>4099.17288031479</v>
       </c>
       <c r="J34" s="40" t="n">
         <f aca="false">J13+J31+J32</f>
-        <v>4022.60364060437</v>
+        <v>4130.13475361942</v>
       </c>
       <c r="K34" s="40" t="n">
         <f aca="false">K13+K31+K32</f>
-        <v>4794.05203588624</v>
+        <v>4914.42439665393</v>
       </c>
       <c r="L34" s="40" t="n">
         <f aca="false">L13+L31+L32</f>
-        <v>4754.94654430966</v>
+        <v>4841.00820423759</v>
       </c>
       <c r="M34" s="40" t="n">
         <f aca="false">M13+M31+M32</f>
-        <v>4776.77786548037</v>
+        <v>4877.33551631915</v>
       </c>
       <c r="N34" s="40" t="n">
         <f aca="false">N13+N31+N32</f>
-        <v>4792.57396301596</v>
+        <v>4902.73415434867</v>
       </c>
       <c r="O34" s="40" t="n">
         <f aca="false">O13+O31+O32</f>
-        <v>9337.51569051282</v>
+        <v>9464.3418988191</v>
       </c>
       <c r="P34" s="40" t="n">
         <f aca="false">P13+P31+P32</f>
-        <v>9363.89884039744</v>
+        <v>9504.40421539394</v>
       </c>
       <c r="Q34" s="40" t="n">
         <f aca="false">Q13+Q31+Q32</f>
-        <v>9392.56595418552</v>
+        <v>9549.21662067628</v>
       </c>
       <c r="R34" s="40" t="n">
         <f aca="false">R13+R31+R32</f>
-        <v>9423.51148775995</v>
+        <v>9598.76099795937</v>
       </c>
       <c r="S34" s="40" t="n">
         <f aca="false">S13+S31+S32</f>
-        <v>9456.73006332715</v>
+        <v>9653.01968345414</v>
       </c>
       <c r="T34" s="40" t="n">
         <f aca="false">T13+T31+T32</f>
-        <v>9492.21646442734</v>
+        <v>9711.97545496622</v>
       </c>
       <c r="U34" s="40" t="n">
         <f aca="false">U13+U31+U32</f>
-        <v>9529.96563109452</v>
+        <v>9775.61152085613</v>
       </c>
       <c r="V34" s="40" t="n">
         <f aca="false">V13+V31+V32</f>
-        <v>9569.97265516168</v>
+        <v>9843.91150927535</v>
       </c>
       <c r="W34" s="40" t="n">
         <f aca="false">W13+W31+W32</f>
-        <v>9610.13361570683</v>
+        <v>9912.83403723409</v>
       </c>
       <c r="X34" s="40" t="n">
         <f aca="false">X13+X31+X32</f>
-        <v>9650.44389463563</v>
+        <v>9982.36354124386</v>
       </c>
       <c r="Y34" s="40" t="n">
         <f aca="false">Y13+Y31+Y32</f>
-        <v>9690.89901239656</v>
+        <v>10052.4848469034</v>
       </c>
       <c r="Z34" s="40" t="n">
         <f aca="false">Z13+Z31+Z32</f>
-        <v>9731.49462382466</v>
+        <v>10123.1831591714</v>
       </c>
       <c r="AA34" s="40" t="n">
         <f aca="false">AA13+AA31+AA32</f>
-        <v>14895.3698091172</v>
+        <v>15343.1316109993</v>
       </c>
       <c r="AB34" s="40" t="n">
         <f aca="false">AB13+AB31+AB32</f>
-        <v>21247.9914428537</v>
+        <v>21732.7650652551</v>
       </c>
       <c r="AC34" s="40" t="n">
         <f aca="false">AC13+AC31+AC32</f>
-        <v>15001.8024220381</v>
+        <v>15524.5142603121</v>
       </c>
       <c r="AD34" s="40" t="n">
         <f aca="false">AD13+AD31+AD32</f>
-        <v>15056.8001280769</v>
+        <v>15618.3652760391</v>
       </c>
       <c r="AE34" s="40" t="n">
         <f aca="false">AE13+AE31+AE32</f>
-        <v>15112.9820209346</v>
+        <v>15714.3045403081</v>
       </c>
       <c r="AF34" s="40" t="n">
         <f aca="false">AF13+AF31+AF32</f>
-        <v>15170.3456367766</v>
+        <v>15812.3188202944</v>
       </c>
       <c r="AG34" s="40" t="n">
         <f aca="false">AG13+AG31+AG32</f>
-        <v>15228.8885856833</v>
+        <v>15912.3952139937</v>
       </c>
       <c r="AH34" s="40" t="n">
         <f aca="false">AH13+AH31+AH32</f>
-        <v>15288.6085494328</v>
+        <v>16014.5211419521</v>
       </c>
       <c r="AI34" s="40" t="n">
         <f aca="false">AI13+AI31+AI32</f>
-        <v>15348.4012203498</v>
+        <v>16117.1254036506</v>
       </c>
       <c r="AJ34" s="40" t="n">
         <f aca="false">AJ13+AJ31+AJ32</f>
-        <v>15408.2644172193</v>
+        <v>16220.1960407457</v>
       </c>
       <c r="AK34" s="40" t="n">
         <f aca="false">AK13+AK31+AK32</f>
-        <v>15468.1960242627</v>
+        <v>16323.7213938525</v>
       </c>
       <c r="AL34" s="40" t="n">
         <f aca="false">AL13+AL31+AL32</f>
-        <v>15528.1939891749</v>
+        <v>16427.6900950707</v>
       </c>
     </row>
   </sheetData>
@@ -12359,143 +12359,143 @@
       </c>
       <c r="D8" s="44" t="n">
         <f aca="false">Revenue!D28</f>
-        <v>181.475</v>
+        <v>246.84</v>
       </c>
       <c r="E8" s="44" t="n">
         <f aca="false">Revenue!E28</f>
-        <v>357.50575</v>
+        <v>487.509</v>
       </c>
       <c r="F8" s="44" t="n">
         <f aca="false">Revenue!F28</f>
-        <v>813.8555775</v>
+        <v>1236.241275</v>
       </c>
       <c r="G8" s="44" t="n">
         <f aca="false">Revenue!G28</f>
-        <v>970.914910175</v>
+        <v>1452.175243125</v>
       </c>
       <c r="H8" s="44" t="n">
         <f aca="false">Revenue!H28</f>
-        <v>1156.58246286975</v>
+        <v>1723.25211204688</v>
       </c>
       <c r="I8" s="44" t="n">
         <f aca="false">Revenue!I28</f>
-        <v>1341.43998898366</v>
+        <v>1995.7333092457</v>
       </c>
       <c r="J8" s="44" t="n">
         <f aca="false">Revenue!J28</f>
-        <v>1525.51178931415</v>
+        <v>2269.58372651456</v>
       </c>
       <c r="K8" s="44" t="n">
         <f aca="false">Revenue!K28</f>
-        <v>1708.82143563472</v>
+        <v>2544.7691333517</v>
       </c>
       <c r="L8" s="44" t="n">
         <f aca="false">Revenue!L28</f>
-        <v>1891.39179256568</v>
+        <v>2821.2561550179</v>
       </c>
       <c r="M8" s="44" t="n">
         <f aca="false">Revenue!M28</f>
-        <v>2073.24503878871</v>
+        <v>3099.01225114246</v>
       </c>
       <c r="N8" s="44" t="n">
         <f aca="false">Revenue!N28</f>
-        <v>2254.40268762505</v>
+        <v>3378.0056948639</v>
       </c>
       <c r="O8" s="44" t="n">
         <f aca="false">Revenue!O28</f>
-        <v>2556.62988734611</v>
+        <v>3895.9889134043</v>
       </c>
       <c r="P8" s="44" t="n">
         <f aca="false">Revenue!P28</f>
-        <v>2939.12224072573</v>
+        <v>4454.55597181919</v>
       </c>
       <c r="Q8" s="44" t="n">
         <f aca="false">Revenue!Q28</f>
-        <v>3325.13382350396</v>
+        <v>5027.04055377371</v>
       </c>
       <c r="R8" s="44" t="n">
         <f aca="false">Revenue!R28</f>
-        <v>3714.55905879884</v>
+        <v>5613.09472117937</v>
       </c>
       <c r="S8" s="44" t="n">
         <f aca="false">Revenue!S28</f>
-        <v>4107.29553703488</v>
+        <v>6212.37923439989</v>
       </c>
       <c r="T8" s="44" t="n">
         <f aca="false">Revenue!T28</f>
-        <v>4503.24392092383</v>
+        <v>6824.56333478989</v>
       </c>
       <c r="U8" s="44" t="n">
         <f aca="false">Revenue!U28</f>
-        <v>4902.30785329611</v>
+        <v>7449.32453267014</v>
       </c>
       <c r="V8" s="44" t="n">
         <f aca="false">Revenue!V28</f>
-        <v>5304.39386769723</v>
+        <v>8086.34840060339</v>
       </c>
       <c r="W8" s="44" t="n">
         <f aca="false">Revenue!W28</f>
-        <v>5709.41130166631</v>
+        <v>8735.3283718383</v>
       </c>
       <c r="X8" s="44" t="n">
         <f aca="false">Revenue!X28</f>
-        <v>6117.27221261632</v>
+        <v>9395.96554379235</v>
       </c>
       <c r="Y8" s="44" t="n">
         <f aca="false">Revenue!Y28</f>
-        <v>6527.89129623784</v>
+        <v>10067.9684864475</v>
       </c>
       <c r="Z8" s="44" t="n">
         <f aca="false">Revenue!Z28</f>
-        <v>6941.1858073507</v>
+        <v>10751.0530555363</v>
       </c>
       <c r="AA8" s="44" t="n">
         <f aca="false">Revenue!AA28</f>
-        <v>7724.92925728669</v>
+        <v>12188.8634540738</v>
       </c>
       <c r="AB8" s="44" t="n">
         <f aca="false">Revenue!AB28</f>
-        <v>8367.61271706809</v>
+        <v>13229.6517185032</v>
       </c>
       <c r="AC8" s="44" t="n">
         <f aca="false">Revenue!AC28</f>
-        <v>9012.00727305605</v>
+        <v>14281.5377894469</v>
       </c>
       <c r="AD8" s="44" t="n">
         <f aca="false">Revenue!AD28</f>
-        <v>9658.06159236436</v>
+        <v>15344.244221742</v>
       </c>
       <c r="AE8" s="44" t="n">
         <f aca="false">Revenue!AE28</f>
-        <v>10305.7258820934</v>
+        <v>16417.5005063547</v>
       </c>
       <c r="AF8" s="44" t="n">
         <f aca="false">Revenue!AF28</f>
-        <v>10954.9518431306</v>
+        <v>17501.042896977</v>
       </c>
       <c r="AG8" s="44" t="n">
         <f aca="false">Revenue!AG28</f>
-        <v>11605.6926253367</v>
+        <v>18594.6142409589</v>
       </c>
       <c r="AH8" s="44" t="n">
         <f aca="false">Revenue!AH28</f>
-        <v>12257.9027840766</v>
+        <v>19697.9638144661</v>
       </c>
       <c r="AI8" s="44" t="n">
         <f aca="false">Revenue!AI28</f>
-        <v>12911.5382380543</v>
+        <v>20810.8471617607</v>
       </c>
       <c r="AJ8" s="44" t="n">
         <f aca="false">Revenue!AJ28</f>
-        <v>13566.5562284127</v>
+        <v>21933.025938498</v>
       </c>
       <c r="AK8" s="44" t="n">
         <f aca="false">Revenue!AK28</f>
-        <v>14222.9152790603</v>
+        <v>23064.2677589418</v>
       </c>
       <c r="AL8" s="44" t="n">
         <f aca="false">Revenue!AL28</f>
-        <v>14880.5751581885</v>
+        <v>24204.3460469995</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12511,143 +12511,143 @@
       </c>
       <c r="D9" s="6" t="n">
         <f aca="false">Costs!D17+Costs!D18+Costs!D20+Costs!D11</f>
-        <v>359.34825</v>
+        <v>362.715371428571</v>
       </c>
       <c r="E9" s="6" t="n">
         <f aca="false">Costs!E17+Costs!E18+Costs!E20+Costs!E11</f>
-        <v>368.4160525</v>
+        <v>375.112858571429</v>
       </c>
       <c r="F9" s="6" t="n">
         <f aca="false">Costs!F17+Costs!F18+Costs!F20+Costs!F11</f>
-        <v>391.923820925</v>
+        <v>413.682008535714</v>
       </c>
       <c r="G9" s="6" t="n">
         <f aca="false">Costs!G17+Costs!G18+Costs!G20+Costs!G11</f>
-        <v>400.01435629725</v>
+        <v>424.805329750893</v>
       </c>
       <c r="H9" s="6" t="n">
         <f aca="false">Costs!H17+Costs!H18+Costs!H20+Costs!H11</f>
-        <v>409.578575608332</v>
+        <v>438.769205435692</v>
       </c>
       <c r="I9" s="6" t="n">
         <f aca="false">Costs!I17+Costs!I18+Costs!I20+Costs!I11</f>
-        <v>419.101068340083</v>
+        <v>452.805421728371</v>
       </c>
       <c r="J9" s="6" t="n">
         <f aca="false">Costs!J17+Costs!J18+Costs!J20+Costs!J11</f>
-        <v>428.58308628988</v>
+        <v>466.912170113733</v>
       </c>
       <c r="K9" s="6" t="n">
         <f aca="false">Costs!K17+Costs!K18+Costs!K20+Costs!K11</f>
-        <v>1153.77584370118</v>
+        <v>1196.83768728946</v>
       </c>
       <c r="L9" s="6" t="n">
         <f aca="false">Costs!L17+Costs!L18+Costs!L20+Costs!L11</f>
-        <v>1163.18051839015</v>
+        <v>1211.0802540358</v>
       </c>
       <c r="M9" s="6" t="n">
         <f aca="false">Costs!M17+Costs!M18+Costs!M20+Costs!M11</f>
-        <v>1172.54825283844</v>
+        <v>1225.38819411347</v>
       </c>
       <c r="N9" s="6" t="n">
         <f aca="false">Costs!N17+Costs!N18+Costs!N20+Costs!N11</f>
-        <v>1181.88015525329</v>
+        <v>1239.75987318921</v>
       </c>
       <c r="O9" s="6" t="n">
         <f aca="false">Costs!O17+Costs!O18+Costs!O20+Costs!O11</f>
-        <v>1229.39968620269</v>
+        <v>1294.73686500629</v>
       </c>
       <c r="P9" s="6" t="n">
         <f aca="false">Costs!P17+Costs!P18+Costs!P20+Costs!P11</f>
-        <v>1248.52889561661</v>
+        <v>1322.43581472042</v>
       </c>
       <c r="Q9" s="6" t="n">
         <f aca="false">Costs!Q17+Costs!Q18+Costs!Q20+Costs!Q11</f>
-        <v>1267.83410874811</v>
+        <v>1350.82492469169</v>
       </c>
       <c r="R9" s="6" t="n">
         <f aca="false">Costs!R17+Costs!R18+Costs!R20+Costs!R11</f>
-        <v>1287.31004548567</v>
+        <v>1379.88694091369</v>
       </c>
       <c r="S9" s="6" t="n">
         <f aca="false">Costs!S17+Costs!S18+Costs!S20+Costs!S11</f>
-        <v>1306.9515841211</v>
+        <v>1409.60504073013</v>
       </c>
       <c r="T9" s="6" t="n">
         <f aca="false">Costs!T17+Costs!T18+Costs!T20+Costs!T11</f>
-        <v>1326.75375659746</v>
+        <v>1439.96282205116</v>
       </c>
       <c r="U9" s="6" t="n">
         <f aca="false">Costs!U17+Costs!U18+Costs!U20+Costs!U11</f>
-        <v>1346.71174389954</v>
+        <v>1470.94429283917</v>
       </c>
       <c r="V9" s="6" t="n">
         <f aca="false">Costs!V17+Costs!V18+Costs!V20+Costs!V11</f>
-        <v>1366.82087158255</v>
+        <v>1502.53386085748</v>
       </c>
       <c r="W9" s="6" t="n">
         <f aca="false">Costs!W17+Costs!W18+Costs!W20+Costs!W11</f>
-        <v>1387.07660543508</v>
+        <v>1534.71632367532</v>
       </c>
       <c r="X9" s="6" t="n">
         <f aca="false">Costs!X17+Costs!X18+Costs!X20+Costs!X11</f>
-        <v>1407.47454727202</v>
+        <v>1567.47685892273</v>
       </c>
       <c r="Y9" s="6" t="n">
         <f aca="false">Costs!Y17+Costs!Y18+Costs!Y20+Costs!Y11</f>
-        <v>1428.01043085386</v>
+        <v>1600.80101478894</v>
       </c>
       <c r="Z9" s="6" t="n">
         <f aca="false">Costs!Z17+Costs!Z18+Costs!Z20+Costs!Z11</f>
-        <v>1448.68011792825</v>
+        <v>1634.67470075851</v>
       </c>
       <c r="AA9" s="6" t="n">
         <f aca="false">Costs!AA17+Costs!AA18+Costs!AA20+Costs!AA11</f>
-        <v>2303.52791987353</v>
+        <v>2510.65385345235</v>
       </c>
       <c r="AB9" s="6" t="n">
         <f aca="false">Costs!AB17+Costs!AB18+Costs!AB20+Costs!AB11</f>
-        <v>2334.75132152732</v>
+        <v>2560.38623538166</v>
       </c>
       <c r="AC9" s="6" t="n">
         <f aca="false">Costs!AC17+Costs!AC18+Costs!AC20+Costs!AC11</f>
-        <v>2366.0578531315</v>
+        <v>2610.64890802525</v>
       </c>
       <c r="AD9" s="6" t="n">
         <f aca="false">Costs!AD17+Costs!AD18+Costs!AD20+Costs!AD11</f>
-        <v>2397.44502078756</v>
+        <v>2661.42861411524</v>
       </c>
       <c r="AE9" s="6" t="n">
         <f aca="false">Costs!AE17+Costs!AE18+Costs!AE20+Costs!AE11</f>
-        <v>2428.91040541393</v>
+        <v>2712.71242781548</v>
       </c>
       <c r="AF9" s="6" t="n">
         <f aca="false">Costs!AF17+Costs!AF18+Costs!AF20+Costs!AF11</f>
-        <v>2460.45166050151</v>
+        <v>2764.48774643572</v>
       </c>
       <c r="AG9" s="6" t="n">
         <f aca="false">Costs!AG17+Costs!AG18+Costs!AG20+Costs!AG11</f>
-        <v>2492.06650993647</v>
+        <v>2816.74228235295</v>
       </c>
       <c r="AH9" s="6" t="n">
         <f aca="false">Costs!AH17+Costs!AH18+Costs!AH20+Costs!AH11</f>
-        <v>2523.75274588838</v>
+        <v>2869.46405513475</v>
       </c>
       <c r="AI9" s="6" t="n">
         <f aca="false">Costs!AI17+Costs!AI18+Costs!AI20+Costs!AI11</f>
-        <v>2555.50822676172</v>
+        <v>2922.64138385951</v>
       </c>
       <c r="AJ9" s="6" t="n">
         <f aca="false">Costs!AJ17+Costs!AJ18+Costs!AJ20+Costs!AJ11</f>
-        <v>2587.33087520887</v>
+        <v>2976.26287962865</v>
       </c>
       <c r="AK9" s="6" t="n">
         <f aca="false">Costs!AK17+Costs!AK18+Costs!AK20+Costs!AK11</f>
-        <v>2619.21867620261</v>
+        <v>3030.31743826606</v>
       </c>
       <c r="AL9" s="6" t="n">
         <f aca="false">Costs!AL17+Costs!AL18+Costs!AL20+Costs!AL11</f>
-        <v>2651.16967516653</v>
+        <v>3084.79423320003</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12663,143 +12663,143 @@
       </c>
       <c r="D10" s="40" t="n">
         <f aca="false">D8-D9</f>
-        <v>-177.87325</v>
+        <v>-115.875371428571</v>
       </c>
       <c r="E10" s="40" t="n">
         <f aca="false">E8-E9</f>
-        <v>-10.9103025</v>
+        <v>112.396141428572</v>
       </c>
       <c r="F10" s="40" t="n">
         <f aca="false">F8-F9</f>
-        <v>421.931756575</v>
+        <v>822.559266464286</v>
       </c>
       <c r="G10" s="40" t="n">
         <f aca="false">G8-G9</f>
-        <v>570.90055387775</v>
+        <v>1027.36991337411</v>
       </c>
       <c r="H10" s="40" t="n">
         <f aca="false">H8-H9</f>
-        <v>747.003887261418</v>
+        <v>1284.48290661118</v>
       </c>
       <c r="I10" s="40" t="n">
         <f aca="false">I8-I9</f>
-        <v>922.338920643575</v>
+        <v>1542.92788751733</v>
       </c>
       <c r="J10" s="40" t="n">
         <f aca="false">J8-J9</f>
-        <v>1096.92870302427</v>
+        <v>1802.67155640083</v>
       </c>
       <c r="K10" s="40" t="n">
         <f aca="false">K8-K9</f>
-        <v>555.04559193354</v>
+        <v>1347.93144606224</v>
       </c>
       <c r="L10" s="40" t="n">
         <f aca="false">L8-L9</f>
-        <v>728.211274175534</v>
+        <v>1610.17590098211</v>
       </c>
       <c r="M10" s="40" t="n">
         <f aca="false">M8-M9</f>
-        <v>900.696785950268</v>
+        <v>1873.62405702898</v>
       </c>
       <c r="N10" s="40" t="n">
         <f aca="false">N8-N9</f>
-        <v>1072.52253237176</v>
+        <v>2138.24582167469</v>
       </c>
       <c r="O10" s="40" t="n">
         <f aca="false">O8-O9</f>
-        <v>1327.23020114343</v>
+        <v>2601.25204839801</v>
       </c>
       <c r="P10" s="40" t="n">
         <f aca="false">P8-P9</f>
-        <v>1690.59334510912</v>
+        <v>3132.12015709877</v>
       </c>
       <c r="Q10" s="40" t="n">
         <f aca="false">Q8-Q9</f>
-        <v>2057.29971475585</v>
+        <v>3676.21562908202</v>
       </c>
       <c r="R10" s="40" t="n">
         <f aca="false">R8-R9</f>
-        <v>2427.24901331317</v>
+        <v>4233.20778026568</v>
       </c>
       <c r="S10" s="40" t="n">
         <f aca="false">S8-S9</f>
-        <v>2800.34395291378</v>
+        <v>4802.77419366976</v>
       </c>
       <c r="T10" s="40" t="n">
         <f aca="false">T8-T9</f>
-        <v>3176.49016432637</v>
+        <v>5384.60051273873</v>
       </c>
       <c r="U10" s="40" t="n">
         <f aca="false">U8-U9</f>
-        <v>3555.59610939658</v>
+        <v>5978.38023983097</v>
       </c>
       <c r="V10" s="40" t="n">
         <f aca="false">V8-V9</f>
-        <v>3937.57299611468</v>
+        <v>6583.81453974591</v>
       </c>
       <c r="W10" s="40" t="n">
         <f aca="false">W8-W9</f>
-        <v>4322.33469623124</v>
+        <v>7200.61204816298</v>
       </c>
       <c r="X10" s="40" t="n">
         <f aca="false">X8-X9</f>
-        <v>4709.7976653443</v>
+        <v>7828.48868486962</v>
       </c>
       <c r="Y10" s="40" t="n">
         <f aca="false">Y8-Y9</f>
-        <v>5099.88086538397</v>
+        <v>8467.16747165859</v>
       </c>
       <c r="Z10" s="40" t="n">
         <f aca="false">Z8-Z9</f>
-        <v>5492.50568942245</v>
+        <v>9116.37835477784</v>
       </c>
       <c r="AA10" s="40" t="n">
         <f aca="false">AA8-AA9</f>
-        <v>5421.40133741316</v>
+        <v>9678.20960062146</v>
       </c>
       <c r="AB10" s="40" t="n">
         <f aca="false">AB8-AB9</f>
-        <v>6032.86139554076</v>
+        <v>10669.2654831215</v>
       </c>
       <c r="AC10" s="40" t="n">
         <f aca="false">AC8-AC9</f>
-        <v>6645.94941992454</v>
+        <v>11670.8888814216</v>
       </c>
       <c r="AD10" s="40" t="n">
         <f aca="false">AD8-AD9</f>
-        <v>7260.6165715768</v>
+        <v>12682.8156076267</v>
       </c>
       <c r="AE10" s="40" t="n">
         <f aca="false">AE8-AE9</f>
-        <v>7876.8154766795</v>
+        <v>13704.7880785392</v>
       </c>
       <c r="AF10" s="40" t="n">
         <f aca="false">AF8-AF9</f>
-        <v>8494.50018262912</v>
+        <v>14736.5551505413</v>
       </c>
       <c r="AG10" s="40" t="n">
         <f aca="false">AG8-AG9</f>
-        <v>9113.62611540024</v>
+        <v>15777.8719586059</v>
       </c>
       <c r="AH10" s="40" t="n">
         <f aca="false">AH8-AH9</f>
-        <v>9734.15003818823</v>
+        <v>16828.4997593314</v>
       </c>
       <c r="AI10" s="40" t="n">
         <f aca="false">AI8-AI9</f>
-        <v>10356.0300112926</v>
+        <v>17888.2057779012</v>
       </c>
       <c r="AJ10" s="40" t="n">
         <f aca="false">AJ8-AJ9</f>
-        <v>10979.2253532038</v>
+        <v>18956.7630588693</v>
       </c>
       <c r="AK10" s="40" t="n">
         <f aca="false">AK8-AK9</f>
-        <v>11603.6966028577</v>
+        <v>20033.9503206757</v>
       </c>
       <c r="AL10" s="40" t="n">
         <f aca="false">AL8-AL9</f>
-        <v>12229.405483022</v>
+        <v>21119.5518137994</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12815,143 +12815,143 @@
       </c>
       <c r="D11" s="24" t="n">
         <f aca="false">IF(D8&gt;0,D10/D8,0)</f>
-        <v>-0.980152913624466</v>
+        <v>-0.46943514595921</v>
       </c>
       <c r="E11" s="24" t="n">
         <f aca="false">IF(E8&gt;0,E10/E8,0)</f>
-        <v>-0.030517837824986</v>
+        <v>0.230551931202442</v>
       </c>
       <c r="F11" s="24" t="n">
         <f aca="false">IF(F8&gt;0,F10/F8,0)</f>
-        <v>0.518435663820219</v>
+        <v>0.665371140002008</v>
       </c>
       <c r="G11" s="24" t="n">
         <f aca="false">IF(G8&gt;0,G10/G8,0)</f>
-        <v>0.588002664182848</v>
+        <v>0.707469651640159</v>
       </c>
       <c r="H11" s="24" t="n">
         <f aca="false">IF(H8&gt;0,H10/H8,0)</f>
-        <v>0.64587170499536</v>
+        <v>0.745383045017991</v>
       </c>
       <c r="I11" s="24" t="n">
         <f aca="false">IF(I8&gt;0,I10/I8,0)</f>
-        <v>0.687573747777107</v>
+        <v>0.773113261360802</v>
       </c>
       <c r="J11" s="24" t="n">
         <f aca="false">IF(J8&gt;0,J10/J8,0)</f>
-        <v>0.719056195244112</v>
+        <v>0.794274093236129</v>
       </c>
       <c r="K11" s="24" t="n">
         <f aca="false">IF(K8&gt;0,K10/K8,0)</f>
-        <v>0.324811931989473</v>
+        <v>0.529687125011173</v>
       </c>
       <c r="L11" s="24" t="n">
         <f aca="false">IF(L8&gt;0,L10/L8,0)</f>
-        <v>0.385013447260291</v>
+        <v>0.570730133142373</v>
       </c>
       <c r="M11" s="24" t="n">
         <f aca="false">IF(M8&gt;0,M10/M8,0)</f>
-        <v>0.43443817257438</v>
+        <v>0.604587496012082</v>
       </c>
       <c r="N11" s="24" t="n">
         <f aca="false">IF(N8&gt;0,N10/N8,0)</f>
-        <v>0.47574576550103</v>
+        <v>0.632990591142518</v>
       </c>
       <c r="O11" s="24" t="n">
         <f aca="false">IF(O8&gt;0,O10/O8,0)</f>
-        <v>0.519132709709948</v>
+        <v>0.667674396980008</v>
       </c>
       <c r="P11" s="24" t="n">
         <f aca="false">IF(P8&gt;0,P10/P8,0)</f>
-        <v>0.575203481394391</v>
+        <v>0.703127354760715</v>
       </c>
       <c r="Q11" s="24" t="n">
         <f aca="false">IF(Q8&gt;0,Q10/Q8,0)</f>
-        <v>0.618711854606775</v>
+        <v>0.731288238031489</v>
       </c>
       <c r="R11" s="24" t="n">
         <f aca="false">IF(R8&gt;0,R10/R8,0)</f>
-        <v>0.653442030370642</v>
+        <v>0.754166460846084</v>
       </c>
       <c r="S11" s="24" t="n">
         <f aca="false">IF(S8&gt;0,S10/S8,0)</f>
-        <v>0.681797530190728</v>
+        <v>0.773097393519586</v>
       </c>
       <c r="T11" s="24" t="n">
         <f aca="false">IF(T8&gt;0,T10/T8,0)</f>
-        <v>0.705378216260317</v>
+        <v>0.789002936684521</v>
       </c>
       <c r="U11" s="24" t="n">
         <f aca="false">IF(U8&gt;0,U10/U8,0)</f>
-        <v>0.725290254263803</v>
+        <v>0.802539909975982</v>
       </c>
       <c r="V11" s="24" t="n">
         <f aca="false">IF(V8&gt;0,V10/V8,0)</f>
-        <v>0.742322891988426</v>
+        <v>0.814188829565474</v>
       </c>
       <c r="W11" s="24" t="n">
         <f aca="false">IF(W8&gt;0,W10/W8,0)</f>
-        <v>0.757054356019113</v>
+        <v>0.824309257952675</v>
       </c>
       <c r="X11" s="24" t="n">
         <f aca="false">IF(X8&gt;0,X10/X8,0)</f>
-        <v>0.769917947354176</v>
+        <v>0.833175542032685</v>
       </c>
       <c r="Y11" s="24" t="n">
         <f aca="false">IF(Y8&gt;0,Y10/Y8,0)</f>
-        <v>0.78124475944064</v>
+        <v>0.84100059342222</v>
       </c>
       <c r="Z11" s="24" t="n">
         <f aca="false">IF(Z8&gt;0,Z10/Z8,0)</f>
-        <v>0.791292128155668</v>
+        <v>0.847952131543364</v>
       </c>
       <c r="AA11" s="24" t="n">
         <f aca="false">IF(AA8&gt;0,AA10/AA8,0)</f>
-        <v>0.701805952759932</v>
+        <v>0.794020676094027</v>
       </c>
       <c r="AB11" s="24" t="n">
         <f aca="false">IF(AB8&gt;0,AB10/AB8,0)</f>
-        <v>0.720977607297127</v>
+        <v>0.806466089216796</v>
       </c>
       <c r="AC11" s="24" t="n">
         <f aca="false">IF(AC8&gt;0,AC10/AC8,0)</f>
-        <v>0.737454955212308</v>
+        <v>0.81720113432362</v>
       </c>
       <c r="AD11" s="24" t="n">
         <f aca="false">IF(AD8&gt;0,AD10/AD8,0)</f>
-        <v>0.751767474470967</v>
+        <v>0.826551990723392</v>
       </c>
       <c r="AE11" s="24" t="n">
         <f aca="false">IF(AE8&gt;0,AE10/AE8,0)</f>
-        <v>0.764314475932816</v>
+        <v>0.834767026395676</v>
       </c>
       <c r="AF11" s="24" t="n">
         <f aca="false">IF(AF8&gt;0,AF10/AF8,0)</f>
-        <v>0.775402786271091</v>
+        <v>0.842038685196684</v>
       </c>
       <c r="AG11" s="24" t="n">
         <f aca="false">IF(AG8&gt;0,AG10/AG8,0)</f>
-        <v>0.785272056534052</v>
+        <v>0.848518380330341</v>
       </c>
       <c r="AH11" s="24" t="n">
         <f aca="false">IF(AH8&gt;0,AH10/AH8,0)</f>
-        <v>0.794112191102804</v>
+        <v>0.854326869408328</v>
       </c>
       <c r="AI11" s="24" t="n">
         <f aca="false">IF(AI8&gt;0,AI10/AI8,0)</f>
-        <v>0.802075617974793</v>
+        <v>0.859561633356773</v>
       </c>
       <c r="AJ11" s="24" t="n">
         <f aca="false">IF(AJ8&gt;0,AJ10/AJ8,0)</f>
-        <v>0.809286097986298</v>
+        <v>0.864302222229877</v>
       </c>
       <c r="AK11" s="24" t="n">
         <f aca="false">IF(AK8&gt;0,AK10/AK8,0)</f>
-        <v>0.815845160797748</v>
+        <v>0.868614192744479</v>
       </c>
       <c r="AL11" s="24" t="n">
         <f aca="false">IF(AL8&gt;0,AL10/AL8,0)</f>
-        <v>0.821836881506046</v>
+        <v>0.872552052131049</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13127,135 +13127,135 @@
       </c>
       <c r="F13" s="6" t="n">
         <f aca="false">Costs!F10+Costs!F21+Costs!F22+Costs!F23</f>
-        <v>2779.62</v>
+        <v>2825.316</v>
       </c>
       <c r="G13" s="6" t="n">
         <f aca="false">Costs!G10+Costs!G21+Costs!G22+Costs!G23</f>
-        <v>2779.62</v>
+        <v>2825.316</v>
       </c>
       <c r="H13" s="6" t="n">
         <f aca="false">Costs!H10+Costs!H21+Costs!H22+Costs!H23</f>
-        <v>2786.284</v>
+        <v>2837.42425</v>
       </c>
       <c r="I13" s="6" t="n">
         <f aca="false">Costs!I10+Costs!I21+Costs!I22+Costs!I23</f>
-        <v>2793.9</v>
+        <v>2851.16875</v>
       </c>
       <c r="J13" s="6" t="n">
         <f aca="false">Costs!J10+Costs!J21+Costs!J22+Costs!J23</f>
-        <v>2802.468</v>
+        <v>2866.5495</v>
       </c>
       <c r="K13" s="6" t="n">
         <f aca="false">Costs!K10+Costs!K21+Costs!K22+Costs!K23</f>
-        <v>2811.988</v>
+        <v>2883.5665</v>
       </c>
       <c r="L13" s="6" t="n">
         <f aca="false">Costs!L10+Costs!L21+Costs!L22+Costs!L23</f>
-        <v>2765.34</v>
+        <v>2799.40375</v>
       </c>
       <c r="M13" s="6" t="n">
         <f aca="false">Costs!M10+Costs!M21+Costs!M22+Costs!M23</f>
-        <v>2776.764</v>
+        <v>2819.69325</v>
       </c>
       <c r="N13" s="6" t="n">
         <f aca="false">Costs!N10+Costs!N21+Costs!N22+Costs!N23</f>
-        <v>2782.476</v>
+        <v>2829.51075</v>
       </c>
       <c r="O13" s="6" t="n">
         <f aca="false">Costs!O10+Costs!O21+Costs!O22+Costs!O23</f>
-        <v>4916.2224</v>
+        <v>4971.67208625</v>
       </c>
       <c r="P13" s="6" t="n">
         <f aca="false">Costs!P10+Costs!P21+Costs!P22+Costs!P23</f>
-        <v>4922.22</v>
+        <v>4982.12772375</v>
       </c>
       <c r="Q13" s="6" t="n">
         <f aca="false">Costs!Q10+Costs!Q21+Costs!Q22+Costs!Q23</f>
-        <v>4930.2168</v>
+        <v>4996.417095</v>
       </c>
       <c r="R13" s="6" t="n">
         <f aca="false">Costs!R10+Costs!R21+Costs!R22+Costs!R23</f>
-        <v>4940.2128</v>
+        <v>5014.5402</v>
       </c>
       <c r="S13" s="6" t="n">
         <f aca="false">Costs!S10+Costs!S21+Costs!S22+Costs!S23</f>
-        <v>4952.208</v>
+        <v>5036.49703875</v>
       </c>
       <c r="T13" s="6" t="n">
         <f aca="false">Costs!T10+Costs!T21+Costs!T22+Costs!T23</f>
-        <v>4966.2024</v>
+        <v>5062.28761125</v>
       </c>
       <c r="U13" s="6" t="n">
         <f aca="false">Costs!U10+Costs!U21+Costs!U22+Costs!U23</f>
-        <v>4982.196</v>
+        <v>5091.9119175</v>
       </c>
       <c r="V13" s="6" t="n">
         <f aca="false">Costs!V10+Costs!V21+Costs!V22+Costs!V23</f>
-        <v>5000.1888</v>
+        <v>5125.3699575</v>
       </c>
       <c r="W13" s="6" t="n">
         <f aca="false">Costs!W10+Costs!W21+Costs!W22+Costs!W23</f>
-        <v>5018.1816</v>
+        <v>5158.8279975</v>
       </c>
       <c r="X13" s="6" t="n">
         <f aca="false">Costs!X10+Costs!X21+Costs!X22+Costs!X23</f>
-        <v>5036.1744</v>
+        <v>5192.2860375</v>
       </c>
       <c r="Y13" s="6" t="n">
         <f aca="false">Costs!Y10+Costs!Y21+Costs!Y22+Costs!Y23</f>
-        <v>5054.1672</v>
+        <v>5225.7440775</v>
       </c>
       <c r="Z13" s="6" t="n">
         <f aca="false">Costs!Z10+Costs!Z21+Costs!Z22+Costs!Z23</f>
-        <v>5072.16</v>
+        <v>5259.2021175</v>
       </c>
       <c r="AA13" s="6" t="n">
         <f aca="false">Costs!AA10+Costs!AA21+Costs!AA22+Costs!AA23</f>
-        <v>6209.66044</v>
+        <v>6428.9743177375</v>
       </c>
       <c r="AB13" s="6" t="n">
         <f aca="false">Costs!AB10+Costs!AB21+Costs!AB22+Costs!AB23</f>
-        <v>6228.55288</v>
+        <v>6464.6071303375</v>
       </c>
       <c r="AC13" s="6" t="n">
         <f aca="false">Costs!AC10+Costs!AC21+Costs!AC22+Costs!AC23</f>
-        <v>6248.4949</v>
+        <v>6501.7246434625</v>
       </c>
       <c r="AD13" s="6" t="n">
         <f aca="false">Costs!AD10+Costs!AD21+Costs!AD22+Costs!AD23</f>
-        <v>6269.4865</v>
+        <v>6540.3268571125</v>
       </c>
       <c r="AE13" s="6" t="n">
         <f aca="false">Costs!AE10+Costs!AE21+Costs!AE22+Costs!AE23</f>
-        <v>6291.52768</v>
+        <v>6580.4137712875</v>
       </c>
       <c r="AF13" s="6" t="n">
         <f aca="false">Costs!AF10+Costs!AF21+Costs!AF22+Costs!AF23</f>
-        <v>6314.61844</v>
+        <v>6621.9853859875</v>
       </c>
       <c r="AG13" s="6" t="n">
         <f aca="false">Costs!AG10+Costs!AG21+Costs!AG22+Costs!AG23</f>
-        <v>6338.75878</v>
+        <v>6665.0417012125</v>
       </c>
       <c r="AH13" s="6" t="n">
         <f aca="false">Costs!AH10+Costs!AH21+Costs!AH22+Costs!AH23</f>
-        <v>6363.9487</v>
+        <v>6709.5827169625</v>
       </c>
       <c r="AI13" s="6" t="n">
         <f aca="false">Costs!AI10+Costs!AI21+Costs!AI22+Costs!AI23</f>
-        <v>6389.13862</v>
+        <v>6754.1237327125</v>
       </c>
       <c r="AJ13" s="6" t="n">
         <f aca="false">Costs!AJ10+Costs!AJ21+Costs!AJ22+Costs!AJ23</f>
-        <v>6414.32854</v>
+        <v>6798.6647484625</v>
       </c>
       <c r="AK13" s="6" t="n">
         <f aca="false">Costs!AK10+Costs!AK21+Costs!AK22+Costs!AK23</f>
-        <v>6439.51846</v>
+        <v>6843.2057642125</v>
       </c>
       <c r="AL13" s="6" t="n">
         <f aca="false">Costs!AL10+Costs!AL21+Costs!AL22+Costs!AL23</f>
-        <v>6464.70838</v>
+        <v>6887.7467799625</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13271,143 +13271,143 @@
       </c>
       <c r="D14" s="6" t="n">
         <f aca="false">Costs!D24+Costs!D25+Costs!D26+Costs!D27+Costs!D28+Costs!D29+Costs!D30+Costs!D32</f>
-        <v>5207.9674125</v>
+        <v>5208.13576857143</v>
       </c>
       <c r="E14" s="6" t="n">
         <f aca="false">Costs!E24+Costs!E25+Costs!E26+Costs!E27+Costs!E28+Costs!E29+Costs!E30+Costs!E32</f>
-        <v>2634.545802625</v>
+        <v>2634.88064292857</v>
       </c>
       <c r="F14" s="6" t="n">
         <f aca="false">Costs!F24+Costs!F25+Costs!F26+Costs!F27+Costs!F28+Costs!F29+Costs!F30+Costs!F32</f>
-        <v>2638.57719104625</v>
+        <v>2641.94990042679</v>
       </c>
       <c r="G14" s="6" t="n">
         <f aca="false">Costs!G24+Costs!G25+Costs!G26+Costs!G27+Costs!G28+Costs!G29+Costs!G30+Costs!G32</f>
-        <v>4213.98171781486</v>
+        <v>4217.50606648755</v>
       </c>
       <c r="H14" s="6" t="n">
         <f aca="false">Costs!H24+Costs!H25+Costs!H26+Costs!H27+Costs!H28+Costs!H29+Costs!H30+Costs!H32</f>
-        <v>2114.79312878042</v>
+        <v>2118.80967277179</v>
       </c>
       <c r="I14" s="6" t="n">
         <f aca="false">Costs!I24+Costs!I25+Costs!I26+Costs!I27+Costs!I28+Costs!I29+Costs!I30+Costs!I32</f>
-        <v>540.650053417004</v>
+        <v>545.198708586419</v>
       </c>
       <c r="J14" s="6" t="n">
         <f aca="false">Costs!J24+Costs!J25+Costs!J26+Costs!J27+Costs!J28+Costs!J29+Costs!J30+Costs!J32</f>
-        <v>541.552554314494</v>
+        <v>546.673083505687</v>
       </c>
       <c r="K14" s="6" t="n">
         <f aca="false">Costs!K24+Costs!K25+Costs!K26+Costs!K27+Costs!K28+Costs!K29+Costs!K30+Costs!K32</f>
-        <v>578.288192185059</v>
+        <v>584.020209364473</v>
       </c>
       <c r="L14" s="6" t="n">
         <f aca="false">Costs!L24+Costs!L25+Costs!L26+Costs!L27+Costs!L28+Costs!L29+Costs!L30+Costs!L32</f>
-        <v>576.426025919507</v>
+        <v>580.52420020179</v>
       </c>
       <c r="M14" s="6" t="n">
         <f aca="false">Costs!M24+Costs!M25+Costs!M26+Costs!M27+Costs!M28+Costs!M29+Costs!M30+Costs!M32</f>
-        <v>577.465612641922</v>
+        <v>582.254072205674</v>
       </c>
       <c r="N14" s="6" t="n">
         <f aca="false">Costs!N24+Costs!N25+Costs!N26+Costs!N27+Costs!N28+Costs!N29+Costs!N30+Costs!N32</f>
-        <v>578.217807762665</v>
+        <v>583.46353115946</v>
       </c>
       <c r="O14" s="6" t="n">
         <f aca="false">Costs!O24+Costs!O25+Costs!O26+Costs!O27+Costs!O28+Costs!O29+Costs!O30+Costs!O32</f>
-        <v>794.643604310135</v>
+        <v>800.682947562814</v>
       </c>
       <c r="P14" s="6" t="n">
         <f aca="false">Costs!P24+Costs!P25+Costs!P26+Costs!P27+Costs!P28+Costs!P29+Costs!P30+Costs!P32</f>
-        <v>795.89994478083</v>
+        <v>802.590676923521</v>
       </c>
       <c r="Q14" s="6" t="n">
         <f aca="false">Costs!Q24+Costs!Q25+Costs!Q26+Costs!Q27+Costs!Q28+Costs!Q29+Costs!Q30+Costs!Q32</f>
-        <v>797.265045437405</v>
+        <v>804.724600984585</v>
       </c>
       <c r="R14" s="6" t="n">
         <f aca="false">Costs!R24+Costs!R25+Costs!R26+Costs!R27+Costs!R28+Costs!R29+Costs!R30+Costs!R32</f>
-        <v>798.738642274283</v>
+        <v>807.083857045684</v>
       </c>
       <c r="S14" s="6" t="n">
         <f aca="false">Costs!S24+Costs!S25+Costs!S26+Costs!S27+Costs!S28+Costs!S29+Costs!S30+Costs!S32</f>
-        <v>800.320479206055</v>
+        <v>809.667603974007</v>
       </c>
       <c r="T14" s="6" t="n">
         <f aca="false">Costs!T24+Costs!T25+Costs!T26+Costs!T27+Costs!T28+Costs!T29+Costs!T30+Costs!T32</f>
-        <v>802.010307829873</v>
+        <v>812.475021665058</v>
       </c>
       <c r="U14" s="6" t="n">
         <f aca="false">Costs!U24+Costs!U25+Costs!U26+Costs!U27+Costs!U28+Costs!U29+Costs!U30+Costs!U32</f>
-        <v>803.807887194977</v>
+        <v>815.505310516958</v>
       </c>
       <c r="V14" s="6" t="n">
         <f aca="false">Costs!V24+Costs!V25+Costs!V26+Costs!V27+Costs!V28+Costs!V29+Costs!V30+Costs!V32</f>
-        <v>805.712983579128</v>
+        <v>818.757690917874</v>
       </c>
       <c r="W14" s="6" t="n">
         <f aca="false">Costs!W24+Costs!W25+Costs!W26+Costs!W27+Costs!W28+Costs!W29+Costs!W30+Costs!W32</f>
-        <v>807.625410271754</v>
+        <v>822.039716058766</v>
       </c>
       <c r="X14" s="6" t="n">
         <f aca="false">Costs!X24+Costs!X25+Costs!X26+Costs!X27+Costs!X28+Costs!X29+Costs!X30+Costs!X32</f>
-        <v>809.544947363601</v>
+        <v>825.350644821136</v>
       </c>
       <c r="Y14" s="6" t="n">
         <f aca="false">Costs!Y24+Costs!Y25+Costs!Y26+Costs!Y27+Costs!Y28+Costs!Y29+Costs!Y30+Costs!Y32</f>
-        <v>811.471381542693</v>
+        <v>828.689754614447</v>
       </c>
       <c r="Z14" s="6" t="n">
         <f aca="false">Costs!Z24+Costs!Z25+Costs!Z26+Costs!Z27+Costs!Z28+Costs!Z29+Costs!Z30+Costs!Z32</f>
-        <v>813.404505896413</v>
+        <v>832.056340912925</v>
       </c>
       <c r="AA14" s="6" t="n">
         <f aca="false">Costs!AA24+Costs!AA25+Costs!AA26+Costs!AA27+Costs!AA28+Costs!AA29+Costs!AA30+Costs!AA32</f>
-        <v>1059.30332424368</v>
+        <v>1080.62531480949</v>
       </c>
       <c r="AB14" s="6" t="n">
         <f aca="false">Costs!AB24+Costs!AB25+Costs!AB26+Costs!AB27+Costs!AB28+Costs!AB29+Costs!AB30+Costs!AB32</f>
-        <v>7361.80911632637</v>
+        <v>7384.89357453596</v>
       </c>
       <c r="AC14" s="6" t="n">
         <f aca="false">Costs!AC24+Costs!AC25+Costs!AC26+Costs!AC27+Costs!AC28+Costs!AC29+Costs!AC30+Costs!AC32</f>
-        <v>1064.37154390658</v>
+        <v>1089.26258382439</v>
       </c>
       <c r="AD14" s="6" t="n">
         <f aca="false">Costs!AD24+Costs!AD25+Costs!AD26+Costs!AD27+Costs!AD28+Costs!AD29+Costs!AD30+Costs!AD32</f>
-        <v>1066.99048228938</v>
+        <v>1093.73167981139</v>
       </c>
       <c r="AE14" s="6" t="n">
         <f aca="false">Costs!AE24+Costs!AE25+Costs!AE26+Costs!AE27+Costs!AE28+Costs!AE29+Costs!AE30+Costs!AE32</f>
-        <v>1069.6658105207</v>
+        <v>1098.30021620515</v>
       </c>
       <c r="AF14" s="6" t="n">
         <f aca="false">Costs!AF24+Costs!AF25+Costs!AF26+Costs!AF27+Costs!AF28+Costs!AF29+Costs!AF30+Costs!AF32</f>
-        <v>1072.39741127508</v>
+        <v>1102.96756287116</v>
       </c>
       <c r="AG14" s="6" t="n">
         <f aca="false">Costs!AG24+Costs!AG25+Costs!AG26+Costs!AG27+Costs!AG28+Costs!AG29+Costs!AG30+Costs!AG32</f>
-        <v>1075.18517074682</v>
+        <v>1107.73310542827</v>
       </c>
       <c r="AH14" s="6" t="n">
         <f aca="false">Costs!AH24+Costs!AH25+Costs!AH26+Costs!AH27+Costs!AH28+Costs!AH29+Costs!AH30+Costs!AH32</f>
-        <v>1078.02897854442</v>
+        <v>1112.59624485486</v>
       </c>
       <c r="AI14" s="6" t="n">
         <f aca="false">Costs!AI24+Costs!AI25+Costs!AI26+Costs!AI27+Costs!AI28+Costs!AI29+Costs!AI30+Costs!AI32</f>
-        <v>1080.87624858809</v>
+        <v>1117.4821620786</v>
       </c>
       <c r="AJ14" s="6" t="n">
         <f aca="false">Costs!AJ24+Costs!AJ25+Costs!AJ26+Costs!AJ27+Costs!AJ28+Costs!AJ29+Costs!AJ30+Costs!AJ32</f>
-        <v>1083.72687701044</v>
+        <v>1122.39028765456</v>
       </c>
       <c r="AK14" s="6" t="n">
         <f aca="false">Costs!AK24+Costs!AK25+Costs!AK26+Costs!AK27+Costs!AK28+Costs!AK29+Costs!AK30+Costs!AK32</f>
-        <v>1086.58076306013</v>
+        <v>1127.32006637393</v>
       </c>
       <c r="AL14" s="6" t="n">
         <f aca="false">Costs!AL24+Costs!AL25+Costs!AL26+Costs!AL27+Costs!AL28+Costs!AL29+Costs!AL30+Costs!AL32</f>
-        <v>1089.43780900833</v>
+        <v>1132.27095690813</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13423,143 +13423,143 @@
       </c>
       <c r="D15" s="40" t="n">
         <f aca="false">D10-D12-D13-D14</f>
-        <v>-7335.8406625</v>
+        <v>-7274.01114</v>
       </c>
       <c r="E15" s="40" t="n">
         <f aca="false">E10-E12-E13-E14</f>
-        <v>-5617.956105125</v>
+        <v>-5494.9845015</v>
       </c>
       <c r="F15" s="40" t="n">
         <f aca="false">F10-F12-F13-F14</f>
-        <v>-5246.26543447125</v>
+        <v>-4894.7066339625</v>
       </c>
       <c r="G15" s="40" t="n">
         <f aca="false">G10-G12-G13-G14</f>
-        <v>-6672.70116393711</v>
+        <v>-6265.45215311344</v>
       </c>
       <c r="H15" s="40" t="n">
         <f aca="false">H10-H12-H13-H14</f>
-        <v>-4404.073241519</v>
+        <v>-3921.7510161606</v>
       </c>
       <c r="I15" s="40" t="n">
         <f aca="false">I10-I12-I13-I14</f>
-        <v>-2662.21113277343</v>
+        <v>-2103.43957106909</v>
       </c>
       <c r="J15" s="40" t="n">
         <f aca="false">J10-J12-J13-J14</f>
-        <v>-2497.09185129023</v>
+        <v>-1860.55102710486</v>
       </c>
       <c r="K15" s="40" t="n">
         <f aca="false">K10-K12-K13-K14</f>
-        <v>-3085.23060025152</v>
+        <v>-2369.65526330224</v>
       </c>
       <c r="L15" s="40" t="n">
         <f aca="false">L10-L12-L13-L14</f>
-        <v>-2863.55475174397</v>
+        <v>-2019.75204921968</v>
       </c>
       <c r="M15" s="40" t="n">
         <f aca="false">M10-M12-M13-M14</f>
-        <v>-2703.53282669165</v>
+        <v>-1778.32326517669</v>
       </c>
       <c r="N15" s="40" t="n">
         <f aca="false">N10-N12-N13-N14</f>
-        <v>-2538.17127539091</v>
+        <v>-1524.72845948477</v>
       </c>
       <c r="O15" s="40" t="n">
         <f aca="false">O10-O12-O13-O14</f>
-        <v>-6780.88580316671</v>
+        <v>-5568.35298541481</v>
       </c>
       <c r="P15" s="40" t="n">
         <f aca="false">P10-P12-P13-P14</f>
-        <v>-6424.77659967171</v>
+        <v>-5049.84824357475</v>
       </c>
       <c r="Q15" s="40" t="n">
         <f aca="false">Q10-Q12-Q13-Q14</f>
-        <v>-6067.43213068156</v>
+        <v>-4522.17606690257</v>
       </c>
       <c r="R15" s="40" t="n">
         <f aca="false">R10-R12-R13-R14</f>
-        <v>-5708.95242896111</v>
+        <v>-3985.66627678</v>
       </c>
       <c r="S15" s="40" t="n">
         <f aca="false">S10-S12-S13-S14</f>
-        <v>-5349.43452629228</v>
+        <v>-3440.64044905425</v>
       </c>
       <c r="T15" s="40" t="n">
         <f aca="false">T10-T12-T13-T14</f>
-        <v>-4988.97254350351</v>
+        <v>-2887.41212017633</v>
       </c>
       <c r="U15" s="40" t="n">
         <f aca="false">U10-U12-U13-U14</f>
-        <v>-4627.6577777984</v>
+        <v>-2326.28698818599</v>
       </c>
       <c r="V15" s="40" t="n">
         <f aca="false">V10-V12-V13-V14</f>
-        <v>-4265.57878746445</v>
+        <v>-1757.56310867196</v>
       </c>
       <c r="W15" s="40" t="n">
         <f aca="false">W10-W12-W13-W14</f>
-        <v>-3900.72231404052</v>
+        <v>-1177.50566539579</v>
       </c>
       <c r="X15" s="40" t="n">
         <f aca="false">X10-X12-X13-X14</f>
-        <v>-3533.1716820193</v>
+        <v>-586.397997451518</v>
       </c>
       <c r="Y15" s="40" t="n">
         <f aca="false">Y10-Y12-Y13-Y14</f>
-        <v>-3163.00771615872</v>
+        <v>15.4836395441453</v>
       </c>
       <c r="Z15" s="40" t="n">
         <f aca="false">Z10-Z12-Z13-Z14</f>
-        <v>-2790.30881647396</v>
+        <v>627.869896364917</v>
       </c>
       <c r="AA15" s="40" t="n">
         <f aca="false">AA10-AA12-AA13-AA14</f>
-        <v>-7170.44055183052</v>
+        <v>-3154.26815692554</v>
       </c>
       <c r="AB15" s="40" t="n">
         <f aca="false">AB10-AB12-AB13-AB14</f>
-        <v>-12880.3787257856</v>
+        <v>-8503.11334675191</v>
       </c>
       <c r="AC15" s="40" t="n">
         <f aca="false">AC10-AC12-AC13-AC14</f>
-        <v>-5989.79514898203</v>
+        <v>-1242.97647086526</v>
       </c>
       <c r="AD15" s="40" t="n">
         <f aca="false">AD10-AD12-AD13-AD14</f>
-        <v>-5398.73853571258</v>
+        <v>-274.121054297172</v>
       </c>
       <c r="AE15" s="40" t="n">
         <f aca="false">AE10-AE12-AE13-AE14</f>
-        <v>-4807.2561388412</v>
+        <v>703.195966046523</v>
       </c>
       <c r="AF15" s="40" t="n">
         <f aca="false">AF10-AF12-AF13-AF14</f>
-        <v>-4215.39379364596</v>
+        <v>1688.72407668266</v>
       </c>
       <c r="AG15" s="40" t="n">
         <f aca="false">AG10-AG12-AG13-AG14</f>
-        <v>-3623.19596034658</v>
+        <v>2682.21902696513</v>
       </c>
       <c r="AH15" s="40" t="n">
         <f aca="false">AH10-AH12-AH13-AH14</f>
-        <v>-3030.70576535619</v>
+        <v>3683.44267251402</v>
       </c>
       <c r="AI15" s="40" t="n">
         <f aca="false">AI10-AI12-AI13-AI14</f>
-        <v>-2436.8629822955</v>
+        <v>4693.72175811013</v>
       </c>
       <c r="AJ15" s="40" t="n">
         <f aca="false">AJ10-AJ12-AJ13-AJ14</f>
-        <v>-1841.70818880664</v>
+        <v>5712.82989775226</v>
       </c>
       <c r="AK15" s="40" t="n">
         <f aca="false">AK10-AK12-AK13-AK14</f>
-        <v>-1245.28074520243</v>
+        <v>6740.54636508928</v>
       </c>
       <c r="AL15" s="40" t="n">
         <f aca="false">AL10-AL12-AL13-AL14</f>
-        <v>-647.61883098636</v>
+        <v>7776.65595192882</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13727,143 +13727,143 @@
       </c>
       <c r="D17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*D8,MAX(0,in_ProfitTax*D15))</f>
-        <v>1.81475</v>
+        <v>2.4684</v>
       </c>
       <c r="E17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*E8,MAX(0,in_ProfitTax*E15))</f>
-        <v>3.5750575</v>
+        <v>4.87509</v>
       </c>
       <c r="F17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*F8,MAX(0,in_ProfitTax*F15))</f>
-        <v>8.138555775</v>
+        <v>12.36241275</v>
       </c>
       <c r="G17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*G8,MAX(0,in_ProfitTax*G15))</f>
-        <v>9.70914910175</v>
+        <v>14.52175243125</v>
       </c>
       <c r="H17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*H8,MAX(0,in_ProfitTax*H15))</f>
-        <v>11.5658246286975</v>
+        <v>17.2325211204688</v>
       </c>
       <c r="I17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*I8,MAX(0,in_ProfitTax*I15))</f>
-        <v>13.4143998898366</v>
+        <v>19.957333092457</v>
       </c>
       <c r="J17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*J8,MAX(0,in_ProfitTax*J15))</f>
-        <v>15.2551178931415</v>
+        <v>22.6958372651456</v>
       </c>
       <c r="K17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*K8,MAX(0,in_ProfitTax*K15))</f>
-        <v>17.0882143563472</v>
+        <v>25.447691333517</v>
       </c>
       <c r="L17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*L8,MAX(0,in_ProfitTax*L15))</f>
-        <v>18.9139179256568</v>
+        <v>28.212561550179</v>
       </c>
       <c r="M17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*M8,MAX(0,in_ProfitTax*M15))</f>
-        <v>20.7324503878871</v>
+        <v>30.9901225114246</v>
       </c>
       <c r="N17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*N8,MAX(0,in_ProfitTax*N15))</f>
-        <v>22.5440268762505</v>
+        <v>33.780056948639</v>
       </c>
       <c r="O17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*O8,MAX(0,in_ProfitTax*O15))</f>
-        <v>25.5662988734611</v>
+        <v>38.959889134043</v>
       </c>
       <c r="P17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*P8,MAX(0,in_ProfitTax*P15))</f>
-        <v>29.3912224072573</v>
+        <v>44.5455597181919</v>
       </c>
       <c r="Q17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*Q8,MAX(0,in_ProfitTax*Q15))</f>
-        <v>33.2513382350396</v>
+        <v>50.2704055377371</v>
       </c>
       <c r="R17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*R8,MAX(0,in_ProfitTax*R15))</f>
-        <v>37.1455905879884</v>
+        <v>56.1309472117937</v>
       </c>
       <c r="S17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*S8,MAX(0,in_ProfitTax*S15))</f>
-        <v>41.0729553703488</v>
+        <v>62.1237923439989</v>
       </c>
       <c r="T17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*T8,MAX(0,in_ProfitTax*T15))</f>
-        <v>45.0324392092383</v>
+        <v>68.2456333478989</v>
       </c>
       <c r="U17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*U8,MAX(0,in_ProfitTax*U15))</f>
-        <v>49.0230785329611</v>
+        <v>74.4932453267014</v>
       </c>
       <c r="V17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*V8,MAX(0,in_ProfitTax*V15))</f>
-        <v>53.0439386769723</v>
+        <v>80.8634840060339</v>
       </c>
       <c r="W17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*W8,MAX(0,in_ProfitTax*W15))</f>
-        <v>57.0941130166631</v>
+        <v>87.353283718383</v>
       </c>
       <c r="X17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*X8,MAX(0,in_ProfitTax*X15))</f>
-        <v>61.1727221261632</v>
+        <v>93.9596554379234</v>
       </c>
       <c r="Y17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*Y8,MAX(0,in_ProfitTax*Y15))</f>
-        <v>65.2789129623784</v>
+        <v>100.679684864475</v>
       </c>
       <c r="Z17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*Z8,MAX(0,in_ProfitTax*Z15))</f>
-        <v>69.411858073507</v>
+        <v>107.510530555363</v>
       </c>
       <c r="AA17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AA8,MAX(0,in_ProfitTax*AA15))</f>
-        <v>77.2492925728669</v>
+        <v>121.888634540738</v>
       </c>
       <c r="AB17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AB8,MAX(0,in_ProfitTax*AB15))</f>
-        <v>83.6761271706809</v>
+        <v>132.296517185032</v>
       </c>
       <c r="AC17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AC8,MAX(0,in_ProfitTax*AC15))</f>
-        <v>90.1200727305605</v>
+        <v>142.815377894469</v>
       </c>
       <c r="AD17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AD8,MAX(0,in_ProfitTax*AD15))</f>
-        <v>96.5806159236436</v>
+        <v>153.44244221742</v>
       </c>
       <c r="AE17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AE8,MAX(0,in_ProfitTax*AE15))</f>
-        <v>103.057258820934</v>
+        <v>164.175005063547</v>
       </c>
       <c r="AF17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AF8,MAX(0,in_ProfitTax*AF15))</f>
-        <v>109.549518431306</v>
+        <v>175.01042896977</v>
       </c>
       <c r="AG17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AG8,MAX(0,in_ProfitTax*AG15))</f>
-        <v>116.056926253367</v>
+        <v>185.946142409589</v>
       </c>
       <c r="AH17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AH8,MAX(0,in_ProfitTax*AH15))</f>
-        <v>122.579027840766</v>
+        <v>196.979638144661</v>
       </c>
       <c r="AI17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AI8,MAX(0,in_ProfitTax*AI15))</f>
-        <v>129.115382380543</v>
+        <v>208.108471617607</v>
       </c>
       <c r="AJ17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AJ8,MAX(0,in_ProfitTax*AJ15))</f>
-        <v>135.665562284127</v>
+        <v>219.33025938498</v>
       </c>
       <c r="AK17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AK8,MAX(0,in_ProfitTax*AK15))</f>
-        <v>142.229152790603</v>
+        <v>230.642677589418</v>
       </c>
       <c r="AL17" s="39" t="n">
         <f aca="false">IF(in_TaxRegime=1,in_MicroRate*AL8,MAX(0,in_ProfitTax*AL15))</f>
-        <v>148.805751581885</v>
+        <v>242.043460469995</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13879,143 +13879,143 @@
       </c>
       <c r="D18" s="40" t="n">
         <f aca="false">D15-D17</f>
-        <v>-7337.6554125</v>
+        <v>-7276.47954</v>
       </c>
       <c r="E18" s="40" t="n">
         <f aca="false">E15-E17</f>
-        <v>-5621.531162625</v>
+        <v>-5499.8595915</v>
       </c>
       <c r="F18" s="40" t="n">
         <f aca="false">F15-F17</f>
-        <v>-5254.40399024625</v>
+        <v>-4907.0690467125</v>
       </c>
       <c r="G18" s="40" t="n">
         <f aca="false">G15-G17</f>
-        <v>-6682.41031303886</v>
+        <v>-6279.97390554469</v>
       </c>
       <c r="H18" s="40" t="n">
         <f aca="false">H15-H17</f>
-        <v>-4415.6390661477</v>
+        <v>-3938.98353728107</v>
       </c>
       <c r="I18" s="40" t="n">
         <f aca="false">I15-I17</f>
-        <v>-2675.62553266327</v>
+        <v>-2123.39690416154</v>
       </c>
       <c r="J18" s="40" t="n">
         <f aca="false">J15-J17</f>
-        <v>-2512.34696918337</v>
+        <v>-1883.24686437001</v>
       </c>
       <c r="K18" s="40" t="n">
         <f aca="false">K15-K17</f>
-        <v>-3102.31881460787</v>
+        <v>-2395.10295463576</v>
       </c>
       <c r="L18" s="40" t="n">
         <f aca="false">L15-L17</f>
-        <v>-2882.46866966963</v>
+        <v>-2047.96461076986</v>
       </c>
       <c r="M18" s="40" t="n">
         <f aca="false">M15-M17</f>
-        <v>-2724.26527707954</v>
+        <v>-1809.31338768811</v>
       </c>
       <c r="N18" s="40" t="n">
         <f aca="false">N15-N17</f>
-        <v>-2560.71530226716</v>
+        <v>-1558.50851643341</v>
       </c>
       <c r="O18" s="40" t="n">
         <f aca="false">O15-O17</f>
-        <v>-6806.45210204017</v>
+        <v>-5607.31287454885</v>
       </c>
       <c r="P18" s="40" t="n">
         <f aca="false">P15-P17</f>
-        <v>-6454.16782207896</v>
+        <v>-5094.39380329294</v>
       </c>
       <c r="Q18" s="40" t="n">
         <f aca="false">Q15-Q17</f>
-        <v>-6100.6834689166</v>
+        <v>-4572.4464724403</v>
       </c>
       <c r="R18" s="40" t="n">
         <f aca="false">R15-R17</f>
-        <v>-5746.0980195491</v>
+        <v>-4041.7972239918</v>
       </c>
       <c r="S18" s="40" t="n">
         <f aca="false">S15-S17</f>
-        <v>-5390.50748166262</v>
+        <v>-3502.76424139825</v>
       </c>
       <c r="T18" s="40" t="n">
         <f aca="false">T15-T17</f>
-        <v>-5034.00498271275</v>
+        <v>-2955.65775352423</v>
       </c>
       <c r="U18" s="40" t="n">
         <f aca="false">U15-U17</f>
-        <v>-4676.68085633136</v>
+        <v>-2400.78023351269</v>
       </c>
       <c r="V18" s="40" t="n">
         <f aca="false">V15-V17</f>
-        <v>-4318.62272614142</v>
+        <v>-1838.426592678</v>
       </c>
       <c r="W18" s="40" t="n">
         <f aca="false">W15-W17</f>
-        <v>-3957.81642705718</v>
+        <v>-1264.85894911417</v>
       </c>
       <c r="X18" s="40" t="n">
         <f aca="false">X15-X17</f>
-        <v>-3594.34440414546</v>
+        <v>-680.357652889441</v>
       </c>
       <c r="Y18" s="40" t="n">
         <f aca="false">Y15-Y17</f>
-        <v>-3228.2866291211</v>
+        <v>-85.1960453203301</v>
       </c>
       <c r="Z18" s="40" t="n">
         <f aca="false">Z15-Z17</f>
-        <v>-2859.72067454747</v>
+        <v>520.359365809553</v>
       </c>
       <c r="AA18" s="40" t="n">
         <f aca="false">AA15-AA17</f>
-        <v>-7247.68984440339</v>
+        <v>-3276.15679146627</v>
       </c>
       <c r="AB18" s="40" t="n">
         <f aca="false">AB15-AB17</f>
-        <v>-12964.0548529563</v>
+        <v>-8635.40986393695</v>
       </c>
       <c r="AC18" s="40" t="n">
         <f aca="false">AC15-AC17</f>
-        <v>-6079.9152217126</v>
+        <v>-1385.79184875973</v>
       </c>
       <c r="AD18" s="40" t="n">
         <f aca="false">AD15-AD17</f>
-        <v>-5495.31915163622</v>
+        <v>-427.563496514592</v>
       </c>
       <c r="AE18" s="40" t="n">
         <f aca="false">AE15-AE17</f>
-        <v>-4910.31339766213</v>
+        <v>539.020960982977</v>
       </c>
       <c r="AF18" s="40" t="n">
         <f aca="false">AF15-AF17</f>
-        <v>-4324.94331207727</v>
+        <v>1513.71364771289</v>
       </c>
       <c r="AG18" s="40" t="n">
         <f aca="false">AG15-AG17</f>
-        <v>-3739.25288659995</v>
+        <v>2496.27288455555</v>
       </c>
       <c r="AH18" s="40" t="n">
         <f aca="false">AH15-AH17</f>
-        <v>-3153.28479319695</v>
+        <v>3486.46303436936</v>
       </c>
       <c r="AI18" s="40" t="n">
         <f aca="false">AI15-AI17</f>
-        <v>-2565.97836467604</v>
+        <v>4485.61328649252</v>
       </c>
       <c r="AJ18" s="40" t="n">
         <f aca="false">AJ15-AJ17</f>
-        <v>-1977.37375109076</v>
+        <v>5493.49963836729</v>
       </c>
       <c r="AK18" s="40" t="n">
         <f aca="false">AK15-AK17</f>
-        <v>-1387.50989799304</v>
+        <v>6509.90368749987</v>
       </c>
       <c r="AL18" s="40" t="n">
         <f aca="false">AL15-AL17</f>
-        <v>-796.424582568245</v>
+        <v>7534.61249145882</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14117,139 +14117,139 @@
       </c>
       <c r="E21" s="39" t="n">
         <f aca="false">D23</f>
-        <v>87254.8445875</v>
+        <v>87316.02046</v>
       </c>
       <c r="F21" s="39" t="n">
         <f aca="false">E23</f>
-        <v>81633.313424875</v>
+        <v>81816.1608685</v>
       </c>
       <c r="G21" s="39" t="n">
         <f aca="false">F23</f>
-        <v>76378.9094346288</v>
+        <v>76909.0918217875</v>
       </c>
       <c r="H21" s="39" t="n">
         <f aca="false">G23</f>
-        <v>69696.4991215899</v>
+        <v>70629.1179162428</v>
       </c>
       <c r="I21" s="39" t="n">
         <f aca="false">H23</f>
-        <v>65280.8600554422</v>
+        <v>66690.1343789618</v>
       </c>
       <c r="J21" s="39" t="n">
         <f aca="false">I23</f>
-        <v>62605.2345227789</v>
+        <v>64566.7374748002</v>
       </c>
       <c r="K21" s="39" t="n">
         <f aca="false">J23</f>
-        <v>60092.8875535955</v>
+        <v>62683.4906104302</v>
       </c>
       <c r="L21" s="39" t="n">
         <f aca="false">K23</f>
-        <v>56990.5687389877</v>
+        <v>60288.3876557945</v>
       </c>
       <c r="M21" s="39" t="n">
         <f aca="false">L23</f>
-        <v>54108.1000693181</v>
+        <v>58240.4230450246</v>
       </c>
       <c r="N21" s="39" t="n">
         <f aca="false">M23</f>
-        <v>51383.8347922385</v>
+        <v>56431.1096573365</v>
       </c>
       <c r="O21" s="39" t="n">
         <f aca="false">N23</f>
-        <v>48823.1194899714</v>
+        <v>54872.6011409031</v>
       </c>
       <c r="P21" s="39" t="n">
         <f aca="false">O23</f>
-        <v>42016.6673879312</v>
+        <v>49265.2882663542</v>
       </c>
       <c r="Q21" s="39" t="n">
         <f aca="false">P23</f>
-        <v>35562.4995658522</v>
+        <v>44170.8944630613</v>
       </c>
       <c r="R21" s="39" t="n">
         <f aca="false">Q23</f>
-        <v>29461.8160969356</v>
+        <v>39598.447990621</v>
       </c>
       <c r="S21" s="39" t="n">
         <f aca="false">R23</f>
-        <v>23715.7180773865</v>
+        <v>35556.6507666292</v>
       </c>
       <c r="T21" s="39" t="n">
         <f aca="false">S23</f>
-        <v>18325.2105957239</v>
+        <v>32053.8865252309</v>
       </c>
       <c r="U21" s="39" t="n">
         <f aca="false">T23</f>
-        <v>13291.2056130112</v>
+        <v>29098.2287717067</v>
       </c>
       <c r="V21" s="39" t="n">
         <f aca="false">U23</f>
-        <v>8614.5247566798</v>
+        <v>26697.448538194</v>
       </c>
       <c r="W21" s="39" t="n">
         <f aca="false">V23</f>
-        <v>4295.90203053838</v>
+        <v>24859.021945516</v>
       </c>
       <c r="X21" s="39" t="n">
         <f aca="false">W23</f>
-        <v>338.085603481202</v>
+        <v>23594.1629964019</v>
       </c>
       <c r="Y21" s="39" t="n">
         <f aca="false">X23</f>
-        <v>-3256.25880066426</v>
+        <v>22913.8053435124</v>
       </c>
       <c r="Z21" s="39" t="n">
         <f aca="false">Y23</f>
-        <v>-6484.54542978536</v>
+        <v>22828.6092981921</v>
       </c>
       <c r="AA21" s="39" t="n">
         <f aca="false">Z23</f>
-        <v>-9344.26610433283</v>
+        <v>23348.9686640016</v>
       </c>
       <c r="AB21" s="39" t="n">
         <f aca="false">AA23</f>
-        <v>-16591.9559487362</v>
+        <v>20072.8118725354</v>
       </c>
       <c r="AC21" s="39" t="n">
         <f aca="false">AB23</f>
-        <v>-29556.0108016925</v>
+        <v>11437.4020085984</v>
       </c>
       <c r="AD21" s="39" t="n">
         <f aca="false">AC23</f>
-        <v>-35635.9260234051</v>
+        <v>10051.6101598387</v>
       </c>
       <c r="AE21" s="39" t="n">
         <f aca="false">AD23</f>
-        <v>-41131.2451750413</v>
+        <v>9624.04666332409</v>
       </c>
       <c r="AF21" s="39" t="n">
         <f aca="false">AE23</f>
-        <v>-46041.5585727034</v>
+        <v>10163.0676243071</v>
       </c>
       <c r="AG21" s="39" t="n">
         <f aca="false">AF23</f>
-        <v>-50366.5018847807</v>
+        <v>11676.78127202</v>
       </c>
       <c r="AH21" s="39" t="n">
         <f aca="false">AG23</f>
-        <v>-54105.7547713807</v>
+        <v>14173.0541565755</v>
       </c>
       <c r="AI21" s="39" t="n">
         <f aca="false">AH23</f>
-        <v>-57259.0395645776</v>
+        <v>17659.5171909449</v>
       </c>
       <c r="AJ21" s="39" t="n">
         <f aca="false">AI23</f>
-        <v>-59825.0179292537</v>
+        <v>22145.1304774374</v>
       </c>
       <c r="AK21" s="39" t="n">
         <f aca="false">AJ23</f>
-        <v>-61802.3916803444</v>
+        <v>27638.6301158047</v>
       </c>
       <c r="AL21" s="39" t="n">
         <f aca="false">AK23</f>
-        <v>-63189.9015783374</v>
+        <v>34148.5338033045</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14417,143 +14417,143 @@
       </c>
       <c r="D23" s="40" t="n">
         <f aca="false">D21+D22+D18</f>
-        <v>87254.8445875</v>
+        <v>87316.02046</v>
       </c>
       <c r="E23" s="40" t="n">
         <f aca="false">E21+E22+E18</f>
-        <v>81633.313424875</v>
+        <v>81816.1608685</v>
       </c>
       <c r="F23" s="40" t="n">
         <f aca="false">F21+F22+F18</f>
-        <v>76378.9094346288</v>
+        <v>76909.0918217875</v>
       </c>
       <c r="G23" s="40" t="n">
         <f aca="false">G21+G22+G18</f>
-        <v>69696.4991215899</v>
+        <v>70629.1179162428</v>
       </c>
       <c r="H23" s="40" t="n">
         <f aca="false">H21+H22+H18</f>
-        <v>65280.8600554422</v>
+        <v>66690.1343789618</v>
       </c>
       <c r="I23" s="40" t="n">
         <f aca="false">I21+I22+I18</f>
-        <v>62605.2345227789</v>
+        <v>64566.7374748002</v>
       </c>
       <c r="J23" s="40" t="n">
         <f aca="false">J21+J22+J18</f>
-        <v>60092.8875535955</v>
+        <v>62683.4906104302</v>
       </c>
       <c r="K23" s="40" t="n">
         <f aca="false">K21+K22+K18</f>
-        <v>56990.5687389877</v>
+        <v>60288.3876557945</v>
       </c>
       <c r="L23" s="40" t="n">
         <f aca="false">L21+L22+L18</f>
-        <v>54108.1000693181</v>
+        <v>58240.4230450246</v>
       </c>
       <c r="M23" s="40" t="n">
         <f aca="false">M21+M22+M18</f>
-        <v>51383.8347922385</v>
+        <v>56431.1096573365</v>
       </c>
       <c r="N23" s="40" t="n">
         <f aca="false">N21+N22+N18</f>
-        <v>48823.1194899714</v>
+        <v>54872.6011409031</v>
       </c>
       <c r="O23" s="40" t="n">
         <f aca="false">O21+O22+O18</f>
-        <v>42016.6673879312</v>
+        <v>49265.2882663542</v>
       </c>
       <c r="P23" s="40" t="n">
         <f aca="false">P21+P22+P18</f>
-        <v>35562.4995658522</v>
+        <v>44170.8944630613</v>
       </c>
       <c r="Q23" s="40" t="n">
         <f aca="false">Q21+Q22+Q18</f>
-        <v>29461.8160969356</v>
+        <v>39598.447990621</v>
       </c>
       <c r="R23" s="40" t="n">
         <f aca="false">R21+R22+R18</f>
-        <v>23715.7180773865</v>
+        <v>35556.6507666292</v>
       </c>
       <c r="S23" s="40" t="n">
         <f aca="false">S21+S22+S18</f>
-        <v>18325.2105957239</v>
+        <v>32053.8865252309</v>
       </c>
       <c r="T23" s="40" t="n">
         <f aca="false">T21+T22+T18</f>
-        <v>13291.2056130112</v>
+        <v>29098.2287717067</v>
       </c>
       <c r="U23" s="40" t="n">
         <f aca="false">U21+U22+U18</f>
-        <v>8614.5247566798</v>
+        <v>26697.448538194</v>
       </c>
       <c r="V23" s="40" t="n">
         <f aca="false">V21+V22+V18</f>
-        <v>4295.90203053838</v>
+        <v>24859.021945516</v>
       </c>
       <c r="W23" s="40" t="n">
         <f aca="false">W21+W22+W18</f>
-        <v>338.085603481202</v>
+        <v>23594.1629964019</v>
       </c>
       <c r="X23" s="40" t="n">
         <f aca="false">X21+X22+X18</f>
-        <v>-3256.25880066426</v>
+        <v>22913.8053435124</v>
       </c>
       <c r="Y23" s="40" t="n">
         <f aca="false">Y21+Y22+Y18</f>
-        <v>-6484.54542978536</v>
+        <v>22828.6092981921</v>
       </c>
       <c r="Z23" s="40" t="n">
         <f aca="false">Z21+Z22+Z18</f>
-        <v>-9344.26610433283</v>
+        <v>23348.9686640016</v>
       </c>
       <c r="AA23" s="40" t="n">
         <f aca="false">AA21+AA22+AA18</f>
-        <v>-16591.9559487362</v>
+        <v>20072.8118725354</v>
       </c>
       <c r="AB23" s="40" t="n">
         <f aca="false">AB21+AB22+AB18</f>
-        <v>-29556.0108016925</v>
+        <v>11437.4020085984</v>
       </c>
       <c r="AC23" s="40" t="n">
         <f aca="false">AC21+AC22+AC18</f>
-        <v>-35635.9260234051</v>
+        <v>10051.6101598387</v>
       </c>
       <c r="AD23" s="40" t="n">
         <f aca="false">AD21+AD22+AD18</f>
-        <v>-41131.2451750413</v>
+        <v>9624.04666332409</v>
       </c>
       <c r="AE23" s="40" t="n">
         <f aca="false">AE21+AE22+AE18</f>
-        <v>-46041.5585727034</v>
+        <v>10163.0676243071</v>
       </c>
       <c r="AF23" s="40" t="n">
         <f aca="false">AF21+AF22+AF18</f>
-        <v>-50366.5018847807</v>
+        <v>11676.78127202</v>
       </c>
       <c r="AG23" s="40" t="n">
         <f aca="false">AG21+AG22+AG18</f>
-        <v>-54105.7547713807</v>
+        <v>14173.0541565755</v>
       </c>
       <c r="AH23" s="40" t="n">
         <f aca="false">AH21+AH22+AH18</f>
-        <v>-57259.0395645776</v>
+        <v>17659.5171909449</v>
       </c>
       <c r="AI23" s="40" t="n">
         <f aca="false">AI21+AI22+AI18</f>
-        <v>-59825.0179292537</v>
+        <v>22145.1304774374</v>
       </c>
       <c r="AJ23" s="40" t="n">
         <f aca="false">AJ21+AJ22+AJ18</f>
-        <v>-61802.3916803444</v>
+        <v>27638.6301158047</v>
       </c>
       <c r="AK23" s="40" t="n">
         <f aca="false">AK21+AK22+AK18</f>
-        <v>-63189.9015783374</v>
+        <v>34148.5338033045</v>
       </c>
       <c r="AL23" s="40" t="n">
         <f aca="false">AL21+AL22+AL18</f>
-        <v>-63986.3261609057</v>
+        <v>41683.1462947634</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14569,143 +14569,143 @@
       </c>
       <c r="D24" s="39" t="n">
         <f aca="false">C24+Costs!D34</f>
-        <v>12924.8156625</v>
+        <v>12928.35114</v>
       </c>
       <c r="E24" s="39" t="n">
         <f aca="false">D24+Costs!E34</f>
-        <v>18900.277517625</v>
+        <v>18910.8446415</v>
       </c>
       <c r="F24" s="39" t="n">
         <f aca="false">E24+Costs!F34</f>
-        <v>24960.3985295963</v>
+        <v>25041.7925504625</v>
       </c>
       <c r="G24" s="39" t="n">
         <f aca="false">F24+Costs!G34</f>
-        <v>32604.0146037084</v>
+        <v>32759.4199467009</v>
       </c>
       <c r="H24" s="39" t="n">
         <f aca="false">G24+Costs!H34</f>
-        <v>38164.6703080971</v>
+        <v>38404.4230749084</v>
       </c>
       <c r="I24" s="39" t="n">
         <f aca="false">H24+Costs!I34</f>
-        <v>42168.3214298542</v>
+        <v>42503.5959552232</v>
       </c>
       <c r="J24" s="39" t="n">
         <f aca="false">I24+Costs!J34</f>
-        <v>46190.9250704586</v>
+        <v>46633.7307088426</v>
       </c>
       <c r="K24" s="39" t="n">
         <f aca="false">J24+Costs!K34</f>
-        <v>50984.9771063448</v>
+        <v>51548.1551054966</v>
       </c>
       <c r="L24" s="39" t="n">
         <f aca="false">K24+Costs!L34</f>
-        <v>55739.9236506545</v>
+        <v>56389.1633097342</v>
       </c>
       <c r="M24" s="39" t="n">
         <f aca="false">L24+Costs!M34</f>
-        <v>60516.7015161348</v>
+        <v>61266.4988260533</v>
       </c>
       <c r="N24" s="39" t="n">
         <f aca="false">M24+Costs!N34</f>
-        <v>65309.2754791508</v>
+        <v>66169.232980402</v>
       </c>
       <c r="O24" s="39" t="n">
         <f aca="false">N24+Costs!O34</f>
-        <v>74646.7911696636</v>
+        <v>75633.5748792211</v>
       </c>
       <c r="P24" s="39" t="n">
         <f aca="false">O24+Costs!P34</f>
-        <v>84010.6900100611</v>
+        <v>85137.979094615</v>
       </c>
       <c r="Q24" s="39" t="n">
         <f aca="false">P24+Costs!Q34</f>
-        <v>93403.2559642466</v>
+        <v>94687.1957152913</v>
       </c>
       <c r="R24" s="39" t="n">
         <f aca="false">Q24+Costs!R34</f>
-        <v>102826.767452007</v>
+        <v>104285.956713251</v>
       </c>
       <c r="S24" s="39" t="n">
         <f aca="false">R24+Costs!S34</f>
-        <v>112283.497515334</v>
+        <v>113938.976396705</v>
       </c>
       <c r="T24" s="39" t="n">
         <f aca="false">S24+Costs!T34</f>
-        <v>121775.713979761</v>
+        <v>123650.951851671</v>
       </c>
       <c r="U24" s="39" t="n">
         <f aca="false">T24+Costs!U34</f>
-        <v>131305.679610856</v>
+        <v>133426.563372527</v>
       </c>
       <c r="V24" s="39" t="n">
         <f aca="false">U24+Costs!V34</f>
-        <v>140875.652266017</v>
+        <v>143270.474881802</v>
       </c>
       <c r="W24" s="39" t="n">
         <f aca="false">V24+Costs!W34</f>
-        <v>150485.785881724</v>
+        <v>153183.308919037</v>
       </c>
       <c r="X24" s="39" t="n">
         <f aca="false">W24+Costs!X34</f>
-        <v>160136.22977636</v>
+        <v>163165.67246028</v>
       </c>
       <c r="Y24" s="39" t="n">
         <f aca="false">X24+Costs!Y34</f>
-        <v>169827.128788756</v>
+        <v>173218.157307184</v>
       </c>
       <c r="Z24" s="39" t="n">
         <f aca="false">Y24+Costs!Z34</f>
-        <v>179558.623412581</v>
+        <v>183341.340466355</v>
       </c>
       <c r="AA24" s="39" t="n">
         <f aca="false">Z24+Costs!AA34</f>
-        <v>194453.993221698</v>
+        <v>198684.472077355</v>
       </c>
       <c r="AB24" s="39" t="n">
         <f aca="false">AA24+Costs!AB34</f>
-        <v>215701.984664552</v>
+        <v>220417.23714261</v>
       </c>
       <c r="AC24" s="39" t="n">
         <f aca="false">AB24+Costs!AC34</f>
-        <v>230703.78708659</v>
+        <v>235941.751402922</v>
       </c>
       <c r="AD24" s="39" t="n">
         <f aca="false">AC24+Costs!AD34</f>
-        <v>245760.587214667</v>
+        <v>251560.116678961</v>
       </c>
       <c r="AE24" s="39" t="n">
         <f aca="false">AD24+Costs!AE34</f>
-        <v>260873.569235601</v>
+        <v>267274.421219269</v>
       </c>
       <c r="AF24" s="39" t="n">
         <f aca="false">AE24+Costs!AF34</f>
-        <v>276043.914872378</v>
+        <v>283086.740039564</v>
       </c>
       <c r="AG24" s="39" t="n">
         <f aca="false">AF24+Costs!AG34</f>
-        <v>291272.803458061</v>
+        <v>298999.135253557</v>
       </c>
       <c r="AH24" s="39" t="n">
         <f aca="false">AG24+Costs!AH34</f>
-        <v>306561.412007494</v>
+        <v>315013.656395509</v>
       </c>
       <c r="AI24" s="39" t="n">
         <f aca="false">AH24+Costs!AI34</f>
-        <v>321909.813227844</v>
+        <v>331130.78179916</v>
       </c>
       <c r="AJ24" s="39" t="n">
         <f aca="false">AI24+Costs!AJ34</f>
-        <v>337318.077645063</v>
+        <v>347350.977839906</v>
       </c>
       <c r="AK24" s="39" t="n">
         <f aca="false">AJ24+Costs!AK34</f>
-        <v>352786.273669326</v>
+        <v>363674.699233758</v>
       </c>
       <c r="AL24" s="39" t="n">
         <f aca="false">AK24+Costs!AL34</f>
-        <v>368314.467658501</v>
+        <v>380102.389328829</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14721,143 +14721,143 @@
       </c>
       <c r="D25" s="39" t="n">
         <f aca="false">C25+D18</f>
-        <v>-12745.1554125</v>
+        <v>-12683.97954</v>
       </c>
       <c r="E25" s="39" t="n">
         <f aca="false">D25+E18</f>
-        <v>-18366.686575125</v>
+        <v>-18183.8391315</v>
       </c>
       <c r="F25" s="39" t="n">
         <f aca="false">E25+F18</f>
-        <v>-23621.0905653713</v>
+        <v>-23090.9081782125</v>
       </c>
       <c r="G25" s="39" t="n">
         <f aca="false">F25+G18</f>
-        <v>-30303.5008784101</v>
+        <v>-29370.8820837572</v>
       </c>
       <c r="H25" s="39" t="n">
         <f aca="false">G25+H18</f>
-        <v>-34719.1399445578</v>
+        <v>-33309.8656210383</v>
       </c>
       <c r="I25" s="39" t="n">
         <f aca="false">H25+I18</f>
-        <v>-37394.7654772211</v>
+        <v>-35433.2625251998</v>
       </c>
       <c r="J25" s="39" t="n">
         <f aca="false">I25+J18</f>
-        <v>-39907.1124464044</v>
+        <v>-37316.5093895698</v>
       </c>
       <c r="K25" s="39" t="n">
         <f aca="false">J25+K18</f>
-        <v>-43009.4312610123</v>
+        <v>-39711.6123442056</v>
       </c>
       <c r="L25" s="39" t="n">
         <f aca="false">K25+L18</f>
-        <v>-45891.8999306819</v>
+        <v>-41759.5769549754</v>
       </c>
       <c r="M25" s="39" t="n">
         <f aca="false">L25+M18</f>
-        <v>-48616.1652077615</v>
+        <v>-43568.8903426635</v>
       </c>
       <c r="N25" s="39" t="n">
         <f aca="false">M25+N18</f>
-        <v>-51176.8805100286</v>
+        <v>-45127.3988590969</v>
       </c>
       <c r="O25" s="39" t="n">
         <f aca="false">N25+O18</f>
-        <v>-57983.3326120688</v>
+        <v>-50734.7117336458</v>
       </c>
       <c r="P25" s="39" t="n">
         <f aca="false">O25+P18</f>
-        <v>-64437.5004341478</v>
+        <v>-55829.1055369387</v>
       </c>
       <c r="Q25" s="39" t="n">
         <f aca="false">P25+Q18</f>
-        <v>-70538.1839030644</v>
+        <v>-60401.552009379</v>
       </c>
       <c r="R25" s="39" t="n">
         <f aca="false">Q25+R18</f>
-        <v>-76284.2819226135</v>
+        <v>-64443.3492333708</v>
       </c>
       <c r="S25" s="39" t="n">
         <f aca="false">R25+S18</f>
-        <v>-81674.7894042761</v>
+        <v>-67946.1134747691</v>
       </c>
       <c r="T25" s="39" t="n">
         <f aca="false">S25+T18</f>
-        <v>-86708.7943869888</v>
+        <v>-70901.7712282933</v>
       </c>
       <c r="U25" s="39" t="n">
         <f aca="false">T25+U18</f>
-        <v>-91385.4752433202</v>
+        <v>-73302.551461806</v>
       </c>
       <c r="V25" s="39" t="n">
         <f aca="false">U25+V18</f>
-        <v>-95704.0979694616</v>
+        <v>-75140.978054484</v>
       </c>
       <c r="W25" s="39" t="n">
         <f aca="false">V25+W18</f>
-        <v>-99661.9143965188</v>
+        <v>-76405.8370035982</v>
       </c>
       <c r="X25" s="39" t="n">
         <f aca="false">W25+X18</f>
-        <v>-103256.258800664</v>
+        <v>-77086.1946564876</v>
       </c>
       <c r="Y25" s="39" t="n">
         <f aca="false">X25+Y18</f>
-        <v>-106484.545429785</v>
+        <v>-77171.390701808</v>
       </c>
       <c r="Z25" s="39" t="n">
         <f aca="false">Y25+Z18</f>
-        <v>-109344.266104333</v>
+        <v>-76651.0313359984</v>
       </c>
       <c r="AA25" s="39" t="n">
         <f aca="false">Z25+AA18</f>
-        <v>-116591.955948736</v>
+        <v>-79927.1881274647</v>
       </c>
       <c r="AB25" s="39" t="n">
         <f aca="false">AA25+AB18</f>
-        <v>-129556.010801693</v>
+        <v>-88562.5979914016</v>
       </c>
       <c r="AC25" s="39" t="n">
         <f aca="false">AB25+AC18</f>
-        <v>-135635.926023405</v>
+        <v>-89948.3898401613</v>
       </c>
       <c r="AD25" s="39" t="n">
         <f aca="false">AC25+AD18</f>
-        <v>-141131.245175041</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AE25" s="39" t="n">
         <f aca="false">AD25+AE18</f>
-        <v>-146041.558572703</v>
+        <v>-89836.932375693</v>
       </c>
       <c r="AF25" s="39" t="n">
         <f aca="false">AE25+AF18</f>
-        <v>-150366.501884781</v>
+        <v>-88323.2187279801</v>
       </c>
       <c r="AG25" s="39" t="n">
         <f aca="false">AF25+AG18</f>
-        <v>-154105.754771381</v>
+        <v>-85826.9458434245</v>
       </c>
       <c r="AH25" s="39" t="n">
         <f aca="false">AG25+AH18</f>
-        <v>-157259.039564578</v>
+        <v>-82340.4828090552</v>
       </c>
       <c r="AI25" s="39" t="n">
         <f aca="false">AH25+AI18</f>
-        <v>-159825.017929254</v>
+        <v>-77854.8695225627</v>
       </c>
       <c r="AJ25" s="39" t="n">
         <f aca="false">AI25+AJ18</f>
-        <v>-161802.391680344</v>
+        <v>-72361.3698841954</v>
       </c>
       <c r="AK25" s="39" t="n">
         <f aca="false">AJ25+AK18</f>
-        <v>-163189.901578337</v>
+        <v>-65851.4661966955</v>
       </c>
       <c r="AL25" s="39" t="n">
         <f aca="false">AK25+AL18</f>
-        <v>-163986.326160906</v>
+        <v>-58316.8537052367</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14953,63 +14953,63 @@
       </c>
       <c r="X26" s="45" t="n">
         <f aca="false">IF(X23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="45" t="n">
         <f aca="false">IF(Y23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="45" t="n">
         <f aca="false">IF(Z23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" s="45" t="n">
         <f aca="false">IF(AA23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="45" t="n">
         <f aca="false">IF(AB23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="45" t="n">
         <f aca="false">IF(AC23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="45" t="n">
         <f aca="false">IF(AD23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="45" t="n">
         <f aca="false">IF(AE23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="45" t="n">
         <f aca="false">IF(AF23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="45" t="n">
         <f aca="false">IF(AG23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="45" t="n">
         <f aca="false">IF(AH23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="45" t="n">
         <f aca="false">IF(AI23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ26" s="45" t="n">
         <f aca="false">IF(AJ23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK26" s="45" t="n">
         <f aca="false">IF(AK23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL26" s="45" t="n">
         <f aca="false">IF(AL23&lt;0,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="Z27" s="45" t="n">
         <f aca="false">IF(Z18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" s="45" t="n">
         <f aca="false">IF(AA18&gt;=0,1,0)</f>
@@ -15133,35 +15133,35 @@
       </c>
       <c r="AE27" s="45" t="n">
         <f aca="false">IF(AE18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" s="45" t="n">
         <f aca="false">IF(AF18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG27" s="45" t="n">
         <f aca="false">IF(AG18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH27" s="45" t="n">
         <f aca="false">IF(AH18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" s="45" t="n">
         <f aca="false">IF(AI18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" s="45" t="n">
         <f aca="false">IF(AJ18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK27" s="45" t="n">
         <f aca="false">IF(AK18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL27" s="45" t="n">
         <f aca="false">IF(AL18&gt;=0,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15177,143 +15177,143 @@
       </c>
       <c r="D28" s="39" t="n">
         <f aca="false">MIN(C28,D25)</f>
-        <v>-12745.1554125</v>
+        <v>-12683.97954</v>
       </c>
       <c r="E28" s="39" t="n">
         <f aca="false">MIN(D28,E25)</f>
-        <v>-18366.686575125</v>
+        <v>-18183.8391315</v>
       </c>
       <c r="F28" s="39" t="n">
         <f aca="false">MIN(E28,F25)</f>
-        <v>-23621.0905653713</v>
+        <v>-23090.9081782125</v>
       </c>
       <c r="G28" s="39" t="n">
         <f aca="false">MIN(F28,G25)</f>
-        <v>-30303.5008784101</v>
+        <v>-29370.8820837572</v>
       </c>
       <c r="H28" s="39" t="n">
         <f aca="false">MIN(G28,H25)</f>
-        <v>-34719.1399445578</v>
+        <v>-33309.8656210383</v>
       </c>
       <c r="I28" s="39" t="n">
         <f aca="false">MIN(H28,I25)</f>
-        <v>-37394.7654772211</v>
+        <v>-35433.2625251998</v>
       </c>
       <c r="J28" s="39" t="n">
         <f aca="false">MIN(I28,J25)</f>
-        <v>-39907.1124464044</v>
+        <v>-37316.5093895698</v>
       </c>
       <c r="K28" s="39" t="n">
         <f aca="false">MIN(J28,K25)</f>
-        <v>-43009.4312610123</v>
+        <v>-39711.6123442056</v>
       </c>
       <c r="L28" s="39" t="n">
         <f aca="false">MIN(K28,L25)</f>
-        <v>-45891.8999306819</v>
+        <v>-41759.5769549754</v>
       </c>
       <c r="M28" s="39" t="n">
         <f aca="false">MIN(L28,M25)</f>
-        <v>-48616.1652077615</v>
+        <v>-43568.8903426635</v>
       </c>
       <c r="N28" s="39" t="n">
         <f aca="false">MIN(M28,N25)</f>
-        <v>-51176.8805100286</v>
+        <v>-45127.3988590969</v>
       </c>
       <c r="O28" s="39" t="n">
         <f aca="false">MIN(N28,O25)</f>
-        <v>-57983.3326120688</v>
+        <v>-50734.7117336458</v>
       </c>
       <c r="P28" s="39" t="n">
         <f aca="false">MIN(O28,P25)</f>
-        <v>-64437.5004341478</v>
+        <v>-55829.1055369387</v>
       </c>
       <c r="Q28" s="39" t="n">
         <f aca="false">MIN(P28,Q25)</f>
-        <v>-70538.1839030644</v>
+        <v>-60401.552009379</v>
       </c>
       <c r="R28" s="39" t="n">
         <f aca="false">MIN(Q28,R25)</f>
-        <v>-76284.2819226135</v>
+        <v>-64443.3492333708</v>
       </c>
       <c r="S28" s="39" t="n">
         <f aca="false">MIN(R28,S25)</f>
-        <v>-81674.7894042761</v>
+        <v>-67946.1134747691</v>
       </c>
       <c r="T28" s="39" t="n">
         <f aca="false">MIN(S28,T25)</f>
-        <v>-86708.7943869888</v>
+        <v>-70901.7712282933</v>
       </c>
       <c r="U28" s="39" t="n">
         <f aca="false">MIN(T28,U25)</f>
-        <v>-91385.4752433202</v>
+        <v>-73302.551461806</v>
       </c>
       <c r="V28" s="39" t="n">
         <f aca="false">MIN(U28,V25)</f>
-        <v>-95704.0979694616</v>
+        <v>-75140.978054484</v>
       </c>
       <c r="W28" s="39" t="n">
         <f aca="false">MIN(V28,W25)</f>
-        <v>-99661.9143965188</v>
+        <v>-76405.8370035982</v>
       </c>
       <c r="X28" s="39" t="n">
         <f aca="false">MIN(W28,X25)</f>
-        <v>-103256.258800664</v>
+        <v>-77086.1946564876</v>
       </c>
       <c r="Y28" s="39" t="n">
         <f aca="false">MIN(X28,Y25)</f>
-        <v>-106484.545429785</v>
+        <v>-77171.390701808</v>
       </c>
       <c r="Z28" s="39" t="n">
         <f aca="false">MIN(Y28,Z25)</f>
-        <v>-109344.266104333</v>
+        <v>-77171.390701808</v>
       </c>
       <c r="AA28" s="39" t="n">
         <f aca="false">MIN(Z28,AA25)</f>
-        <v>-116591.955948736</v>
+        <v>-79927.1881274647</v>
       </c>
       <c r="AB28" s="39" t="n">
         <f aca="false">MIN(AA28,AB25)</f>
-        <v>-129556.010801693</v>
+        <v>-88562.5979914016</v>
       </c>
       <c r="AC28" s="39" t="n">
         <f aca="false">MIN(AB28,AC25)</f>
-        <v>-135635.926023405</v>
+        <v>-89948.3898401613</v>
       </c>
       <c r="AD28" s="39" t="n">
         <f aca="false">MIN(AC28,AD25)</f>
-        <v>-141131.245175041</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AE28" s="39" t="n">
         <f aca="false">MIN(AD28,AE25)</f>
-        <v>-146041.558572703</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AF28" s="39" t="n">
         <f aca="false">MIN(AE28,AF25)</f>
-        <v>-150366.501884781</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AG28" s="39" t="n">
         <f aca="false">MIN(AF28,AG25)</f>
-        <v>-154105.754771381</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AH28" s="39" t="n">
         <f aca="false">MIN(AG28,AH25)</f>
-        <v>-157259.039564578</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AI28" s="39" t="n">
         <f aca="false">MIN(AH28,AI25)</f>
-        <v>-159825.017929254</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AJ28" s="39" t="n">
         <f aca="false">MIN(AI28,AJ25)</f>
-        <v>-161802.391680344</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AK28" s="39" t="n">
         <f aca="false">MIN(AJ28,AK25)</f>
-        <v>-163189.901578337</v>
+        <v>-90375.9533366759</v>
       </c>
       <c r="AL28" s="39" t="n">
         <f aca="false">MIN(AK28,AL25)</f>
-        <v>-163986.326160906</v>
+        <v>-90375.9533366759</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15450,9 +15450,9 @@
         <v>294</v>
       </c>
       <c r="B32" s="1"/>
-      <c r="C32" s="46" t="n">
+      <c r="C32" s="46" t="str">
         <f aca="false">IF(MAX('P&amp;L &amp; Cash'!$C$26:$AL$26)=0,"&gt; 36",MATCH(1,'P&amp;L &amp; Cash'!$C$26:$AL$26,0)-1)</f>
-        <v>21</v>
+        <v>&gt; 36</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="12" t="s">
@@ -15497,13 +15497,13 @@
         <v>296</v>
       </c>
       <c r="B33" s="1"/>
-      <c r="C33" s="47" t="str">
+      <c r="C33" s="47" t="n">
         <f aca="false">IF(MAX('P&amp;L &amp; Cash'!$C$27:$AL$27)=0,"not within 36 months",MATCH(1,'P&amp;L &amp; Cash'!$C$27:$AL$27,0))</f>
-        <v>not within 36 months</v>
-      </c>
-      <c r="D33" s="41" t="str">
+        <v>24</v>
+      </c>
+      <c r="D33" s="41" t="n">
         <f aca="false">IF(ISNUMBER(C33),INDEX(Revenue!$C$4:$AL$4,1,C33),"-")</f>
-        <v>-</v>
+        <v>47088</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>297</v>
@@ -15549,7 +15549,7 @@
       <c r="B34" s="1"/>
       <c r="C34" s="21" t="n">
         <f aca="false">MIN('P&amp;L &amp; Cash'!$C$23:$AL$23)</f>
-        <v>-63986.3261609057</v>
+        <v>9624.04666332409</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="12"/>
@@ -15594,11 +15594,11 @@
       <c r="B35" s="1"/>
       <c r="C35" s="47" t="n">
         <f aca="false">MATCH(in_CashLow,'P&amp;L &amp; Cash'!$C$23:$AL$23,0)</f>
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D35" s="41" t="n">
         <f aca="false">INDEX(Revenue!$C$4:$AL$4,1,C35)</f>
-        <v>47453</v>
+        <v>47209</v>
       </c>
       <c r="E35" s="12"/>
       <c r="F35" s="1"/>
@@ -15642,7 +15642,7 @@
       <c r="B36" s="1"/>
       <c r="C36" s="21" t="n">
         <f aca="false">AL23</f>
-        <v>-63986.3261609057</v>
+        <v>41683.1462947634</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="12"/>
@@ -15687,7 +15687,7 @@
       <c r="B37" s="1"/>
       <c r="C37" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,1,'P&amp;L &amp; Cash'!$C$8:$AL$8)</f>
-        <v>14275.1464334567</v>
+        <v>21254.3779003081</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="12"/>
@@ -15732,7 +15732,7 @@
       <c r="B38" s="1"/>
       <c r="C38" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,2,'P&amp;L &amp; Cash'!$C$8:$AL$8)</f>
-        <v>56648.4468071979</v>
+        <v>86513.6111202544</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="12"/>
@@ -15777,7 +15777,7 @@
       <c r="B39" s="1"/>
       <c r="C39" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,3,'P&amp;L &amp; Cash'!$C$8:$AL$8)</f>
-        <v>135468.468878128</v>
+        <v>217267.905548722</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="12"/>
@@ -15822,7 +15822,7 @@
       <c r="B40" s="1"/>
       <c r="C40" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,1,Costs!$C$34:$AL$34)</f>
-        <v>65309.2754791508</v>
+        <v>66169.232980402</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="12"/>
@@ -15867,7 +15867,7 @@
       <c r="B41" s="1"/>
       <c r="C41" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,2,Costs!$C$34:$AL$34)</f>
-        <v>114249.34793343</v>
+        <v>117172.107485953</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="12"/>
@@ -15912,7 +15912,7 @@
       <c r="B42" s="1"/>
       <c r="C42" s="21" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,3,Costs!$C$34:$AL$34)</f>
-        <v>188755.84424592</v>
+        <v>196761.048862474</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="12"/>
@@ -16055,7 +16055,7 @@
       </c>
       <c r="B5" s="39" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$28:$AL$28)</f>
-        <v>56648.4468071979</v>
+        <v>86513.6111202544</v>
       </c>
       <c r="C5" s="12"/>
     </row>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="B6" s="45" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$21:$AL$21)</f>
-        <v>1133.42230506598</v>
+        <v>1706.58482503362</v>
       </c>
       <c r="C6" s="12" t="s">
         <v>313</v>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="B7" s="37" t="n">
         <f aca="false">IF(in_UE_CustMonths&gt;0,in_UE_Rev/in_UE_CustMonths,0)</f>
-        <v>49.98</v>
+        <v>50.694</v>
       </c>
       <c r="C7" s="12" t="s">
         <v>315</v>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="B8" s="37" t="n">
         <f aca="false">in_InfraVar+in_PayFee*in_ARPA</f>
-        <v>2.4996</v>
+        <v>2.51388</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>317</v>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">IF(in_ARPA&gt;0,(in_ARPA-in_VarCost)/in_ARPA,0)</f>
-        <v>0.949987995198079</v>
+        <v>0.950410699491064</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>319</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">IF(in_UE_Rev&gt;0,SUMIF(Revenue!$C$5:$AL$5,in_UEYear,'P&amp;L &amp; Cash'!$C$10:$AL$10)/in_UE_Rev,0)</f>
-        <v>0.716646204822276</v>
+        <v>0.797620290804664</v>
       </c>
       <c r="C10" s="12" t="s">
         <v>321</v>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="B11" s="39" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,'P&amp;L &amp; Cash'!$C$13:$AL$13)</f>
-        <v>59790.3504</v>
+        <v>61116.88386</v>
       </c>
       <c r="C11" s="12" t="s">
         <v>323</v>
@@ -16137,7 +16137,7 @@
       </c>
       <c r="B12" s="45" t="n">
         <f aca="false">SUMIF(Revenue!$C$5:$AL$5,in_UEYear,Revenue!$C$18:$AL$18)</f>
-        <v>122.775</v>
+        <v>180.247767857143</v>
       </c>
       <c r="C12" s="12"/>
     </row>
@@ -16147,7 +16147,7 @@
       </c>
       <c r="B13" s="39" t="n">
         <f aca="false">IF(in_UE_New&gt;0,in_UE_SnM/in_UE_New,0)</f>
-        <v>486.991247403787</v>
+        <v>339.071515761786</v>
       </c>
       <c r="C13" s="12" t="s">
         <v>326</v>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">in_CostPerTrial/in_TrialConv</f>
-        <v>320</v>
+        <v>254.545454545455</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>328</v>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">in_Churn</f>
-        <v>0.03</v>
+        <v>0.025</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>329</v>
@@ -16183,7 +16183,7 @@
       </c>
       <c r="B16" s="48" t="n">
         <f aca="false">IF(in_Churn&gt;0,1/in_Churn,0)</f>
-        <v>33.3333333333333</v>
+        <v>40</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>331</v>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="B17" s="39" t="n">
         <f aca="false">IF(in_Churn&gt;0,in_ARPA*in_CM/in_Churn,0)</f>
-        <v>1582.68</v>
+        <v>1927.2048</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>333</v>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="B18" s="49" t="n">
         <f aca="false">IF(in_CAC&gt;0,in_LTV/in_CAC,0)</f>
-        <v>3.24991467184979</v>
+        <v>5.6837708578091</v>
       </c>
       <c r="C18" s="12" t="s">
         <v>335</v>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="B19" s="50" t="n">
         <f aca="false">IF(in_ARPA*in_CM&gt;0,in_CAC/(in_ARPA*in_CM),0)</f>
-        <v>10.2566795436388</v>
+        <v>7.03758138754711</v>
       </c>
       <c r="C19" s="12" t="s">
         <v>337</v>
@@ -16306,10 +16306,10 @@
         <v>181</v>
       </c>
       <c r="C5" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="18" t="n">
         <v>6</v>
-      </c>
-      <c r="D5" s="18" t="n">
-        <v>3</v>
       </c>
       <c r="E5" s="18" t="n">
         <v>10</v>
@@ -16326,10 +16326,10 @@
         <v>184</v>
       </c>
       <c r="C6" s="51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="D6" s="51" t="n">
         <v>2</v>
-      </c>
-      <c r="D6" s="51" t="n">
-        <v>1.5</v>
       </c>
       <c r="E6" s="51" t="n">
         <v>2.5</v>
@@ -16346,10 +16346,10 @@
         <v>82</v>
       </c>
       <c r="C7" s="23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" s="23" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>0.33</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>0.7</v>
@@ -16366,10 +16366,10 @@
         <v>189</v>
       </c>
       <c r="C8" s="51" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D8" s="51" t="n">
         <v>2</v>
-      </c>
-      <c r="D8" s="51" t="n">
-        <v>1</v>
       </c>
       <c r="E8" s="51" t="n">
         <v>3</v>
@@ -16386,10 +16386,10 @@
         <v>189</v>
       </c>
       <c r="C9" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="51" t="n">
         <v>3</v>
-      </c>
-      <c r="D9" s="51" t="n">
-        <v>1.5</v>
       </c>
       <c r="E9" s="51" t="n">
         <v>5</v>
@@ -16406,10 +16406,10 @@
         <v>189</v>
       </c>
       <c r="C10" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="51" t="n">
         <v>4</v>
-      </c>
-      <c r="D10" s="51" t="n">
-        <v>2</v>
       </c>
       <c r="E10" s="51" t="n">
         <v>6</v>
@@ -16426,10 +16426,10 @@
         <v>184</v>
       </c>
       <c r="C11" s="16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>0.2</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>0.12</v>
       </c>
       <c r="E11" s="16" t="n">
         <v>0.3</v>
@@ -16446,10 +16446,10 @@
         <v>82</v>
       </c>
       <c r="C12" s="23" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D12" s="23" t="n">
         <v>0.5</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>0.4</v>
       </c>
       <c r="E12" s="23" t="n">
         <v>0.6</v>
@@ -16466,10 +16466,10 @@
         <v>198</v>
       </c>
       <c r="C13" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="D13" s="51" t="n">
         <v>4</v>
-      </c>
-      <c r="D13" s="51" t="n">
-        <v>2</v>
       </c>
       <c r="E13" s="51" t="n">
         <v>8</v>
@@ -16486,10 +16486,10 @@
         <v>198</v>
       </c>
       <c r="C14" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="D14" s="51" t="n">
         <v>12</v>
-      </c>
-      <c r="D14" s="51" t="n">
-        <v>6</v>
       </c>
       <c r="E14" s="51" t="n">
         <v>20</v>
@@ -16506,10 +16506,10 @@
         <v>198</v>
       </c>
       <c r="C15" s="51" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" s="51" t="n">
         <v>20</v>
-      </c>
-      <c r="D15" s="51" t="n">
-        <v>10</v>
       </c>
       <c r="E15" s="51" t="n">
         <v>35</v>
@@ -16526,10 +16526,10 @@
         <v>82</v>
       </c>
       <c r="C16" s="23" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="D16" s="23" t="n">
         <v>0.25</v>
-      </c>
-      <c r="D16" s="23" t="n">
-        <v>0.15</v>
       </c>
       <c r="E16" s="23" t="n">
         <v>0.3</v>
@@ -16546,10 +16546,10 @@
         <v>61</v>
       </c>
       <c r="C17" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="19" t="n">
         <v>80</v>
-      </c>
-      <c r="D17" s="19" t="n">
-        <v>120</v>
       </c>
       <c r="E17" s="19" t="n">
         <v>60</v>
@@ -16566,10 +16566,10 @@
         <v>207</v>
       </c>
       <c r="C18" s="23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="D18" s="23" t="n">
         <v>0.03</v>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>0.05</v>
       </c>
       <c r="E18" s="23" t="n">
         <v>0.02</v>
@@ -16586,10 +16586,10 @@
         <v>210</v>
       </c>
       <c r="C19" s="23" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="D19" s="23" t="n">
         <v>0.05</v>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>0</v>
       </c>
       <c r="E19" s="23" t="n">
         <v>0.08</v>
@@ -16609,7 +16609,7 @@
         <v>25</v>
       </c>
       <c r="D20" s="18" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E20" s="18" t="n">
         <v>19</v>
@@ -16680,10 +16680,10 @@
         <v>184</v>
       </c>
       <c r="C26" s="45" t="n">
+        <v>71</v>
+      </c>
+      <c r="D26" s="45" t="n">
         <v>47</v>
-      </c>
-      <c r="D26" s="45" t="n">
-        <v>15</v>
       </c>
       <c r="E26" s="45" t="n">
         <v>103</v>
@@ -16698,10 +16698,10 @@
         <v>61</v>
       </c>
       <c r="C27" s="39" t="n">
+        <v>3378</v>
+      </c>
+      <c r="D27" s="39" t="n">
         <v>2254</v>
-      </c>
-      <c r="D27" s="39" t="n">
-        <v>702</v>
       </c>
       <c r="E27" s="39" t="n">
         <v>4892</v>
@@ -16716,10 +16716,10 @@
         <v>184</v>
       </c>
       <c r="C28" s="45" t="n">
+        <v>212</v>
+      </c>
+      <c r="D28" s="45" t="n">
         <v>139</v>
-      </c>
-      <c r="D28" s="45" t="n">
-        <v>39</v>
       </c>
       <c r="E28" s="45" t="n">
         <v>313</v>
@@ -16734,10 +16734,10 @@
         <v>61</v>
       </c>
       <c r="C29" s="39" t="n">
+        <v>10751</v>
+      </c>
+      <c r="D29" s="39" t="n">
         <v>6941</v>
-      </c>
-      <c r="D29" s="39" t="n">
-        <v>1877</v>
       </c>
       <c r="E29" s="39" t="n">
         <v>16072</v>
@@ -16752,10 +16752,10 @@
         <v>184</v>
       </c>
       <c r="C30" s="45" t="n">
+        <v>448</v>
+      </c>
+      <c r="D30" s="45" t="n">
         <v>284</v>
-      </c>
-      <c r="D30" s="45" t="n">
-        <v>74</v>
       </c>
       <c r="E30" s="45" t="n">
         <v>682</v>
@@ -16770,10 +16770,10 @@
         <v>61</v>
       </c>
       <c r="C31" s="39" t="n">
+        <v>24204</v>
+      </c>
+      <c r="D31" s="39" t="n">
         <v>14881</v>
-      </c>
-      <c r="D31" s="39" t="n">
-        <v>3533</v>
       </c>
       <c r="E31" s="39" t="n">
         <v>37888</v>
@@ -16788,10 +16788,10 @@
         <v>61</v>
       </c>
       <c r="C32" s="39" t="n">
+        <v>290452</v>
+      </c>
+      <c r="D32" s="39" t="n">
         <v>178567</v>
-      </c>
-      <c r="D32" s="39" t="n">
-        <v>42401</v>
       </c>
       <c r="E32" s="39" t="n">
         <v>454657</v>
@@ -16805,8 +16805,8 @@
       <c r="B33" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C33" s="52" t="s">
-        <v>354</v>
+      <c r="C33" s="45" t="n">
+        <v>24</v>
       </c>
       <c r="D33" s="52" t="s">
         <v>354</v>
@@ -16824,10 +16824,10 @@
         <v>61</v>
       </c>
       <c r="C34" s="39" t="n">
+        <v>9624</v>
+      </c>
+      <c r="D34" s="39" t="n">
         <v>-63986</v>
-      </c>
-      <c r="D34" s="39" t="n">
-        <v>-184015</v>
       </c>
       <c r="E34" s="39" t="n">
         <v>46856</v>
@@ -16842,10 +16842,10 @@
         <v>61</v>
       </c>
       <c r="C35" s="39" t="n">
+        <v>41683</v>
+      </c>
+      <c r="D35" s="39" t="n">
         <v>-63986</v>
-      </c>
-      <c r="D35" s="39" t="n">
-        <v>-184015</v>
       </c>
       <c r="E35" s="39" t="n">
         <v>175550</v>
@@ -16860,10 +16860,10 @@
         <v>58</v>
       </c>
       <c r="C36" s="45" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="45" t="n">
         <v>8</v>
-      </c>
-      <c r="D36" s="45" t="n">
-        <v>20</v>
       </c>
       <c r="E36" s="45" t="n">
         <v>4</v>
@@ -16878,10 +16878,10 @@
         <v>58</v>
       </c>
       <c r="C37" s="45" t="n">
+        <v>16</v>
+      </c>
+      <c r="D37" s="45" t="n">
         <v>20</v>
-      </c>
-      <c r="D37" s="52" t="s">
-        <v>354</v>
       </c>
       <c r="E37" s="45" t="n">
         <v>12</v>
@@ -16895,8 +16895,8 @@
       <c r="B38" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="52" t="s">
-        <v>354</v>
+      <c r="C38" s="45" t="n">
+        <v>29</v>
       </c>
       <c r="D38" s="52" t="s">
         <v>354</v>
@@ -17026,11 +17026,11 @@
       </c>
       <c r="C9" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B9/$B$16*$B$4,0)</f>
-        <v>6896.70818591785</v>
+        <v>6803.19017934513</v>
       </c>
       <c r="D9" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C9/$B$4,0)</f>
-        <v>0.0689670818591786</v>
+        <v>0.0680319017934513</v>
       </c>
       <c r="E9" s="12" t="s">
         <v>367</v>
@@ -17042,15 +17042,15 @@
       </c>
       <c r="B10" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$10:$AL$10)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$22:$AL$22)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$23:$AL$23)</f>
-        <v>20469.6192</v>
+        <v>21110.665655</v>
       </c>
       <c r="C10" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B10/$B$16*$B$4,0)</f>
-        <v>21915.3165365407</v>
+        <v>22295.1640879473</v>
       </c>
       <c r="D10" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C10/$B$4,0)</f>
-        <v>0.219153165365407</v>
+        <v>0.222951640879473</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>369</v>
@@ -17066,11 +17066,11 @@
       </c>
       <c r="C11" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B11/$B$16*$B$4,0)</f>
-        <v>5479.05150325696</v>
+        <v>5404.75664247974</v>
       </c>
       <c r="D11" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C11/$B$4,0)</f>
-        <v>0.0547905150325696</v>
+        <v>0.0540475664247974</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>371</v>
@@ -17086,11 +17086,11 @@
       </c>
       <c r="C12" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B12/$B$16*$B$4,0)</f>
-        <v>27300.9754710918</v>
+        <v>26930.7796131953</v>
       </c>
       <c r="D12" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C12/$B$4,0)</f>
-        <v>0.273009754710918</v>
+        <v>0.269307796131953</v>
       </c>
       <c r="E12" s="12" t="s">
         <v>373</v>
@@ -17106,11 +17106,11 @@
       </c>
       <c r="C13" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B13/$B$16*$B$4,0)</f>
-        <v>18735.9635585924</v>
+        <v>18481.9075776831</v>
       </c>
       <c r="D13" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C13/$B$4,0)</f>
-        <v>0.187359635585924</v>
+        <v>0.184819075776831</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>375</v>
@@ -17122,15 +17122,15 @@
       </c>
       <c r="B14" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$17:$AL$17)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$18:$AL$18)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$19:$AL$19)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$20:$AL$20)</f>
-        <v>10176.500170711</v>
+        <v>10758.2534786107</v>
       </c>
       <c r="C14" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B14/$B$16*$B$4,0)</f>
-        <v>10895.2306487115</v>
+        <v>11361.8883707983</v>
       </c>
       <c r="D14" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C14/$B$4,0)</f>
-        <v>0.108952306487115</v>
+        <v>0.113618883707983</v>
       </c>
       <c r="E14" s="12" t="s">
         <v>377</v>
@@ -17142,15 +17142,15 @@
       </c>
       <c r="B15" s="39" t="n">
         <f aca="false">SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$24:$AL$24)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$26:$AL$26)+SUMPRODUCT((Revenue!$C$3:$AL$3&lt;=$B$5)*Costs!$C$32:$AL$32)</f>
-        <v>8197.77409353555</v>
+        <v>8258.91408168054</v>
       </c>
       <c r="C15" s="39" t="n">
         <f aca="false">IF($B$16&gt;0,B15/$B$16*$B$4,0)</f>
-        <v>8776.75409588884</v>
+        <v>8722.31352855113</v>
       </c>
       <c r="D15" s="24" t="n">
         <f aca="false">IF($B$4&gt;0,C15/$B$4,0)</f>
-        <v>0.0877675409588885</v>
+        <v>0.0872231352855113</v>
       </c>
       <c r="E15" s="12" t="s">
         <v>379</v>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="B16" s="53" t="n">
         <f aca="false">SUM(B9:B15)</f>
-        <v>93403.2559642466</v>
+        <v>94687.1957152913</v>
       </c>
       <c r="C16" s="53" t="n">
         <f aca="false">SUM(C9:C15)</f>
@@ -17214,11 +17214,11 @@
       </c>
       <c r="C20" s="48" t="n">
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B20+in_OpeningCash))</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D20" s="48" t="n">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B20+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B20+in_OpeningCash)))</f>
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E20" s="1"/>
     </row>
@@ -17234,9 +17234,9 @@
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B21+in_OpeningCash))</f>
         <v>15</v>
       </c>
-      <c r="D21" s="48" t="n">
+      <c r="D21" s="48" t="str">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B21+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B21+in_OpeningCash)))</f>
-        <v>21</v>
+        <v>&gt; 36</v>
       </c>
       <c r="E21" s="1"/>
     </row>
@@ -17251,9 +17251,9 @@
         <f aca="false">COUNTIF('P&amp;L &amp; Cash'!$C$24:$AL$24,"&lt;="&amp;(B22+in_OpeningCash))</f>
         <v>20</v>
       </c>
-      <c r="D22" s="48" t="n">
+      <c r="D22" s="48" t="str">
         <f aca="false">IF(COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B22+in_OpeningCash))&gt;=36,"&gt; 36",COUNTIF('P&amp;L &amp; Cash'!$C$28:$AL$28,"&gt;="&amp;-(B22+in_OpeningCash)))</f>
-        <v>29</v>
+        <v>&gt; 36</v>
       </c>
       <c r="E22" s="1"/>
     </row>
@@ -17305,7 +17305,7 @@
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="str">
         <f aca="false">IF(in_CashLow&lt;0,"On the selected scenario cash lasts "&amp;in_RunwayPlan&amp;" months on plan without further funding; the seed round is raised from the 100-paying-customer milestone (model month "&amp;in_M100&amp;").","On the selected scenario cash never falls below €"&amp;TEXT(in_CashLow,"#,##0")&amp;"; break-even in model month "&amp;in_Breakeven&amp;".")</f>
-        <v>On the selected scenario cash lasts 21 months on plan without further funding; the seed round is raised from the 100-paying-customer milestone (model month 20).</v>
+        <v>On the selected scenario cash never falls below €9,624; break-even in model month 24.</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -17315,7 +17315,7 @@
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="str">
         <f aca="false">"Next milestone (seed readiness) inside the runway: 100 paying firms by model month "&amp;in_M100&amp;", payroll validated, REGES-Online in daily use, accountant channel repeatable."</f>
-        <v>Next milestone (seed readiness) inside the runway: 100 paying firms by model month 20, payroll validated, REGES-Online in daily use, accountant channel repeatable.</v>
+        <v>Next milestone (seed readiness) inside the runway: 100 paying firms by model month 16, payroll validated, REGES-Online in daily use, accountant channel repeatable.</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -17325,7 +17325,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="str">
         <f aca="false">"Why this size: the round funds the path to the seed trigger (100 paying firms, model month "&amp;in_M100&amp;") with "&amp;in_RunwayPlan&amp;" months of runway on plan, on a lean cost plan: co-founders unpaid until model month "&amp;in_FounderPayStart&amp;", then €"&amp;TEXT(in_SalFounder,"#,##0")&amp;" gross, partner manager at "&amp;TEXT(in_SalesFTE,"0%")&amp;" until model month "&amp;in_SalesFullStart&amp;" (partner signings scaled to the manager's hours), support specialist at "&amp;TEXT(in_SupportFTE,"0%")&amp;" from model month "&amp;in_SupportStart&amp;", developer after the seed (model month "&amp;in_DevStart&amp;")."</f>
-        <v>Why this size: the round funds the path to the seed trigger (100 paying firms, model month 20) with 21 months of runway on plan, on a lean cost plan: co-founders unpaid until model month 13, then €1,000 gross, partner manager at 50% until model month 13 (partner signings scaled to the manager's hours), support specialist at 50% from model month 9, developer after the seed (model month 25).</v>
+        <v>Why this size: the round funds the path to the seed trigger (100 paying firms, model month 16) with &gt; 36 months of runway on plan, on a lean cost plan: co-founders unpaid until model month 13, then €1,000 gross, partner manager at 50% until model month 13 (partner signings scaled to the manager's hours), support specialist at 50% from model month 9, developer after the seed (model month 25).</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -17335,7 +17335,7 @@
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="str">
         <f aca="false">"A smaller ticket (€"&amp;TEXT(B20,"#,##0")&amp;") gives "&amp;C20&amp;" months with zero revenue and "&amp;D20&amp;" on plan"&amp;IF(AND(ISNUMBER(D20),ISNUMBER(in_M100)),IF(D20&lt;in_M100," - cash runs out before the seed trigger."," - with little margin before the seed trigger."),".")</f>
-        <v>A smaller ticket (€75,000) gives 13 months with zero revenue and 15 on plan - cash runs out before the seed trigger.</v>
+        <v>A smaller ticket (€75,000) gives 12 months with zero revenue and 19 on plan - with little margin before the seed trigger.</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -17345,7 +17345,7 @@
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="str">
         <f aca="false">"A larger ticket (€"&amp;TEXT(B22,"#,##0")&amp;") would buy "&amp;C22&amp;" months with zero revenue and "&amp;D22&amp;" on plan on the same lean plan: more than the plan needs, so we ask for the smallest ticket that reaches the seed trigger."</f>
-        <v>A larger ticket (€150,000) would buy 20 months with zero revenue and 29 on plan on the same lean plan: more than the plan needs, so we ask for the smallest ticket that reaches the seed trigger.</v>
+        <v>A larger ticket (€150,000) would buy 20 months with zero revenue and &gt; 36 on plan on the same lean plan: more than the plan needs, so we ask for the smallest ticket that reaches the seed trigger.</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
